--- a/data/global/2026-05-week03/titles.xlsx
+++ b/data/global/2026-05-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L208"/>
+  <dimension ref="A1:L213"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Harry Styles - Dance No More (Official Video)</v>
+        <v>שלומי ימין - פרפר סגול</v>
       </c>
       <c r="B2" t="str">
-        <v>7 days ago</v>
+        <v>2026-05-15</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410899&amp;sid=4e49e5e22b0cc4c7806cc2f3c9c4e591</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-15</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>7 days ago</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Harry Styles</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
+        <v>שלומי ימין - פרפר סגול</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
+        <v>עדן גבריאל &amp; אליאן כהן - הפסקת אש</v>
       </c>
       <c r="B3" t="str">
-        <v>7 days ago</v>
+        <v>2026-05-15</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410898&amp;sid=4e49e5e22b0cc4c7806cc2f3c9c4e591</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-15</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>7 days ago</v>
+        <v/>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Eagles</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
+        <v>עדן גבריאל &amp; אליאן כהן - הפסקת אש</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
+        <v>נשמה וקצב - מחפשת רק אותך</v>
       </c>
       <c r="B4" t="str">
-        <v>5 days ago</v>
+        <v>2026-05-15</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410897&amp;sid=4e49e5e22b0cc4c7806cc2f3c9c4e591</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-15</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>5 days ago</v>
+        <v/>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Nora Fatehi</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
+        <v>נשמה וקצב - מחפשת רק אותך</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
+        <v>נשמה וקצב - השיר הזה שלך</v>
       </c>
       <c r="B5" t="str">
-        <v>2 months ago</v>
+        <v>2026-05-15</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410896&amp;sid=4e49e5e22b0cc4c7806cc2f3c9c4e591</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-15</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 months ago</v>
+        <v/>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Eurovision Song Contest</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>נשמה וקצב - השיר הזה שלך</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
+        <v>נשמה וקצב - אתה לא בחיי</v>
       </c>
       <c r="B6" t="str">
-        <v>2 months ago</v>
+        <v>2026-05-15</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410895&amp;sid=4e49e5e22b0cc4c7806cc2f3c9c4e591</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-15</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 months ago</v>
+        <v/>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Eurovision Song Contest and Alis</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
+        <v>נשמה וקצב - אתה לא בחיי</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
+        <v>ניר עבדו - בורח מעצמי</v>
       </c>
       <c r="B7" t="str">
-        <v>2 months ago</v>
+        <v>2026-05-15</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410894&amp;sid=4e49e5e22b0cc4c7806cc2f3c9c4e591</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-15</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 months ago</v>
+        <v/>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Eurovision Song Contest</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
+        <v>ניר עבדו - בורח מעצמי</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video)</v>
+        <v>נהוראי אביסרור - בלעדייך</v>
       </c>
       <c r="B8" t="str">
-        <v>6 days ago</v>
+        <v>2026-05-15</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410893&amp;sid=4e49e5e22b0cc4c7806cc2f3c9c4e591</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-15</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>6 days ago</v>
+        <v/>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>The Head And The Heart</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
+        <v>נהוראי אביסרור - בלעדייך</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
+        <v>מרדכי אברג'ל - חי בן איש חי</v>
       </c>
       <c r="B9" t="str">
-        <v>8 days ago</v>
+        <v>2026-05-15</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410892&amp;sid=4e49e5e22b0cc4c7806cc2f3c9c4e591</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-15</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>8 days ago</v>
+        <v/>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Simply Red</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
+        <v>מרדכי אברג'ל - חי בן איש חי</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video)</v>
+        <v>מיקי בן עטר - מחרוזת מזמורי ירושלים 2026</v>
       </c>
       <c r="B10" t="str">
-        <v>4 days ago</v>
+        <v>2026-05-15</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410891&amp;sid=4e49e5e22b0cc4c7806cc2f3c9c4e591</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-15</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>4 days ago</v>
+        <v/>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Talking Heads</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
+        <v>מיקי בן עטר - מחרוזת מזמורי ירושלים 2026</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Ellise - Liplock (Official Music Video)</v>
+        <v>ינון טייב - ובנה אותה</v>
       </c>
       <c r="B11" t="str">
-        <v>6 days ago</v>
+        <v>2026-05-15</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410889&amp;sid=4e49e5e22b0cc4c7806cc2f3c9c4e591</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-15</v>
@@ -793,16 +793,16 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>6 days ago</v>
+        <v/>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Ellise</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
+        <v>ינון טייב - ובנה אותה</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Tori Kelly - Dive (Official Music Video)</v>
+        <v>ינאי פדידה - נוף מגדלים</v>
       </c>
       <c r="B12" t="str">
-        <v>6 days ago</v>
+        <v>2026-05-15</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410888&amp;sid=4e49e5e22b0cc4c7806cc2f3c9c4e591</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-15</v>
@@ -831,16 +831,16 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>6 days ago</v>
+        <v/>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Tori Kelly</v>
+        <v/>
       </c>
       <c r="I12" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
+        <v>ינאי פדידה - נוף מגדלים</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
+        <v>ינאי פדידה - מפרט</v>
       </c>
       <c r="B13" t="str">
-        <v>6 days ago</v>
+        <v>2026-05-15</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410887&amp;sid=4e49e5e22b0cc4c7806cc2f3c9c4e591</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-15</v>
@@ -869,16 +869,16 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>6 days ago</v>
+        <v/>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>David Gilmour</v>
+        <v/>
       </c>
       <c r="I13" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024) - David Gilmour</v>
+        <v>ינאי פדידה - מפרט</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
+        <v>יוסי שטרית - פצע ישן</v>
       </c>
       <c r="B14" t="str">
-        <v>6 days ago</v>
+        <v>2026-05-15</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410886&amp;sid=4e49e5e22b0cc4c7806cc2f3c9c4e591</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-15</v>
@@ -907,16 +907,16 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>6 days ago</v>
+        <v/>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Scorpions</v>
+        <v/>
       </c>
       <c r="I14" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022) - Scorpions</v>
+        <v>יוסי שטרית - פצע ישן</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
+        <v>טודיאל - קרקס</v>
       </c>
       <c r="B15" t="str">
-        <v>6 days ago</v>
+        <v>2026-05-15</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410885&amp;sid=4e49e5e22b0cc4c7806cc2f3c9c4e591</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-15</v>
@@ -945,16 +945,16 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>6 days ago</v>
+        <v/>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Claire Leslie</v>
+        <v/>
       </c>
       <c r="I15" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Claire Leslie - Passenger Seat (Official Music Video) - Claire Leslie</v>
+        <v>טודיאל - קרקס</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Michael Schulte - Lovesick (Official Video)</v>
+        <v>דניאל חן - לילה טוב</v>
       </c>
       <c r="B16" t="str">
-        <v>6 days ago</v>
+        <v>2026-05-15</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410884&amp;sid=4e49e5e22b0cc4c7806cc2f3c9c4e591</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-15</v>
@@ -983,16 +983,16 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>6 days ago</v>
+        <v/>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Michael Schulte</v>
+        <v/>
       </c>
       <c r="I16" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Michael Schulte - Lovesick (Official Video) - Michael Schulte</v>
+        <v>דניאל חן - לילה טוב</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Caity Baser - Holiday Song (Official Video)</v>
+        <v>בנאל בן ציון - לא חוקי #2</v>
       </c>
       <c r="B17" t="str">
-        <v>6 days ago</v>
+        <v>2026-05-15</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410883&amp;sid=4e49e5e22b0cc4c7806cc2f3c9c4e591</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-15</v>
@@ -1021,16 +1021,16 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>6 days ago</v>
+        <v/>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Caity Baser</v>
+        <v/>
       </c>
       <c r="I17" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J17" t="str">
         <v/>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Caity Baser - Holiday Song (Official Video) - Caity Baser</v>
+        <v>בנאל בן ציון - לא חוקי #2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
+        <v>אלעד אביבי - בית״ר ירושלים - ההמנון 2026</v>
       </c>
       <c r="B18" t="str">
-        <v>6 days ago</v>
+        <v>2026-05-15</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410882&amp;sid=4e49e5e22b0cc4c7806cc2f3c9c4e591</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-15</v>
@@ -1059,16 +1059,16 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>6 days ago</v>
+        <v/>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Sam Fischer</v>
+        <v/>
       </c>
       <c r="I18" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J18" t="str">
         <v/>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser) - Sam Fischer</v>
+        <v>אלעד אביבי - בית״ר ירושלים - ההמנון 2026</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Porches- HABIT (Official Video)</v>
+        <v>ליאור קקון - ירושלים של זהב קאבר</v>
       </c>
       <c r="B19" t="str">
-        <v>6 days ago</v>
+        <v>2026-05-15</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410890&amp;sid=513c45e169eaf116aa2433598953ea9f</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-15</v>
@@ -1097,16 +1097,16 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>6 days ago</v>
+        <v/>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Porches</v>
+        <v/>
       </c>
       <c r="I19" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J19" t="str">
         <v/>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Porches- HABIT (Official Video) - Porches</v>
+        <v>ליאור קקון - ירושלים של זהב קאבר</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Charli xcx - Rock Music (Official Video)</v>
+        <v>זהו זה - זהו זה 2020 עונה 5 (2023)</v>
       </c>
       <c r="B20" t="str">
-        <v>6 days ago</v>
+        <v>2026-05-15</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24191&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-15</v>
@@ -1135,16 +1135,16 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>6 days ago</v>
+        <v>06:50</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Charli xcx</v>
+        <v/>
       </c>
       <c r="I20" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J20" t="str">
         <v/>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Charli xcx - Rock Music (Official Video) - Charli xcx</v>
+        <v>זהו זה - זהו זה 2020 עונה 5 (2023)</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Jon Batiste - Alla Blues (Audio)</v>
+        <v>אריק סיני - כל השירים היפים באמת</v>
       </c>
       <c r="B21" t="str">
-        <v>6 days ago</v>
+        <v>2026-05-15</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24470&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-15</v>
@@ -1173,16 +1173,16 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>6 days ago</v>
+        <v>06:45</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Jon Batiste</v>
+        <v/>
       </c>
       <c r="I21" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J21" t="str">
         <v/>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Jon Batiste - Alla Blues (Audio) - Jon Batiste</v>
+        <v>אריק סיני - כל השירים היפים באמת</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
+        <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
+        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-15</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Tigirlily Gold</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Tigirlily Gold - I Do or Die (Official Music Video) - Tigirlily Gold</v>
+        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
+        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-15</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Eagles</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video) - PAUL McCARTNEY</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B24" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
+        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-15</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Bruno Mars</v>
+        <v>Nora Fatehi</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video] - Bruno Mars</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Tori Kelly - Control (Official Visualizer)</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B25" t="str">
-        <v>6 days ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
+        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-15</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>6 days ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Tori Kelly</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Tori Kelly - Control (Official Visualizer) - Tori Kelly</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Bea Miller - depressed on the internet (Lyric Video)</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B26" t="str">
-        <v>6 days ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
+        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-15</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>6 days ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>bea miller</v>
+        <v>Eurovision Song Contest and Alis</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Bea Miller - depressed on the internet (Lyric Video) - bea miller</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
       </c>
       <c r="B27" t="str">
-        <v>6 days ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
+        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-15</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>6 days ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>The Chainsmokers</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer) - The Chainsmokers</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Madison Beer - free (Official Audio)</v>
+        <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B28" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
+        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-15</v>
@@ -1445,7 +1445,7 @@
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Madison Beer</v>
+        <v>The Head And The Heart</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Madison Beer - free (Official Audio) - Madison Beer</v>
+        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Tori Kelly - Dive (Official Audio)</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B29" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
+        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-15</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Tori Kelly</v>
+        <v>Simply Red</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Tori Kelly - Dive (Official Audio) - Tori Kelly</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Jeremy Camp - Reflector (Official Audio)</v>
+        <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
+        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-15</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>JeremyCampMusic</v>
+        <v>Talking Heads</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Jeremy Camp - Reflector (Official Audio) - JeremyCampMusic</v>
+        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
+        <v>Ellise - Liplock (Official Music Video)</v>
       </c>
       <c r="B31" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
+        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-15</v>
@@ -1559,7 +1559,7 @@
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>The Chainsmokers</v>
+        <v>Ellise</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer) - The Chainsmokers</v>
+        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Ashley Cooke - high school sweetheart</v>
+        <v>Tori Kelly - Dive (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
+        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-15</v>
@@ -1597,7 +1597,7 @@
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Ashley Cooke</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Ashley Cooke - high school sweetheart - Ashley Cooke</v>
+        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Ari Abdul - Ego (Visualizer)</v>
+        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
       </c>
       <c r="B33" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=L0FjVr6LpVU</v>
+        <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-15</v>
@@ -1635,7 +1635,7 @@
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Ari Abdul</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Ari Abdul - Ego (Visualizer) - Ari Abdul</v>
+        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024) - David Gilmour</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Quinn XCII - HOOPLA (Official Music Video)</v>
+        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
       </c>
       <c r="B34" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=eNbGA1pgmFk</v>
+        <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-15</v>
@@ -1673,7 +1673,7 @@
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Quinn XCII</v>
+        <v>Scorpions</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Quinn XCII - HOOPLA (Official Music Video) - Quinn XCII</v>
+        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Madison Beer - lovergirl (Official Music Video)</v>
+        <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
       </c>
       <c r="B35" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=q4lU1N3oqYQ</v>
+        <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-15</v>
@@ -1711,7 +1711,7 @@
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Madison Beer</v>
+        <v>Claire Leslie</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Madison Beer - lovergirl (Official Music Video) - Madison Beer</v>
+        <v>Claire Leslie - Passenger Seat (Official Music Video) - Claire Leslie</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>David J - WHAT IF I'M IN LOVE (Official Video)</v>
+        <v>Michael Schulte - Lovesick (Official Video)</v>
       </c>
       <c r="B36" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=-SF7Hm_ikaY</v>
+        <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-15</v>
@@ -1749,7 +1749,7 @@
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>David J</v>
+        <v>Michael Schulte</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>David J - WHAT IF I'M IN LOVE (Official Video) - David J</v>
+        <v>Michael Schulte - Lovesick (Official Video) - Michael Schulte</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>The Last Dinner Party - Big Dog (On The Road)</v>
+        <v>Caity Baser - Holiday Song (Official Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
+        <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-15</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>The Last Dinner Party</v>
+        <v>Caity Baser</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>The Last Dinner Party - Big Dog (On The Road) - The Last Dinner Party</v>
+        <v>Caity Baser - Holiday Song (Official Video) - Caity Baser</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>OCEAN ALLEY - HOLD ON (Official Video)</v>
+        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
       </c>
       <c r="B38" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
+        <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-15</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Ocean Alley</v>
+        <v>Sam Fischer</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>OCEAN ALLEY - HOLD ON (Official Video) - Ocean Alley</v>
+        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser) - Sam Fischer</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Dagny - Closet Disco Queen (Lyric Video)</v>
+        <v>Porches- HABIT (Official Video)</v>
       </c>
       <c r="B39" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
+        <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-15</v>
@@ -1863,7 +1863,7 @@
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Dagny</v>
+        <v>Porches</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Dagny - Closet Disco Queen (Lyric Video) - Dagny</v>
+        <v>Porches- HABIT (Official Video) - Porches</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Purple Disco Machine - Disco Cherry (Official Video)</v>
+        <v>Charli xcx - Rock Music (Official Video)</v>
       </c>
       <c r="B40" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
+        <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-15</v>
@@ -1901,7 +1901,7 @@
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Purple Disco Machine - Disco Cherry (Official Video) - Purple Disco Machine</v>
+        <v>Charli xcx - Rock Music (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Paris Paloma - Stem the Flow [Official Music Video]</v>
+        <v>Jon Batiste - Alla Blues (Audio)</v>
       </c>
       <c r="B41" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
+        <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-15</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Paris Paloma</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Paris Paloma - Stem the Flow [Official Music Video] - Paris Paloma</v>
+        <v>Jon Batiste - Alla Blues (Audio) - Jon Batiste</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Lucy Blue - Who you love (Visualiser)</v>
+        <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
+        <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-15</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Lucy Blue</v>
+        <v>Tigirlily Gold</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Lucy Blue - Who you love (Visualiser) - Lucy Blue</v>
+        <v>Tigirlily Gold - I Do or Die (Official Music Video) - Tigirlily Gold</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026)</v>
+        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
+        <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-15</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Olivia Dean</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026) - Olivia Dean</v>
+        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Aaron Frazer - It's A Shame (Official Video)</v>
+        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
       </c>
       <c r="B44" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
+        <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-15</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Aaron Frazer</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Aaron Frazer - It's A Shame (Official Video) - Aaron Frazer</v>
+        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify</v>
+        <v>Tori Kelly - Control (Official Visualizer)</v>
       </c>
       <c r="B45" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
+        <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-15</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Holly Humberstone</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>Tori Kelly - Control (Official Visualizer) - Tori Kelly</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>DANNA - OUT OF MY BODY</v>
+        <v>Bea Miller - depressed on the internet (Lyric Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=uW_Ye0kQ9Ac</v>
+        <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-15</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Danna</v>
+        <v>bea miller</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>DANNA - OUT OF MY BODY - Danna</v>
+        <v>Bea Miller - depressed on the internet (Lyric Video) - bea miller</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>The Rolling Stones - In The Stars (Official Lyric Video)</v>
+        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
       </c>
       <c r="B47" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
+        <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-15</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>The Rolling Stones</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>The Rolling Stones - In The Stars (Official Lyric Video) - The Rolling Stones</v>
+        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser)</v>
+        <v>Madison Beer - free (Official Audio)</v>
       </c>
       <c r="B48" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
+        <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-15</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser) - Dermot Kennedy</v>
+        <v>Madison Beer - free (Official Audio) - Madison Beer</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
+        <v>Tori Kelly - Dive (Official Audio)</v>
       </c>
       <c r="B49" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
+        <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-15</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2) - SIENNA SPIRO</v>
+        <v>Tori Kelly - Dive (Official Audio) - Tori Kelly</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Rick Astley - Raindrops (Official Video)</v>
+        <v>Jeremy Camp - Reflector (Official Audio)</v>
       </c>
       <c r="B50" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
+        <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-15</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Rick Astley</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Rick Astley - Raindrops (Official Video) - Rick Astley</v>
+        <v>Jeremy Camp - Reflector (Official Audio) - JeremyCampMusic</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Jessie J - THREW IT AWAY (Official Video)</v>
+        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
       </c>
       <c r="B51" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
+        <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-15</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Jessie J</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Jessie J - THREW IT AWAY (Official Video) - Jessie J</v>
+        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>The Takes - Ain't Love (Lyric Video)</v>
+        <v>Ashley Cooke - high school sweetheart</v>
       </c>
       <c r="B52" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
+        <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-15</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>The Takes</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>The Takes - Ain't Love (Lyric Video) - The Takes</v>
+        <v>Ashley Cooke - high school sweetheart - Ashley Cooke</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary</v>
+        <v>Ari Abdul - Ego (Visualizer)</v>
       </c>
       <c r="B53" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
+        <v>https://www.youtube.com/watch?v=L0FjVr6LpVU</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-15</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>The Offspring</v>
+        <v>Ari Abdul</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary - The Offspring</v>
+        <v>Ari Abdul - Ego (Visualizer) - Ari Abdul</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Louis Tomlinson - Sunflowers (Official Performance Video)</v>
+        <v>Quinn XCII - HOOPLA (Official Music Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
+        <v>https://www.youtube.com/watch?v=eNbGA1pgmFk</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-15</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Quinn XCII</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Louis Tomlinson - Sunflowers (Official Performance Video) - Louis Tomlinson</v>
+        <v>Quinn XCII - HOOPLA (Official Music Video) - Quinn XCII</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>The Beaches - Should've Known Better (Official Visualizer)</v>
+        <v>Madison Beer - lovergirl (Official Music Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
+        <v>https://www.youtube.com/watch?v=q4lU1N3oqYQ</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-15</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>The Beaches</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>The Beaches - Should've Known Better (Official Visualizer) - The Beaches</v>
+        <v>Madison Beer - lovergirl (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>The Kiffness - Serafino (Singing Cat Song)</v>
+        <v>David J - WHAT IF I'M IN LOVE (Official Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
+        <v>https://www.youtube.com/watch?v=-SF7Hm_ikaY</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-15</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>The Kiffness</v>
+        <v>David J</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>The Kiffness - Serafino (Singing Cat Song) - The Kiffness</v>
+        <v>David J - WHAT IF I'M IN LOVE (Official Video) - David J</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer)</v>
+        <v>The Last Dinner Party - Big Dog (On The Road)</v>
       </c>
       <c r="B57" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
+        <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-15</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Dennis Lloyd</v>
+        <v>The Last Dinner Party</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer) - Dennis Lloyd</v>
+        <v>The Last Dinner Party - Big Dog (On The Road) - The Last Dinner Party</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Anna Graves - Damn In Love (Official Visualizer)</v>
+        <v>OCEAN ALLEY - HOLD ON (Official Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
+        <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-15</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Anna Graves</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Anna Graves - Damn In Love (Official Visualizer) - Anna Graves</v>
+        <v>OCEAN ALLEY - HOLD ON (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video)</v>
+        <v>Dagny - Closet Disco Queen (Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=vKzPmy3VUzY</v>
+        <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-15</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Brandon Lake and NICK JONAS</v>
+        <v>Dagny</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video) - Brandon Lake and NICK JONAS</v>
+        <v>Dagny - Closet Disco Queen (Lyric Video) - Dagny</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Letdown. - Do It For The Love (Visualizer)</v>
+        <v>Purple Disco Machine - Disco Cherry (Official Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=vCvZbTEywr8</v>
+        <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-15</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Letdown.</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Letdown. - Do It For The Love (Visualizer) - Letdown.</v>
+        <v>Purple Disco Machine - Disco Cherry (Official Video) - Purple Disco Machine</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Maroon 5 - Heroine (Official Lyric Video)</v>
+        <v>Paris Paloma - Stem the Flow [Official Music Video]</v>
       </c>
       <c r="B61" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=izP-4q4YtNw</v>
+        <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-15</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Maroon 5</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Maroon 5 - Heroine (Official Lyric Video) - Maroon 5</v>
+        <v>Paris Paloma - Stem the Flow [Official Music Video] - Paris Paloma</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Olivia O'Brien - I'm Perfect (Official Visualizer)</v>
+        <v>Lucy Blue - Who you love (Visualiser)</v>
       </c>
       <c r="B62" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=leHb8CowDSw</v>
+        <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-15</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Olivia O'Brien</v>
+        <v>Lucy Blue</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Olivia O'Brien - I'm Perfect (Official Visualizer) - Olivia O'Brien</v>
+        <v>Lucy Blue - Who you love (Visualiser) - Lucy Blue</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>ERNEST - What's A Little Rain (Official Music Video)</v>
+        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026)</v>
       </c>
       <c r="B63" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=U-3AGDH3mf4</v>
+        <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-15</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>ERNEST</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>ERNEST - What's A Little Rain (Official Music Video) - ERNEST</v>
+        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026) - Olivia Dean</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Claire Rosinkranz - Just A Man (Official Audio)</v>
+        <v>Aaron Frazer - It's A Shame (Official Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=Ta2I3EHXaDI</v>
+        <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-15</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Aaron Frazer</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Claire Rosinkranz - Just A Man (Official Audio) - Claire Rosinkranz</v>
+        <v>Aaron Frazer - It's A Shame (Official Video) - Aaron Frazer</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Halsey - Nothing! (Official Audio)</v>
+        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify</v>
       </c>
       <c r="B65" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=PBv71KbKvHA</v>
+        <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-15</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Halsey</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Halsey - Nothing! (Official Audio) - Halsey</v>
+        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer)</v>
+        <v>DANNA - OUT OF MY BODY</v>
       </c>
       <c r="B66" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=5-f07ca1Zfg</v>
+        <v>https://www.youtube.com/watch?v=uW_Ye0kQ9Ac</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-15</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Zara Larsson</v>
+        <v>Danna</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer) - Zara Larsson</v>
+        <v>DANNA - OUT OF MY BODY - Danna</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Halsey - Carry the Weight (Official Audio)</v>
+        <v>The Rolling Stones - In The Stars (Official Lyric Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=6MewHp8BX0w</v>
+        <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-15</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Halsey</v>
+        <v>The Rolling Stones</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Halsey - Carry the Weight (Official Audio) - Halsey</v>
+        <v>The Rolling Stones - In The Stars (Official Lyric Video) - The Rolling Stones</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Bishop Briggs - Blood From A Stone (Official)</v>
+        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser)</v>
       </c>
       <c r="B68" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=3CK6Zbdk-Nw</v>
+        <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-15</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Bishop Briggs</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Bishop Briggs - Blood From A Stone (Official) - Bishop Briggs</v>
+        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio)</v>
+        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
       </c>
       <c r="B69" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=6-AWBV5FCN4</v>
+        <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-15</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Louis Tomlinson</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio) - Louis Tomlinson</v>
+        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>almost monday - no more regrets (official video)</v>
+        <v>Rick Astley - Raindrops (Official Video)</v>
       </c>
       <c r="B70" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=iczsZVZxHKs</v>
+        <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-15</v>
@@ -3041,7 +3041,7 @@
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>almost monday</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>almost monday - no more regrets (official video) - almost monday</v>
+        <v>Rick Astley - Raindrops (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video)</v>
+        <v>Jessie J - THREW IT AWAY (Official Video)</v>
       </c>
       <c r="B71" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=lJM-z0ohbkc</v>
+        <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-15</v>
@@ -3079,7 +3079,7 @@
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>Jessie J</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video) - FULL CIRCLE BOYS</v>
+        <v>Jessie J - THREW IT AWAY (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video)</v>
+        <v>The Takes - Ain't Love (Lyric Video)</v>
       </c>
       <c r="B72" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=6AjhDPwpoLI</v>
+        <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-15</v>
@@ -3117,7 +3117,7 @@
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
+        <v>The Takes</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video) - ★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
+        <v>The Takes - Ain't Love (Lyric Video) - The Takes</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video)</v>
+        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary</v>
       </c>
       <c r="B73" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=F4ndJUCsHKg</v>
+        <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-15</v>
@@ -3155,7 +3155,7 @@
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>NIGHTLY and Fly By Midnight</v>
+        <v>The Offspring</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video) - NIGHTLY and Fly By Midnight</v>
+        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary - The Offspring</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer)</v>
+        <v>Louis Tomlinson - Sunflowers (Official Performance Video)</v>
       </c>
       <c r="B74" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=-IEb-ym7VeQ</v>
+        <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-15</v>
@@ -3193,7 +3193,7 @@
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Zara Larsson</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer) - Zara Larsson</v>
+        <v>Louis Tomlinson - Sunflowers (Official Performance Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>JORDANA BRYANT - Truth Is (Official Video)</v>
+        <v>The Beaches - Should've Known Better (Official Visualizer)</v>
       </c>
       <c r="B75" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=D4meCyyV7SQ</v>
+        <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-15</v>
@@ -3231,7 +3231,7 @@
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Jordana Bryant</v>
+        <v>The Beaches</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>JORDANA BRYANT - Truth Is (Official Video) - Jordana Bryant</v>
+        <v>The Beaches - Should've Known Better (Official Visualizer) - The Beaches</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Leanna Crawford - Thank God (Lyric Video)</v>
+        <v>The Kiffness - Serafino (Singing Cat Song)</v>
       </c>
       <c r="B76" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=QqcSoUft03s</v>
+        <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-15</v>
@@ -3269,7 +3269,7 @@
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Leanna Crawford</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Leanna Crawford - Thank God (Lyric Video) - Leanna Crawford</v>
+        <v>The Kiffness - Serafino (Singing Cat Song) - The Kiffness</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Girl Tones - Stubborn Mouth (Official Music Video)</v>
+        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer)</v>
       </c>
       <c r="B77" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=_-PyPUWZTDY</v>
+        <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-15</v>
@@ -3307,7 +3307,7 @@
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Girl Tones</v>
+        <v>Dennis Lloyd</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Girl Tones - Stubborn Mouth (Official Music Video) - Girl Tones</v>
+        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer) - Dennis Lloyd</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Tauren Wells - What A Miracle Feels Like (Official Audio)</v>
+        <v>Anna Graves - Damn In Love (Official Visualizer)</v>
       </c>
       <c r="B78" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=ZojFIe4Swmk</v>
+        <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-15</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Tauren Wells</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Tauren Wells - What A Miracle Feels Like (Official Audio) - Tauren Wells</v>
+        <v>Anna Graves - Damn In Love (Official Visualizer) - Anna Graves</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Matthew Ifield - Thinking (Official Video)</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
+        <v>https://www.youtube.com/watch?v=vKzPmy3VUzY</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-15</v>
@@ -3383,7 +3383,7 @@
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Matthew Ifield</v>
+        <v>Brandon Lake and NICK JONAS</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Matthew Ifield - Thinking (Official Video) - Matthew Ifield</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video) - Brandon Lake and NICK JONAS</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Dons - Is There Something</v>
+        <v>Letdown. - Do It For The Love (Visualizer)</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=AgWIjvD-i0E</v>
+        <v>https://www.youtube.com/watch?v=vCvZbTEywr8</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-15</v>
@@ -3421,7 +3421,7 @@
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Dons</v>
+        <v>Letdown.</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Dons - Is There Something - Dons</v>
+        <v>Letdown. - Do It For The Love (Visualizer) - Letdown.</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris</v>
+        <v>Maroon 5 - Heroine (Official Lyric Video)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=JXW3SOr7C4w</v>
+        <v>https://www.youtube.com/watch?v=izP-4q4YtNw</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-15</v>
@@ -3459,7 +3459,7 @@
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Recording Academy / GRAMMYs and 3 more</v>
+        <v>Maroon 5</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris - Recording Academy / GRAMMYs and 3 more</v>
+        <v>Maroon 5 - Heroine (Official Lyric Video) - Maroon 5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Maya Hawke - Lioness (Official Audio)</v>
+        <v>Olivia O'Brien - I'm Perfect (Official Visualizer)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
+        <v>https://www.youtube.com/watch?v=leHb8CowDSw</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-15</v>
@@ -3497,7 +3497,7 @@
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Maya Hawke</v>
+        <v>Olivia O'Brien</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Maya Hawke - Lioness (Official Audio) - Maya Hawke</v>
+        <v>Olivia O'Brien - I'm Perfect (Official Visualizer) - Olivia O'Brien</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance</v>
+        <v>ERNEST - What's A Little Rain (Official Music Video)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
+        <v>https://www.youtube.com/watch?v=U-3AGDH3mf4</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-15</v>
@@ -3535,7 +3535,7 @@
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Laufey</v>
+        <v>ERNEST</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance - Laufey</v>
+        <v>ERNEST - What's A Little Rain (Official Music Video) - ERNEST</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
+        <v>Claire Rosinkranz - Just A Man (Official Audio)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
+        <v>https://www.youtube.com/watch?v=Ta2I3EHXaDI</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-15</v>
@@ -3573,7 +3573,7 @@
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Keith Urban</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
+        <v>Claire Rosinkranz - Just A Man (Official Audio) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>DANNA - AGAIN</v>
+        <v>Halsey - Nothing! (Official Audio)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
+        <v>https://www.youtube.com/watch?v=PBv71KbKvHA</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-15</v>
@@ -3611,7 +3611,7 @@
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Danna</v>
+        <v>Halsey</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>DANNA - AGAIN - Danna</v>
+        <v>Halsey - Nothing! (Official Audio) - Halsey</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
+        <v>https://www.youtube.com/watch?v=5-f07ca1Zfg</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-15</v>
@@ -3649,7 +3649,7 @@
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Armik</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer) - Zara Larsson</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>EUROPE - One on One (Official Video)</v>
+        <v>Halsey - Carry the Weight (Official Audio)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
+        <v>https://www.youtube.com/watch?v=6MewHp8BX0w</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-15</v>
@@ -3687,7 +3687,7 @@
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Europe</v>
+        <v>Halsey</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>EUROPE - One on One (Official Video) - Europe</v>
+        <v>Halsey - Carry the Weight (Official Audio) - Halsey</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
+        <v>Bishop Briggs - Blood From A Stone (Official)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
+        <v>https://www.youtube.com/watch?v=3CK6Zbdk-Nw</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-15</v>
@@ -3725,7 +3725,7 @@
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Foo Fighters</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
+        <v>Bishop Briggs - Blood From A Stone (Official) - Bishop Briggs</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video)</v>
+        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
+        <v>https://www.youtube.com/watch?v=6-AWBV5FCN4</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-15</v>
@@ -3763,7 +3763,7 @@
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Lady Gaga and Doechii</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video) - Lady Gaga and Doechii</v>
+        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
+        <v>almost monday - no more regrets (official video)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
+        <v>https://www.youtube.com/watch?v=iczsZVZxHKs</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-15</v>
@@ -3801,7 +3801,7 @@
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Muse</v>
+        <v>almost monday</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
+        <v>almost monday - no more regrets (official video) - almost monday</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
+        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
+        <v>https://www.youtube.com/watch?v=lJM-z0ohbkc</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-15</v>
@@ -3839,7 +3839,7 @@
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Nothing But Thieves</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
+        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Shaboozey - Born To Die (Official Video)</v>
+        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
+        <v>https://www.youtube.com/watch?v=6AjhDPwpoLI</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-15</v>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Shaboozey</v>
+        <v>★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
+        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video) - ★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
+        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
+        <v>https://www.youtube.com/watch?v=F4ndJUCsHKg</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-15</v>
@@ -3915,7 +3915,7 @@
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Scorpions</v>
+        <v>NIGHTLY and Fly By Midnight</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
+        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video) - NIGHTLY and Fly By Midnight</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
+        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
+        <v>https://www.youtube.com/watch?v=-IEb-ym7VeQ</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-15</v>
@@ -3953,7 +3953,7 @@
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Meghan Trainor</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
+        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer) - Zara Larsson</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
+        <v>JORDANA BRYANT - Truth Is (Official Video)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
+        <v>https://www.youtube.com/watch?v=D4meCyyV7SQ</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-15</v>
@@ -3991,7 +3991,7 @@
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Lolo Zouaï</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
+        <v>JORDANA BRYANT - Truth Is (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Bonnie Tyler - One World One Home</v>
+        <v>Leanna Crawford - Thank God (Lyric Video)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
+        <v>https://www.youtube.com/watch?v=QqcSoUft03s</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-15</v>
@@ -4029,7 +4029,7 @@
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Bonnie Tyler</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
+        <v>Leanna Crawford - Thank God (Lyric Video) - Leanna Crawford</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
+        <v>Girl Tones - Stubborn Mouth (Official Music Video)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
+        <v>https://www.youtube.com/watch?v=_-PyPUWZTDY</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-15</v>
@@ -4067,7 +4067,7 @@
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Girl Tones - Stubborn Mouth (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Icona Pop - Dance To This (Official Video)</v>
+        <v>Tauren Wells - What A Miracle Feels Like (Official Audio)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
+        <v>https://www.youtube.com/watch?v=ZojFIe4Swmk</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-15</v>
@@ -4105,7 +4105,7 @@
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Icona Pop</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
+        <v>Tauren Wells - What A Miracle Feels Like (Official Audio) - Tauren Wells</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Michael Jackson - Human Nature (Official Video)</v>
+        <v>Matthew Ifield - Thinking (Official Video)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
+        <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-15</v>
@@ -4143,7 +4143,7 @@
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Michael Jackson</v>
+        <v>Matthew Ifield</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
+        <v>Matthew Ifield - Thinking (Official Video) - Matthew Ifield</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>The All-American Rejects - King Kong</v>
+        <v>Dons - Is There Something</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
+        <v>https://www.youtube.com/watch?v=AgWIjvD-i0E</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-15</v>
@@ -4181,7 +4181,7 @@
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>The All-American Rejects</v>
+        <v>Dons</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
+        <v>Dons - Is There Something - Dons</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
+        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
+        <v>https://www.youtube.com/watch?v=JXW3SOr7C4w</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-15</v>
@@ -4219,7 +4219,7 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Ringo Starr</v>
+        <v>Recording Academy / GRAMMYs and 3 more</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
+        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris - Recording Academy / GRAMMYs and 3 more</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Tu recuerdo</v>
+        <v>Maya Hawke - Lioness (Official Audio)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/tu-recuerdo/6763660843</v>
+        <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-15</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Loco X Volver</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:55</v>
+        <v/>
       </c>
       <c r="H102" t="str">
-        <v>Maluma</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/tu-recuerdo/1895423065</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Tu recuerdo - Maluma</v>
+        <v>Maya Hawke - Lioness (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Hardy (feat. Clairo)</v>
+        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/hardy-feat-clairo/1876953073</v>
+        <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-15</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>American Stories</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G103" t="str">
-        <v>3:53</v>
+        <v/>
       </c>
       <c r="H103" t="str">
-        <v>Rostam</v>
+        <v>Laufey</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/hardy-feat-clairo/1876952750</v>
+        <v/>
       </c>
       <c r="L103" t="str">
-        <v>Hardy (feat. Clairo) - Rostam</v>
+        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance - Laufey</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Una A La Vez</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/una-a-la-vez/1890287855</v>
+        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
       </c>
       <c r="D104" t="str">
         <v>2026-05-15</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>OMERTA</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G104" t="str">
-        <v>2:32</v>
+        <v/>
       </c>
       <c r="H104" t="str">
-        <v>J Balvin</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v/>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/una-a-la-vez/1890287852</v>
+        <v/>
       </c>
       <c r="L104" t="str">
-        <v>Una A La Vez - J Balvin</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Rock Music</v>
+        <v>DANNA - AGAIN</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/rock-music/6766314234</v>
+        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
       </c>
       <c r="D105" t="str">
         <v>2026-05-15</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Rock Music - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G105" t="str">
-        <v>1:55</v>
+        <v/>
       </c>
       <c r="H105" t="str">
-        <v>Charli xcx</v>
+        <v>Danna</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
+        <v/>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/rock-music/6766314069</v>
+        <v/>
       </c>
       <c r="L105" t="str">
-        <v>Rock Music - Charli xcx</v>
+        <v>DANNA - AGAIN - Danna</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>TNT</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/tnt/1887671066</v>
+        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
       </c>
       <c r="D106" t="str">
         <v>2026-05-15</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>GREENGREEN - EP</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G106" t="str">
-        <v>2:02</v>
+        <v/>
       </c>
       <c r="H106" t="str">
-        <v>CORTIS</v>
+        <v>Armik</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
+        <v/>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/tnt/1887671065</v>
+        <v/>
       </c>
       <c r="L106" t="str">
-        <v>TNT - CORTIS</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Go</v>
+        <v>EUROPE - One on One (Official Video)</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/go/6765588421</v>
+        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-15</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Go - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G107" t="str">
-        <v>2:24</v>
+        <v/>
       </c>
       <c r="H107" t="str">
-        <v>Key Glock</v>
+        <v>Europe</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/key-glock/1199258326</v>
+        <v/>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/go/1896001876</v>
+        <v/>
       </c>
       <c r="L107" t="str">
-        <v>Go - Key Glock</v>
+        <v>EUROPE - One on One (Official Video) - Europe</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>For The Moment</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/for-the-moment/6764419271</v>
+        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
       </c>
       <c r="D108" t="str">
         <v>2026-05-15</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>BROWN</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G108" t="str">
-        <v>3:26</v>
+        <v/>
       </c>
       <c r="H108" t="str">
-        <v>Chris Brown</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
+        <v/>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/for-the-moment/1895772091</v>
+        <v/>
       </c>
       <c r="L108" t="str">
-        <v>For The Moment - Chris Brown</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Smoking pt. 2</v>
+        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video)</v>
       </c>
       <c r="B109" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/smoking-pt-2/1894333434</v>
+        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-15</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Wave Gods 2: Cosmos Brothers</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G109" t="str">
-        <v>3:21</v>
+        <v/>
       </c>
       <c r="H109" t="str">
-        <v>French Montana</v>
+        <v>Lady Gaga and Doechii</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/french-montana/475816358</v>
+        <v/>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/smoking-pt-2/1894333428</v>
+        <v/>
       </c>
       <c r="L109" t="str">
-        <v>Smoking pt. 2 - French Montana</v>
+        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video) - Lady Gaga and Doechii</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Dirty Rosie</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
       </c>
       <c r="B110" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/dirty-rosie/6767044374</v>
+        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-15</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Little Miss Twain</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G110" t="str">
-        <v>2:46</v>
+        <v/>
       </c>
       <c r="H110" t="str">
-        <v>Shania Twain</v>
+        <v>Muse</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/shania-twain/129974</v>
+        <v/>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/dirty-rosie/1896356105</v>
+        <v/>
       </c>
       <c r="L110" t="str">
-        <v>Dirty Rosie - Shania Twain</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Therapy at the Club</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
       </c>
       <c r="B111" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/therapy-at-the-club/6764050150</v>
+        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-15</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>THERAPY AT THE CLUB</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G111" t="str">
-        <v>2:47</v>
+        <v/>
       </c>
       <c r="H111" t="str">
-        <v>FLO</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/flo/1615611716</v>
+        <v/>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/therapy-at-the-club/1895613904</v>
+        <v/>
       </c>
       <c r="L111" t="str">
-        <v>Therapy at the Club - FLO</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Like you mean it</v>
+        <v>Shaboozey - Born To Die (Official Video)</v>
       </c>
       <c r="B112" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/like-you-mean-it/6767024693</v>
+        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-15</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>When the lights turn on</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G112" t="str">
-        <v>2:27</v>
+        <v/>
       </c>
       <c r="H112" t="str">
-        <v>MICO</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/mico/1457367370</v>
+        <v/>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/like-you-mean-it/6767024688</v>
+        <v/>
       </c>
       <c r="L112" t="str">
-        <v>Like you mean it - MICO</v>
+        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>linknb</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
       </c>
       <c r="B113" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/linknb/1888561848</v>
+        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-15</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>new avatar</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G113" t="str">
-        <v>1:55</v>
+        <v/>
       </c>
       <c r="H113" t="str">
-        <v>Kelela</v>
+        <v>Scorpions</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/kelela/549186342</v>
+        <v/>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/linknb/1888561538</v>
+        <v/>
       </c>
       <c r="L113" t="str">
-        <v>linknb - Kelela</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Robotic Love</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
       </c>
       <c r="B114" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/robotic-love/6763638857</v>
+        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-15</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Robotic Love - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G114" t="str">
-        <v>3:25</v>
+        <v/>
       </c>
       <c r="H114" t="str">
-        <v>elkan</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/elkan/1805013361</v>
+        <v/>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/robotic-love/1895412608</v>
+        <v/>
       </c>
       <c r="L114" t="str">
-        <v>Robotic Love - elkan</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Baby</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
       </c>
       <c r="B115" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/baby/6763651180</v>
+        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-15</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Baby - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G115" t="str">
-        <v>3:13</v>
+        <v/>
       </c>
       <c r="H115" t="str">
-        <v>Prospa</v>
+        <v>Lolo Zouaï</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/prospa/962366708</v>
+        <v/>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/baby/1895418297</v>
+        <v/>
       </c>
       <c r="L115" t="str">
-        <v>Baby - Prospa</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Boots (feat. Fetty Wap)</v>
+        <v>Bonnie Tyler - One World One Home</v>
       </c>
       <c r="B116" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/boots-feat-fetty-wap/6763152116</v>
+        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-15</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Boots (feat. Fetty Wap) - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G116" t="str">
-        <v>2:39</v>
+        <v/>
       </c>
       <c r="H116" t="str">
-        <v>Russell Dickerson</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/russell-dickerson/415673786</v>
+        <v/>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/boots-feat-fetty-wap/1895187005</v>
+        <v/>
       </c>
       <c r="L116" t="str">
-        <v>Boots (feat. Fetty Wap) - Russell Dickerson</v>
+        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Bed of Roses</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
       </c>
       <c r="B117" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/bed-of-roses/6765599768</v>
+        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-15</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Bed of Roses - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G117" t="str">
-        <v>3:05</v>
+        <v/>
       </c>
       <c r="H117" t="str">
-        <v>Teyana Taylor</v>
+        <v>Jacob Gurevitsch and Prisma Music Group</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/teyana-taylor/216698214</v>
+        <v/>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/bed-of-roses/1896005623</v>
+        <v/>
       </c>
       <c r="L117" t="str">
-        <v>Bed of Roses - Teyana Taylor</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Lo Arriesgo Todo</v>
+        <v>Icona Pop - Dance To This (Official Video)</v>
       </c>
       <c r="B118" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/lo-arriesgo-todo/6766999307</v>
+        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-15</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Lo Arriesgo Todo - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G118" t="str">
-        <v>3:24</v>
+        <v/>
       </c>
       <c r="H118" t="str">
-        <v>Bruno Mars</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v/>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/lo-arriesgo-todo/6766999303</v>
+        <v/>
       </c>
       <c r="L118" t="str">
-        <v>Lo Arriesgo Todo - Bruno Mars</v>
+        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Big Dog</v>
+        <v>Michael Jackson - Human Nature (Official Video)</v>
       </c>
       <c r="B119" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/big-dog/6762481627</v>
+        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-15</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Big Dog - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G119" t="str">
-        <v>2:59</v>
+        <v/>
       </c>
       <c r="H119" t="str">
-        <v>The Last Dinner Party</v>
+        <v>Michael Jackson</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/the-last-dinner-party/1680519203</v>
+        <v/>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/big-dog/1894318010</v>
+        <v/>
       </c>
       <c r="L119" t="str">
-        <v>Big Dog - The Last Dinner Party</v>
+        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Eastside Girls</v>
+        <v>The All-American Rejects - King Kong</v>
       </c>
       <c r="B120" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/eastside-girls/1870703307</v>
+        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-15</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Dancing On The Wall</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G120" t="str">
-        <v>3:50</v>
+        <v/>
       </c>
       <c r="H120" t="str">
-        <v>MUNA</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v/>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/eastside-girls/1870702692</v>
+        <v/>
       </c>
       <c r="L120" t="str">
-        <v>Eastside Girls - MUNA</v>
+        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>In The Stars</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
       </c>
       <c r="B121" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/in-the-stars/6764865395</v>
+        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-15</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Foreign Tongues</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G121" t="str">
-        <v>4:13</v>
+        <v/>
       </c>
       <c r="H121" t="str">
-        <v>The Rolling Stones</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/the-rolling-stones/1249595</v>
+        <v/>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/in-the-stars/1895941732</v>
+        <v/>
       </c>
       <c r="L121" t="str">
-        <v>In The Stars - The Rolling Stones</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Home to Us</v>
+        <v>Hit the Wall</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/home-to-us/1887403096</v>
+        <v>https://music.apple.com/us/song/hit-the-wall/6766750846</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-15</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>Daughter from Hell</v>
       </c>
       <c r="G122" t="str">
-        <v>3:11</v>
+        <v>3:14</v>
       </c>
       <c r="H122" t="str">
-        <v>Paul McCartney</v>
+        <v>Gracie Abrams</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v>https://music.apple.com/us/artist/gracie-abrams/1450554836</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/home-to-us/1887402919</v>
+        <v>https://music.apple.com/us/album/hit-the-wall/6766750836</v>
       </c>
       <c r="L122" t="str">
-        <v>Home to Us - Paul McCartney</v>
+        <v>Hit the Wall - Gracie Abrams</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Hurts Like You</v>
+        <v>Ran To Atlanta</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/hurts-like-you/6765521189</v>
+        <v>https://music.apple.com/us/song/ran-to-atlanta/6769568597</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-15</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>The Night Champion</v>
+        <v>ICEMAN</v>
       </c>
       <c r="G123" t="str">
-        <v>3:15</v>
+        <v>4:07</v>
       </c>
       <c r="H123" t="str">
-        <v>Koe Wetzel</v>
+        <v>Drake</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/hurts-like-you/1895978438</v>
+        <v>https://music.apple.com/us/album/ran-to-atlanta/6769568449</v>
       </c>
       <c r="L123" t="str">
-        <v>Hurts Like You - Koe Wetzel</v>
+        <v>Ran To Atlanta - Drake</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Find Us Again</v>
+        <v>Hoe Phase</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/find-us-again/6764638179</v>
+        <v>https://music.apple.com/us/song/hoe-phase/6769556949</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-15</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Find Us Again - Single</v>
+        <v>MAID OF HONOUR</v>
       </c>
       <c r="G124" t="str">
-        <v>2:58</v>
+        <v>3:23</v>
       </c>
       <c r="H124" t="str">
-        <v>Xavi</v>
+        <v>Drake</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/find-us-again/1895860349</v>
+        <v>https://music.apple.com/us/album/hoe-phase/6769556940</v>
       </c>
       <c r="L124" t="str">
-        <v>Find Us Again - Xavi</v>
+        <v>Hoe Phase - Drake</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Tied Up</v>
+        <v>I’m Spent</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/tied-up/6765699130</v>
+        <v>https://music.apple.com/us/song/im-spent/6769551476</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-15</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Tied Up - Single</v>
+        <v>HABIBTI</v>
       </c>
       <c r="G125" t="str">
-        <v>2:56</v>
+        <v>2:24</v>
       </c>
       <c r="H125" t="str">
-        <v>Khalid</v>
+        <v>Drake</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/khalid/82842423</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/tied-up/1896041630</v>
+        <v>https://music.apple.com/us/album/im-spent/6769551464</v>
       </c>
       <c r="L125" t="str">
-        <v>Tied Up - Khalid</v>
+        <v>I’m Spent - Drake</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Antes De Ti</v>
+        <v>Abracadabra (Apple Music Live)</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/antes-de-ti/1891167102</v>
+        <v>https://music.apple.com/us/song/abracadabra-apple-music-live/6768201780</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-15</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Antes De Ti - Single</v>
+        <v>Apple Music Live: MAYHEM Requiem</v>
       </c>
       <c r="G126" t="str">
-        <v>2:56</v>
+        <v>4:04</v>
       </c>
       <c r="H126" t="str">
-        <v>Silvana Estrada</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/silvana-estrada/1277235729</v>
+        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/antes-de-ti/1891167099</v>
+        <v>https://music.apple.com/us/album/abracadabra-apple-music-live/6768201775</v>
       </c>
       <c r="L126" t="str">
-        <v>Antes De Ti - Silvana Estrada</v>
+        <v>Abracadabra (Apple Music Live) - Lady Gaga</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>En La Misma Cama</v>
+        <v>Falling out of Love</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/en-la-misma-cama/6763670999</v>
+        <v>https://music.apple.com/us/song/falling-out-of-love/1891161448</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-15</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>MUDA</v>
+        <v>Reality Awaits</v>
       </c>
       <c r="G127" t="str">
-        <v>2:51</v>
+        <v>6:21</v>
       </c>
       <c r="H127" t="str">
-        <v>Carín León</v>
+        <v>The Strokes</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
+        <v>https://music.apple.com/us/artist/the-strokes/560289</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/en-la-misma-cama/1895429814</v>
+        <v>https://music.apple.com/us/album/falling-out-of-love/1891161441</v>
       </c>
       <c r="L127" t="str">
-        <v>En La Misma Cama - Carín León</v>
+        <v>Falling out of Love - The Strokes</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>lovergirl</v>
+        <v>Dai Dai</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/lovergirl/6766366578</v>
+        <v>https://music.apple.com/us/song/dai-dai/6768469976</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-15</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>locket deluxe</v>
+        <v>Dai Dai - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>3:21</v>
+        <v>3:43</v>
       </c>
       <c r="H128" t="str">
-        <v>Madison Beer</v>
+        <v>Shakira</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/madison-beer/696146587</v>
+        <v>https://music.apple.com/us/artist/shakira/889327</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/lovergirl/6766366564</v>
+        <v>https://music.apple.com/us/album/dai-dai/6768469975</v>
       </c>
       <c r="L128" t="str">
-        <v>lovergirl - Madison Beer</v>
+        <v>Dai Dai - Shakira</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>PANIKI</v>
+        <v>Tu recuerdo</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/paniki/1892534080</v>
+        <v>https://music.apple.com/us/song/tu-recuerdo/6763660843</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-15</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Los Locos Nunca Mueren</v>
+        <v>Loco X Volver</v>
       </c>
       <c r="G129" t="str">
-        <v>2:36</v>
+        <v>3:55</v>
       </c>
       <c r="H129" t="str">
-        <v>Chuyin</v>
+        <v>Maluma</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/chuyin/1766532018</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/paniki/1892533803</v>
+        <v>https://music.apple.com/us/album/tu-recuerdo/1895423065</v>
       </c>
       <c r="L129" t="str">
-        <v>PANIKI - Chuyin</v>
+        <v>Tu recuerdo - Maluma</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>DesOrden</v>
+        <v>Traitor (Roles Reversed)</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/desorden/6765776443</v>
+        <v>https://music.apple.com/us/song/traitor-roles-reversed/6767665959</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-15</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>DesOrden - Single</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G130" t="str">
-        <v>2:36</v>
+        <v>3:27</v>
       </c>
       <c r="H130" t="str">
-        <v>Alleh</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/alleh/1644755393</v>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/desorden/1896069663</v>
+        <v>https://music.apple.com/us/album/traitor-roles-reversed/6767665713</v>
       </c>
       <c r="L130" t="str">
-        <v>DesOrden - Alleh</v>
+        <v>Traitor (Roles Reversed) - Megan Moroney</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>LA Nights</v>
+        <v>Dirty Rosie</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/la-nights/6763580223</v>
+        <v>https://music.apple.com/us/song/dirty-rosie/6767044374</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-15</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>The Ville</v>
+        <v>Little Miss Twain</v>
       </c>
       <c r="G131" t="str">
-        <v>2:18</v>
+        <v>2:46</v>
       </c>
       <c r="H131" t="str">
-        <v>Trap Dickey</v>
+        <v>Shania Twain</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/shania-twain/129974</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/la-nights/1895384937</v>
+        <v>https://music.apple.com/us/album/dirty-rosie/1896356105</v>
       </c>
       <c r="L131" t="str">
-        <v>LA Nights - Trap Dickey</v>
+        <v>Dirty Rosie - Shania Twain</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>The Payoff</v>
+        <v>Like you mean it</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/the-payoff/1891518506</v>
+        <v>https://music.apple.com/us/song/like-you-mean-it/6767024693</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-15</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>The Payoff - Single</v>
+        <v>When the lights turn on</v>
       </c>
       <c r="G132" t="str">
-        <v>5:51</v>
+        <v>2:27</v>
       </c>
       <c r="H132" t="str">
-        <v>Father John Misty</v>
+        <v>MICO</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/father-john-misty/514361724</v>
+        <v>https://music.apple.com/us/artist/mico/1457367370</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/the-payoff/1891518505</v>
+        <v>https://music.apple.com/us/album/like-you-mean-it/6767024688</v>
       </c>
       <c r="L132" t="str">
-        <v>The Payoff - Father John Misty</v>
+        <v>Like you mean it - MICO</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>The Weak</v>
+        <v>Hardy (feat. Clairo)</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/the-weak/1880484489</v>
+        <v>https://music.apple.com/us/song/hardy-feat-clairo/1876953073</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-15</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>For Love of Grace &amp; the Hereafter</v>
+        <v>American Stories</v>
       </c>
       <c r="G133" t="str">
-        <v>3:15</v>
+        <v>3:53</v>
       </c>
       <c r="H133" t="str">
-        <v>Iceage</v>
+        <v>Rostam</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/the-weak/1880484160</v>
+        <v>https://music.apple.com/us/album/hardy-feat-clairo/1876952750</v>
       </c>
       <c r="L133" t="str">
-        <v>The Weak - Iceage</v>
+        <v>Hardy (feat. Clairo) - Rostam</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Life Of The Faaji</v>
+        <v>2 Hard 4 The Radio</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/life-of-the-faaji/1893417486</v>
+        <v>https://music.apple.com/us/song/2-hard-4-the-radio/6769568610</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-15</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Fuji Xtra</v>
+        <v>ICEMAN</v>
       </c>
       <c r="G134" t="str">
-        <v>2:29</v>
+        <v>3:03</v>
       </c>
       <c r="H134" t="str">
-        <v>Adekunle Gold</v>
+        <v>Drake</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/adekunle-gold/1035126760</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/life-of-the-faaji/1893417480</v>
+        <v>https://music.apple.com/us/album/2-hard-4-the-radio/6769568449</v>
       </c>
       <c r="L134" t="str">
-        <v>Life Of The Faaji - Adekunle Gold</v>
+        <v>2 Hard 4 The Radio - Drake</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Satisfy</v>
+        <v>Cheetah Print</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/satisfy/1894316978</v>
+        <v>https://music.apple.com/us/song/cheetah-print/6769557055</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-15</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Satisfy - Single</v>
+        <v>MAID OF HONOUR</v>
       </c>
       <c r="G135" t="str">
-        <v>3:06</v>
+        <v>3:22</v>
       </c>
       <c r="H135" t="str">
-        <v>Calvin Harris</v>
+        <v>Drake</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/calvin-harris/201955086</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/satisfy/1894316975</v>
+        <v>https://music.apple.com/us/album/cheetah-print/6769556940</v>
       </c>
       <c r="L135" t="str">
-        <v>Satisfy - Calvin Harris</v>
+        <v>Cheetah Print - Drake</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!)</v>
+        <v>WNBA</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/aftertaste-from-original-motion-picture-soundtrack-k-pops/6766316768</v>
+        <v>https://music.apple.com/us/song/wnba/6769551471</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-15</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!) - Single</v>
+        <v>HABIBTI</v>
       </c>
       <c r="G136" t="str">
-        <v>3:03</v>
+        <v>2:58</v>
       </c>
       <c r="H136" t="str">
-        <v>DEAN</v>
+        <v>Drake</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/dean/2770824</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/aftertaste-from-original-motion-picture-soundtrack-k-pops/6766316765</v>
+        <v>https://music.apple.com/us/album/wnba/6769551464</v>
       </c>
       <c r="L136" t="str">
-        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!) - DEAN</v>
+        <v>WNBA - Drake</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Ashin' the Blunt</v>
+        <v>Shadow Of A Man (Apple Music Live)</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/ashin-the-blunt/1884792300</v>
+        <v>https://music.apple.com/us/song/shadow-of-a-man-apple-music-live/6768201925</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-15</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>Apple Music Live: MAYHEM Requiem</v>
       </c>
       <c r="G137" t="str">
-        <v>3:48</v>
+        <v>3:36</v>
       </c>
       <c r="H137" t="str">
-        <v>6LACK</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/ashin-the-blunt/1884792154</v>
+        <v>https://music.apple.com/us/album/shadow-of-a-man-apple-music-live/6768201775</v>
       </c>
       <c r="L137" t="str">
-        <v>Ashin' the Blunt - 6LACK</v>
+        <v>Shadow Of A Man (Apple Music Live) - Lady Gaga</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>I Wanna Rock</v>
+        <v>EPA</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/i-wanna-rock/1889577010</v>
+        <v>https://music.apple.com/us/song/epa/6768420253</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-15</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>I Wanna Rock - Single</v>
+        <v>EPA - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:44</v>
+        <v>3:22</v>
       </c>
       <c r="H138" t="str">
-        <v>Cash Cobain</v>
+        <v>Becky G</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/cash-cobain/953108105</v>
+        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/i-wanna-rock/1889577009</v>
+        <v>https://music.apple.com/us/album/epa/6768420251</v>
       </c>
       <c r="L138" t="str">
-        <v>I Wanna Rock - Cash Cobain</v>
+        <v>EPA - Becky G</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Trying Times - A COLORS SHOW</v>
+        <v>I’m your girl right?</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/trying-times-a-colors-show/6764557224</v>
+        <v>https://music.apple.com/us/song/im-your-girl-right/6766440186</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-15</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Trying Times - A COLORS SHOW - Single</v>
+        <v>ESTRUS</v>
       </c>
       <c r="G139" t="str">
-        <v>4:33</v>
+        <v>2:49</v>
       </c>
       <c r="H139" t="str">
-        <v>James Blake</v>
+        <v>Tove Lo</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/tove-lo/570136838</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/trying-times-a-colors-show/1895832124</v>
+        <v>https://music.apple.com/us/album/im-your-girl-right/6766440172</v>
       </c>
       <c r="L139" t="str">
-        <v>Trying Times - A COLORS SHOW - James Blake</v>
+        <v>I’m your girl right? - Tove Lo</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>One Two Police</v>
+        <v>fuëgo</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/one-two-police/6766293223</v>
+        <v>https://music.apple.com/us/song/fu%C3%ABgo/6767661766</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-15</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>One Two Police - Single</v>
+        <v>fuëgo - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:46</v>
+        <v>3:46</v>
       </c>
       <c r="H140" t="str">
-        <v>BUNT.</v>
+        <v>BNYX®</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/bnyx/1438325287</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/one-two-police/1896268827</v>
+        <v>https://music.apple.com/us/album/fu%C3%ABgo/6767661604</v>
       </c>
       <c r="L140" t="str">
-        <v>One Two Police - BUNT.</v>
+        <v>fuëgo - BNYX®</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>HOME TO MOTHER</v>
+        <v>jajaja</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/home-to-mother/1880198197</v>
+        <v>https://music.apple.com/us/song/jajaja/6766341319</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-15</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>LOVE, LOVE, LOVE</v>
+        <v>jajaja - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:16</v>
+        <v>2:45</v>
       </c>
       <c r="H141" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Chino Pacas</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
+        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/home-to-mother/1880197844</v>
+        <v>https://music.apple.com/us/album/jajaja/6766341318</v>
       </c>
       <c r="L141" t="str">
-        <v>HOME TO MOTHER - Stephen Sanchez</v>
+        <v>jajaja - Chino Pacas</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Illuminate</v>
+        <v>FIND GOD (feat. Dominic Fike)</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/illuminate/6764646733</v>
+        <v>https://music.apple.com/us/song/find-god-feat-dominic-fike/1894315529</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-15</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Illuminate (FIFA World Cup 2026™) - Single</v>
+        <v>BULLDAWG</v>
       </c>
       <c r="G142" t="str">
-        <v>3:03</v>
+        <v>3:59</v>
       </c>
       <c r="H142" t="str">
-        <v>Jessie Reyez</v>
+        <v>Kenny Mason</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/kenny-mason/79382206</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/illuminate/1895862895</v>
+        <v>https://music.apple.com/us/album/find-god-feat-dominic-fike/1894315301</v>
       </c>
       <c r="L142" t="str">
-        <v>Illuminate - Jessie Reyez</v>
+        <v>FIND GOD (feat. Dominic Fike) - Kenny Mason</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>OKAY!</v>
+        <v>FOOL ME ONCE (feat. Leon Thomas)</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/okay/6765792669</v>
+        <v>https://music.apple.com/us/song/fool-me-once-feat-leon-thomas/1891467239</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-15</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>OKAY! - Single</v>
+        <v>BELOVED: ACT II</v>
       </c>
       <c r="G143" t="str">
-        <v>4:34</v>
+        <v>3:18</v>
       </c>
       <c r="H143" t="str">
-        <v>Forrest Frank</v>
+        <v>GIVĒON</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
+        <v>https://music.apple.com/us/artist/giv%C4%93on/1070668868</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/okay/1896077066</v>
+        <v>https://music.apple.com/us/album/fool-me-once-feat-leon-thomas/1891467233</v>
       </c>
       <c r="L143" t="str">
-        <v>OKAY! - Forrest Frank</v>
+        <v>FOOL ME ONCE (feat. Leon Thomas) - GIVĒON</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>FLOW</v>
+        <v>Shabang</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/flow/6765469196</v>
+        <v>https://music.apple.com/us/song/shabang/6769568598</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-15</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>FLOW - Single</v>
+        <v>ICEMAN</v>
       </c>
       <c r="G144" t="str">
-        <v>4:20</v>
+        <v>3:08</v>
       </c>
       <c r="H144" t="str">
-        <v>iZaak</v>
+        <v>Drake</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/izaak/1295819563</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/flow/1895961693</v>
+        <v>https://music.apple.com/us/album/shabang/6769568449</v>
       </c>
       <c r="L144" t="str">
-        <v>FLOW - iZaak</v>
+        <v>Shabang - Drake</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>aiaiaiaiai</v>
+        <v>Road Trips</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/aiaiaiaiai/6764338271</v>
+        <v>https://music.apple.com/us/song/road-trips/6769557053</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-15</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>aiaiaiaiai - Single</v>
+        <v>MAID OF HONOUR</v>
       </c>
       <c r="G145" t="str">
-        <v>2:20</v>
+        <v>4:03</v>
       </c>
       <c r="H145" t="str">
-        <v>Mau y Ricky</v>
+        <v>Drake</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/aiaiaiaiai/1895739038</v>
+        <v>https://music.apple.com/us/album/road-trips/6769556940</v>
       </c>
       <c r="L145" t="str">
-        <v>aiaiaiaiai - Mau y Ricky</v>
+        <v>Road Trips - Drake</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Control</v>
+        <v>Fortworth</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/control/6765502013</v>
+        <v>https://music.apple.com/us/song/fortworth/6769551482</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-15</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>God Must Really Love Me</v>
+        <v>HABIBTI</v>
       </c>
       <c r="G146" t="str">
-        <v>2:32</v>
+        <v>3:51</v>
       </c>
       <c r="H146" t="str">
-        <v>Tori Kelly</v>
+        <v>Drake</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/tori-kelly/437581991</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/control/1895974889</v>
+        <v>https://music.apple.com/us/album/fortworth/6769551464</v>
       </c>
       <c r="L146" t="str">
-        <v>Control - Tori Kelly</v>
+        <v>Fortworth - Drake</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>ORIGAMI!</v>
+        <v>Repeat It</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/origami/1892544033</v>
+        <v>https://music.apple.com/us/song/repeat-it/6764277864</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-15</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>ORIGAMI! - Single</v>
+        <v>Repeat It - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>2:34</v>
+        <v>3:11</v>
       </c>
       <c r="H147" t="str">
-        <v>Kesha</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/kesha/334854763</v>
+        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/origami/1892544026</v>
+        <v>https://music.apple.com/us/album/repeat-it/1895713789</v>
       </c>
       <c r="L147" t="str">
-        <v>ORIGAMI! - Kesha</v>
+        <v>Repeat It - Martin Garrix</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Love Is Kind</v>
+        <v>Fool Proof</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/love-is-kind/1894074886</v>
+        <v>https://music.apple.com/us/song/fool-proof/1892466004</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-15</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Love Is Kind - EP</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G148" t="str">
-        <v>4:07</v>
+        <v>2:36</v>
       </c>
       <c r="H148" t="str">
-        <v>The Chainsmokers</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/love-is-kind/1894074877</v>
+        <v>https://music.apple.com/us/album/fool-proof/1892465981</v>
       </c>
       <c r="L148" t="str">
-        <v>Love Is Kind - The Chainsmokers</v>
+        <v>Fool Proof - Cody Johnson</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Feathers In A Storm</v>
+        <v>Crisco</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/feathers-in-a-storm/1864390075</v>
+        <v>https://music.apple.com/us/song/crisco/6763369506</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-15</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Let It Die Here</v>
+        <v>Crisco - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>4:00</v>
+        <v>2:56</v>
       </c>
       <c r="H149" t="str">
-        <v>Linda Perry</v>
+        <v>Miranda Lambert</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/miranda-lambert/18732261</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/feathers-in-a-storm/1864389779</v>
+        <v>https://music.apple.com/us/album/crisco/1895284236</v>
       </c>
       <c r="L149" t="str">
-        <v>Feathers In A Storm - Linda Perry</v>
+        <v>Crisco - Miranda Lambert</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Playing God</v>
+        <v>Absolution</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/playing-god/6765780293</v>
+        <v>https://music.apple.com/us/song/absolution/1884987651</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-15</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Decades</v>
+        <v>Forever Now</v>
       </c>
       <c r="G150" t="str">
-        <v>3:39</v>
+        <v>4:05</v>
       </c>
       <c r="H150" t="str">
-        <v>Motionless In White</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
+        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/playing-god/1896071360</v>
+        <v>https://music.apple.com/us/album/absolution/1884987638</v>
       </c>
       <c r="L150" t="str">
-        <v>Playing God - Motionless In White</v>
+        <v>Absolution - Switchfoot</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Cut</v>
+        <v>JESUS IS ALIVE</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/cut/1879494712</v>
+        <v>https://music.apple.com/us/song/jesus-is-alive/6767694896</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-15</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>VINDICATE</v>
+        <v>JESUS IS ALIVE - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:59</v>
+        <v>2:08</v>
       </c>
       <c r="H151" t="str">
-        <v>Black Veil Brides</v>
+        <v>Forrest Frank</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/black-veil-brides/276789923</v>
+        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/cut/1879494510</v>
+        <v>https://music.apple.com/us/album/jesus-is-alive/6767694895</v>
       </c>
       <c r="L151" t="str">
-        <v>Cut - Black Veil Brides</v>
+        <v>JESUS IS ALIVE - Forrest Frank</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Freaking Out</v>
+        <v>Something To Lose</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/freaking-out/1894067912</v>
+        <v>https://music.apple.com/us/song/something-to-lose/6766964605</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-15</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Over Before You Know It</v>
+        <v>Is This Heaven? - EP</v>
       </c>
       <c r="G152" t="str">
-        <v>3:03</v>
+        <v>2:55</v>
       </c>
       <c r="H152" t="str">
-        <v>Michigander</v>
+        <v>STELLA LEFTY</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/michigander/1096482927</v>
+        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/freaking-out/1894067897</v>
+        <v>https://music.apple.com/us/album/something-to-lose/6766964604</v>
       </c>
       <c r="L152" t="str">
-        <v>Freaking Out - Michigander</v>
+        <v>Something To Lose - STELLA LEFTY</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>FIYAH</v>
+        <v>Too Busy Missing You</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/fiyah/6764321306</v>
+        <v>https://music.apple.com/us/song/too-busy-missing-you/6766604915</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-15</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>FIYAH - Single</v>
+        <v>Off Campus: The Mixtape</v>
       </c>
       <c r="G153" t="str">
-        <v>3:12</v>
+        <v>3:25</v>
       </c>
       <c r="H153" t="str">
-        <v>YG Marley</v>
+        <v>Asha Banks</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/yg-marley/1496864889</v>
+        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/fiyah/1895732105</v>
+        <v>https://music.apple.com/us/album/too-busy-missing-you/6766604455</v>
       </c>
       <c r="L153" t="str">
-        <v>FIYAH - YG Marley</v>
+        <v>Too Busy Missing You - Asha Banks</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Ten to Midnight</v>
+        <v>F-Stop Blues (4-track)</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/ten-to-midnight/1885047105</v>
+        <v>https://music.apple.com/us/song/f-stop-blues-4-track/1883173173</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-15</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Wild</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G154" t="str">
-        <v>3:12</v>
+        <v>3:00</v>
       </c>
       <c r="H154" t="str">
-        <v>Ashley McBryde</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/ten-to-midnight/1885046822</v>
+        <v>https://music.apple.com/us/album/f-stop-blues-4-track/1883172879</v>
       </c>
       <c r="L154" t="str">
-        <v>Ten to Midnight - Ashley McBryde</v>
+        <v>F-Stop Blues (4-track) - Jack Johnson</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Carry On</v>
+        <v>PA' LO BONITO</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/carry-on/1893511608</v>
+        <v>https://music.apple.com/us/song/pa-lo-bonito/1886496944</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-15</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Carry On - Single</v>
+        <v>PA' LO BONITO - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:00</v>
+        <v>3:04</v>
       </c>
       <c r="H155" t="str">
-        <v>Kenny Chesney</v>
+        <v>Lenny Tavárez</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/kenny-chesney/205322</v>
+        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/carry-on/1893511607</v>
+        <v>https://music.apple.com/us/album/pa-lo-bonito/1886496943</v>
       </c>
       <c r="L155" t="str">
-        <v>Carry On - Kenny Chesney</v>
+        <v>PA' LO BONITO - Lenny Tavárez</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>[PRESS]</v>
+        <v>LONELY</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/press/6764735125</v>
+        <v>https://music.apple.com/us/song/lonely/6768757857</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-15</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>[PRESS] - Single</v>
+        <v>DESEO</v>
       </c>
       <c r="G156" t="str">
-        <v>1:40</v>
+        <v>2:58</v>
       </c>
       <c r="H156" t="str">
-        <v>Armani White</v>
+        <v>Katteyes</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/armani-white/1129439109</v>
+        <v>https://music.apple.com/us/artist/katteyes/1648818255</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/press/1895898254</v>
+        <v>https://music.apple.com/us/album/lonely/6768757414</v>
       </c>
       <c r="L156" t="str">
-        <v>[PRESS] - Armani White</v>
+        <v>LONELY - Katteyes</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Hold Me In The Dark</v>
+        <v>Lockup</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/hold-me-in-the-dark/1886119371</v>
+        <v>https://music.apple.com/us/song/lockup/1894298102</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-15</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>My Mess, My Heart, My Life.</v>
+        <v>Pure Devotion</v>
       </c>
       <c r="G157" t="str">
-        <v>3:17</v>
+        <v>4:31</v>
       </c>
       <c r="H157" t="str">
-        <v>Myles Smith</v>
+        <v>Overmono</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
+        <v>https://music.apple.com/us/artist/overmono/1129806758</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/hold-me-in-the-dark/1886119367</v>
+        <v>https://music.apple.com/us/album/lockup/1894298100</v>
       </c>
       <c r="L157" t="str">
-        <v>Hold Me In The Dark - Myles Smith</v>
+        <v>Lockup - Overmono</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Lo Que Me Pasa Con Vos</v>
+        <v>Young</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/lo-que-me-pasa-con-vos/6765831961</v>
+        <v>https://music.apple.com/us/song/young/6767698952</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-15</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Lo Que Me Pasa Con Vos - Single</v>
+        <v>Young</v>
       </c>
       <c r="G158" t="str">
-        <v>2:53</v>
+        <v>2:46</v>
       </c>
       <c r="H158" t="str">
-        <v>Sebastián Yatra</v>
+        <v>Dan + Shay</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/sebasti%C3%A1n-yatra/722264654</v>
+        <v>https://music.apple.com/us/artist/dan-shay/690319057</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/lo-que-me-pasa-con-vos/1896093008</v>
+        <v>https://music.apple.com/us/album/young/6767698951</v>
       </c>
       <c r="L158" t="str">
-        <v>Lo Que Me Pasa Con Vos - Sebastián Yatra</v>
+        <v>Young - Dan + Shay</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Wide Eyed</v>
+        <v>Parachute</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/wide-eyed/1884734079</v>
+        <v>https://music.apple.com/us/song/parachute/6764119241</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-15</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Wide Eyed</v>
+        <v>Parachute - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:22</v>
+        <v>2:52</v>
       </c>
       <c r="H159" t="str">
-        <v>Mack Keane</v>
+        <v>Maren Morris</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/mack-keane/899781096</v>
+        <v>https://music.apple.com/us/artist/maren-morris/262260873</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/wide-eyed/1884733813</v>
+        <v>https://music.apple.com/us/album/parachute/1895648983</v>
       </c>
       <c r="L159" t="str">
-        <v>Wide Eyed - Mack Keane</v>
+        <v>Parachute - Maren Morris</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Changes</v>
+        <v>Little Things</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/changes/6763650807</v>
+        <v>https://music.apple.com/us/song/little-things/6766351153</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-15</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Changes - Single</v>
+        <v>Little Things - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:18</v>
+        <v>2:55</v>
       </c>
       <c r="H160" t="str">
-        <v>Tommy Richman</v>
+        <v>Kevin Jonas</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/tommy-richman/1447723583</v>
+        <v>https://music.apple.com/us/artist/kevin-jonas/21138190</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/changes/1895418156</v>
+        <v>https://music.apple.com/us/album/little-things/6766350882</v>
       </c>
       <c r="L160" t="str">
-        <v>Changes - Tommy Richman</v>
+        <v>Little Things - Kevin Jonas</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Don't Say Goodbye</v>
+        <v>Fish Hunt Golf Drink</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/dont-say-goodbye/6765758054</v>
+        <v>https://music.apple.com/us/song/fish-hunt-golf-drink/6766651884</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-15</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>The Story of Michael and Tanya</v>
+        <v>Signs</v>
       </c>
       <c r="G161" t="str">
-        <v>4:33</v>
+        <v>2:34</v>
       </c>
       <c r="H161" t="str">
-        <v>The War And Treaty</v>
+        <v>Luke Bryan</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/the-war-and-treaty/951165936</v>
+        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/dont-say-goodbye/1896061742</v>
+        <v>https://music.apple.com/us/album/fish-hunt-golf-drink/6766651878</v>
       </c>
       <c r="L161" t="str">
-        <v>Don't Say Goodbye - The War And Treaty</v>
+        <v>Fish Hunt Golf Drink - Luke Bryan</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>depressed on the internet</v>
+        <v>PAGEANT STAGE</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/depressed-on-the-internet/6763440792</v>
+        <v>https://music.apple.com/us/song/pageant-stage/6764125889</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-15</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>depressed on the internet - Single</v>
+        <v>THE EDGE</v>
       </c>
       <c r="G162" t="str">
-        <v>2:57</v>
+        <v>2:52</v>
       </c>
       <c r="H162" t="str">
-        <v>Bea Miller</v>
+        <v>Tone Stith</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/bea-miller/706171903</v>
+        <v>https://music.apple.com/us/artist/tone-stith/1167717310</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/depressed-on-the-internet/1895316228</v>
+        <v>https://music.apple.com/us/album/pageant-stage/1895651504</v>
       </c>
       <c r="L162" t="str">
-        <v>depressed on the internet - Bea Miller</v>
+        <v>PAGEANT STAGE - Tone Stith</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Dear Burt</v>
+        <v>Firestorm</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/dear-burt/1886736665</v>
+        <v>https://music.apple.com/us/song/firestorm/1868827004</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-15</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Scenes from a Velvet Room</v>
+        <v>Of Earth &amp; Wires</v>
       </c>
       <c r="G163" t="str">
-        <v>2:53</v>
+        <v>2:29</v>
       </c>
       <c r="H163" t="str">
-        <v>Stephan Moccio</v>
+        <v>Dua Saleh</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
+        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/dear-burt/1886736650</v>
+        <v>https://music.apple.com/us/album/firestorm/1868826829</v>
       </c>
       <c r="L163" t="str">
-        <v>Dear Burt - Stephan Moccio</v>
+        <v>Firestorm - Dua Saleh</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Alla Blues</v>
+        <v>girl next door</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/alla-blues/6764654322</v>
+        <v>https://music.apple.com/us/song/girl-next-door/6768077610</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-15</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Black Mozart</v>
+        <v>girl next door - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:50</v>
+        <v>3:18</v>
       </c>
       <c r="H164" t="str">
-        <v>Jon Batiste</v>
+        <v>mgk</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
+        <v>https://music.apple.com/us/artist/mgk/465954501</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/alla-blues/1895866355</v>
+        <v>https://music.apple.com/us/album/girl-next-door/6768077609</v>
       </c>
       <c r="L164" t="str">
-        <v>Alla Blues - Jon Batiste</v>
+        <v>girl next door - mgk</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Think About Me</v>
+        <v>BIG DOG</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/think-about-me/6765783932</v>
+        <v>https://music.apple.com/us/song/big-dog/1887197046</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-15</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Think About Me - Single</v>
+        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
       </c>
       <c r="G165" t="str">
-        <v>2:39</v>
+        <v>3:36</v>
       </c>
       <c r="H165" t="str">
-        <v>Gabriella Rose</v>
+        <v>Genesis Owusu</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
+        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/think-about-me/1896073124</v>
+        <v>https://music.apple.com/us/album/big-dog/1887196431</v>
       </c>
       <c r="L165" t="str">
-        <v>Think About Me - Gabriella Rose</v>
+        <v>BIG DOG - Genesis Owusu</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Meet Again</v>
+        <v>idea of love - A COLORS SHOW</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/meet-again/6764129305</v>
+        <v>https://music.apple.com/us/song/idea-of-love-a-colors-show/6767667046</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-15</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Meet Again - Single</v>
+        <v>idea of love - A COLORS SHOW - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:26</v>
+        <v>2:34</v>
       </c>
       <c r="H166" t="str">
-        <v>Kaskade</v>
+        <v>kwn</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/kaskade/2827464</v>
+        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/meet-again/1895652592</v>
+        <v>https://music.apple.com/us/album/idea-of-love-a-colors-show/6767666835</v>
       </c>
       <c r="L166" t="str">
-        <v>Meet Again - Kaskade</v>
+        <v>idea of love - A COLORS SHOW - kwn</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Happy Now</v>
+        <v>Heavy Serenade</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/happy-now/1857952261</v>
+        <v>https://music.apple.com/us/song/heavy-serenade/1892154309</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-15</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>The Afterparty</v>
+        <v>Heavy Serenade - EP</v>
       </c>
       <c r="G167" t="str">
-        <v>2:42</v>
+        <v>3:00</v>
       </c>
       <c r="H167" t="str">
-        <v>Lykke Li</v>
+        <v>NMIXX</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
+        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/happy-now/1857952252</v>
+        <v>https://music.apple.com/us/album/heavy-serenade/1892154305</v>
       </c>
       <c r="L167" t="str">
-        <v>Happy Now - Lykke Li</v>
+        <v>Heavy Serenade - NMIXX</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Oblivion</v>
+        <v>ddok ddok ddok</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/oblivion/1888236202</v>
+        <v>https://music.apple.com/us/song/ddok-ddok-ddok/6764203482</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-15</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Oblivion - Single</v>
+        <v>ddok ddok ddok - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>2:21</v>
+        <v>2:35</v>
       </c>
       <c r="H168" t="str">
-        <v>Agents Of Time</v>
+        <v>BOYNEXTDOOR</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/agents-of-time/794971951</v>
+        <v>https://music.apple.com/us/artist/boynextdoor/1687612559</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/oblivion/1888236199</v>
+        <v>https://music.apple.com/us/album/ddok-ddok-ddok/6764203481</v>
       </c>
       <c r="L168" t="str">
-        <v>Oblivion - Agents Of Time</v>
+        <v>ddok ddok ddok - BOYNEXTDOOR</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>See U in Hell (From the Netflix Series "Devil May Cry")</v>
+        <v>Shut It Down</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/see-u-in-hell-from-the-netflix-series-devil-may-cry/1894386678</v>
+        <v>https://music.apple.com/us/song/shut-it-down/6763631128</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-15</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>See U in Hell (From the Netflix Series "Devil May Cry") - Single</v>
+        <v>Shut It Down - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>4:03</v>
+        <v>3:32</v>
       </c>
       <c r="H169" t="str">
-        <v>Papa Roach</v>
+        <v>Boys Noize</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
+        <v>https://music.apple.com/us/artist/boys-noize/60393190</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/see-u-in-hell-from-the-netflix-series-devil-may-cry/1894386676</v>
+        <v>https://music.apple.com/us/album/shut-it-down/1895408470</v>
       </c>
       <c r="L169" t="str">
-        <v>See U in Hell (From the Netflix Series "Devil May Cry") - Papa Roach</v>
+        <v>Shut It Down - Boys Noize</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Top of the Hill</v>
+        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss)</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/top-of-the-hill/6766614503</v>
+        <v>https://music.apple.com/us/song/together-feat-nikki-nair-jessy-lanza-prentiss/6763207821</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-15</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Top of the Hill - Single</v>
+        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss) - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>1:50</v>
+        <v>3:18</v>
       </c>
       <c r="H170" t="str">
-        <v>DDG</v>
+        <v>The Avalanches</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/ddg/3954994</v>
+        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/top-of-the-hill/6766614303</v>
+        <v>https://music.apple.com/us/album/together-feat-nikki-nair-jessy-lanza-prentiss/1895215105</v>
       </c>
       <c r="L170" t="str">
-        <v>Top of the Hill - DDG</v>
+        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss) - The Avalanches</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Oh Savannah</v>
+        <v>Can’t Miss You</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/oh-savannah/1869140944</v>
+        <v>https://music.apple.com/us/song/cant-miss-you/1886810999</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-15</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Change Of Plans</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="G171" t="str">
-        <v>3:05</v>
+        <v>2:32</v>
       </c>
       <c r="H171" t="str">
-        <v>49 Winchester</v>
+        <v>Sublime</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/49-winchester/869425058</v>
+        <v>https://music.apple.com/us/artist/sublime/63480</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/oh-savannah/1869140544</v>
+        <v>https://music.apple.com/us/album/cant-miss-you/1886810990</v>
       </c>
       <c r="L171" t="str">
-        <v>Oh Savannah - 49 Winchester</v>
+        <v>Can’t Miss You - Sublime</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Game On (feat. JT)</v>
+        <v>Razorblades And Runways</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/game-on-feat-jt/6763271985</v>
+        <v>https://music.apple.com/us/song/razorblades-and-runways/1888004809</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-15</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Sugar Girl - EP</v>
+        <v>Get It Honest</v>
       </c>
       <c r="G172" t="str">
-        <v>2:29</v>
+        <v>3:33</v>
       </c>
       <c r="H172" t="str">
-        <v>Little Simz</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/little-simz/627674564</v>
+        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/game-on-feat-jt/1895242144</v>
+        <v>https://music.apple.com/us/album/razorblades-and-runways/1888004802</v>
       </c>
       <c r="L172" t="str">
-        <v>Game On (feat. JT) - Little Simz</v>
+        <v>Razorblades And Runways - The Revivalists</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>How to Forget</v>
+        <v>Massacre</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/how-to-forget/1874100607</v>
+        <v>https://music.apple.com/us/song/massacre/1892127745</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-15</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>ARCADE</v>
+        <v>Massacre - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>4:01</v>
+        <v>2:55</v>
       </c>
       <c r="H173" t="str">
-        <v>Deb Never</v>
+        <v>Murex</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
+        <v>https://music.apple.com/us/artist/murex/1607430925</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/how-to-forget/1874100412</v>
+        <v>https://music.apple.com/us/album/massacre/1892127742</v>
       </c>
       <c r="L173" t="str">
-        <v>How to Forget - Deb Never</v>
+        <v>Massacre - Murex</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Ne Plus Ultra</v>
+        <v>Better That Way</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/ne-plus-ultra/6765530891</v>
+        <v>https://music.apple.com/us/song/better-that-way/6766273199</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-15</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Ne Plus Ultra - Single</v>
+        <v>Christian Name</v>
       </c>
       <c r="G174" t="str">
-        <v>2:49</v>
+        <v>3:45</v>
       </c>
       <c r="H174" t="str">
-        <v>ear</v>
+        <v>Charles Wesley Godwin</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/ear/1829661500</v>
+        <v>https://music.apple.com/us/artist/charles-wesley-godwin/1441994025</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/ne-plus-ultra/1895982136</v>
+        <v>https://music.apple.com/us/album/better-that-way/1896261802</v>
       </c>
       <c r="L174" t="str">
-        <v>Ne Plus Ultra - ear</v>
+        <v>Better That Way - Charles Wesley Godwin</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Mirror</v>
+        <v>Apollo</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/mirror/6763620093</v>
+        <v>https://music.apple.com/us/song/apollo/6765602431</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-15</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Mirror - Single</v>
+        <v>Apollo - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:19</v>
+        <v>3:35</v>
       </c>
       <c r="H175" t="str">
-        <v>MOD SUN</v>
+        <v>Bryant Barnes</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/mod-sun/373888452</v>
+        <v>https://music.apple.com/us/artist/bryant-barnes/1579668433</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/mirror/1895402181</v>
+        <v>https://music.apple.com/us/album/apollo/6765602369</v>
       </c>
       <c r="L175" t="str">
-        <v>Mirror - MOD SUN</v>
+        <v>Apollo - Bryant Barnes</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Miel Con Licor</v>
+        <v>Infinity (123)</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/miel-con-licor/6763085043</v>
+        <v>https://music.apple.com/us/song/infinity-123/6763447312</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-15</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Bandera Blanca</v>
+        <v>Infinity (123) - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:27</v>
+        <v>2:19</v>
       </c>
       <c r="H176" t="str">
-        <v>Christian Nodal</v>
+        <v>December 10</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
+        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/miel-con-licor/1895154946</v>
+        <v>https://music.apple.com/us/album/infinity-123/1895320456</v>
       </c>
       <c r="L176" t="str">
-        <v>Miel Con Licor - Christian Nodal</v>
+        <v>Infinity (123) - December 10</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Macramé (feat. Mei Semones)</v>
+        <v>Ain't Over Me Yet</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/macram%C3%A9-feat-mei-semones/6763155997</v>
+        <v>https://music.apple.com/us/song/aint-over-me-yet/6767283811</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-15</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Macramé (feat. Mei Semones) - Single</v>
+        <v>Cherry Valley Forever</v>
       </c>
       <c r="G177" t="str">
-        <v>3:31</v>
+        <v>3:24</v>
       </c>
       <c r="H177" t="str">
-        <v>aron!</v>
+        <v>Carter Faith</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/aron/1673838787</v>
+        <v>https://music.apple.com/us/artist/carter-faith/1489205896</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/macram%C3%A9-feat-mei-semones/1895189295</v>
+        <v>https://music.apple.com/us/album/aint-over-me-yet/1896458169</v>
       </c>
       <c r="L177" t="str">
-        <v>Macramé (feat. Mei Semones) - aron!</v>
+        <v>Ain't Over Me Yet - Carter Faith</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Nighttime (feat. Austin Brown &amp; David Shaw)</v>
+        <v>Where Did You Go</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/nighttime-feat-austin-brown-david-shaw/1882831738</v>
+        <v>https://music.apple.com/us/song/where-did-you-go/1877958504</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-15</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>The Last Balloon</v>
+        <v>Growing Pains (Deluxe)</v>
       </c>
       <c r="G178" t="str">
-        <v>3:14</v>
+        <v>2:47</v>
       </c>
       <c r="H178" t="str">
-        <v>Tank and the Bangas</v>
+        <v>Trousdale</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/nighttime-feat-austin-brown-david-shaw/1882831446</v>
+        <v>https://music.apple.com/us/album/where-did-you-go/1877958112</v>
       </c>
       <c r="L178" t="str">
-        <v>Nighttime (feat. Austin Brown &amp; David Shaw) - Tank and the Bangas</v>
+        <v>Where Did You Go - Trousdale</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>They Found One Of My Graves</v>
+        <v>I LOVE YOU</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/they-found-one-of-my-graves/1881564857</v>
+        <v>https://music.apple.com/us/song/i-love-you/6766999950</v>
       </c>
       <c r="D179" t="str">
         <v>2026-05-15</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Pre-Historic Metal</v>
+        <v>I LOVE YOU - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>5:14</v>
+        <v>3:11</v>
       </c>
       <c r="H179" t="str">
-        <v>Darkthrone</v>
+        <v>Noga Erez</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/darkthrone/112417640</v>
+        <v>https://music.apple.com/us/artist/noga-erez/1166657901</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/they-found-one-of-my-graves/1881564845</v>
+        <v>https://music.apple.com/us/album/i-love-you/6766999949</v>
       </c>
       <c r="L179" t="str">
-        <v>They Found One Of My Graves - Darkthrone</v>
+        <v>I LOVE YOU - Noga Erez</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Cloudfall</v>
+        <v>Housekeeping</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/cloudfall/1892921580</v>
+        <v>https://music.apple.com/us/song/housekeeping/6766290834</v>
       </c>
       <c r="D180" t="str">
         <v>2026-05-15</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Cycles in the Infinite Dream</v>
+        <v>Housekeeping - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>4:06</v>
+        <v>3:25</v>
       </c>
       <c r="H180" t="str">
-        <v>REZN</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/rezn/1441800527</v>
+        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/cloudfall/1892921394</v>
+        <v>https://music.apple.com/us/album/housekeeping/6766290823</v>
       </c>
       <c r="L180" t="str">
-        <v>Cloudfall - REZN</v>
+        <v>Housekeeping - Ally Salort</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Doom in Bloom</v>
+        <v>Surprise Surprise</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/doom-in-bloom/1883081839</v>
+        <v>https://music.apple.com/us/song/surprise-surprise/6764842119</v>
       </c>
       <c r="D181" t="str">
         <v>2026-05-15</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Hum of Hurt</v>
+        <v>Surprise Surprise - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:17</v>
+        <v>2:55</v>
       </c>
       <c r="H181" t="str">
-        <v>Converge</v>
+        <v>Chloe Qisha</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/doom-in-bloom/1883081837</v>
+        <v>https://music.apple.com/us/album/surprise-surprise/1895934408</v>
       </c>
       <c r="L181" t="str">
-        <v>Doom in Bloom - Converge</v>
+        <v>Surprise Surprise - Chloe Qisha</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Only The Good I Keep</v>
+        <v>Dog</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/only-the-good-i-keep/1871484973</v>
+        <v>https://music.apple.com/us/song/dog/1885967384</v>
       </c>
       <c r="D182" t="str">
         <v>2026-05-15</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Remember The Humans</v>
+        <v>Gentleman</v>
       </c>
       <c r="G182" t="str">
-        <v>3:27</v>
+        <v>3:08</v>
       </c>
       <c r="H182" t="str">
-        <v>Broken Social Scene</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/broken-social-scene/6925799</v>
+        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/only-the-good-i-keep/1871484971</v>
+        <v>https://music.apple.com/us/album/dog/1885967368</v>
       </c>
       <c r="L182" t="str">
-        <v>Only The Good I Keep - Broken Social Scene</v>
+        <v>Dog - Towa Bird</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Zoom 97</v>
+        <v>I Never See Her</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/zoom-97/1884970574</v>
+        <v>https://music.apple.com/us/song/i-never-see-her/6764149225</v>
       </c>
       <c r="D183" t="str">
         <v>2026-05-15</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Philadelphia's been good to me</v>
+        <v>I Never See Her - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>4:54</v>
+        <v>3:04</v>
       </c>
       <c r="H183" t="str">
-        <v>Kurt Vile</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/kurt-vile/274234314</v>
+        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/zoom-97/1884970572</v>
+        <v>https://music.apple.com/us/album/i-never-see-her/1895660748</v>
       </c>
       <c r="L183" t="str">
-        <v>Zoom 97 - Kurt Vile</v>
+        <v>I Never See Her - Spacey Jane</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Switch Up</v>
+        <v>No God</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/switch-up/6764419407</v>
+        <v>https://music.apple.com/us/song/no-god/1891187414</v>
       </c>
       <c r="D184" t="str">
         <v>2026-05-15</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Switch Up - Single</v>
+        <v>Alone Together</v>
       </c>
       <c r="G184" t="str">
-        <v>3:35</v>
+        <v>2:45</v>
       </c>
       <c r="H184" t="str">
-        <v>Mike D</v>
+        <v>Show Me the Body</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/mike-d/1646443127</v>
+        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/switch-up/1895772278</v>
+        <v>https://music.apple.com/us/album/no-god/1891187411</v>
       </c>
       <c r="L184" t="str">
-        <v>Switch Up - Mike D</v>
+        <v>No God - Show Me the Body</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Surprise</v>
+        <v>burden</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/surprise/1894873625</v>
+        <v>https://music.apple.com/us/song/burden/6767688180</v>
       </c>
       <c r="D185" t="str">
         <v>2026-05-15</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Doe Or Die III</v>
+        <v>burden - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:48</v>
+        <v>3:24</v>
       </c>
       <c r="H185" t="str">
-        <v>AZ</v>
+        <v>Abe Parker</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/az/35299</v>
+        <v>https://music.apple.com/us/artist/abe-parker/490444584</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/surprise/1894873352</v>
+        <v>https://music.apple.com/us/album/burden/6767688179</v>
       </c>
       <c r="L185" t="str">
-        <v>Surprise - AZ</v>
+        <v>burden - Abe Parker</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Better Days</v>
+        <v>Chico Raro</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/better-days/6763394083</v>
+        <v>https://music.apple.com/us/song/chico-raro/6767713536</v>
       </c>
       <c r="D186" t="str">
         <v>2026-05-15</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Better Days - Single</v>
+        <v>Chico Raro - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:22</v>
+        <v>3:17</v>
       </c>
       <c r="H186" t="str">
-        <v>Naomi Sharon</v>
+        <v>Arón Piper</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
+        <v>https://music.apple.com/us/artist/ar%C3%B3n-piper/691972942</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/better-days/1895293758</v>
+        <v>https://music.apple.com/us/album/chico-raro/6767713527</v>
       </c>
       <c r="L186" t="str">
-        <v>Better Days - Naomi Sharon</v>
+        <v>Chico Raro - Arón Piper</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Where Have All The Good Men Gone?</v>
+        <v>What's Done Is Done</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/where-have-all-the-good-men-gone/6765484424</v>
+        <v>https://music.apple.com/us/song/whats-done-is-done/6763088629</v>
       </c>
       <c r="D187" t="str">
         <v>2026-05-15</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Where Have All The Good Men Gone? - EP</v>
+        <v>What's Done Is Done - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:14</v>
+        <v>2:53</v>
       </c>
       <c r="H187" t="str">
-        <v>Debbii Dawson</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
+        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/where-have-all-the-good-men-gone/1895967802</v>
+        <v>https://music.apple.com/us/album/whats-done-is-done/1895156626</v>
       </c>
       <c r="L187" t="str">
-        <v>Where Have All The Good Men Gone? - Debbii Dawson</v>
+        <v>What's Done Is Done - Jorja Smith</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>No Pressure</v>
+        <v>round and round</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/no-pressure/6763448750</v>
+        <v>https://music.apple.com/us/song/round-and-round/1885665987</v>
       </c>
       <c r="D188" t="str">
         <v>2026-05-15</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>No Pressure - Single</v>
+        <v>round and round - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:09</v>
+        <v>2:47</v>
       </c>
       <c r="H188" t="str">
-        <v>JYT</v>
+        <v>bbno$</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
+        <v>https://music.apple.com/us/artist/bbno%24/1161580951</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/no-pressure/1895321101</v>
+        <v>https://music.apple.com/us/album/round-and-round/1885665982</v>
       </c>
       <c r="L188" t="str">
-        <v>No Pressure - JYT</v>
+        <v>round and round - bbno$</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>What's the Point!</v>
+        <v>Ain’t That Deep</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/whats-the-point/1886811061</v>
+        <v>https://music.apple.com/us/song/aint-that-deep/1882831449</v>
       </c>
       <c r="D189" t="str">
         <v>2026-05-15</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Night at the Opera - EP</v>
+        <v>The Last Balloon</v>
       </c>
       <c r="G189" t="str">
-        <v>2:43</v>
+        <v>2:39</v>
       </c>
       <c r="H189" t="str">
-        <v>Emei</v>
+        <v>Tank and the Bangas</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/emei/1583968554</v>
+        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/whats-the-point/1886811055</v>
+        <v>https://music.apple.com/us/album/aint-that-deep/1882831446</v>
       </c>
       <c r="L189" t="str">
-        <v>What's the Point! - Emei</v>
+        <v>Ain’t That Deep - Tank and the Bangas</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Pachamama</v>
+        <v>Emily</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/pachamama/1893815453</v>
+        <v>https://music.apple.com/us/song/emily/1893405442</v>
       </c>
       <c r="D190" t="str">
         <v>2026-05-15</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Así Es La Vida</v>
+        <v>So Much To Say - EP</v>
       </c>
       <c r="G190" t="str">
-        <v>3:20</v>
+        <v>2:35</v>
       </c>
       <c r="H190" t="str">
-        <v>Codiciado</v>
+        <v>Daisy Grenade</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/codiciado/1434810911</v>
+        <v>https://music.apple.com/us/artist/daisy-grenade/1611437131</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/pachamama/1893815448</v>
+        <v>https://music.apple.com/us/album/emily/1893405440</v>
       </c>
       <c r="L190" t="str">
-        <v>Pachamama - Codiciado</v>
+        <v>Emily - Daisy Grenade</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Multiplied</v>
+        <v>Hold</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/multiplied/1889977459</v>
+        <v>https://music.apple.com/us/song/hold/6767296480</v>
       </c>
       <c r="D191" t="str">
         <v>2026-05-15</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Multiplied - Single</v>
+        <v>Hold - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:02</v>
+        <v>4:07</v>
       </c>
       <c r="H191" t="str">
-        <v>Luna Li</v>
+        <v>Sabrina Sterling</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/luna-li/1242663809</v>
+        <v>https://music.apple.com/us/artist/sabrina-sterling/1577892147</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/multiplied/1889977458</v>
+        <v>https://music.apple.com/us/album/hold/1896462063</v>
       </c>
       <c r="L191" t="str">
-        <v>Multiplied - Luna Li</v>
+        <v>Hold - Sabrina Sterling</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Six String</v>
+        <v>Flying Monkey</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/six-string/1892171728</v>
+        <v>https://music.apple.com/us/song/flying-monkey/1894351228</v>
       </c>
       <c r="D192" t="str">
         <v>2026-05-15</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Six String - Single</v>
+        <v>Flying Monkey - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:11</v>
+        <v>4:09</v>
       </c>
       <c r="H192" t="str">
-        <v>Lila Dupont</v>
+        <v>Blue Medusa</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/lila-dupont/1508792561</v>
+        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/six-string/1892171725</v>
+        <v>https://music.apple.com/us/album/flying-monkey/1894351227</v>
       </c>
       <c r="L192" t="str">
-        <v>Six String - Lila Dupont</v>
+        <v>Flying Monkey - Blue Medusa</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Take Heart</v>
+        <v>Anything Goes</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/take-heart/1877993013</v>
+        <v>https://music.apple.com/us/song/anything-goes/1891118972</v>
       </c>
       <c r="D193" t="str">
         <v>2026-05-15</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Harbour</v>
+        <v>Anything Goes</v>
       </c>
       <c r="G193" t="str">
-        <v>4:07</v>
+        <v>3:00</v>
       </c>
       <c r="H193" t="str">
-        <v>Jon Bryant</v>
+        <v>Kaleena Zanders</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/jon-bryant/341294359</v>
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/take-heart/1877992810</v>
+        <v>https://music.apple.com/us/album/anything-goes/1891118971</v>
       </c>
       <c r="L193" t="str">
-        <v>Take Heart - Jon Bryant</v>
+        <v>Anything Goes - Kaleena Zanders</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Clarion</v>
+        <v>We Are</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/clarion/1887589702</v>
+        <v>https://music.apple.com/us/song/we-are/1894252873</v>
       </c>
       <c r="D194" t="str">
         <v>2026-05-15</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>You Are Spring!</v>
+        <v>We Are - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:23</v>
+        <v>3:33</v>
       </c>
       <c r="H194" t="str">
-        <v>Tasha</v>
+        <v>Adam Ten</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/tasha/1413936117</v>
+        <v>https://music.apple.com/us/artist/adam-ten/1472226854</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/clarion/1887589690</v>
+        <v>https://music.apple.com/us/album/we-are/1894252870</v>
       </c>
       <c r="L194" t="str">
-        <v>Clarion - Tasha</v>
+        <v>We Are - Adam Ten</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Stepping Stone</v>
+        <v>It's For the Kids</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/stepping-stone/1889387056</v>
+        <v>https://music.apple.com/us/song/its-for-the-kids/1867327679</v>
       </c>
       <c r="D195" t="str">
         <v>2026-05-15</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Beams - Single</v>
+        <v>Cursum Perficio</v>
       </c>
       <c r="G195" t="str">
-        <v>2:49</v>
+        <v>4:20</v>
       </c>
       <c r="H195" t="str">
-        <v>DERBY</v>
+        <v>Anthrax</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/derby/1772719795</v>
+        <v>https://music.apple.com/us/artist/anthrax/80417</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/stepping-stone/1889387054</v>
+        <v>https://music.apple.com/us/album/its-for-the-kids/1867327673</v>
       </c>
       <c r="L195" t="str">
-        <v>Stepping Stone - DERBY</v>
+        <v>It's For the Kids - Anthrax</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>confessions part iii</v>
+        <v>Pure Ecstasy</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/confessions-part-iii/1892181989</v>
+        <v>https://music.apple.com/us/song/pure-ecstasy/6762228978</v>
       </c>
       <c r="D196" t="str">
         <v>2026-05-15</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>autogratis</v>
+        <v>Pure Ecstasy</v>
       </c>
       <c r="G196" t="str">
-        <v>2:01</v>
+        <v>3:05</v>
       </c>
       <c r="H196" t="str">
-        <v>Chanpan</v>
+        <v>Beartooth</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/chanpan/1704417748</v>
+        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/confessions-part-iii/1892181981</v>
+        <v>https://music.apple.com/us/album/pure-ecstasy/1893453878</v>
       </c>
       <c r="L196" t="str">
-        <v>confessions part iii - Chanpan</v>
+        <v>Pure Ecstasy - Beartooth</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>cherry garcia</v>
+        <v>Something Wicked</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/cherry-garcia/1885000655</v>
+        <v>https://music.apple.com/us/song/something-wicked/6766252959</v>
       </c>
       <c r="D197" t="str">
         <v>2026-05-15</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>cherry garcia - Single</v>
+        <v>Something Wicked - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>2:30</v>
+        <v>3:28</v>
       </c>
       <c r="H197" t="str">
-        <v>supermodel*</v>
+        <v>Breaking Benjamin</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/supermodel/1817515489</v>
+        <v>https://music.apple.com/us/artist/breaking-benjamin/3299379</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/cherry-garcia/1885000654</v>
+        <v>https://music.apple.com/us/album/something-wicked/1896253678</v>
       </c>
       <c r="L197" t="str">
-        <v>cherry garcia - supermodel*</v>
+        <v>Something Wicked - Breaking Benjamin</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Disco Cherry</v>
+        <v>Feel The Funk</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/disco-cherry/1890195881</v>
+        <v>https://music.apple.com/us/song/feel-the-funk/6763294007</v>
       </c>
       <c r="D198" t="str">
         <v>2026-05-15</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Disco Cherry - Single</v>
+        <v>The Funk EP - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>3:20</v>
+        <v>3:26</v>
       </c>
       <c r="H198" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Riordan</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/purple-disco-machine/357397685</v>
+        <v>https://music.apple.com/us/artist/riordan/1517575029</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/disco-cherry/1890195880</v>
+        <v>https://music.apple.com/us/album/feel-the-funk/1895251685</v>
       </c>
       <c r="L198" t="str">
-        <v>Disco Cherry - Purple Disco Machine</v>
+        <v>Feel The Funk - Riordan</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Tal Vez</v>
+        <v>Everglades (Remix)</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/tal-vez/1894892261</v>
+        <v>https://music.apple.com/us/song/everglades-remix/6767719584</v>
       </c>
       <c r="D199" t="str">
         <v>2026-05-15</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>El Amante</v>
+        <v>Everglades (Remix) - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>2:14</v>
+        <v>2:42</v>
       </c>
       <c r="H199" t="str">
-        <v>Dariel Amant</v>
+        <v>Aziedoesntexist</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/dariel-amant/1595935945</v>
+        <v>https://music.apple.com/us/artist/aziedoesntexist/1831152556</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/tal-vez/1894892257</v>
+        <v>https://music.apple.com/us/album/everglades-remix/6767719577</v>
       </c>
       <c r="L199" t="str">
-        <v>Tal Vez - Dariel Amant</v>
+        <v>Everglades (Remix) - Aziedoesntexist</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>The Voyager</v>
+        <v>Walk</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/the-voyager/6764897214</v>
+        <v>https://music.apple.com/us/song/walk/1892180098</v>
       </c>
       <c r="D200" t="str">
         <v>2026-05-15</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>The Voyager - Single</v>
+        <v>Walk - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>4:37</v>
+        <v>2:25</v>
       </c>
       <c r="H200" t="str">
-        <v>Chance Peña</v>
+        <v>Melodicb</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/chance-pe%C3%B1a/1042737143</v>
+        <v>https://music.apple.com/us/artist/melodicb/1440206517</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/the-voyager/1895954206</v>
+        <v>https://music.apple.com/us/album/walk/1892180097</v>
       </c>
       <c r="L200" t="str">
-        <v>The Voyager - Chance Peña</v>
+        <v>Walk - Melodicb</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Pictures of You</v>
+        <v>Volver a Ti</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/pictures-of-you/6764176261</v>
+        <v>https://music.apple.com/us/song/volver-a-ti/6766258204</v>
       </c>
       <c r="D201" t="str">
         <v>2026-05-15</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Pictures of You</v>
+        <v>Norteña</v>
       </c>
       <c r="G201" t="str">
-        <v>3:34</v>
+        <v>3:47</v>
       </c>
       <c r="H201" t="str">
-        <v>Buffalo Traffic Jam</v>
+        <v>Julieta Venegas</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
+        <v>https://music.apple.com/us/artist/julieta-venegas/302960</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/pictures-of-you/1895672454</v>
+        <v>https://music.apple.com/us/album/volver-a-ti/1896255736</v>
       </c>
       <c r="L201" t="str">
-        <v>Pictures of You - Buffalo Traffic Jam</v>
+        <v>Volver a Ti - Julieta Venegas</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Buy What U Want</v>
+        <v>Bahamas</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/buy-what-u-want/6763137223</v>
+        <v>https://music.apple.com/us/song/bahamas/6764695848</v>
       </c>
       <c r="D202" t="str">
         <v>2026-05-15</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>Road To Osshland: The Series</v>
+        <v>Bahamas - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>3:47</v>
+        <v>2:06</v>
       </c>
       <c r="H202" t="str">
-        <v>Black Fortune</v>
+        <v>LENCHO</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/black-fortune/557044567</v>
+        <v>https://music.apple.com/us/artist/lencho/1854923384</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/buy-what-u-want/1895178841</v>
+        <v>https://music.apple.com/us/album/bahamas/6764695847</v>
       </c>
       <c r="L202" t="str">
-        <v>Buy What U Want - Black Fortune</v>
+        <v>Bahamas - LENCHO</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>MOOD BRAZIL</v>
+        <v>Same Old Song</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/mood-brazil/6766985126</v>
+        <v>https://music.apple.com/us/song/same-old-song/6762860685</v>
       </c>
       <c r="D203" t="str">
         <v>2026-05-15</v>
@@ -8089,36 +8089,36 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>MOOD BRAZIL - Single</v>
+        <v>Same Old Song - Single</v>
       </c>
       <c r="G203" t="str">
-        <v>2:29</v>
+        <v>4:12</v>
       </c>
       <c r="H203" t="str">
-        <v>Lil Naay</v>
+        <v>Lila Drew</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/lil-naay/1513690516</v>
+        <v>https://music.apple.com/us/artist/lila-drew/1439482732</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/mood-brazil/6766984734</v>
+        <v>https://music.apple.com/us/album/same-old-song/1895047985</v>
       </c>
       <c r="L203" t="str">
-        <v>MOOD BRAZIL - Lil Naay</v>
+        <v>Same Old Song - Lila Drew</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>high school sweetheart</v>
+        <v>gentle</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/high-school-sweetheart/6763491151</v>
+        <v>https://music.apple.com/us/song/gentle/6762828356</v>
       </c>
       <c r="D204" t="str">
         <v>2026-05-15</v>
@@ -8127,36 +8127,36 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>ashley cooke</v>
+        <v>gentle - Single</v>
       </c>
       <c r="G204" t="str">
-        <v>3:11</v>
+        <v>2:48</v>
       </c>
       <c r="H204" t="str">
-        <v>Ashley Cooke</v>
+        <v>Venus Anon</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
+        <v>https://music.apple.com/us/artist/venus-anon/1635970130</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/high-school-sweetheart/1895339553</v>
+        <v>https://music.apple.com/us/album/gentle/1895031896</v>
       </c>
       <c r="L204" t="str">
-        <v>high school sweetheart - Ashley Cooke</v>
+        <v>gentle - Venus Anon</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Vibe Responsibly (feat. Isaiah Rashad)</v>
+        <v>Letters of Your Name</v>
       </c>
       <c r="B205" t="str">
         <v/>
       </c>
       <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/vibe-responsibly-feat-isaiah-rashad/6766279282</v>
+        <v>https://music.apple.com/us/song/letters-of-your-name/1892919741</v>
       </c>
       <c r="D205" t="str">
         <v>2026-05-15</v>
@@ -8165,36 +8165,36 @@
         <v/>
       </c>
       <c r="F205" t="str">
-        <v>Vibe Responsibly (feat. Isaiah Rashad) - Single</v>
+        <v>Congratulations</v>
       </c>
       <c r="G205" t="str">
-        <v>2:55</v>
+        <v>3:21</v>
       </c>
       <c r="H205" t="str">
-        <v>Ray Vaughn</v>
+        <v>Jacob Ungerleider</v>
       </c>
       <c r="I205" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/ray-vaughn/1303356758</v>
+        <v>https://music.apple.com/us/artist/jacob-ungerleider/1460845591</v>
       </c>
       <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/vibe-responsibly-feat-isaiah-rashad/1896264288</v>
+        <v>https://music.apple.com/us/album/letters-of-your-name/1892919737</v>
       </c>
       <c r="L205" t="str">
-        <v>Vibe Responsibly (feat. Isaiah Rashad) - Ray Vaughn</v>
+        <v>Letters of Your Name - Jacob Ungerleider</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>big plans</v>
+        <v>Seratonin</v>
       </c>
       <c r="B206" t="str">
         <v/>
       </c>
       <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/big-plans/1893684291</v>
+        <v>https://music.apple.com/us/song/seratonin/6763447428</v>
       </c>
       <c r="D206" t="str">
         <v>2026-05-15</v>
@@ -8203,36 +8203,36 @@
         <v/>
       </c>
       <c r="F206" t="str">
-        <v>counting horses</v>
+        <v>Seratonin - Single</v>
       </c>
       <c r="G206" t="str">
-        <v>3:14</v>
+        <v>1:55</v>
       </c>
       <c r="H206" t="str">
-        <v>Tom Siletto</v>
+        <v>James Hype</v>
       </c>
       <c r="I206" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
+        <v>https://music.apple.com/us/artist/james-hype/925734064</v>
       </c>
       <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/big-plans/1893684101</v>
+        <v>https://music.apple.com/us/album/seratonin/1895320367</v>
       </c>
       <c r="L206" t="str">
-        <v>big plans - Tom Siletto</v>
+        <v>Seratonin - James Hype</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Running</v>
+        <v>A Digital Touch</v>
       </c>
       <c r="B207" t="str">
         <v/>
       </c>
       <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/running/6764878724</v>
+        <v>https://music.apple.com/us/song/a-digital-touch/6765592539</v>
       </c>
       <c r="D207" t="str">
         <v>2026-05-15</v>
@@ -8241,36 +8241,36 @@
         <v/>
       </c>
       <c r="F207" t="str">
-        <v>Running - Single</v>
+        <v>A Digital Touch - Single</v>
       </c>
       <c r="G207" t="str">
-        <v>2:38</v>
+        <v>2:53</v>
       </c>
       <c r="H207" t="str">
-        <v>Kameron Marlowe</v>
+        <v>Evening Elephants</v>
       </c>
       <c r="I207" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/kameron-marlowe/1467288596</v>
+        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
       </c>
       <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/running/1895947036</v>
+        <v>https://music.apple.com/us/album/a-digital-touch/1896003252</v>
       </c>
       <c r="L207" t="str">
-        <v>Running - Kameron Marlowe</v>
+        <v>A Digital Touch - Evening Elephants</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>FA-TAL!</v>
+        <v>Dead Man's Dog</v>
       </c>
       <c r="B208" t="str">
         <v/>
       </c>
       <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/fa-tal/6764684234</v>
+        <v>https://music.apple.com/us/song/dead-mans-dog/6763447424</v>
       </c>
       <c r="D208" t="str">
         <v>2026-05-15</v>
@@ -8279,30 +8279,220 @@
         <v/>
       </c>
       <c r="F208" t="str">
-        <v>FA-TAL! - Single</v>
+        <v>Aiming Torches At The Sun - EP</v>
       </c>
       <c r="G208" t="str">
+        <v>4:33</v>
+      </c>
+      <c r="H208" t="str">
+        <v>Dermot Henry</v>
+      </c>
+      <c r="I208" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J208" t="str">
+        <v>https://music.apple.com/us/artist/dermot-henry/1704074611</v>
+      </c>
+      <c r="K208" t="str">
+        <v>https://music.apple.com/us/album/dead-mans-dog/1895320369</v>
+      </c>
+      <c r="L208" t="str">
+        <v>Dead Man's Dog - Dermot Henry</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>Fault of God</v>
+      </c>
+      <c r="B209" t="str">
+        <v/>
+      </c>
+      <c r="C209" t="str">
+        <v>https://music.apple.com/us/song/fault-of-god/1887702403</v>
+      </c>
+      <c r="D209" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="E209" t="str">
+        <v/>
+      </c>
+      <c r="F209" t="str">
+        <v>Active Child</v>
+      </c>
+      <c r="G209" t="str">
+        <v>4:13</v>
+      </c>
+      <c r="H209" t="str">
+        <v>Active Child</v>
+      </c>
+      <c r="I209" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J209" t="str">
+        <v>https://music.apple.com/us/artist/active-child/355288617</v>
+      </c>
+      <c r="K209" t="str">
+        <v>https://music.apple.com/us/album/fault-of-god/1887701924</v>
+      </c>
+      <c r="L209" t="str">
+        <v>Fault of God - Active Child</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>Zone (feat. Poppy Baskcomb)</v>
+      </c>
+      <c r="B210" t="str">
+        <v/>
+      </c>
+      <c r="C210" t="str">
+        <v>https://music.apple.com/us/song/zone-feat-poppy-baskcomb/6763982867</v>
+      </c>
+      <c r="D210" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="E210" t="str">
+        <v/>
+      </c>
+      <c r="F210" t="str">
+        <v>Zone (feat. Poppy Baskcomb) - Single</v>
+      </c>
+      <c r="G210" t="str">
+        <v>2:56</v>
+      </c>
+      <c r="H210" t="str">
+        <v>MK</v>
+      </c>
+      <c r="I210" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J210" t="str">
+        <v>https://music.apple.com/us/artist/mk/63097617</v>
+      </c>
+      <c r="K210" t="str">
+        <v>https://music.apple.com/us/album/zone-feat-poppy-baskcomb/1895585800</v>
+      </c>
+      <c r="L210" t="str">
+        <v>Zone (feat. Poppy Baskcomb) - MK</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>Word Vomit</v>
+      </c>
+      <c r="B211" t="str">
+        <v/>
+      </c>
+      <c r="C211" t="str">
+        <v>https://music.apple.com/us/song/word-vomit/1887315297</v>
+      </c>
+      <c r="D211" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="E211" t="str">
+        <v/>
+      </c>
+      <c r="F211" t="str">
+        <v>Word Vomit - Single</v>
+      </c>
+      <c r="G211" t="str">
         <v>2:46</v>
       </c>
-      <c r="H208" t="str">
-        <v>ROBI</v>
-      </c>
-      <c r="I208" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/robi/1458047972</v>
-      </c>
-      <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/fa-tal/1895877867</v>
-      </c>
-      <c r="L208" t="str">
-        <v>FA-TAL! - ROBI</v>
+      <c r="H211" t="str">
+        <v>Baby Queen</v>
+      </c>
+      <c r="I211" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J211" t="str">
+        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
+      </c>
+      <c r="K211" t="str">
+        <v>https://music.apple.com/us/album/word-vomit/1887315294</v>
+      </c>
+      <c r="L211" t="str">
+        <v>Word Vomit - Baby Queen</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>Evil in this House</v>
+      </c>
+      <c r="B212" t="str">
+        <v/>
+      </c>
+      <c r="C212" t="str">
+        <v>https://music.apple.com/us/song/evil-in-this-house/1892398371</v>
+      </c>
+      <c r="D212" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="E212" t="str">
+        <v/>
+      </c>
+      <c r="F212" t="str">
+        <v>Necropolitan</v>
+      </c>
+      <c r="G212" t="str">
+        <v>4:21</v>
+      </c>
+      <c r="H212" t="str">
+        <v>Green Lung</v>
+      </c>
+      <c r="I212" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J212" t="str">
+        <v>https://music.apple.com/us/artist/green-lung/1244071662</v>
+      </c>
+      <c r="K212" t="str">
+        <v>https://music.apple.com/us/album/evil-in-this-house/1892398281</v>
+      </c>
+      <c r="L212" t="str">
+        <v>Evil in this House - Green Lung</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>Heaven on High</v>
+      </c>
+      <c r="B213" t="str">
+        <v/>
+      </c>
+      <c r="C213" t="str">
+        <v>https://music.apple.com/us/song/heaven-on-high/1881724153</v>
+      </c>
+      <c r="D213" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="E213" t="str">
+        <v/>
+      </c>
+      <c r="F213" t="str">
+        <v>A Pale White Dot</v>
+      </c>
+      <c r="G213" t="str">
+        <v>4:19</v>
+      </c>
+      <c r="H213" t="str">
+        <v>Periphery</v>
+      </c>
+      <c r="I213" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J213" t="str">
+        <v>https://music.apple.com/us/artist/periphery/187683869</v>
+      </c>
+      <c r="K213" t="str">
+        <v>https://music.apple.com/us/album/heaven-on-high/1881724003</v>
+      </c>
+      <c r="L213" t="str">
+        <v>Heaven on High - Periphery</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L208"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L213"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-05-week03/titles.xlsx
+++ b/data/global/2026-05-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L213"/>
+  <dimension ref="A1:L195"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלומי ימין - פרפר סגול</v>
+        <v>שני בן משה - שירים לא שלי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-15</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410899&amp;sid=4e49e5e22b0cc4c7806cc2f3c9c4e591</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410900&amp;sid=e8f61624910ad71cfefc2731eed11f18</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-15</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלומי ימין - פרפר סגול</v>
+        <v>שני בן משה - שירים לא שלי</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>עדן גבריאל &amp; אליאן כהן - הפסקת אש</v>
+        <v>ג'קו אייזנברג ורון נשר – קיווינו</v>
       </c>
       <c r="B3" t="str">
         <v>2026-05-15</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410898&amp;sid=4e49e5e22b0cc4c7806cc2f3c9c4e591</v>
+        <v>https://yosmusic.com/%d7%92%d7%a7%d7%95-%d7%90%d7%99%d7%99%d7%96%d7%a0%d7%91%d7%a8%d7%92-%d7%95%d7%a8%d7%95%d7%9f-%d7%a0%d7%a9%d7%a8-%d7%a7%d7%99%d7%95%d7%95%d7%99%d7%a0%d7%95/</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-15</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>השיר "קיווינו” של ג'קו אייזנברג ורון נשר הוא בלדת רוק טעונה שמצליחה להחזיק בו־זמנית גם כאב אישי וגם אמירה חברתית רחבה יותר. זה שיר שלא מציע פתרון ברור. במקום להכריז “יהיה טוב”, הוא נשאר בתוך חוסר הוודאות, בתוך העייפות של</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>עדן גבריאל &amp; אליאן כהן - הפסקת אש</v>
+        <v>ג'קו אייזנברג ורון נשר – קיווינו</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נשמה וקצב - מחפשת רק אותך</v>
+        <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-05-15</v>
+        <v>7 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410897&amp;sid=4e49e5e22b0cc4c7806cc2f3c9c4e591</v>
+        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-15</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>7 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>Harry Styles</v>
       </c>
       <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נשמה וקצב - מחפשת רק אותך</v>
+        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>נשמה וקצב - השיר הזה שלך</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-05-15</v>
+        <v>7 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410896&amp;sid=4e49e5e22b0cc4c7806cc2f3c9c4e591</v>
+        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-15</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>7 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>Eagles</v>
       </c>
       <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>נשמה וקצב - השיר הזה שלך</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>נשמה וקצב - אתה לא בחיי</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-05-15</v>
+        <v>5 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410895&amp;sid=4e49e5e22b0cc4c7806cc2f3c9c4e591</v>
+        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-15</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>5 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>Nora Fatehi</v>
       </c>
       <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>נשמה וקצב - אתה לא בחיי</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ניר עבדו - בורח מעצמי</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-05-15</v>
+        <v>2 months ago</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410894&amp;sid=4e49e5e22b0cc4c7806cc2f3c9c4e591</v>
+        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-15</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>2 months ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>ניר עבדו - בורח מעצמי</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>נהוראי אביסרור - בלעדייך</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-05-15</v>
+        <v>2 months ago</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410893&amp;sid=4e49e5e22b0cc4c7806cc2f3c9c4e591</v>
+        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-15</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>2 months ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>Eurovision Song Contest and Alis</v>
       </c>
       <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>נהוראי אביסרור - בלעדייך</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>מרדכי אברג'ל - חי בן איש חי</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-05-15</v>
+        <v>2 months ago</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410892&amp;sid=4e49e5e22b0cc4c7806cc2f3c9c4e591</v>
+        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-15</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>2 months ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>מרדכי אברג'ל - חי בן איש חי</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>מיקי בן עטר - מחרוזת מזמורי ירושלים 2026</v>
+        <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-05-15</v>
+        <v>6 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410891&amp;sid=4e49e5e22b0cc4c7806cc2f3c9c4e591</v>
+        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-15</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>6 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>The Head And The Heart</v>
       </c>
       <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>מיקי בן עטר - מחרוזת מזמורי ירושלים 2026</v>
+        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ינון טייב - ובנה אותה</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-05-15</v>
+        <v>8 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410889&amp;sid=4e49e5e22b0cc4c7806cc2f3c9c4e591</v>
+        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-15</v>
@@ -793,16 +793,16 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>8 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>Simply Red</v>
       </c>
       <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>ינון טייב - ובנה אותה</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ינאי פדידה - נוף מגדלים</v>
+        <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-05-15</v>
+        <v>5 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410888&amp;sid=4e49e5e22b0cc4c7806cc2f3c9c4e591</v>
+        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-15</v>
@@ -831,16 +831,16 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>5 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>Talking Heads</v>
       </c>
       <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>ינאי פדידה - נוף מגדלים</v>
+        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ינאי פדידה - מפרט</v>
+        <v>Ellise - Liplock (Official Music Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-05-15</v>
+        <v>6 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410887&amp;sid=4e49e5e22b0cc4c7806cc2f3c9c4e591</v>
+        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-15</v>
@@ -869,16 +869,16 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>6 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>Ellise</v>
       </c>
       <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>ינאי פדידה - מפרט</v>
+        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>יוסי שטרית - פצע ישן</v>
+        <v>Tori Kelly - Dive (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-05-15</v>
+        <v>6 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410886&amp;sid=4e49e5e22b0cc4c7806cc2f3c9c4e591</v>
+        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-15</v>
@@ -907,16 +907,16 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v/>
+        <v>6 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v/>
+        <v>Tori Kelly</v>
       </c>
       <c r="I14" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>יוסי שטרית - פצע ישן</v>
+        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>טודיאל - קרקס</v>
+        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-05-15</v>
+        <v>6 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410885&amp;sid=4e49e5e22b0cc4c7806cc2f3c9c4e591</v>
+        <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-15</v>
@@ -945,16 +945,16 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v/>
+        <v>6 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>David Gilmour</v>
       </c>
       <c r="I15" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>טודיאל - קרקס</v>
+        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024) - David Gilmour</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>דניאל חן - לילה טוב</v>
+        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-05-15</v>
+        <v>6 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410884&amp;sid=4e49e5e22b0cc4c7806cc2f3c9c4e591</v>
+        <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-15</v>
@@ -983,16 +983,16 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v/>
+        <v>6 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v/>
+        <v>Scorpions</v>
       </c>
       <c r="I16" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>דניאל חן - לילה טוב</v>
+        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>בנאל בן ציון - לא חוקי #2</v>
+        <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>2026-05-15</v>
+        <v>6 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410883&amp;sid=4e49e5e22b0cc4c7806cc2f3c9c4e591</v>
+        <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-15</v>
@@ -1021,16 +1021,16 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v/>
+        <v>6 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v/>
+        <v>Claire Leslie</v>
       </c>
       <c r="I17" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
         <v/>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>בנאל בן ציון - לא חוקי #2</v>
+        <v>Claire Leslie - Passenger Seat (Official Music Video) - Claire Leslie</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>אלעד אביבי - בית״ר ירושלים - ההמנון 2026</v>
+        <v>Michael Schulte - Lovesick (Official Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>2026-05-15</v>
+        <v>6 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410882&amp;sid=4e49e5e22b0cc4c7806cc2f3c9c4e591</v>
+        <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-15</v>
@@ -1059,16 +1059,16 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v/>
+        <v>6 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v/>
+        <v>Michael Schulte</v>
       </c>
       <c r="I18" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
         <v/>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>אלעד אביבי - בית״ר ירושלים - ההמנון 2026</v>
+        <v>Michael Schulte - Lovesick (Official Video) - Michael Schulte</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ליאור קקון - ירושלים של זהב קאבר</v>
+        <v>Caity Baser - Holiday Song (Official Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>2026-05-15</v>
+        <v>7 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410890&amp;sid=513c45e169eaf116aa2433598953ea9f</v>
+        <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-15</v>
@@ -1097,16 +1097,16 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v/>
+        <v>7 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v/>
+        <v>Caity Baser</v>
       </c>
       <c r="I19" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
         <v/>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>ליאור קקון - ירושלים של זהב קאבר</v>
+        <v>Caity Baser - Holiday Song (Official Video) - Caity Baser</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>זהו זה - זהו זה 2020 עונה 5 (2023)</v>
+        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-05-15</v>
+        <v>7 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24191&amp;forum=music&amp;viewmode=all</v>
+        <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-15</v>
@@ -1135,16 +1135,16 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>06:50</v>
+        <v>7 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v/>
+        <v>Sam Fischer</v>
       </c>
       <c r="I20" t="str">
-        <v>אלבומים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
         <v/>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>זהו זה - זהו זה 2020 עונה 5 (2023)</v>
+        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser) - Sam Fischer</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>אריק סיני - כל השירים היפים באמת</v>
+        <v>Porches- HABIT (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>2026-05-15</v>
+        <v>7 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24470&amp;forum=music&amp;viewmode=all</v>
+        <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-15</v>
@@ -1173,16 +1173,16 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>06:45</v>
+        <v>7 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v/>
+        <v>Porches</v>
       </c>
       <c r="I21" t="str">
-        <v>אלבומים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
         <v/>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>אריק סיני - כל השירים היפים באמת</v>
+        <v>Porches- HABIT (Official Video) - Porches</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Harry Styles - Dance No More (Official Video)</v>
+        <v>Charli xcx - Rock Music (Official Video)</v>
       </c>
       <c r="B22" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
+        <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-15</v>
@@ -1217,7 +1217,7 @@
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Harry Styles</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
+        <v>Charli xcx - Rock Music (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
+        <v>Jon Batiste - Alla Blues (Audio)</v>
       </c>
       <c r="B23" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
+        <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-15</v>
@@ -1255,7 +1255,7 @@
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Eagles</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
+        <v>Jon Batiste - Alla Blues (Audio) - Jon Batiste</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
+        <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
+        <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-15</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Nora Fatehi</v>
+        <v>Tigirlily Gold</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
+        <v>Tigirlily Gold - I Do or Die (Official Music Video) - Tigirlily Gold</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
+        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>2 months ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
+        <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-15</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2 months ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
+        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
       </c>
       <c r="B26" t="str">
-        <v>2 months ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
+        <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-15</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2 months ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Eurovision Song Contest and Alis</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
+        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
+        <v>Tori Kelly - Control (Official Visualizer)</v>
       </c>
       <c r="B27" t="str">
-        <v>2 months ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
+        <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-15</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>2 months ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Tori Kelly - Control (Official Visualizer) - Tori Kelly</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video)</v>
+        <v>Bea Miller - depressed on the internet (Lyric Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
+        <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-15</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>The Head And The Heart</v>
+        <v>bea miller</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
+        <v>Bea Miller - depressed on the internet (Lyric Video) - bea miller</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
+        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
       </c>
       <c r="B29" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
+        <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-15</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Simply Red</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
+        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video)</v>
+        <v>Madison Beer - free (Official Audio)</v>
       </c>
       <c r="B30" t="str">
-        <v>4 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
+        <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-15</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>4 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Talking Heads</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
+        <v>Madison Beer - free (Official Audio) - Madison Beer</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Ellise - Liplock (Official Music Video)</v>
+        <v>Tori Kelly - Dive (Official Audio)</v>
       </c>
       <c r="B31" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
+        <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-15</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Ellise</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
+        <v>Tori Kelly - Dive (Official Audio) - Tori Kelly</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Tori Kelly - Dive (Official Music Video)</v>
+        <v>Jeremy Camp - Reflector (Official Audio)</v>
       </c>
       <c r="B32" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
+        <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-15</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Tori Kelly</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
+        <v>Jeremy Camp - Reflector (Official Audio) - JeremyCampMusic</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
+        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
       </c>
       <c r="B33" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
+        <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-15</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>David Gilmour</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024) - David Gilmour</v>
+        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
+        <v>Ashley Cooke - high school sweetheart</v>
       </c>
       <c r="B34" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
+        <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-15</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Scorpions</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022) - Scorpions</v>
+        <v>Ashley Cooke - high school sweetheart - Ashley Cooke</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
+        <v>Ari Abdul - Ego (Visualizer)</v>
       </c>
       <c r="B35" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
+        <v>https://www.youtube.com/watch?v=L0FjVr6LpVU</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-15</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Claire Leslie</v>
+        <v>Ari Abdul</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Claire Leslie - Passenger Seat (Official Music Video) - Claire Leslie</v>
+        <v>Ari Abdul - Ego (Visualizer) - Ari Abdul</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Michael Schulte - Lovesick (Official Video)</v>
+        <v>Quinn XCII - HOOPLA (Official Music Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
+        <v>https://www.youtube.com/watch?v=eNbGA1pgmFk</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-15</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Michael Schulte</v>
+        <v>Quinn XCII</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Michael Schulte - Lovesick (Official Video) - Michael Schulte</v>
+        <v>Quinn XCII - HOOPLA (Official Music Video) - Quinn XCII</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Caity Baser - Holiday Song (Official Video)</v>
+        <v>Madison Beer - lovergirl (Official Music Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
+        <v>https://www.youtube.com/watch?v=q4lU1N3oqYQ</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-15</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Caity Baser</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Caity Baser - Holiday Song (Official Video) - Caity Baser</v>
+        <v>Madison Beer - lovergirl (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
+        <v>David J - WHAT IF I'M IN LOVE (Official Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
+        <v>https://www.youtube.com/watch?v=-SF7Hm_ikaY</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-15</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Sam Fischer</v>
+        <v>David J</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser) - Sam Fischer</v>
+        <v>David J - WHAT IF I'M IN LOVE (Official Video) - David J</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Porches- HABIT (Official Video)</v>
+        <v>The Last Dinner Party - Big Dog (On The Road)</v>
       </c>
       <c r="B39" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
+        <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-15</v>
@@ -1863,7 +1863,7 @@
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Porches</v>
+        <v>The Last Dinner Party</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Porches- HABIT (Official Video) - Porches</v>
+        <v>The Last Dinner Party - Big Dog (On The Road) - The Last Dinner Party</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Charli xcx - Rock Music (Official Video)</v>
+        <v>OCEAN ALLEY - HOLD ON (Official Video)</v>
       </c>
       <c r="B40" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
+        <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-15</v>
@@ -1901,7 +1901,7 @@
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Charli xcx</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Charli xcx - Rock Music (Official Video) - Charli xcx</v>
+        <v>OCEAN ALLEY - HOLD ON (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Jon Batiste - Alla Blues (Audio)</v>
+        <v>Dagny - Closet Disco Queen (Lyric Video)</v>
       </c>
       <c r="B41" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
+        <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-15</v>
@@ -1939,7 +1939,7 @@
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Jon Batiste</v>
+        <v>Dagny</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Jon Batiste - Alla Blues (Audio) - Jon Batiste</v>
+        <v>Dagny - Closet Disco Queen (Lyric Video) - Dagny</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
+        <v>Purple Disco Machine - Disco Cherry (Official Video)</v>
       </c>
       <c r="B42" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
+        <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-15</v>
@@ -1977,7 +1977,7 @@
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Tigirlily Gold</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Tigirlily Gold - I Do or Die (Official Music Video) - Tigirlily Gold</v>
+        <v>Purple Disco Machine - Disco Cherry (Official Video) - Purple Disco Machine</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
+        <v>Paris Paloma - Stem the Flow [Official Music Video]</v>
       </c>
       <c r="B43" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
+        <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-15</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video) - PAUL McCARTNEY</v>
+        <v>Paris Paloma - Stem the Flow [Official Music Video] - Paris Paloma</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
+        <v>Lucy Blue - Who you love (Visualiser)</v>
       </c>
       <c r="B44" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
+        <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-15</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Bruno Mars</v>
+        <v>Lucy Blue</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video] - Bruno Mars</v>
+        <v>Lucy Blue - Who you love (Visualiser) - Lucy Blue</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Tori Kelly - Control (Official Visualizer)</v>
+        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026)</v>
       </c>
       <c r="B45" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
+        <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-15</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Tori Kelly</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Tori Kelly - Control (Official Visualizer) - Tori Kelly</v>
+        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026) - Olivia Dean</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Bea Miller - depressed on the internet (Lyric Video)</v>
+        <v>Aaron Frazer - It's A Shame (Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
+        <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-15</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>bea miller</v>
+        <v>Aaron Frazer</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Bea Miller - depressed on the internet (Lyric Video) - bea miller</v>
+        <v>Aaron Frazer - It's A Shame (Official Video) - Aaron Frazer</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
+        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify</v>
       </c>
       <c r="B47" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
+        <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-15</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>The Chainsmokers</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer) - The Chainsmokers</v>
+        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Madison Beer - free (Official Audio)</v>
+        <v>DANNA - OUT OF MY BODY</v>
       </c>
       <c r="B48" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
+        <v>https://www.youtube.com/watch?v=uW_Ye0kQ9Ac</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-15</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Madison Beer</v>
+        <v>Danna</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Madison Beer - free (Official Audio) - Madison Beer</v>
+        <v>DANNA - OUT OF MY BODY - Danna</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Tori Kelly - Dive (Official Audio)</v>
+        <v>The Rolling Stones - In The Stars (Official Lyric Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
+        <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-15</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Tori Kelly</v>
+        <v>The Rolling Stones</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Tori Kelly - Dive (Official Audio) - Tori Kelly</v>
+        <v>The Rolling Stones - In The Stars (Official Lyric Video) - The Rolling Stones</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Jeremy Camp - Reflector (Official Audio)</v>
+        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser)</v>
       </c>
       <c r="B50" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
+        <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-15</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>JeremyCampMusic</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Jeremy Camp - Reflector (Official Audio) - JeremyCampMusic</v>
+        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
+        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
       </c>
       <c r="B51" t="str">
-        <v>7 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
+        <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-15</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>7 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>The Chainsmokers</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer) - The Chainsmokers</v>
+        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Ashley Cooke - high school sweetheart</v>
+        <v>Rick Astley - Raindrops (Official Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>7 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
+        <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-15</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>7 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Ashley Cooke</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Ashley Cooke - high school sweetheart - Ashley Cooke</v>
+        <v>Rick Astley - Raindrops (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Ari Abdul - Ego (Visualizer)</v>
+        <v>Jessie J - THREW IT AWAY (Official Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>7 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=L0FjVr6LpVU</v>
+        <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-15</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>7 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Ari Abdul</v>
+        <v>Jessie J</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Ari Abdul - Ego (Visualizer) - Ari Abdul</v>
+        <v>Jessie J - THREW IT AWAY (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Quinn XCII - HOOPLA (Official Music Video)</v>
+        <v>The Takes - Ain't Love (Lyric Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>7 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=eNbGA1pgmFk</v>
+        <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-15</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>7 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Quinn XCII</v>
+        <v>The Takes</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Quinn XCII - HOOPLA (Official Music Video) - Quinn XCII</v>
+        <v>The Takes - Ain't Love (Lyric Video) - The Takes</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Madison Beer - lovergirl (Official Music Video)</v>
+        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary</v>
       </c>
       <c r="B55" t="str">
-        <v>7 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=q4lU1N3oqYQ</v>
+        <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-15</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>7 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Madison Beer</v>
+        <v>The Offspring</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Madison Beer - lovergirl (Official Music Video) - Madison Beer</v>
+        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary - The Offspring</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>David J - WHAT IF I'M IN LOVE (Official Video)</v>
+        <v>Louis Tomlinson - Sunflowers (Official Performance Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>7 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=-SF7Hm_ikaY</v>
+        <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-15</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>7 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>David J</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>David J - WHAT IF I'M IN LOVE (Official Video) - David J</v>
+        <v>Louis Tomlinson - Sunflowers (Official Performance Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>The Last Dinner Party - Big Dog (On The Road)</v>
+        <v>The Beaches - Should've Known Better (Official Visualizer)</v>
       </c>
       <c r="B57" t="str">
-        <v>7 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
+        <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-15</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>7 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>The Last Dinner Party</v>
+        <v>The Beaches</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>The Last Dinner Party - Big Dog (On The Road) - The Last Dinner Party</v>
+        <v>The Beaches - Should've Known Better (Official Visualizer) - The Beaches</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>OCEAN ALLEY - HOLD ON (Official Video)</v>
+        <v>The Kiffness - Serafino (Singing Cat Song)</v>
       </c>
       <c r="B58" t="str">
-        <v>7 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
+        <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-15</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>7 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Ocean Alley</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>OCEAN ALLEY - HOLD ON (Official Video) - Ocean Alley</v>
+        <v>The Kiffness - Serafino (Singing Cat Song) - The Kiffness</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Dagny - Closet Disco Queen (Lyric Video)</v>
+        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer)</v>
       </c>
       <c r="B59" t="str">
-        <v>7 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
+        <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-15</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>7 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Dagny</v>
+        <v>Dennis Lloyd</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Dagny - Closet Disco Queen (Lyric Video) - Dagny</v>
+        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer) - Dennis Lloyd</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Purple Disco Machine - Disco Cherry (Official Video)</v>
+        <v>Anna Graves - Damn In Love (Official Visualizer)</v>
       </c>
       <c r="B60" t="str">
-        <v>7 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
+        <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-15</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>7 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Purple Disco Machine - Disco Cherry (Official Video) - Purple Disco Machine</v>
+        <v>Anna Graves - Damn In Love (Official Visualizer) - Anna Graves</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Paris Paloma - Stem the Flow [Official Music Video]</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>8 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
+        <v>https://www.youtube.com/watch?v=vKzPmy3VUzY</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-15</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>8 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Paris Paloma</v>
+        <v>Brandon Lake and NICK JONAS</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Paris Paloma - Stem the Flow [Official Music Video] - Paris Paloma</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video) - Brandon Lake and NICK JONAS</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Lucy Blue - Who you love (Visualiser)</v>
+        <v>Letdown. - Do It For The Love (Visualizer)</v>
       </c>
       <c r="B62" t="str">
-        <v>8 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
+        <v>https://www.youtube.com/watch?v=vCvZbTEywr8</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-15</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>8 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Lucy Blue</v>
+        <v>Letdown.</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Lucy Blue - Who you love (Visualiser) - Lucy Blue</v>
+        <v>Letdown. - Do It For The Love (Visualizer) - Letdown.</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026)</v>
+        <v>Maroon 5 - Heroine (Official Lyric Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>8 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
+        <v>https://www.youtube.com/watch?v=izP-4q4YtNw</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-15</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>8 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Olivia Dean</v>
+        <v>Maroon 5</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026) - Olivia Dean</v>
+        <v>Maroon 5 - Heroine (Official Lyric Video) - Maroon 5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Aaron Frazer - It's A Shame (Official Video)</v>
+        <v>Olivia O'Brien - I'm Perfect (Official Visualizer)</v>
       </c>
       <c r="B64" t="str">
-        <v>8 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
+        <v>https://www.youtube.com/watch?v=leHb8CowDSw</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-15</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>8 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Aaron Frazer</v>
+        <v>Olivia O'Brien</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Aaron Frazer - It's A Shame (Official Video) - Aaron Frazer</v>
+        <v>Olivia O'Brien - I'm Perfect (Official Visualizer) - Olivia O'Brien</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify</v>
+        <v>ERNEST - What's A Little Rain (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>8 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
+        <v>https://www.youtube.com/watch?v=U-3AGDH3mf4</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-15</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>8 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Holly Humberstone</v>
+        <v>ERNEST</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>ERNEST - What's A Little Rain (Official Music Video) - ERNEST</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>DANNA - OUT OF MY BODY</v>
+        <v>Claire Rosinkranz - Just A Man (Official Audio)</v>
       </c>
       <c r="B66" t="str">
-        <v>9 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=uW_Ye0kQ9Ac</v>
+        <v>https://www.youtube.com/watch?v=Ta2I3EHXaDI</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-15</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>9 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Danna</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>DANNA - OUT OF MY BODY - Danna</v>
+        <v>Claire Rosinkranz - Just A Man (Official Audio) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>The Rolling Stones - In The Stars (Official Lyric Video)</v>
+        <v>Halsey - Nothing! (Official Audio)</v>
       </c>
       <c r="B67" t="str">
-        <v>9 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
+        <v>https://www.youtube.com/watch?v=PBv71KbKvHA</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-15</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>9 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>The Rolling Stones</v>
+        <v>Halsey</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>The Rolling Stones - In The Stars (Official Lyric Video) - The Rolling Stones</v>
+        <v>Halsey - Nothing! (Official Audio) - Halsey</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser)</v>
+        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B68" t="str">
-        <v>9 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
+        <v>https://www.youtube.com/watch?v=5-f07ca1Zfg</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-15</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>9 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser) - Dermot Kennedy</v>
+        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer) - Zara Larsson</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
+        <v>Halsey - Carry the Weight (Official Audio)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
+        <v>https://www.youtube.com/watch?v=6MewHp8BX0w</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-15</v>
@@ -3003,7 +3003,7 @@
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Halsey</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2) - SIENNA SPIRO</v>
+        <v>Halsey - Carry the Weight (Official Audio) - Halsey</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Rick Astley - Raindrops (Official Video)</v>
+        <v>Bishop Briggs - Blood From A Stone (Official)</v>
       </c>
       <c r="B70" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
+        <v>https://www.youtube.com/watch?v=3CK6Zbdk-Nw</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-15</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Rick Astley</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Rick Astley - Raindrops (Official Video) - Rick Astley</v>
+        <v>Bishop Briggs - Blood From A Stone (Official) - Bishop Briggs</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Jessie J - THREW IT AWAY (Official Video)</v>
+        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio)</v>
       </c>
       <c r="B71" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
+        <v>https://www.youtube.com/watch?v=6-AWBV5FCN4</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-15</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Jessie J</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Jessie J - THREW IT AWAY (Official Video) - Jessie J</v>
+        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>The Takes - Ain't Love (Lyric Video)</v>
+        <v>almost monday - no more regrets (official video)</v>
       </c>
       <c r="B72" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
+        <v>https://www.youtube.com/watch?v=iczsZVZxHKs</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-15</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>The Takes</v>
+        <v>almost monday</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>The Takes - Ain't Love (Lyric Video) - The Takes</v>
+        <v>almost monday - no more regrets (official video) - almost monday</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary</v>
+        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
+        <v>https://www.youtube.com/watch?v=lJM-z0ohbkc</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-15</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>The Offspring</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary - The Offspring</v>
+        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Louis Tomlinson - Sunflowers (Official Performance Video)</v>
+        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
+        <v>https://www.youtube.com/watch?v=6AjhDPwpoLI</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-15</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Louis Tomlinson</v>
+        <v>★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Louis Tomlinson - Sunflowers (Official Performance Video) - Louis Tomlinson</v>
+        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video) - ★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>The Beaches - Should've Known Better (Official Visualizer)</v>
+        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
+        <v>https://www.youtube.com/watch?v=F4ndJUCsHKg</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-15</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>The Beaches</v>
+        <v>NIGHTLY and Fly By Midnight</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>The Beaches - Should've Known Better (Official Visualizer) - The Beaches</v>
+        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video) - NIGHTLY and Fly By Midnight</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>The Kiffness - Serafino (Singing Cat Song)</v>
+        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B76" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
+        <v>https://www.youtube.com/watch?v=-IEb-ym7VeQ</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-15</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>The Kiffness</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>The Kiffness - Serafino (Singing Cat Song) - The Kiffness</v>
+        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer) - Zara Larsson</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer)</v>
+        <v>JORDANA BRYANT - Truth Is (Official Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
+        <v>https://www.youtube.com/watch?v=D4meCyyV7SQ</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-15</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Dennis Lloyd</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer) - Dennis Lloyd</v>
+        <v>JORDANA BRYANT - Truth Is (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Anna Graves - Damn In Love (Official Visualizer)</v>
+        <v>Leanna Crawford - Thank God (Lyric Video)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
+        <v>https://www.youtube.com/watch?v=QqcSoUft03s</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-15</v>
@@ -3345,7 +3345,7 @@
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Anna Graves</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Anna Graves - Damn In Love (Official Visualizer) - Anna Graves</v>
+        <v>Leanna Crawford - Thank God (Lyric Video) - Leanna Crawford</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video)</v>
+        <v>Girl Tones - Stubborn Mouth (Official Music Video)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=vKzPmy3VUzY</v>
+        <v>https://www.youtube.com/watch?v=_-PyPUWZTDY</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-15</v>
@@ -3383,7 +3383,7 @@
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Brandon Lake and NICK JONAS</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video) - Brandon Lake and NICK JONAS</v>
+        <v>Girl Tones - Stubborn Mouth (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Letdown. - Do It For The Love (Visualizer)</v>
+        <v>Tauren Wells - What A Miracle Feels Like (Official Audio)</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=vCvZbTEywr8</v>
+        <v>https://www.youtube.com/watch?v=ZojFIe4Swmk</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-15</v>
@@ -3421,7 +3421,7 @@
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Letdown.</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Letdown. - Do It For The Love (Visualizer) - Letdown.</v>
+        <v>Tauren Wells - What A Miracle Feels Like (Official Audio) - Tauren Wells</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Maroon 5 - Heroine (Official Lyric Video)</v>
+        <v>Matthew Ifield - Thinking (Official Video)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=izP-4q4YtNw</v>
+        <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-15</v>
@@ -3459,7 +3459,7 @@
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Maroon 5</v>
+        <v>Matthew Ifield</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Maroon 5 - Heroine (Official Lyric Video) - Maroon 5</v>
+        <v>Matthew Ifield - Thinking (Official Video) - Matthew Ifield</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Olivia O'Brien - I'm Perfect (Official Visualizer)</v>
+        <v>Dons - Is There Something</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=leHb8CowDSw</v>
+        <v>https://www.youtube.com/watch?v=AgWIjvD-i0E</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-15</v>
@@ -3497,7 +3497,7 @@
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Olivia O'Brien</v>
+        <v>Dons</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Olivia O'Brien - I'm Perfect (Official Visualizer) - Olivia O'Brien</v>
+        <v>Dons - Is There Something - Dons</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>ERNEST - What's A Little Rain (Official Music Video)</v>
+        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=U-3AGDH3mf4</v>
+        <v>https://www.youtube.com/watch?v=JXW3SOr7C4w</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-15</v>
@@ -3535,7 +3535,7 @@
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>ERNEST</v>
+        <v>Recording Academy / GRAMMYs and 3 more</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>ERNEST - What's A Little Rain (Official Music Video) - ERNEST</v>
+        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris - Recording Academy / GRAMMYs and 3 more</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Claire Rosinkranz - Just A Man (Official Audio)</v>
+        <v>Maya Hawke - Lioness (Official Audio)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=Ta2I3EHXaDI</v>
+        <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-15</v>
@@ -3573,7 +3573,7 @@
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Claire Rosinkranz - Just A Man (Official Audio) - Claire Rosinkranz</v>
+        <v>Maya Hawke - Lioness (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Halsey - Nothing! (Official Audio)</v>
+        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=PBv71KbKvHA</v>
+        <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-15</v>
@@ -3611,7 +3611,7 @@
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Halsey</v>
+        <v>Laufey</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Halsey - Nothing! (Official Audio) - Halsey</v>
+        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance - Laufey</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer)</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=5-f07ca1Zfg</v>
+        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-15</v>
@@ -3649,7 +3649,7 @@
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Zara Larsson</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer) - Zara Larsson</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Halsey - Carry the Weight (Official Audio)</v>
+        <v>DANNA - AGAIN</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=6MewHp8BX0w</v>
+        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-15</v>
@@ -3687,7 +3687,7 @@
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Halsey</v>
+        <v>Danna</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Halsey - Carry the Weight (Official Audio) - Halsey</v>
+        <v>DANNA - AGAIN - Danna</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Bishop Briggs - Blood From A Stone (Official)</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=3CK6Zbdk-Nw</v>
+        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-15</v>
@@ -3725,7 +3725,7 @@
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Bishop Briggs</v>
+        <v>Armik</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Bishop Briggs - Blood From A Stone (Official) - Bishop Briggs</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio)</v>
+        <v>EUROPE - One on One (Official Video)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=6-AWBV5FCN4</v>
+        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-15</v>
@@ -3763,7 +3763,7 @@
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Europe</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio) - Louis Tomlinson</v>
+        <v>EUROPE - One on One (Official Video) - Europe</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>almost monday - no more regrets (official video)</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=iczsZVZxHKs</v>
+        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-15</v>
@@ -3801,7 +3801,7 @@
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>almost monday</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>almost monday - no more regrets (official video) - almost monday</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video)</v>
+        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=lJM-z0ohbkc</v>
+        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-15</v>
@@ -3839,7 +3839,7 @@
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>Lady Gaga and Doechii</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video) - FULL CIRCLE BOYS</v>
+        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video) - Lady Gaga and Doechii</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video)</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=6AjhDPwpoLI</v>
+        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-15</v>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
+        <v>Muse</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video) - ★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video)</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=F4ndJUCsHKg</v>
+        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-15</v>
@@ -3915,7 +3915,7 @@
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>NIGHTLY and Fly By Midnight</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video) - NIGHTLY and Fly By Midnight</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer)</v>
+        <v>Shaboozey - Born To Die (Official Video)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=-IEb-ym7VeQ</v>
+        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-15</v>
@@ -3953,7 +3953,7 @@
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Zara Larsson</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer) - Zara Larsson</v>
+        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>JORDANA BRYANT - Truth Is (Official Video)</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=D4meCyyV7SQ</v>
+        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-15</v>
@@ -3991,7 +3991,7 @@
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Jordana Bryant</v>
+        <v>Scorpions</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>JORDANA BRYANT - Truth Is (Official Video) - Jordana Bryant</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Leanna Crawford - Thank God (Lyric Video)</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=QqcSoUft03s</v>
+        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-15</v>
@@ -4029,7 +4029,7 @@
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Leanna Crawford</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Leanna Crawford - Thank God (Lyric Video) - Leanna Crawford</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Girl Tones - Stubborn Mouth (Official Music Video)</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=_-PyPUWZTDY</v>
+        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-15</v>
@@ -4067,7 +4067,7 @@
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Girl Tones</v>
+        <v>Lolo Zouaï</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Girl Tones - Stubborn Mouth (Official Music Video) - Girl Tones</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Tauren Wells - What A Miracle Feels Like (Official Audio)</v>
+        <v>Bonnie Tyler - One World One Home</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=ZojFIe4Swmk</v>
+        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-15</v>
@@ -4105,7 +4105,7 @@
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Tauren Wells</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Tauren Wells - What A Miracle Feels Like (Official Audio) - Tauren Wells</v>
+        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Matthew Ifield - Thinking (Official Video)</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
+        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-15</v>
@@ -4143,7 +4143,7 @@
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Matthew Ifield</v>
+        <v>Jacob Gurevitsch and Prisma Music Group</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Matthew Ifield - Thinking (Official Video) - Matthew Ifield</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Dons - Is There Something</v>
+        <v>Icona Pop - Dance To This (Official Video)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=AgWIjvD-i0E</v>
+        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-15</v>
@@ -4181,7 +4181,7 @@
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Dons</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Dons - Is There Something - Dons</v>
+        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris</v>
+        <v>Michael Jackson - Human Nature (Official Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=JXW3SOr7C4w</v>
+        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-15</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Recording Academy / GRAMMYs and 3 more</v>
+        <v>Michael Jackson</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris - Recording Academy / GRAMMYs and 3 more</v>
+        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Maya Hawke - Lioness (Official Audio)</v>
+        <v>The All-American Rejects - King Kong</v>
       </c>
       <c r="B102" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
+        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-15</v>
@@ -4251,13 +4251,13 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G102" t="str">
         <v/>
       </c>
       <c r="H102" t="str">
-        <v>Maya Hawke</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4269,18 +4269,18 @@
         <v/>
       </c>
       <c r="L102" t="str">
-        <v>Maya Hawke - Lioness (Official Audio) - Maya Hawke</v>
+        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
       </c>
       <c r="B103" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
+        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-15</v>
@@ -4289,13 +4289,13 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G103" t="str">
         <v/>
       </c>
       <c r="H103" t="str">
-        <v>Laufey</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4307,18 +4307,18 @@
         <v/>
       </c>
       <c r="L103" t="str">
-        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance - Laufey</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
+        <v>Hit the Wall</v>
       </c>
       <c r="B104" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
+        <v>https://music.apple.com/us/song/hit-the-wall/6766750846</v>
       </c>
       <c r="D104" t="str">
         <v>2026-05-15</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>2 weeks ago</v>
+        <v>Daughter from Hell</v>
       </c>
       <c r="G104" t="str">
-        <v/>
+        <v>3:14</v>
       </c>
       <c r="H104" t="str">
-        <v>Keith Urban</v>
+        <v>Gracie Abrams</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/gracie-abrams/1450554836</v>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/hit-the-wall/6766750836</v>
       </c>
       <c r="L104" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
+        <v>Hit the Wall - Gracie Abrams</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>DANNA - AGAIN</v>
+        <v>Ran To Atlanta</v>
       </c>
       <c r="B105" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
+        <v>https://music.apple.com/us/song/ran-to-atlanta/6769568597</v>
       </c>
       <c r="D105" t="str">
         <v>2026-05-15</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>2 weeks ago</v>
+        <v>ICEMAN</v>
       </c>
       <c r="G105" t="str">
-        <v/>
+        <v>4:07</v>
       </c>
       <c r="H105" t="str">
-        <v>Danna</v>
+        <v>Drake</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/ran-to-atlanta/6769568449</v>
       </c>
       <c r="L105" t="str">
-        <v>DANNA - AGAIN - Danna</v>
+        <v>Ran To Atlanta - Drake</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>Hoe Phase</v>
       </c>
       <c r="B106" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
+        <v>https://music.apple.com/us/song/hoe-phase/6769556949</v>
       </c>
       <c r="D106" t="str">
         <v>2026-05-15</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>2 weeks ago</v>
+        <v>MAID OF HONOUR</v>
       </c>
       <c r="G106" t="str">
-        <v/>
+        <v>3:23</v>
       </c>
       <c r="H106" t="str">
-        <v>Armik</v>
+        <v>Drake</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/hoe-phase/6769556940</v>
       </c>
       <c r="L106" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>Hoe Phase - Drake</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>EUROPE - One on One (Official Video)</v>
+        <v>I’m Spent</v>
       </c>
       <c r="B107" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
+        <v>https://music.apple.com/us/song/im-spent/6769551476</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-15</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>2 weeks ago</v>
+        <v>HABIBTI</v>
       </c>
       <c r="G107" t="str">
-        <v/>
+        <v>2:24</v>
       </c>
       <c r="H107" t="str">
-        <v>Europe</v>
+        <v>Drake</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/im-spent/6769551464</v>
       </c>
       <c r="L107" t="str">
-        <v>EUROPE - One on One (Official Video) - Europe</v>
+        <v>I’m Spent - Drake</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
+        <v>Abracadabra (Apple Music Live)</v>
       </c>
       <c r="B108" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
+        <v>https://music.apple.com/us/song/abracadabra-apple-music-live/6768201780</v>
       </c>
       <c r="D108" t="str">
         <v>2026-05-15</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>2 weeks ago</v>
+        <v>Apple Music Live: MAYHEM Requiem</v>
       </c>
       <c r="G108" t="str">
-        <v/>
+        <v>4:04</v>
       </c>
       <c r="H108" t="str">
-        <v>Foo Fighters</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
       </c>
       <c r="K108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/abracadabra-apple-music-live/6768201775</v>
       </c>
       <c r="L108" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
+        <v>Abracadabra (Apple Music Live) - Lady Gaga</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video)</v>
+        <v>Falling out of Love</v>
       </c>
       <c r="B109" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
+        <v>https://music.apple.com/us/song/falling-out-of-love/1891161448</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-15</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>2 weeks ago</v>
+        <v>Reality Awaits</v>
       </c>
       <c r="G109" t="str">
-        <v/>
+        <v>6:21</v>
       </c>
       <c r="H109" t="str">
-        <v>Lady Gaga and Doechii</v>
+        <v>The Strokes</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/the-strokes/560289</v>
       </c>
       <c r="K109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/falling-out-of-love/1891161441</v>
       </c>
       <c r="L109" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video) - Lady Gaga and Doechii</v>
+        <v>Falling out of Love - The Strokes</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
+        <v>Dai Dai</v>
       </c>
       <c r="B110" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
+        <v>https://music.apple.com/us/song/dai-dai/6768469976</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-15</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>2 weeks ago</v>
+        <v>Dai Dai - Single</v>
       </c>
       <c r="G110" t="str">
-        <v/>
+        <v>3:43</v>
       </c>
       <c r="H110" t="str">
-        <v>Muse</v>
+        <v>Shakira</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/shakira/889327</v>
       </c>
       <c r="K110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/dai-dai/6768469975</v>
       </c>
       <c r="L110" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
+        <v>Dai Dai - Shakira</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
+        <v>Tu recuerdo</v>
       </c>
       <c r="B111" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
+        <v>https://music.apple.com/us/song/tu-recuerdo/6763660843</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-15</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>2 weeks ago</v>
+        <v>Loco X Volver</v>
       </c>
       <c r="G111" t="str">
-        <v/>
+        <v>3:55</v>
       </c>
       <c r="H111" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Maluma</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/tu-recuerdo/1895423065</v>
       </c>
       <c r="L111" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
+        <v>Tu recuerdo - Maluma</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Shaboozey - Born To Die (Official Video)</v>
+        <v>Traitor (Roles Reversed)</v>
       </c>
       <c r="B112" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
+        <v>https://music.apple.com/us/song/traitor-roles-reversed/6767665959</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-15</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>2 weeks ago</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G112" t="str">
-        <v/>
+        <v>3:27</v>
       </c>
       <c r="H112" t="str">
-        <v>Shaboozey</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K112" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/traitor-roles-reversed/6767665713</v>
       </c>
       <c r="L112" t="str">
-        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
+        <v>Traitor (Roles Reversed) - Megan Moroney</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
+        <v>Dirty Rosie</v>
       </c>
       <c r="B113" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
+        <v>https://music.apple.com/us/song/dirty-rosie/6767044374</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-15</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>2 weeks ago</v>
+        <v>Little Miss Twain</v>
       </c>
       <c r="G113" t="str">
-        <v/>
+        <v>2:46</v>
       </c>
       <c r="H113" t="str">
-        <v>Scorpions</v>
+        <v>Shania Twain</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/shania-twain/129974</v>
       </c>
       <c r="K113" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/dirty-rosie/1896356105</v>
       </c>
       <c r="L113" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
+        <v>Dirty Rosie - Shania Twain</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
+        <v>Like you mean it</v>
       </c>
       <c r="B114" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
+        <v>https://music.apple.com/us/song/like-you-mean-it/6767024693</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-15</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>2 weeks ago</v>
+        <v>When the lights turn on</v>
       </c>
       <c r="G114" t="str">
-        <v/>
+        <v>2:27</v>
       </c>
       <c r="H114" t="str">
-        <v>Meghan Trainor</v>
+        <v>MICO</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/mico/1457367370</v>
       </c>
       <c r="K114" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/like-you-mean-it/6767024688</v>
       </c>
       <c r="L114" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
+        <v>Like you mean it - MICO</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
+        <v>Hardy (feat. Clairo)</v>
       </c>
       <c r="B115" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
+        <v>https://music.apple.com/us/song/hardy-feat-clairo/1876953073</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-15</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>2 weeks ago</v>
+        <v>American Stories</v>
       </c>
       <c r="G115" t="str">
-        <v/>
+        <v>3:53</v>
       </c>
       <c r="H115" t="str">
-        <v>Lolo Zouaï</v>
+        <v>Rostam</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K115" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/hardy-feat-clairo/1876952750</v>
       </c>
       <c r="L115" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
+        <v>Hardy (feat. Clairo) - Rostam</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Bonnie Tyler - One World One Home</v>
+        <v>2 Hard 4 The Radio</v>
       </c>
       <c r="B116" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
+        <v>https://music.apple.com/us/song/2-hard-4-the-radio/6769568610</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-15</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>2 weeks ago</v>
+        <v>ICEMAN</v>
       </c>
       <c r="G116" t="str">
-        <v/>
+        <v>3:03</v>
       </c>
       <c r="H116" t="str">
-        <v>Bonnie Tyler</v>
+        <v>Drake</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K116" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/2-hard-4-the-radio/6769568449</v>
       </c>
       <c r="L116" t="str">
-        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
+        <v>2 Hard 4 The Radio - Drake</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
+        <v>Cheetah Print</v>
       </c>
       <c r="B117" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
+        <v>https://music.apple.com/us/song/cheetah-print/6769557055</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-15</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>2 weeks ago</v>
+        <v>MAID OF HONOUR</v>
       </c>
       <c r="G117" t="str">
-        <v/>
+        <v>3:22</v>
       </c>
       <c r="H117" t="str">
-        <v>Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Drake</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K117" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/cheetah-print/6769556940</v>
       </c>
       <c r="L117" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Cheetah Print - Drake</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Icona Pop - Dance To This (Official Video)</v>
+        <v>WNBA</v>
       </c>
       <c r="B118" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
+        <v>https://music.apple.com/us/song/wnba/6769551471</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-15</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>2 weeks ago</v>
+        <v>HABIBTI</v>
       </c>
       <c r="G118" t="str">
-        <v/>
+        <v>2:58</v>
       </c>
       <c r="H118" t="str">
-        <v>Icona Pop</v>
+        <v>Drake</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K118" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/wnba/6769551464</v>
       </c>
       <c r="L118" t="str">
-        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
+        <v>WNBA - Drake</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Michael Jackson - Human Nature (Official Video)</v>
+        <v>Shadow Of A Man (Apple Music Live)</v>
       </c>
       <c r="B119" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
+        <v>https://music.apple.com/us/song/shadow-of-a-man-apple-music-live/6768201925</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-15</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>2 weeks ago</v>
+        <v>Apple Music Live: MAYHEM Requiem</v>
       </c>
       <c r="G119" t="str">
-        <v/>
+        <v>3:36</v>
       </c>
       <c r="H119" t="str">
-        <v>Michael Jackson</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
       </c>
       <c r="K119" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/shadow-of-a-man-apple-music-live/6768201775</v>
       </c>
       <c r="L119" t="str">
-        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
+        <v>Shadow Of A Man (Apple Music Live) - Lady Gaga</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>The All-American Rejects - King Kong</v>
+        <v>EPA</v>
       </c>
       <c r="B120" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
+        <v>https://music.apple.com/us/song/epa/6768420253</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-15</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>2 weeks ago</v>
+        <v>EPA - Single</v>
       </c>
       <c r="G120" t="str">
-        <v/>
+        <v>3:22</v>
       </c>
       <c r="H120" t="str">
-        <v>The All-American Rejects</v>
+        <v>Becky G</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
       </c>
       <c r="K120" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/epa/6768420251</v>
       </c>
       <c r="L120" t="str">
-        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
+        <v>EPA - Becky G</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
+        <v>I’m your girl right?</v>
       </c>
       <c r="B121" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
+        <v>https://music.apple.com/us/song/im-your-girl-right/6766440186</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-15</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>2 weeks ago</v>
+        <v>ESTRUS</v>
       </c>
       <c r="G121" t="str">
-        <v/>
+        <v>2:49</v>
       </c>
       <c r="H121" t="str">
-        <v>Ringo Starr</v>
+        <v>Tove Lo</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/tove-lo/570136838</v>
       </c>
       <c r="K121" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/im-your-girl-right/6766440172</v>
       </c>
       <c r="L121" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
+        <v>I’m your girl right? - Tove Lo</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Hit the Wall</v>
+        <v>fuëgo</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/hit-the-wall/6766750846</v>
+        <v>https://music.apple.com/us/song/fu%C3%ABgo/6767661766</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-15</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Daughter from Hell</v>
+        <v>fuëgo - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:14</v>
+        <v>3:46</v>
       </c>
       <c r="H122" t="str">
-        <v>Gracie Abrams</v>
+        <v>BNYX®</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/gracie-abrams/1450554836</v>
+        <v>https://music.apple.com/us/artist/bnyx/1438325287</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/hit-the-wall/6766750836</v>
+        <v>https://music.apple.com/us/album/fu%C3%ABgo/6767661604</v>
       </c>
       <c r="L122" t="str">
-        <v>Hit the Wall - Gracie Abrams</v>
+        <v>fuëgo - BNYX®</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Ran To Atlanta</v>
+        <v>jajaja</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/ran-to-atlanta/6769568597</v>
+        <v>https://music.apple.com/us/song/jajaja/6766341319</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-15</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>ICEMAN</v>
+        <v>jajaja - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>4:07</v>
+        <v>2:45</v>
       </c>
       <c r="H123" t="str">
-        <v>Drake</v>
+        <v>Chino Pacas</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/drake/271256</v>
+        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/ran-to-atlanta/6769568449</v>
+        <v>https://music.apple.com/us/album/jajaja/6766341318</v>
       </c>
       <c r="L123" t="str">
-        <v>Ran To Atlanta - Drake</v>
+        <v>jajaja - Chino Pacas</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Hoe Phase</v>
+        <v>FIND GOD (feat. Dominic Fike)</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/hoe-phase/6769556949</v>
+        <v>https://music.apple.com/us/song/find-god-feat-dominic-fike/1894315529</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-15</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>MAID OF HONOUR</v>
+        <v>BULLDAWG</v>
       </c>
       <c r="G124" t="str">
-        <v>3:23</v>
+        <v>3:59</v>
       </c>
       <c r="H124" t="str">
-        <v>Drake</v>
+        <v>Kenny Mason</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/drake/271256</v>
+        <v>https://music.apple.com/us/artist/kenny-mason/79382206</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/hoe-phase/6769556940</v>
+        <v>https://music.apple.com/us/album/find-god-feat-dominic-fike/1894315301</v>
       </c>
       <c r="L124" t="str">
-        <v>Hoe Phase - Drake</v>
+        <v>FIND GOD (feat. Dominic Fike) - Kenny Mason</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>I’m Spent</v>
+        <v>FOOL ME ONCE (feat. Leon Thomas)</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/im-spent/6769551476</v>
+        <v>https://music.apple.com/us/song/fool-me-once-feat-leon-thomas/1891467239</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-15</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>HABIBTI</v>
+        <v>BELOVED: ACT II</v>
       </c>
       <c r="G125" t="str">
-        <v>2:24</v>
+        <v>3:18</v>
       </c>
       <c r="H125" t="str">
-        <v>Drake</v>
+        <v>GIVĒON</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/drake/271256</v>
+        <v>https://music.apple.com/us/artist/giv%C4%93on/1070668868</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/im-spent/6769551464</v>
+        <v>https://music.apple.com/us/album/fool-me-once-feat-leon-thomas/1891467233</v>
       </c>
       <c r="L125" t="str">
-        <v>I’m Spent - Drake</v>
+        <v>FOOL ME ONCE (feat. Leon Thomas) - GIVĒON</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Abracadabra (Apple Music Live)</v>
+        <v>Shabang</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/abracadabra-apple-music-live/6768201780</v>
+        <v>https://music.apple.com/us/song/shabang/6769568598</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-15</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Apple Music Live: MAYHEM Requiem</v>
+        <v>ICEMAN</v>
       </c>
       <c r="G126" t="str">
-        <v>4:04</v>
+        <v>3:08</v>
       </c>
       <c r="H126" t="str">
-        <v>Lady Gaga</v>
+        <v>Drake</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/abracadabra-apple-music-live/6768201775</v>
+        <v>https://music.apple.com/us/album/shabang/6769568449</v>
       </c>
       <c r="L126" t="str">
-        <v>Abracadabra (Apple Music Live) - Lady Gaga</v>
+        <v>Shabang - Drake</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Falling out of Love</v>
+        <v>Road Trips</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/falling-out-of-love/1891161448</v>
+        <v>https://music.apple.com/us/song/road-trips/6769557053</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-15</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Reality Awaits</v>
+        <v>MAID OF HONOUR</v>
       </c>
       <c r="G127" t="str">
-        <v>6:21</v>
+        <v>4:03</v>
       </c>
       <c r="H127" t="str">
-        <v>The Strokes</v>
+        <v>Drake</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/the-strokes/560289</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/falling-out-of-love/1891161441</v>
+        <v>https://music.apple.com/us/album/road-trips/6769556940</v>
       </c>
       <c r="L127" t="str">
-        <v>Falling out of Love - The Strokes</v>
+        <v>Road Trips - Drake</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Dai Dai</v>
+        <v>Fortworth</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/dai-dai/6768469976</v>
+        <v>https://music.apple.com/us/song/fortworth/6769551482</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-15</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Dai Dai - Single</v>
+        <v>HABIBTI</v>
       </c>
       <c r="G128" t="str">
-        <v>3:43</v>
+        <v>3:51</v>
       </c>
       <c r="H128" t="str">
-        <v>Shakira</v>
+        <v>Drake</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/shakira/889327</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/dai-dai/6768469975</v>
+        <v>https://music.apple.com/us/album/fortworth/6769551464</v>
       </c>
       <c r="L128" t="str">
-        <v>Dai Dai - Shakira</v>
+        <v>Fortworth - Drake</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Tu recuerdo</v>
+        <v>Repeat It</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/tu-recuerdo/6763660843</v>
+        <v>https://music.apple.com/us/song/repeat-it/6764277864</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-15</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Loco X Volver</v>
+        <v>Repeat It - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:55</v>
+        <v>3:11</v>
       </c>
       <c r="H129" t="str">
-        <v>Maluma</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/tu-recuerdo/1895423065</v>
+        <v>https://music.apple.com/us/album/repeat-it/1895713789</v>
       </c>
       <c r="L129" t="str">
-        <v>Tu recuerdo - Maluma</v>
+        <v>Repeat It - Martin Garrix</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Traitor (Roles Reversed)</v>
+        <v>Fool Proof</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/traitor-roles-reversed/6767665959</v>
+        <v>https://music.apple.com/us/song/fool-proof/1892466004</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-15</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Cloud 9</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G130" t="str">
-        <v>3:27</v>
+        <v>2:36</v>
       </c>
       <c r="H130" t="str">
-        <v>Megan Moroney</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/traitor-roles-reversed/6767665713</v>
+        <v>https://music.apple.com/us/album/fool-proof/1892465981</v>
       </c>
       <c r="L130" t="str">
-        <v>Traitor (Roles Reversed) - Megan Moroney</v>
+        <v>Fool Proof - Cody Johnson</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Dirty Rosie</v>
+        <v>Crisco</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/dirty-rosie/6767044374</v>
+        <v>https://music.apple.com/us/song/crisco/6763369506</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-15</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Little Miss Twain</v>
+        <v>Crisco - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>2:46</v>
+        <v>2:56</v>
       </c>
       <c r="H131" t="str">
-        <v>Shania Twain</v>
+        <v>Miranda Lambert</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/shania-twain/129974</v>
+        <v>https://music.apple.com/us/artist/miranda-lambert/18732261</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/dirty-rosie/1896356105</v>
+        <v>https://music.apple.com/us/album/crisco/1895284236</v>
       </c>
       <c r="L131" t="str">
-        <v>Dirty Rosie - Shania Twain</v>
+        <v>Crisco - Miranda Lambert</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Like you mean it</v>
+        <v>Absolution</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/like-you-mean-it/6767024693</v>
+        <v>https://music.apple.com/us/song/absolution/1884987651</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-15</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>When the lights turn on</v>
+        <v>Forever Now</v>
       </c>
       <c r="G132" t="str">
-        <v>2:27</v>
+        <v>4:05</v>
       </c>
       <c r="H132" t="str">
-        <v>MICO</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/mico/1457367370</v>
+        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/like-you-mean-it/6767024688</v>
+        <v>https://music.apple.com/us/album/absolution/1884987638</v>
       </c>
       <c r="L132" t="str">
-        <v>Like you mean it - MICO</v>
+        <v>Absolution - Switchfoot</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Hardy (feat. Clairo)</v>
+        <v>JESUS IS ALIVE</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/hardy-feat-clairo/1876953073</v>
+        <v>https://music.apple.com/us/song/jesus-is-alive/6767694896</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-15</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>American Stories</v>
+        <v>JESUS IS ALIVE - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:53</v>
+        <v>2:08</v>
       </c>
       <c r="H133" t="str">
-        <v>Rostam</v>
+        <v>Forrest Frank</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/hardy-feat-clairo/1876952750</v>
+        <v>https://music.apple.com/us/album/jesus-is-alive/6767694895</v>
       </c>
       <c r="L133" t="str">
-        <v>Hardy (feat. Clairo) - Rostam</v>
+        <v>JESUS IS ALIVE - Forrest Frank</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>2 Hard 4 The Radio</v>
+        <v>Something To Lose</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/2-hard-4-the-radio/6769568610</v>
+        <v>https://music.apple.com/us/song/something-to-lose/6766964605</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-15</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>ICEMAN</v>
+        <v>Is This Heaven? - EP</v>
       </c>
       <c r="G134" t="str">
-        <v>3:03</v>
+        <v>2:55</v>
       </c>
       <c r="H134" t="str">
-        <v>Drake</v>
+        <v>STELLA LEFTY</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/drake/271256</v>
+        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/2-hard-4-the-radio/6769568449</v>
+        <v>https://music.apple.com/us/album/something-to-lose/6766964604</v>
       </c>
       <c r="L134" t="str">
-        <v>2 Hard 4 The Radio - Drake</v>
+        <v>Something To Lose - STELLA LEFTY</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Cheetah Print</v>
+        <v>Too Busy Missing You</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/cheetah-print/6769557055</v>
+        <v>https://music.apple.com/us/song/too-busy-missing-you/6766604915</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-15</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>MAID OF HONOUR</v>
+        <v>Off Campus: The Mixtape</v>
       </c>
       <c r="G135" t="str">
-        <v>3:22</v>
+        <v>3:25</v>
       </c>
       <c r="H135" t="str">
-        <v>Drake</v>
+        <v>Asha Banks</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/drake/271256</v>
+        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/cheetah-print/6769556940</v>
+        <v>https://music.apple.com/us/album/too-busy-missing-you/6766604455</v>
       </c>
       <c r="L135" t="str">
-        <v>Cheetah Print - Drake</v>
+        <v>Too Busy Missing You - Asha Banks</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>WNBA</v>
+        <v>F-Stop Blues (4-track)</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/wnba/6769551471</v>
+        <v>https://music.apple.com/us/song/f-stop-blues-4-track/1883173173</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-15</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>HABIBTI</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G136" t="str">
-        <v>2:58</v>
+        <v>3:00</v>
       </c>
       <c r="H136" t="str">
-        <v>Drake</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/drake/271256</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/wnba/6769551464</v>
+        <v>https://music.apple.com/us/album/f-stop-blues-4-track/1883172879</v>
       </c>
       <c r="L136" t="str">
-        <v>WNBA - Drake</v>
+        <v>F-Stop Blues (4-track) - Jack Johnson</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Shadow Of A Man (Apple Music Live)</v>
+        <v>PA' LO BONITO</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/shadow-of-a-man-apple-music-live/6768201925</v>
+        <v>https://music.apple.com/us/song/pa-lo-bonito/1886496944</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-15</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Apple Music Live: MAYHEM Requiem</v>
+        <v>PA' LO BONITO - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:36</v>
+        <v>3:04</v>
       </c>
       <c r="H137" t="str">
-        <v>Lady Gaga</v>
+        <v>Lenny Tavárez</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
+        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/shadow-of-a-man-apple-music-live/6768201775</v>
+        <v>https://music.apple.com/us/album/pa-lo-bonito/1886496943</v>
       </c>
       <c r="L137" t="str">
-        <v>Shadow Of A Man (Apple Music Live) - Lady Gaga</v>
+        <v>PA' LO BONITO - Lenny Tavárez</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>EPA</v>
+        <v>LONELY</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/epa/6768420253</v>
+        <v>https://music.apple.com/us/song/lonely/6768757857</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-15</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>EPA - Single</v>
+        <v>DESEO</v>
       </c>
       <c r="G138" t="str">
-        <v>3:22</v>
+        <v>2:58</v>
       </c>
       <c r="H138" t="str">
-        <v>Becky G</v>
+        <v>Katteyes</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
+        <v>https://music.apple.com/us/artist/katteyes/1648818255</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/epa/6768420251</v>
+        <v>https://music.apple.com/us/album/lonely/6768757414</v>
       </c>
       <c r="L138" t="str">
-        <v>EPA - Becky G</v>
+        <v>LONELY - Katteyes</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>I’m your girl right?</v>
+        <v>Lockup</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/im-your-girl-right/6766440186</v>
+        <v>https://music.apple.com/us/song/lockup/1894298102</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-15</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>ESTRUS</v>
+        <v>Pure Devotion</v>
       </c>
       <c r="G139" t="str">
-        <v>2:49</v>
+        <v>4:31</v>
       </c>
       <c r="H139" t="str">
-        <v>Tove Lo</v>
+        <v>Overmono</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/tove-lo/570136838</v>
+        <v>https://music.apple.com/us/artist/overmono/1129806758</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/im-your-girl-right/6766440172</v>
+        <v>https://music.apple.com/us/album/lockup/1894298100</v>
       </c>
       <c r="L139" t="str">
-        <v>I’m your girl right? - Tove Lo</v>
+        <v>Lockup - Overmono</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>fuëgo</v>
+        <v>Young</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/fu%C3%ABgo/6767661766</v>
+        <v>https://music.apple.com/us/song/young/6767698952</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-15</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>fuëgo - Single</v>
+        <v>Young</v>
       </c>
       <c r="G140" t="str">
-        <v>3:46</v>
+        <v>2:46</v>
       </c>
       <c r="H140" t="str">
-        <v>BNYX®</v>
+        <v>Dan + Shay</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/bnyx/1438325287</v>
+        <v>https://music.apple.com/us/artist/dan-shay/690319057</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/fu%C3%ABgo/6767661604</v>
+        <v>https://music.apple.com/us/album/young/6767698951</v>
       </c>
       <c r="L140" t="str">
-        <v>fuëgo - BNYX®</v>
+        <v>Young - Dan + Shay</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>jajaja</v>
+        <v>Parachute</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/jajaja/6766341319</v>
+        <v>https://music.apple.com/us/song/parachute/6764119241</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-15</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>jajaja - Single</v>
+        <v>Parachute - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:45</v>
+        <v>2:52</v>
       </c>
       <c r="H141" t="str">
-        <v>Chino Pacas</v>
+        <v>Maren Morris</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
+        <v>https://music.apple.com/us/artist/maren-morris/262260873</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/jajaja/6766341318</v>
+        <v>https://music.apple.com/us/album/parachute/1895648983</v>
       </c>
       <c r="L141" t="str">
-        <v>jajaja - Chino Pacas</v>
+        <v>Parachute - Maren Morris</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>FIND GOD (feat. Dominic Fike)</v>
+        <v>Little Things</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/find-god-feat-dominic-fike/1894315529</v>
+        <v>https://music.apple.com/us/song/little-things/6766351153</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-15</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>BULLDAWG</v>
+        <v>Little Things - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:59</v>
+        <v>2:55</v>
       </c>
       <c r="H142" t="str">
-        <v>Kenny Mason</v>
+        <v>Kevin Jonas</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/kenny-mason/79382206</v>
+        <v>https://music.apple.com/us/artist/kevin-jonas/21138190</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/find-god-feat-dominic-fike/1894315301</v>
+        <v>https://music.apple.com/us/album/little-things/6766350882</v>
       </c>
       <c r="L142" t="str">
-        <v>FIND GOD (feat. Dominic Fike) - Kenny Mason</v>
+        <v>Little Things - Kevin Jonas</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>FOOL ME ONCE (feat. Leon Thomas)</v>
+        <v>Fish Hunt Golf Drink</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/fool-me-once-feat-leon-thomas/1891467239</v>
+        <v>https://music.apple.com/us/song/fish-hunt-golf-drink/6766651884</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-15</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>BELOVED: ACT II</v>
+        <v>Signs</v>
       </c>
       <c r="G143" t="str">
-        <v>3:18</v>
+        <v>2:34</v>
       </c>
       <c r="H143" t="str">
-        <v>GIVĒON</v>
+        <v>Luke Bryan</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/giv%C4%93on/1070668868</v>
+        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/fool-me-once-feat-leon-thomas/1891467233</v>
+        <v>https://music.apple.com/us/album/fish-hunt-golf-drink/6766651878</v>
       </c>
       <c r="L143" t="str">
-        <v>FOOL ME ONCE (feat. Leon Thomas) - GIVĒON</v>
+        <v>Fish Hunt Golf Drink - Luke Bryan</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Shabang</v>
+        <v>PAGEANT STAGE</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/shabang/6769568598</v>
+        <v>https://music.apple.com/us/song/pageant-stage/6764125889</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-15</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>ICEMAN</v>
+        <v>THE EDGE</v>
       </c>
       <c r="G144" t="str">
-        <v>3:08</v>
+        <v>2:52</v>
       </c>
       <c r="H144" t="str">
-        <v>Drake</v>
+        <v>Tone Stith</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/drake/271256</v>
+        <v>https://music.apple.com/us/artist/tone-stith/1167717310</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/shabang/6769568449</v>
+        <v>https://music.apple.com/us/album/pageant-stage/1895651504</v>
       </c>
       <c r="L144" t="str">
-        <v>Shabang - Drake</v>
+        <v>PAGEANT STAGE - Tone Stith</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Road Trips</v>
+        <v>Firestorm</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/road-trips/6769557053</v>
+        <v>https://music.apple.com/us/song/firestorm/1868827004</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-15</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>MAID OF HONOUR</v>
+        <v>Of Earth &amp; Wires</v>
       </c>
       <c r="G145" t="str">
-        <v>4:03</v>
+        <v>2:29</v>
       </c>
       <c r="H145" t="str">
-        <v>Drake</v>
+        <v>Dua Saleh</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/drake/271256</v>
+        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/road-trips/6769556940</v>
+        <v>https://music.apple.com/us/album/firestorm/1868826829</v>
       </c>
       <c r="L145" t="str">
-        <v>Road Trips - Drake</v>
+        <v>Firestorm - Dua Saleh</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Fortworth</v>
+        <v>girl next door</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/fortworth/6769551482</v>
+        <v>https://music.apple.com/us/song/girl-next-door/6768077610</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-15</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>HABIBTI</v>
+        <v>girl next door - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:51</v>
+        <v>3:18</v>
       </c>
       <c r="H146" t="str">
-        <v>Drake</v>
+        <v>mgk</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/drake/271256</v>
+        <v>https://music.apple.com/us/artist/mgk/465954501</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/fortworth/6769551464</v>
+        <v>https://music.apple.com/us/album/girl-next-door/6768077609</v>
       </c>
       <c r="L146" t="str">
-        <v>Fortworth - Drake</v>
+        <v>girl next door - mgk</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Repeat It</v>
+        <v>BIG DOG</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/repeat-it/6764277864</v>
+        <v>https://music.apple.com/us/song/big-dog/1887197046</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-15</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Repeat It - Single</v>
+        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
       </c>
       <c r="G147" t="str">
-        <v>3:11</v>
+        <v>3:36</v>
       </c>
       <c r="H147" t="str">
-        <v>Martin Garrix</v>
+        <v>Genesis Owusu</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
+        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/repeat-it/1895713789</v>
+        <v>https://music.apple.com/us/album/big-dog/1887196431</v>
       </c>
       <c r="L147" t="str">
-        <v>Repeat It - Martin Garrix</v>
+        <v>BIG DOG - Genesis Owusu</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Fool Proof</v>
+        <v>idea of love - A COLORS SHOW</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/fool-proof/1892466004</v>
+        <v>https://music.apple.com/us/song/idea-of-love-a-colors-show/6767667046</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-15</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>idea of love - A COLORS SHOW - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>2:36</v>
+        <v>2:34</v>
       </c>
       <c r="H148" t="str">
-        <v>Cody Johnson</v>
+        <v>kwn</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/fool-proof/1892465981</v>
+        <v>https://music.apple.com/us/album/idea-of-love-a-colors-show/6767666835</v>
       </c>
       <c r="L148" t="str">
-        <v>Fool Proof - Cody Johnson</v>
+        <v>idea of love - A COLORS SHOW - kwn</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Crisco</v>
+        <v>Heavy Serenade</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/crisco/6763369506</v>
+        <v>https://music.apple.com/us/song/heavy-serenade/1892154309</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-15</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Crisco - Single</v>
+        <v>Heavy Serenade - EP</v>
       </c>
       <c r="G149" t="str">
-        <v>2:56</v>
+        <v>3:00</v>
       </c>
       <c r="H149" t="str">
-        <v>Miranda Lambert</v>
+        <v>NMIXX</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/miranda-lambert/18732261</v>
+        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/crisco/1895284236</v>
+        <v>https://music.apple.com/us/album/heavy-serenade/1892154305</v>
       </c>
       <c r="L149" t="str">
-        <v>Crisco - Miranda Lambert</v>
+        <v>Heavy Serenade - NMIXX</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Absolution</v>
+        <v>ddok ddok ddok</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/absolution/1884987651</v>
+        <v>https://music.apple.com/us/song/ddok-ddok-ddok/6764203482</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-15</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Forever Now</v>
+        <v>ddok ddok ddok - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>4:05</v>
+        <v>2:35</v>
       </c>
       <c r="H150" t="str">
-        <v>Switchfoot</v>
+        <v>BOYNEXTDOOR</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
+        <v>https://music.apple.com/us/artist/boynextdoor/1687612559</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/absolution/1884987638</v>
+        <v>https://music.apple.com/us/album/ddok-ddok-ddok/6764203481</v>
       </c>
       <c r="L150" t="str">
-        <v>Absolution - Switchfoot</v>
+        <v>ddok ddok ddok - BOYNEXTDOOR</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>JESUS IS ALIVE</v>
+        <v>Shut It Down</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/jesus-is-alive/6767694896</v>
+        <v>https://music.apple.com/us/song/shut-it-down/6763631128</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-15</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>JESUS IS ALIVE - Single</v>
+        <v>Shut It Down - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:08</v>
+        <v>3:32</v>
       </c>
       <c r="H151" t="str">
-        <v>Forrest Frank</v>
+        <v>Boys Noize</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
+        <v>https://music.apple.com/us/artist/boys-noize/60393190</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/jesus-is-alive/6767694895</v>
+        <v>https://music.apple.com/us/album/shut-it-down/1895408470</v>
       </c>
       <c r="L151" t="str">
-        <v>JESUS IS ALIVE - Forrest Frank</v>
+        <v>Shut It Down - Boys Noize</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Something To Lose</v>
+        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss)</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/something-to-lose/6766964605</v>
+        <v>https://music.apple.com/us/song/together-feat-nikki-nair-jessy-lanza-prentiss/6763207821</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-15</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Is This Heaven? - EP</v>
+        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss) - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>2:55</v>
+        <v>3:18</v>
       </c>
       <c r="H152" t="str">
-        <v>STELLA LEFTY</v>
+        <v>The Avalanches</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
+        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/something-to-lose/6766964604</v>
+        <v>https://music.apple.com/us/album/together-feat-nikki-nair-jessy-lanza-prentiss/1895215105</v>
       </c>
       <c r="L152" t="str">
-        <v>Something To Lose - STELLA LEFTY</v>
+        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss) - The Avalanches</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Too Busy Missing You</v>
+        <v>Can’t Miss You</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/too-busy-missing-you/6766604915</v>
+        <v>https://music.apple.com/us/song/cant-miss-you/1886810999</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-15</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Off Campus: The Mixtape</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="G153" t="str">
-        <v>3:25</v>
+        <v>2:32</v>
       </c>
       <c r="H153" t="str">
-        <v>Asha Banks</v>
+        <v>Sublime</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
+        <v>https://music.apple.com/us/artist/sublime/63480</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/too-busy-missing-you/6766604455</v>
+        <v>https://music.apple.com/us/album/cant-miss-you/1886810990</v>
       </c>
       <c r="L153" t="str">
-        <v>Too Busy Missing You - Asha Banks</v>
+        <v>Can’t Miss You - Sublime</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>F-Stop Blues (4-track)</v>
+        <v>Razorblades And Runways</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/f-stop-blues-4-track/1883173173</v>
+        <v>https://music.apple.com/us/song/razorblades-and-runways/1888004809</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-15</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>Get It Honest</v>
       </c>
       <c r="G154" t="str">
-        <v>3:00</v>
+        <v>3:33</v>
       </c>
       <c r="H154" t="str">
-        <v>Jack Johnson</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/f-stop-blues-4-track/1883172879</v>
+        <v>https://music.apple.com/us/album/razorblades-and-runways/1888004802</v>
       </c>
       <c r="L154" t="str">
-        <v>F-Stop Blues (4-track) - Jack Johnson</v>
+        <v>Razorblades And Runways - The Revivalists</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>PA' LO BONITO</v>
+        <v>Massacre</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/pa-lo-bonito/1886496944</v>
+        <v>https://music.apple.com/us/song/massacre/1892127745</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-15</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>PA' LO BONITO - Single</v>
+        <v>Massacre - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:04</v>
+        <v>2:55</v>
       </c>
       <c r="H155" t="str">
-        <v>Lenny Tavárez</v>
+        <v>Murex</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
+        <v>https://music.apple.com/us/artist/murex/1607430925</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/pa-lo-bonito/1886496943</v>
+        <v>https://music.apple.com/us/album/massacre/1892127742</v>
       </c>
       <c r="L155" t="str">
-        <v>PA' LO BONITO - Lenny Tavárez</v>
+        <v>Massacre - Murex</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>LONELY</v>
+        <v>Better That Way</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/lonely/6768757857</v>
+        <v>https://music.apple.com/us/song/better-that-way/6766273199</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-15</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>DESEO</v>
+        <v>Christian Name</v>
       </c>
       <c r="G156" t="str">
-        <v>2:58</v>
+        <v>3:45</v>
       </c>
       <c r="H156" t="str">
-        <v>Katteyes</v>
+        <v>Charles Wesley Godwin</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/katteyes/1648818255</v>
+        <v>https://music.apple.com/us/artist/charles-wesley-godwin/1441994025</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/lonely/6768757414</v>
+        <v>https://music.apple.com/us/album/better-that-way/1896261802</v>
       </c>
       <c r="L156" t="str">
-        <v>LONELY - Katteyes</v>
+        <v>Better That Way - Charles Wesley Godwin</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Lockup</v>
+        <v>Apollo</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/lockup/1894298102</v>
+        <v>https://music.apple.com/us/song/apollo/6765602431</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-15</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Pure Devotion</v>
+        <v>Apollo - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>4:31</v>
+        <v>3:35</v>
       </c>
       <c r="H157" t="str">
-        <v>Overmono</v>
+        <v>Bryant Barnes</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/overmono/1129806758</v>
+        <v>https://music.apple.com/us/artist/bryant-barnes/1579668433</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/lockup/1894298100</v>
+        <v>https://music.apple.com/us/album/apollo/6765602369</v>
       </c>
       <c r="L157" t="str">
-        <v>Lockup - Overmono</v>
+        <v>Apollo - Bryant Barnes</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Young</v>
+        <v>Infinity (123)</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/young/6767698952</v>
+        <v>https://music.apple.com/us/song/infinity-123/6763447312</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-15</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Young</v>
+        <v>Infinity (123) - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>2:46</v>
+        <v>2:19</v>
       </c>
       <c r="H158" t="str">
-        <v>Dan + Shay</v>
+        <v>December 10</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/dan-shay/690319057</v>
+        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/young/6767698951</v>
+        <v>https://music.apple.com/us/album/infinity-123/1895320456</v>
       </c>
       <c r="L158" t="str">
-        <v>Young - Dan + Shay</v>
+        <v>Infinity (123) - December 10</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Parachute</v>
+        <v>Ain't Over Me Yet</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/parachute/6764119241</v>
+        <v>https://music.apple.com/us/song/aint-over-me-yet/6767283811</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-15</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Parachute - Single</v>
+        <v>Cherry Valley Forever</v>
       </c>
       <c r="G159" t="str">
-        <v>2:52</v>
+        <v>3:24</v>
       </c>
       <c r="H159" t="str">
-        <v>Maren Morris</v>
+        <v>Carter Faith</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/maren-morris/262260873</v>
+        <v>https://music.apple.com/us/artist/carter-faith/1489205896</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/parachute/1895648983</v>
+        <v>https://music.apple.com/us/album/aint-over-me-yet/1896458169</v>
       </c>
       <c r="L159" t="str">
-        <v>Parachute - Maren Morris</v>
+        <v>Ain't Over Me Yet - Carter Faith</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Little Things</v>
+        <v>Where Did You Go</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/little-things/6766351153</v>
+        <v>https://music.apple.com/us/song/where-did-you-go/1877958504</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-15</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Little Things - Single</v>
+        <v>Growing Pains (Deluxe)</v>
       </c>
       <c r="G160" t="str">
-        <v>2:55</v>
+        <v>2:47</v>
       </c>
       <c r="H160" t="str">
-        <v>Kevin Jonas</v>
+        <v>Trousdale</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/kevin-jonas/21138190</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/little-things/6766350882</v>
+        <v>https://music.apple.com/us/album/where-did-you-go/1877958112</v>
       </c>
       <c r="L160" t="str">
-        <v>Little Things - Kevin Jonas</v>
+        <v>Where Did You Go - Trousdale</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Fish Hunt Golf Drink</v>
+        <v>I LOVE YOU</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/fish-hunt-golf-drink/6766651884</v>
+        <v>https://music.apple.com/us/song/i-love-you/6766999950</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-15</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Signs</v>
+        <v>I LOVE YOU - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:34</v>
+        <v>3:11</v>
       </c>
       <c r="H161" t="str">
-        <v>Luke Bryan</v>
+        <v>Noga Erez</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
+        <v>https://music.apple.com/us/artist/noga-erez/1166657901</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/fish-hunt-golf-drink/6766651878</v>
+        <v>https://music.apple.com/us/album/i-love-you/6766999949</v>
       </c>
       <c r="L161" t="str">
-        <v>Fish Hunt Golf Drink - Luke Bryan</v>
+        <v>I LOVE YOU - Noga Erez</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>PAGEANT STAGE</v>
+        <v>Housekeeping</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/pageant-stage/6764125889</v>
+        <v>https://music.apple.com/us/song/housekeeping/6766290834</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-15</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>THE EDGE</v>
+        <v>Housekeeping - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:52</v>
+        <v>3:25</v>
       </c>
       <c r="H162" t="str">
-        <v>Tone Stith</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/tone-stith/1167717310</v>
+        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/pageant-stage/1895651504</v>
+        <v>https://music.apple.com/us/album/housekeeping/6766290823</v>
       </c>
       <c r="L162" t="str">
-        <v>PAGEANT STAGE - Tone Stith</v>
+        <v>Housekeeping - Ally Salort</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Firestorm</v>
+        <v>Surprise Surprise</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/firestorm/1868827004</v>
+        <v>https://music.apple.com/us/song/surprise-surprise/6764842119</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-15</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Of Earth &amp; Wires</v>
+        <v>Surprise Surprise - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>2:29</v>
+        <v>2:55</v>
       </c>
       <c r="H163" t="str">
-        <v>Dua Saleh</v>
+        <v>Chloe Qisha</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
+        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/firestorm/1868826829</v>
+        <v>https://music.apple.com/us/album/surprise-surprise/1895934408</v>
       </c>
       <c r="L163" t="str">
-        <v>Firestorm - Dua Saleh</v>
+        <v>Surprise Surprise - Chloe Qisha</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>girl next door</v>
+        <v>Dog</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/girl-next-door/6768077610</v>
+        <v>https://music.apple.com/us/song/dog/1885967384</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-15</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>girl next door - Single</v>
+        <v>Gentleman</v>
       </c>
       <c r="G164" t="str">
-        <v>3:18</v>
+        <v>3:08</v>
       </c>
       <c r="H164" t="str">
-        <v>mgk</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/mgk/465954501</v>
+        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/girl-next-door/6768077609</v>
+        <v>https://music.apple.com/us/album/dog/1885967368</v>
       </c>
       <c r="L164" t="str">
-        <v>girl next door - mgk</v>
+        <v>Dog - Towa Bird</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>BIG DOG</v>
+        <v>I Never See Her</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/big-dog/1887197046</v>
+        <v>https://music.apple.com/us/song/i-never-see-her/6764149225</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-15</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
+        <v>I Never See Her - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:36</v>
+        <v>3:04</v>
       </c>
       <c r="H165" t="str">
-        <v>Genesis Owusu</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
+        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/big-dog/1887196431</v>
+        <v>https://music.apple.com/us/album/i-never-see-her/1895660748</v>
       </c>
       <c r="L165" t="str">
-        <v>BIG DOG - Genesis Owusu</v>
+        <v>I Never See Her - Spacey Jane</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>idea of love - A COLORS SHOW</v>
+        <v>No God</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/idea-of-love-a-colors-show/6767667046</v>
+        <v>https://music.apple.com/us/song/no-god/1891187414</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-15</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>idea of love - A COLORS SHOW - Single</v>
+        <v>Alone Together</v>
       </c>
       <c r="G166" t="str">
-        <v>2:34</v>
+        <v>2:45</v>
       </c>
       <c r="H166" t="str">
-        <v>kwn</v>
+        <v>Show Me the Body</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
+        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/idea-of-love-a-colors-show/6767666835</v>
+        <v>https://music.apple.com/us/album/no-god/1891187411</v>
       </c>
       <c r="L166" t="str">
-        <v>idea of love - A COLORS SHOW - kwn</v>
+        <v>No God - Show Me the Body</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Heavy Serenade</v>
+        <v>burden</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/heavy-serenade/1892154309</v>
+        <v>https://music.apple.com/us/song/burden/6767688180</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-15</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Heavy Serenade - EP</v>
+        <v>burden - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:00</v>
+        <v>3:24</v>
       </c>
       <c r="H167" t="str">
-        <v>NMIXX</v>
+        <v>Abe Parker</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
+        <v>https://music.apple.com/us/artist/abe-parker/490444584</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/heavy-serenade/1892154305</v>
+        <v>https://music.apple.com/us/album/burden/6767688179</v>
       </c>
       <c r="L167" t="str">
-        <v>Heavy Serenade - NMIXX</v>
+        <v>burden - Abe Parker</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>ddok ddok ddok</v>
+        <v>Chico Raro</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/ddok-ddok-ddok/6764203482</v>
+        <v>https://music.apple.com/us/song/chico-raro/6767713536</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-15</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>ddok ddok ddok - Single</v>
+        <v>Chico Raro - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>2:35</v>
+        <v>3:17</v>
       </c>
       <c r="H168" t="str">
-        <v>BOYNEXTDOOR</v>
+        <v>Arón Piper</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/boynextdoor/1687612559</v>
+        <v>https://music.apple.com/us/artist/ar%C3%B3n-piper/691972942</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/ddok-ddok-ddok/6764203481</v>
+        <v>https://music.apple.com/us/album/chico-raro/6767713527</v>
       </c>
       <c r="L168" t="str">
-        <v>ddok ddok ddok - BOYNEXTDOOR</v>
+        <v>Chico Raro - Arón Piper</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Shut It Down</v>
+        <v>What's Done Is Done</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/shut-it-down/6763631128</v>
+        <v>https://music.apple.com/us/song/whats-done-is-done/6763088629</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-15</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Shut It Down - Single</v>
+        <v>What's Done Is Done - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:32</v>
+        <v>2:53</v>
       </c>
       <c r="H169" t="str">
-        <v>Boys Noize</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/boys-noize/60393190</v>
+        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/shut-it-down/1895408470</v>
+        <v>https://music.apple.com/us/album/whats-done-is-done/1895156626</v>
       </c>
       <c r="L169" t="str">
-        <v>Shut It Down - Boys Noize</v>
+        <v>What's Done Is Done - Jorja Smith</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss)</v>
+        <v>round and round</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/together-feat-nikki-nair-jessy-lanza-prentiss/6763207821</v>
+        <v>https://music.apple.com/us/song/round-and-round/1885665987</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-15</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss) - Single</v>
+        <v>round and round - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:18</v>
+        <v>2:47</v>
       </c>
       <c r="H170" t="str">
-        <v>The Avalanches</v>
+        <v>bbno$</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
+        <v>https://music.apple.com/us/artist/bbno%24/1161580951</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/together-feat-nikki-nair-jessy-lanza-prentiss/1895215105</v>
+        <v>https://music.apple.com/us/album/round-and-round/1885665982</v>
       </c>
       <c r="L170" t="str">
-        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss) - The Avalanches</v>
+        <v>round and round - bbno$</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Can’t Miss You</v>
+        <v>Ain’t That Deep</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/cant-miss-you/1886810999</v>
+        <v>https://music.apple.com/us/song/aint-that-deep/1882831449</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-15</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>The Last Balloon</v>
       </c>
       <c r="G171" t="str">
-        <v>2:32</v>
+        <v>2:39</v>
       </c>
       <c r="H171" t="str">
-        <v>Sublime</v>
+        <v>Tank and the Bangas</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/sublime/63480</v>
+        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/cant-miss-you/1886810990</v>
+        <v>https://music.apple.com/us/album/aint-that-deep/1882831446</v>
       </c>
       <c r="L171" t="str">
-        <v>Can’t Miss You - Sublime</v>
+        <v>Ain’t That Deep - Tank and the Bangas</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Razorblades And Runways</v>
+        <v>Emily</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/razorblades-and-runways/1888004809</v>
+        <v>https://music.apple.com/us/song/emily/1893405442</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-15</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Get It Honest</v>
+        <v>So Much To Say - EP</v>
       </c>
       <c r="G172" t="str">
-        <v>3:33</v>
+        <v>2:35</v>
       </c>
       <c r="H172" t="str">
-        <v>The Revivalists</v>
+        <v>Daisy Grenade</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
+        <v>https://music.apple.com/us/artist/daisy-grenade/1611437131</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/razorblades-and-runways/1888004802</v>
+        <v>https://music.apple.com/us/album/emily/1893405440</v>
       </c>
       <c r="L172" t="str">
-        <v>Razorblades And Runways - The Revivalists</v>
+        <v>Emily - Daisy Grenade</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Massacre</v>
+        <v>Hold</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/massacre/1892127745</v>
+        <v>https://music.apple.com/us/song/hold/6767296480</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-15</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Massacre - Single</v>
+        <v>Hold - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:55</v>
+        <v>4:07</v>
       </c>
       <c r="H173" t="str">
-        <v>Murex</v>
+        <v>Sabrina Sterling</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/murex/1607430925</v>
+        <v>https://music.apple.com/us/artist/sabrina-sterling/1577892147</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/massacre/1892127742</v>
+        <v>https://music.apple.com/us/album/hold/1896462063</v>
       </c>
       <c r="L173" t="str">
-        <v>Massacre - Murex</v>
+        <v>Hold - Sabrina Sterling</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Better That Way</v>
+        <v>Flying Monkey</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/better-that-way/6766273199</v>
+        <v>https://music.apple.com/us/song/flying-monkey/1894351228</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-15</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Christian Name</v>
+        <v>Flying Monkey - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:45</v>
+        <v>4:09</v>
       </c>
       <c r="H174" t="str">
-        <v>Charles Wesley Godwin</v>
+        <v>Blue Medusa</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/charles-wesley-godwin/1441994025</v>
+        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/better-that-way/1896261802</v>
+        <v>https://music.apple.com/us/album/flying-monkey/1894351227</v>
       </c>
       <c r="L174" t="str">
-        <v>Better That Way - Charles Wesley Godwin</v>
+        <v>Flying Monkey - Blue Medusa</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Apollo</v>
+        <v>Anything Goes</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/apollo/6765602431</v>
+        <v>https://music.apple.com/us/song/anything-goes/1891118972</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-15</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Apollo - Single</v>
+        <v>Anything Goes</v>
       </c>
       <c r="G175" t="str">
-        <v>3:35</v>
+        <v>3:00</v>
       </c>
       <c r="H175" t="str">
-        <v>Bryant Barnes</v>
+        <v>Kaleena Zanders</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/bryant-barnes/1579668433</v>
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/apollo/6765602369</v>
+        <v>https://music.apple.com/us/album/anything-goes/1891118971</v>
       </c>
       <c r="L175" t="str">
-        <v>Apollo - Bryant Barnes</v>
+        <v>Anything Goes - Kaleena Zanders</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Infinity (123)</v>
+        <v>We Are</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/infinity-123/6763447312</v>
+        <v>https://music.apple.com/us/song/we-are/1894252873</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-15</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Infinity (123) - Single</v>
+        <v>We Are - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:19</v>
+        <v>3:33</v>
       </c>
       <c r="H176" t="str">
-        <v>December 10</v>
+        <v>Adam Ten</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
+        <v>https://music.apple.com/us/artist/adam-ten/1472226854</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/infinity-123/1895320456</v>
+        <v>https://music.apple.com/us/album/we-are/1894252870</v>
       </c>
       <c r="L176" t="str">
-        <v>Infinity (123) - December 10</v>
+        <v>We Are - Adam Ten</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Ain't Over Me Yet</v>
+        <v>It's For the Kids</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/aint-over-me-yet/6767283811</v>
+        <v>https://music.apple.com/us/song/its-for-the-kids/1867327679</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-15</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Cherry Valley Forever</v>
+        <v>Cursum Perficio</v>
       </c>
       <c r="G177" t="str">
-        <v>3:24</v>
+        <v>4:20</v>
       </c>
       <c r="H177" t="str">
-        <v>Carter Faith</v>
+        <v>Anthrax</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/carter-faith/1489205896</v>
+        <v>https://music.apple.com/us/artist/anthrax/80417</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/aint-over-me-yet/1896458169</v>
+        <v>https://music.apple.com/us/album/its-for-the-kids/1867327673</v>
       </c>
       <c r="L177" t="str">
-        <v>Ain't Over Me Yet - Carter Faith</v>
+        <v>It's For the Kids - Anthrax</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Where Did You Go</v>
+        <v>Pure Ecstasy</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/where-did-you-go/1877958504</v>
+        <v>https://music.apple.com/us/song/pure-ecstasy/6762228978</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-15</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Growing Pains (Deluxe)</v>
+        <v>Pure Ecstasy</v>
       </c>
       <c r="G178" t="str">
-        <v>2:47</v>
+        <v>3:05</v>
       </c>
       <c r="H178" t="str">
-        <v>Trousdale</v>
+        <v>Beartooth</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/where-did-you-go/1877958112</v>
+        <v>https://music.apple.com/us/album/pure-ecstasy/1893453878</v>
       </c>
       <c r="L178" t="str">
-        <v>Where Did You Go - Trousdale</v>
+        <v>Pure Ecstasy - Beartooth</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>I LOVE YOU</v>
+        <v>Something Wicked</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/i-love-you/6766999950</v>
+        <v>https://music.apple.com/us/song/something-wicked/6766252959</v>
       </c>
       <c r="D179" t="str">
         <v>2026-05-15</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>I LOVE YOU - Single</v>
+        <v>Something Wicked - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:11</v>
+        <v>3:28</v>
       </c>
       <c r="H179" t="str">
-        <v>Noga Erez</v>
+        <v>Breaking Benjamin</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/noga-erez/1166657901</v>
+        <v>https://music.apple.com/us/artist/breaking-benjamin/3299379</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/i-love-you/6766999949</v>
+        <v>https://music.apple.com/us/album/something-wicked/1896253678</v>
       </c>
       <c r="L179" t="str">
-        <v>I LOVE YOU - Noga Erez</v>
+        <v>Something Wicked - Breaking Benjamin</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Housekeeping</v>
+        <v>Feel The Funk</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/housekeeping/6766290834</v>
+        <v>https://music.apple.com/us/song/feel-the-funk/6763294007</v>
       </c>
       <c r="D180" t="str">
         <v>2026-05-15</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Housekeeping - Single</v>
+        <v>The Funk EP - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:25</v>
+        <v>3:26</v>
       </c>
       <c r="H180" t="str">
-        <v>Ally Salort</v>
+        <v>Riordan</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
+        <v>https://music.apple.com/us/artist/riordan/1517575029</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/housekeeping/6766290823</v>
+        <v>https://music.apple.com/us/album/feel-the-funk/1895251685</v>
       </c>
       <c r="L180" t="str">
-        <v>Housekeeping - Ally Salort</v>
+        <v>Feel The Funk - Riordan</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Surprise Surprise</v>
+        <v>Everglades (Remix)</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/surprise-surprise/6764842119</v>
+        <v>https://music.apple.com/us/song/everglades-remix/6767719584</v>
       </c>
       <c r="D181" t="str">
         <v>2026-05-15</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Surprise Surprise - Single</v>
+        <v>Everglades (Remix) - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:55</v>
+        <v>2:42</v>
       </c>
       <c r="H181" t="str">
-        <v>Chloe Qisha</v>
+        <v>Aziedoesntexist</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
+        <v>https://music.apple.com/us/artist/aziedoesntexist/1831152556</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/surprise-surprise/1895934408</v>
+        <v>https://music.apple.com/us/album/everglades-remix/6767719577</v>
       </c>
       <c r="L181" t="str">
-        <v>Surprise Surprise - Chloe Qisha</v>
+        <v>Everglades (Remix) - Aziedoesntexist</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Dog</v>
+        <v>Walk</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/dog/1885967384</v>
+        <v>https://music.apple.com/us/song/walk/1892180098</v>
       </c>
       <c r="D182" t="str">
         <v>2026-05-15</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Gentleman</v>
+        <v>Walk - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:08</v>
+        <v>2:25</v>
       </c>
       <c r="H182" t="str">
-        <v>Towa Bird</v>
+        <v>Melodicb</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
+        <v>https://music.apple.com/us/artist/melodicb/1440206517</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/dog/1885967368</v>
+        <v>https://music.apple.com/us/album/walk/1892180097</v>
       </c>
       <c r="L182" t="str">
-        <v>Dog - Towa Bird</v>
+        <v>Walk - Melodicb</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>I Never See Her</v>
+        <v>Volver a Ti</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/i-never-see-her/6764149225</v>
+        <v>https://music.apple.com/us/song/volver-a-ti/6766258204</v>
       </c>
       <c r="D183" t="str">
         <v>2026-05-15</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>I Never See Her - Single</v>
+        <v>Norteña</v>
       </c>
       <c r="G183" t="str">
-        <v>3:04</v>
+        <v>3:47</v>
       </c>
       <c r="H183" t="str">
-        <v>Spacey Jane</v>
+        <v>Julieta Venegas</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
+        <v>https://music.apple.com/us/artist/julieta-venegas/302960</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/i-never-see-her/1895660748</v>
+        <v>https://music.apple.com/us/album/volver-a-ti/1896255736</v>
       </c>
       <c r="L183" t="str">
-        <v>I Never See Her - Spacey Jane</v>
+        <v>Volver a Ti - Julieta Venegas</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>No God</v>
+        <v>Bahamas</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/no-god/1891187414</v>
+        <v>https://music.apple.com/us/song/bahamas/6764695848</v>
       </c>
       <c r="D184" t="str">
         <v>2026-05-15</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Alone Together</v>
+        <v>Bahamas - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:45</v>
+        <v>2:06</v>
       </c>
       <c r="H184" t="str">
-        <v>Show Me the Body</v>
+        <v>LENCHO</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
+        <v>https://music.apple.com/us/artist/lencho/1854923384</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/no-god/1891187411</v>
+        <v>https://music.apple.com/us/album/bahamas/6764695847</v>
       </c>
       <c r="L184" t="str">
-        <v>No God - Show Me the Body</v>
+        <v>Bahamas - LENCHO</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>burden</v>
+        <v>Same Old Song</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/burden/6767688180</v>
+        <v>https://music.apple.com/us/song/same-old-song/6762860685</v>
       </c>
       <c r="D185" t="str">
         <v>2026-05-15</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>burden - Single</v>
+        <v>Same Old Song - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:24</v>
+        <v>4:12</v>
       </c>
       <c r="H185" t="str">
-        <v>Abe Parker</v>
+        <v>Lila Drew</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/abe-parker/490444584</v>
+        <v>https://music.apple.com/us/artist/lila-drew/1439482732</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/burden/6767688179</v>
+        <v>https://music.apple.com/us/album/same-old-song/1895047985</v>
       </c>
       <c r="L185" t="str">
-        <v>burden - Abe Parker</v>
+        <v>Same Old Song - Lila Drew</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Chico Raro</v>
+        <v>gentle</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/chico-raro/6767713536</v>
+        <v>https://music.apple.com/us/song/gentle/6762828356</v>
       </c>
       <c r="D186" t="str">
         <v>2026-05-15</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Chico Raro - Single</v>
+        <v>gentle - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:17</v>
+        <v>2:48</v>
       </c>
       <c r="H186" t="str">
-        <v>Arón Piper</v>
+        <v>Venus Anon</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/ar%C3%B3n-piper/691972942</v>
+        <v>https://music.apple.com/us/artist/venus-anon/1635970130</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/chico-raro/6767713527</v>
+        <v>https://music.apple.com/us/album/gentle/1895031896</v>
       </c>
       <c r="L186" t="str">
-        <v>Chico Raro - Arón Piper</v>
+        <v>gentle - Venus Anon</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>What's Done Is Done</v>
+        <v>Letters of Your Name</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/whats-done-is-done/6763088629</v>
+        <v>https://music.apple.com/us/song/letters-of-your-name/1892919741</v>
       </c>
       <c r="D187" t="str">
         <v>2026-05-15</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>What's Done Is Done - Single</v>
+        <v>Congratulations</v>
       </c>
       <c r="G187" t="str">
-        <v>2:53</v>
+        <v>3:21</v>
       </c>
       <c r="H187" t="str">
-        <v>Jorja Smith</v>
+        <v>Jacob Ungerleider</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
+        <v>https://music.apple.com/us/artist/jacob-ungerleider/1460845591</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/whats-done-is-done/1895156626</v>
+        <v>https://music.apple.com/us/album/letters-of-your-name/1892919737</v>
       </c>
       <c r="L187" t="str">
-        <v>What's Done Is Done - Jorja Smith</v>
+        <v>Letters of Your Name - Jacob Ungerleider</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>round and round</v>
+        <v>Seratonin</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/round-and-round/1885665987</v>
+        <v>https://music.apple.com/us/song/seratonin/6763447428</v>
       </c>
       <c r="D188" t="str">
         <v>2026-05-15</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>round and round - Single</v>
+        <v>Seratonin - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>2:47</v>
+        <v>1:55</v>
       </c>
       <c r="H188" t="str">
-        <v>bbno$</v>
+        <v>James Hype</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/bbno%24/1161580951</v>
+        <v>https://music.apple.com/us/artist/james-hype/925734064</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/round-and-round/1885665982</v>
+        <v>https://music.apple.com/us/album/seratonin/1895320367</v>
       </c>
       <c r="L188" t="str">
-        <v>round and round - bbno$</v>
+        <v>Seratonin - James Hype</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Ain’t That Deep</v>
+        <v>A Digital Touch</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/aint-that-deep/1882831449</v>
+        <v>https://music.apple.com/us/song/a-digital-touch/6765592539</v>
       </c>
       <c r="D189" t="str">
         <v>2026-05-15</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>The Last Balloon</v>
+        <v>A Digital Touch - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>2:39</v>
+        <v>2:53</v>
       </c>
       <c r="H189" t="str">
-        <v>Tank and the Bangas</v>
+        <v>Evening Elephants</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
+        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/aint-that-deep/1882831446</v>
+        <v>https://music.apple.com/us/album/a-digital-touch/1896003252</v>
       </c>
       <c r="L189" t="str">
-        <v>Ain’t That Deep - Tank and the Bangas</v>
+        <v>A Digital Touch - Evening Elephants</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Emily</v>
+        <v>Dead Man's Dog</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/emily/1893405442</v>
+        <v>https://music.apple.com/us/song/dead-mans-dog/6763447424</v>
       </c>
       <c r="D190" t="str">
         <v>2026-05-15</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>So Much To Say - EP</v>
+        <v>Aiming Torches At The Sun - EP</v>
       </c>
       <c r="G190" t="str">
-        <v>2:35</v>
+        <v>4:33</v>
       </c>
       <c r="H190" t="str">
-        <v>Daisy Grenade</v>
+        <v>Dermot Henry</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/daisy-grenade/1611437131</v>
+        <v>https://music.apple.com/us/artist/dermot-henry/1704074611</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/emily/1893405440</v>
+        <v>https://music.apple.com/us/album/dead-mans-dog/1895320369</v>
       </c>
       <c r="L190" t="str">
-        <v>Emily - Daisy Grenade</v>
+        <v>Dead Man's Dog - Dermot Henry</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Hold</v>
+        <v>Fault of God</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/hold/6767296480</v>
+        <v>https://music.apple.com/us/song/fault-of-god/1887702403</v>
       </c>
       <c r="D191" t="str">
         <v>2026-05-15</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Hold - Single</v>
+        <v>Active Child</v>
       </c>
       <c r="G191" t="str">
-        <v>4:07</v>
+        <v>4:13</v>
       </c>
       <c r="H191" t="str">
-        <v>Sabrina Sterling</v>
+        <v>Active Child</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/sabrina-sterling/1577892147</v>
+        <v>https://music.apple.com/us/artist/active-child/355288617</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/hold/1896462063</v>
+        <v>https://music.apple.com/us/album/fault-of-god/1887701924</v>
       </c>
       <c r="L191" t="str">
-        <v>Hold - Sabrina Sterling</v>
+        <v>Fault of God - Active Child</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Flying Monkey</v>
+        <v>Zone (feat. Poppy Baskcomb)</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/flying-monkey/1894351228</v>
+        <v>https://music.apple.com/us/song/zone-feat-poppy-baskcomb/6763982867</v>
       </c>
       <c r="D192" t="str">
         <v>2026-05-15</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Flying Monkey - Single</v>
+        <v>Zone (feat. Poppy Baskcomb) - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>4:09</v>
+        <v>2:56</v>
       </c>
       <c r="H192" t="str">
-        <v>Blue Medusa</v>
+        <v>MK</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
+        <v>https://music.apple.com/us/artist/mk/63097617</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/flying-monkey/1894351227</v>
+        <v>https://music.apple.com/us/album/zone-feat-poppy-baskcomb/1895585800</v>
       </c>
       <c r="L192" t="str">
-        <v>Flying Monkey - Blue Medusa</v>
+        <v>Zone (feat. Poppy Baskcomb) - MK</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Anything Goes</v>
+        <v>Word Vomit</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/anything-goes/1891118972</v>
+        <v>https://music.apple.com/us/song/word-vomit/1887315297</v>
       </c>
       <c r="D193" t="str">
         <v>2026-05-15</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Anything Goes</v>
+        <v>Word Vomit - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:00</v>
+        <v>2:46</v>
       </c>
       <c r="H193" t="str">
-        <v>Kaleena Zanders</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/anything-goes/1891118971</v>
+        <v>https://music.apple.com/us/album/word-vomit/1887315294</v>
       </c>
       <c r="L193" t="str">
-        <v>Anything Goes - Kaleena Zanders</v>
+        <v>Word Vomit - Baby Queen</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>We Are</v>
+        <v>Evil in this House</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/we-are/1894252873</v>
+        <v>https://music.apple.com/us/song/evil-in-this-house/1892398371</v>
       </c>
       <c r="D194" t="str">
         <v>2026-05-15</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>We Are - Single</v>
+        <v>Necropolitan</v>
       </c>
       <c r="G194" t="str">
-        <v>3:33</v>
+        <v>4:21</v>
       </c>
       <c r="H194" t="str">
-        <v>Adam Ten</v>
+        <v>Green Lung</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/adam-ten/1472226854</v>
+        <v>https://music.apple.com/us/artist/green-lung/1244071662</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/we-are/1894252870</v>
+        <v>https://music.apple.com/us/album/evil-in-this-house/1892398281</v>
       </c>
       <c r="L194" t="str">
-        <v>We Are - Adam Ten</v>
+        <v>Evil in this House - Green Lung</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>It's For the Kids</v>
+        <v>Heaven on High</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/its-for-the-kids/1867327679</v>
+        <v>https://music.apple.com/us/song/heaven-on-high/1881724153</v>
       </c>
       <c r="D195" t="str">
         <v>2026-05-15</v>
@@ -7785,714 +7785,30 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Cursum Perficio</v>
+        <v>A Pale White Dot</v>
       </c>
       <c r="G195" t="str">
-        <v>4:20</v>
+        <v>4:19</v>
       </c>
       <c r="H195" t="str">
-        <v>Anthrax</v>
+        <v>Periphery</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/anthrax/80417</v>
+        <v>https://music.apple.com/us/artist/periphery/187683869</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/its-for-the-kids/1867327673</v>
+        <v>https://music.apple.com/us/album/heaven-on-high/1881724003</v>
       </c>
       <c r="L195" t="str">
-        <v>It's For the Kids - Anthrax</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="str">
-        <v>Pure Ecstasy</v>
-      </c>
-      <c r="B196" t="str">
-        <v/>
-      </c>
-      <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/pure-ecstasy/6762228978</v>
-      </c>
-      <c r="D196" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E196" t="str">
-        <v/>
-      </c>
-      <c r="F196" t="str">
-        <v>Pure Ecstasy</v>
-      </c>
-      <c r="G196" t="str">
-        <v>3:05</v>
-      </c>
-      <c r="H196" t="str">
-        <v>Beartooth</v>
-      </c>
-      <c r="I196" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
-      </c>
-      <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/pure-ecstasy/1893453878</v>
-      </c>
-      <c r="L196" t="str">
-        <v>Pure Ecstasy - Beartooth</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="str">
-        <v>Something Wicked</v>
-      </c>
-      <c r="B197" t="str">
-        <v/>
-      </c>
-      <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/something-wicked/6766252959</v>
-      </c>
-      <c r="D197" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E197" t="str">
-        <v/>
-      </c>
-      <c r="F197" t="str">
-        <v>Something Wicked - Single</v>
-      </c>
-      <c r="G197" t="str">
-        <v>3:28</v>
-      </c>
-      <c r="H197" t="str">
-        <v>Breaking Benjamin</v>
-      </c>
-      <c r="I197" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/breaking-benjamin/3299379</v>
-      </c>
-      <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/something-wicked/1896253678</v>
-      </c>
-      <c r="L197" t="str">
-        <v>Something Wicked - Breaking Benjamin</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="str">
-        <v>Feel The Funk</v>
-      </c>
-      <c r="B198" t="str">
-        <v/>
-      </c>
-      <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/feel-the-funk/6763294007</v>
-      </c>
-      <c r="D198" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E198" t="str">
-        <v/>
-      </c>
-      <c r="F198" t="str">
-        <v>The Funk EP - Single</v>
-      </c>
-      <c r="G198" t="str">
-        <v>3:26</v>
-      </c>
-      <c r="H198" t="str">
-        <v>Riordan</v>
-      </c>
-      <c r="I198" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/riordan/1517575029</v>
-      </c>
-      <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/feel-the-funk/1895251685</v>
-      </c>
-      <c r="L198" t="str">
-        <v>Feel The Funk - Riordan</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>Everglades (Remix)</v>
-      </c>
-      <c r="B199" t="str">
-        <v/>
-      </c>
-      <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/everglades-remix/6767719584</v>
-      </c>
-      <c r="D199" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E199" t="str">
-        <v/>
-      </c>
-      <c r="F199" t="str">
-        <v>Everglades (Remix) - Single</v>
-      </c>
-      <c r="G199" t="str">
-        <v>2:42</v>
-      </c>
-      <c r="H199" t="str">
-        <v>Aziedoesntexist</v>
-      </c>
-      <c r="I199" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/aziedoesntexist/1831152556</v>
-      </c>
-      <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/everglades-remix/6767719577</v>
-      </c>
-      <c r="L199" t="str">
-        <v>Everglades (Remix) - Aziedoesntexist</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>Walk</v>
-      </c>
-      <c r="B200" t="str">
-        <v/>
-      </c>
-      <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/walk/1892180098</v>
-      </c>
-      <c r="D200" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E200" t="str">
-        <v/>
-      </c>
-      <c r="F200" t="str">
-        <v>Walk - Single</v>
-      </c>
-      <c r="G200" t="str">
-        <v>2:25</v>
-      </c>
-      <c r="H200" t="str">
-        <v>Melodicb</v>
-      </c>
-      <c r="I200" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/melodicb/1440206517</v>
-      </c>
-      <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/walk/1892180097</v>
-      </c>
-      <c r="L200" t="str">
-        <v>Walk - Melodicb</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="str">
-        <v>Volver a Ti</v>
-      </c>
-      <c r="B201" t="str">
-        <v/>
-      </c>
-      <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/volver-a-ti/6766258204</v>
-      </c>
-      <c r="D201" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E201" t="str">
-        <v/>
-      </c>
-      <c r="F201" t="str">
-        <v>Norteña</v>
-      </c>
-      <c r="G201" t="str">
-        <v>3:47</v>
-      </c>
-      <c r="H201" t="str">
-        <v>Julieta Venegas</v>
-      </c>
-      <c r="I201" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/julieta-venegas/302960</v>
-      </c>
-      <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/volver-a-ti/1896255736</v>
-      </c>
-      <c r="L201" t="str">
-        <v>Volver a Ti - Julieta Venegas</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="str">
-        <v>Bahamas</v>
-      </c>
-      <c r="B202" t="str">
-        <v/>
-      </c>
-      <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/bahamas/6764695848</v>
-      </c>
-      <c r="D202" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E202" t="str">
-        <v/>
-      </c>
-      <c r="F202" t="str">
-        <v>Bahamas - Single</v>
-      </c>
-      <c r="G202" t="str">
-        <v>2:06</v>
-      </c>
-      <c r="H202" t="str">
-        <v>LENCHO</v>
-      </c>
-      <c r="I202" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/lencho/1854923384</v>
-      </c>
-      <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/bahamas/6764695847</v>
-      </c>
-      <c r="L202" t="str">
-        <v>Bahamas - LENCHO</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="str">
-        <v>Same Old Song</v>
-      </c>
-      <c r="B203" t="str">
-        <v/>
-      </c>
-      <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/same-old-song/6762860685</v>
-      </c>
-      <c r="D203" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E203" t="str">
-        <v/>
-      </c>
-      <c r="F203" t="str">
-        <v>Same Old Song - Single</v>
-      </c>
-      <c r="G203" t="str">
-        <v>4:12</v>
-      </c>
-      <c r="H203" t="str">
-        <v>Lila Drew</v>
-      </c>
-      <c r="I203" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/lila-drew/1439482732</v>
-      </c>
-      <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/same-old-song/1895047985</v>
-      </c>
-      <c r="L203" t="str">
-        <v>Same Old Song - Lila Drew</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="str">
-        <v>gentle</v>
-      </c>
-      <c r="B204" t="str">
-        <v/>
-      </c>
-      <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/gentle/6762828356</v>
-      </c>
-      <c r="D204" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E204" t="str">
-        <v/>
-      </c>
-      <c r="F204" t="str">
-        <v>gentle - Single</v>
-      </c>
-      <c r="G204" t="str">
-        <v>2:48</v>
-      </c>
-      <c r="H204" t="str">
-        <v>Venus Anon</v>
-      </c>
-      <c r="I204" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/venus-anon/1635970130</v>
-      </c>
-      <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/gentle/1895031896</v>
-      </c>
-      <c r="L204" t="str">
-        <v>gentle - Venus Anon</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="str">
-        <v>Letters of Your Name</v>
-      </c>
-      <c r="B205" t="str">
-        <v/>
-      </c>
-      <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/letters-of-your-name/1892919741</v>
-      </c>
-      <c r="D205" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E205" t="str">
-        <v/>
-      </c>
-      <c r="F205" t="str">
-        <v>Congratulations</v>
-      </c>
-      <c r="G205" t="str">
-        <v>3:21</v>
-      </c>
-      <c r="H205" t="str">
-        <v>Jacob Ungerleider</v>
-      </c>
-      <c r="I205" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/jacob-ungerleider/1460845591</v>
-      </c>
-      <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/letters-of-your-name/1892919737</v>
-      </c>
-      <c r="L205" t="str">
-        <v>Letters of Your Name - Jacob Ungerleider</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="str">
-        <v>Seratonin</v>
-      </c>
-      <c r="B206" t="str">
-        <v/>
-      </c>
-      <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/seratonin/6763447428</v>
-      </c>
-      <c r="D206" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E206" t="str">
-        <v/>
-      </c>
-      <c r="F206" t="str">
-        <v>Seratonin - Single</v>
-      </c>
-      <c r="G206" t="str">
-        <v>1:55</v>
-      </c>
-      <c r="H206" t="str">
-        <v>James Hype</v>
-      </c>
-      <c r="I206" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/james-hype/925734064</v>
-      </c>
-      <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/seratonin/1895320367</v>
-      </c>
-      <c r="L206" t="str">
-        <v>Seratonin - James Hype</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="str">
-        <v>A Digital Touch</v>
-      </c>
-      <c r="B207" t="str">
-        <v/>
-      </c>
-      <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/a-digital-touch/6765592539</v>
-      </c>
-      <c r="D207" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E207" t="str">
-        <v/>
-      </c>
-      <c r="F207" t="str">
-        <v>A Digital Touch - Single</v>
-      </c>
-      <c r="G207" t="str">
-        <v>2:53</v>
-      </c>
-      <c r="H207" t="str">
-        <v>Evening Elephants</v>
-      </c>
-      <c r="I207" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
-      </c>
-      <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/a-digital-touch/1896003252</v>
-      </c>
-      <c r="L207" t="str">
-        <v>A Digital Touch - Evening Elephants</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="str">
-        <v>Dead Man's Dog</v>
-      </c>
-      <c r="B208" t="str">
-        <v/>
-      </c>
-      <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/dead-mans-dog/6763447424</v>
-      </c>
-      <c r="D208" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E208" t="str">
-        <v/>
-      </c>
-      <c r="F208" t="str">
-        <v>Aiming Torches At The Sun - EP</v>
-      </c>
-      <c r="G208" t="str">
-        <v>4:33</v>
-      </c>
-      <c r="H208" t="str">
-        <v>Dermot Henry</v>
-      </c>
-      <c r="I208" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/dermot-henry/1704074611</v>
-      </c>
-      <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/dead-mans-dog/1895320369</v>
-      </c>
-      <c r="L208" t="str">
-        <v>Dead Man's Dog - Dermot Henry</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="str">
-        <v>Fault of God</v>
-      </c>
-      <c r="B209" t="str">
-        <v/>
-      </c>
-      <c r="C209" t="str">
-        <v>https://music.apple.com/us/song/fault-of-god/1887702403</v>
-      </c>
-      <c r="D209" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E209" t="str">
-        <v/>
-      </c>
-      <c r="F209" t="str">
-        <v>Active Child</v>
-      </c>
-      <c r="G209" t="str">
-        <v>4:13</v>
-      </c>
-      <c r="H209" t="str">
-        <v>Active Child</v>
-      </c>
-      <c r="I209" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J209" t="str">
-        <v>https://music.apple.com/us/artist/active-child/355288617</v>
-      </c>
-      <c r="K209" t="str">
-        <v>https://music.apple.com/us/album/fault-of-god/1887701924</v>
-      </c>
-      <c r="L209" t="str">
-        <v>Fault of God - Active Child</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="str">
-        <v>Zone (feat. Poppy Baskcomb)</v>
-      </c>
-      <c r="B210" t="str">
-        <v/>
-      </c>
-      <c r="C210" t="str">
-        <v>https://music.apple.com/us/song/zone-feat-poppy-baskcomb/6763982867</v>
-      </c>
-      <c r="D210" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E210" t="str">
-        <v/>
-      </c>
-      <c r="F210" t="str">
-        <v>Zone (feat. Poppy Baskcomb) - Single</v>
-      </c>
-      <c r="G210" t="str">
-        <v>2:56</v>
-      </c>
-      <c r="H210" t="str">
-        <v>MK</v>
-      </c>
-      <c r="I210" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J210" t="str">
-        <v>https://music.apple.com/us/artist/mk/63097617</v>
-      </c>
-      <c r="K210" t="str">
-        <v>https://music.apple.com/us/album/zone-feat-poppy-baskcomb/1895585800</v>
-      </c>
-      <c r="L210" t="str">
-        <v>Zone (feat. Poppy Baskcomb) - MK</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="str">
-        <v>Word Vomit</v>
-      </c>
-      <c r="B211" t="str">
-        <v/>
-      </c>
-      <c r="C211" t="str">
-        <v>https://music.apple.com/us/song/word-vomit/1887315297</v>
-      </c>
-      <c r="D211" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E211" t="str">
-        <v/>
-      </c>
-      <c r="F211" t="str">
-        <v>Word Vomit - Single</v>
-      </c>
-      <c r="G211" t="str">
-        <v>2:46</v>
-      </c>
-      <c r="H211" t="str">
-        <v>Baby Queen</v>
-      </c>
-      <c r="I211" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J211" t="str">
-        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
-      </c>
-      <c r="K211" t="str">
-        <v>https://music.apple.com/us/album/word-vomit/1887315294</v>
-      </c>
-      <c r="L211" t="str">
-        <v>Word Vomit - Baby Queen</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="str">
-        <v>Evil in this House</v>
-      </c>
-      <c r="B212" t="str">
-        <v/>
-      </c>
-      <c r="C212" t="str">
-        <v>https://music.apple.com/us/song/evil-in-this-house/1892398371</v>
-      </c>
-      <c r="D212" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E212" t="str">
-        <v/>
-      </c>
-      <c r="F212" t="str">
-        <v>Necropolitan</v>
-      </c>
-      <c r="G212" t="str">
-        <v>4:21</v>
-      </c>
-      <c r="H212" t="str">
-        <v>Green Lung</v>
-      </c>
-      <c r="I212" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J212" t="str">
-        <v>https://music.apple.com/us/artist/green-lung/1244071662</v>
-      </c>
-      <c r="K212" t="str">
-        <v>https://music.apple.com/us/album/evil-in-this-house/1892398281</v>
-      </c>
-      <c r="L212" t="str">
-        <v>Evil in this House - Green Lung</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="str">
-        <v>Heaven on High</v>
-      </c>
-      <c r="B213" t="str">
-        <v/>
-      </c>
-      <c r="C213" t="str">
-        <v>https://music.apple.com/us/song/heaven-on-high/1881724153</v>
-      </c>
-      <c r="D213" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E213" t="str">
-        <v/>
-      </c>
-      <c r="F213" t="str">
-        <v>A Pale White Dot</v>
-      </c>
-      <c r="G213" t="str">
-        <v>4:19</v>
-      </c>
-      <c r="H213" t="str">
-        <v>Periphery</v>
-      </c>
-      <c r="I213" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J213" t="str">
-        <v>https://music.apple.com/us/artist/periphery/187683869</v>
-      </c>
-      <c r="K213" t="str">
-        <v>https://music.apple.com/us/album/heaven-on-high/1881724003</v>
-      </c>
-      <c r="L213" t="str">
         <v>Heaven on High - Periphery</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L213"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L195"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-05-week03/titles.xlsx
+++ b/data/global/2026-05-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L195"/>
+  <dimension ref="A1:L193"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שני בן משה - שירים לא שלי</v>
+        <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-15</v>
+        <v>8 days ago</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410900&amp;sid=e8f61624910ad71cfefc2731eed11f18</v>
+        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-15</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>8 days ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Harry Styles</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שני בן משה - שירים לא שלי</v>
+        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ג'קו אייזנברג ורון נשר – קיווינו</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-05-15</v>
+        <v>8 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://yosmusic.com/%d7%92%d7%a7%d7%95-%d7%90%d7%99%d7%99%d7%96%d7%a0%d7%91%d7%a8%d7%92-%d7%95%d7%a8%d7%95%d7%9f-%d7%a0%d7%a9%d7%a8-%d7%a7%d7%99%d7%95%d7%95%d7%99%d7%a0%d7%95/</v>
+        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-15</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>השיר "קיווינו” של ג'קו אייזנברג ורון נשר הוא בלדת רוק טעונה שמצליחה להחזיק בו־זמנית גם כאב אישי וגם אמירה חברתית רחבה יותר. זה שיר שלא מציע פתרון ברור. במקום להכריז “יהיה טוב”, הוא נשאר בתוך חוסר הוודאות, בתוך העייפות של</v>
+        <v>8 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>Eagles</v>
       </c>
       <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>ג'קו אייזנברג ורון נשר – קיווינו</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Harry Styles - Dance No More (Official Video)</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B4" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
+        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-15</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Harry Styles</v>
+        <v>Nora Fatehi</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B5" t="str">
-        <v>7 days ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
+        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-15</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>7 days ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Eagles</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B6" t="str">
-        <v>5 days ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
+        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-15</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>5 days ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Nora Fatehi</v>
+        <v>Eurovision Song Contest and Alis</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
       </c>
       <c r="B7" t="str">
         <v>2 months ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
+        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-15</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
+        <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>2 months ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
+        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-15</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 months ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Eurovision Song Contest and Alis</v>
+        <v>The Head And The Heart</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
+        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B9" t="str">
-        <v>2 months ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
+        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-15</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 months ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Simply Red</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video)</v>
+        <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
+        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-15</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>The Head And The Heart</v>
+        <v>Talking Heads</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
+        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
+        <v>Ellise - Liplock (Official Music Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
+        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-15</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Simply Red</v>
+        <v>Ellise</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
+        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video)</v>
+        <v>Tori Kelly - Dive (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
+        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-15</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Talking Heads</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
+        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Ellise - Liplock (Official Music Video)</v>
+        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
       </c>
       <c r="B13" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
+        <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-15</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Ellise</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
+        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024) - David Gilmour</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Tori Kelly - Dive (Official Music Video)</v>
+        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
       </c>
       <c r="B14" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
+        <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-15</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Tori Kelly</v>
+        <v>Scorpions</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
+        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
+        <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
+        <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-15</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>David Gilmour</v>
+        <v>Claire Leslie</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024) - David Gilmour</v>
+        <v>Claire Leslie - Passenger Seat (Official Music Video) - Claire Leslie</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
+        <v>Michael Schulte - Lovesick (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
+        <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-15</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Scorpions</v>
+        <v>Michael Schulte</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022) - Scorpions</v>
+        <v>Michael Schulte - Lovesick (Official Video) - Michael Schulte</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
+        <v>Caity Baser - Holiday Song (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
+        <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-15</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Claire Leslie</v>
+        <v>Caity Baser</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Claire Leslie - Passenger Seat (Official Music Video) - Claire Leslie</v>
+        <v>Caity Baser - Holiday Song (Official Video) - Caity Baser</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Michael Schulte - Lovesick (Official Video)</v>
+        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
       </c>
       <c r="B18" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
+        <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-15</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Michael Schulte</v>
+        <v>Sam Fischer</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Michael Schulte - Lovesick (Official Video) - Michael Schulte</v>
+        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser) - Sam Fischer</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Caity Baser - Holiday Song (Official Video)</v>
+        <v>Porches- HABIT (Official Video)</v>
       </c>
       <c r="B19" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
+        <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-15</v>
@@ -1103,7 +1103,7 @@
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Caity Baser</v>
+        <v>Porches</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Caity Baser - Holiday Song (Official Video) - Caity Baser</v>
+        <v>Porches- HABIT (Official Video) - Porches</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
+        <v>Charli xcx - Rock Music (Official Video)</v>
       </c>
       <c r="B20" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
+        <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-15</v>
@@ -1141,7 +1141,7 @@
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Sam Fischer</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser) - Sam Fischer</v>
+        <v>Charli xcx - Rock Music (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Porches- HABIT (Official Video)</v>
+        <v>Jon Batiste - Alla Blues (Audio)</v>
       </c>
       <c r="B21" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
+        <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-15</v>
@@ -1179,7 +1179,7 @@
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Porches</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Porches- HABIT (Official Video) - Porches</v>
+        <v>Jon Batiste - Alla Blues (Audio) - Jon Batiste</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Charli xcx - Rock Music (Official Video)</v>
+        <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
       </c>
       <c r="B22" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
+        <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-15</v>
@@ -1217,7 +1217,7 @@
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Charli xcx</v>
+        <v>Tigirlily Gold</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Charli xcx - Rock Music (Official Video) - Charli xcx</v>
+        <v>Tigirlily Gold - I Do or Die (Official Music Video) - Tigirlily Gold</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Jon Batiste - Alla Blues (Audio)</v>
+        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
       </c>
       <c r="B23" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
+        <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-15</v>
@@ -1255,7 +1255,7 @@
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Jon Batiste</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Jon Batiste - Alla Blues (Audio) - Jon Batiste</v>
+        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
+        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
       </c>
       <c r="B24" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
+        <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-15</v>
@@ -1293,7 +1293,7 @@
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Tigirlily Gold</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Tigirlily Gold - I Do or Die (Official Music Video) - Tigirlily Gold</v>
+        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
+        <v>Tori Kelly - Control (Official Visualizer)</v>
       </c>
       <c r="B25" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
+        <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-15</v>
@@ -1331,7 +1331,7 @@
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video) - PAUL McCARTNEY</v>
+        <v>Tori Kelly - Control (Official Visualizer) - Tori Kelly</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
+        <v>Bea Miller - depressed on the internet (Lyric Video)</v>
       </c>
       <c r="B26" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
+        <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-15</v>
@@ -1369,7 +1369,7 @@
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Bruno Mars</v>
+        <v>bea miller</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video] - Bruno Mars</v>
+        <v>Bea Miller - depressed on the internet (Lyric Video) - bea miller</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Tori Kelly - Control (Official Visualizer)</v>
+        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
       </c>
       <c r="B27" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
+        <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-15</v>
@@ -1407,7 +1407,7 @@
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Tori Kelly</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Tori Kelly - Control (Official Visualizer) - Tori Kelly</v>
+        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Bea Miller - depressed on the internet (Lyric Video)</v>
+        <v>Madison Beer - free (Official Audio)</v>
       </c>
       <c r="B28" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
+        <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-15</v>
@@ -1445,7 +1445,7 @@
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>bea miller</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Bea Miller - depressed on the internet (Lyric Video) - bea miller</v>
+        <v>Madison Beer - free (Official Audio) - Madison Beer</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
+        <v>Tori Kelly - Dive (Official Audio)</v>
       </c>
       <c r="B29" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
+        <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-15</v>
@@ -1483,7 +1483,7 @@
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>The Chainsmokers</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer) - The Chainsmokers</v>
+        <v>Tori Kelly - Dive (Official Audio) - Tori Kelly</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Madison Beer - free (Official Audio)</v>
+        <v>Jeremy Camp - Reflector (Official Audio)</v>
       </c>
       <c r="B30" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
+        <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-15</v>
@@ -1521,7 +1521,7 @@
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Madison Beer</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Madison Beer - free (Official Audio) - Madison Beer</v>
+        <v>Jeremy Camp - Reflector (Official Audio) - JeremyCampMusic</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Tori Kelly - Dive (Official Audio)</v>
+        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
       </c>
       <c r="B31" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
+        <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-15</v>
@@ -1559,7 +1559,7 @@
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Tori Kelly</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Tori Kelly - Dive (Official Audio) - Tori Kelly</v>
+        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Jeremy Camp - Reflector (Official Audio)</v>
+        <v>Ashley Cooke - high school sweetheart</v>
       </c>
       <c r="B32" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
+        <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-15</v>
@@ -1597,7 +1597,7 @@
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>JeremyCampMusic</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Jeremy Camp - Reflector (Official Audio) - JeremyCampMusic</v>
+        <v>Ashley Cooke - high school sweetheart - Ashley Cooke</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
+        <v>Ari Abdul - Ego (Visualizer)</v>
       </c>
       <c r="B33" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
+        <v>https://www.youtube.com/watch?v=L0FjVr6LpVU</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-15</v>
@@ -1635,7 +1635,7 @@
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>The Chainsmokers</v>
+        <v>Ari Abdul</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer) - The Chainsmokers</v>
+        <v>Ari Abdul - Ego (Visualizer) - Ari Abdul</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Ashley Cooke - high school sweetheart</v>
+        <v>Quinn XCII - HOOPLA (Official Music Video)</v>
       </c>
       <c r="B34" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
+        <v>https://www.youtube.com/watch?v=eNbGA1pgmFk</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-15</v>
@@ -1673,7 +1673,7 @@
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Ashley Cooke</v>
+        <v>Quinn XCII</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Ashley Cooke - high school sweetheart - Ashley Cooke</v>
+        <v>Quinn XCII - HOOPLA (Official Music Video) - Quinn XCII</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Ari Abdul - Ego (Visualizer)</v>
+        <v>Madison Beer - lovergirl (Official Music Video)</v>
       </c>
       <c r="B35" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=L0FjVr6LpVU</v>
+        <v>https://www.youtube.com/watch?v=q4lU1N3oqYQ</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-15</v>
@@ -1711,7 +1711,7 @@
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Ari Abdul</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Ari Abdul - Ego (Visualizer) - Ari Abdul</v>
+        <v>Madison Beer - lovergirl (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Quinn XCII - HOOPLA (Official Music Video)</v>
+        <v>David J - WHAT IF I'M IN LOVE (Official Video)</v>
       </c>
       <c r="B36" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=eNbGA1pgmFk</v>
+        <v>https://www.youtube.com/watch?v=-SF7Hm_ikaY</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-15</v>
@@ -1749,7 +1749,7 @@
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Quinn XCII</v>
+        <v>David J</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Quinn XCII - HOOPLA (Official Music Video) - Quinn XCII</v>
+        <v>David J - WHAT IF I'M IN LOVE (Official Video) - David J</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Madison Beer - lovergirl (Official Music Video)</v>
+        <v>The Last Dinner Party - Big Dog (On The Road)</v>
       </c>
       <c r="B37" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=q4lU1N3oqYQ</v>
+        <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-15</v>
@@ -1787,7 +1787,7 @@
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Madison Beer</v>
+        <v>The Last Dinner Party</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Madison Beer - lovergirl (Official Music Video) - Madison Beer</v>
+        <v>The Last Dinner Party - Big Dog (On The Road) - The Last Dinner Party</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>David J - WHAT IF I'M IN LOVE (Official Video)</v>
+        <v>OCEAN ALLEY - HOLD ON (Official Video)</v>
       </c>
       <c r="B38" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=-SF7Hm_ikaY</v>
+        <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-15</v>
@@ -1825,7 +1825,7 @@
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>David J</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>David J - WHAT IF I'M IN LOVE (Official Video) - David J</v>
+        <v>OCEAN ALLEY - HOLD ON (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>The Last Dinner Party - Big Dog (On The Road)</v>
+        <v>Dagny - Closet Disco Queen (Lyric Video)</v>
       </c>
       <c r="B39" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
+        <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-15</v>
@@ -1863,7 +1863,7 @@
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>The Last Dinner Party</v>
+        <v>Dagny</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>The Last Dinner Party - Big Dog (On The Road) - The Last Dinner Party</v>
+        <v>Dagny - Closet Disco Queen (Lyric Video) - Dagny</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>OCEAN ALLEY - HOLD ON (Official Video)</v>
+        <v>Purple Disco Machine - Disco Cherry (Official Video)</v>
       </c>
       <c r="B40" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
+        <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-15</v>
@@ -1901,7 +1901,7 @@
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Ocean Alley</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>OCEAN ALLEY - HOLD ON (Official Video) - Ocean Alley</v>
+        <v>Purple Disco Machine - Disco Cherry (Official Video) - Purple Disco Machine</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Dagny - Closet Disco Queen (Lyric Video)</v>
+        <v>Paris Paloma - Stem the Flow [Official Music Video]</v>
       </c>
       <c r="B41" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
+        <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-15</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Dagny</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Dagny - Closet Disco Queen (Lyric Video) - Dagny</v>
+        <v>Paris Paloma - Stem the Flow [Official Music Video] - Paris Paloma</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Purple Disco Machine - Disco Cherry (Official Video)</v>
+        <v>Lucy Blue - Who you love (Visualiser)</v>
       </c>
       <c r="B42" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
+        <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-15</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Lucy Blue</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Purple Disco Machine - Disco Cherry (Official Video) - Purple Disco Machine</v>
+        <v>Lucy Blue - Who you love (Visualiser) - Lucy Blue</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Paris Paloma - Stem the Flow [Official Music Video]</v>
+        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026)</v>
       </c>
       <c r="B43" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
+        <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-15</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Paris Paloma</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Paris Paloma - Stem the Flow [Official Music Video] - Paris Paloma</v>
+        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026) - Olivia Dean</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Lucy Blue - Who you love (Visualiser)</v>
+        <v>Aaron Frazer - It's A Shame (Official Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
+        <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-15</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Lucy Blue</v>
+        <v>Aaron Frazer</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Lucy Blue - Who you love (Visualiser) - Lucy Blue</v>
+        <v>Aaron Frazer - It's A Shame (Official Video) - Aaron Frazer</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026)</v>
+        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify</v>
       </c>
       <c r="B45" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
+        <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-15</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Olivia Dean</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026) - Olivia Dean</v>
+        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Aaron Frazer - It's A Shame (Official Video)</v>
+        <v>DANNA - OUT OF MY BODY</v>
       </c>
       <c r="B46" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
+        <v>https://www.youtube.com/watch?v=uW_Ye0kQ9Ac</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-15</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Aaron Frazer</v>
+        <v>Danna</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Aaron Frazer - It's A Shame (Official Video) - Aaron Frazer</v>
+        <v>DANNA - OUT OF MY BODY - Danna</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify</v>
+        <v>The Rolling Stones - In The Stars (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
+        <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-15</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Holly Humberstone</v>
+        <v>The Rolling Stones</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>The Rolling Stones - In The Stars (Official Lyric Video) - The Rolling Stones</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>DANNA - OUT OF MY BODY</v>
+        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser)</v>
       </c>
       <c r="B48" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=uW_Ye0kQ9Ac</v>
+        <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-15</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Danna</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>DANNA - OUT OF MY BODY - Danna</v>
+        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>The Rolling Stones - In The Stars (Official Lyric Video)</v>
+        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
       </c>
       <c r="B49" t="str">
-        <v>9 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
+        <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-15</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>9 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>The Rolling Stones</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>The Rolling Stones - In The Stars (Official Lyric Video) - The Rolling Stones</v>
+        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser)</v>
+        <v>Rick Astley - Raindrops (Official Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>9 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
+        <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-15</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>9 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser) - Dermot Kennedy</v>
+        <v>Rick Astley - Raindrops (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
+        <v>Jessie J - THREW IT AWAY (Official Video)</v>
       </c>
       <c r="B51" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
+        <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-15</v>
@@ -2319,7 +2319,7 @@
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Jessie J</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2) - SIENNA SPIRO</v>
+        <v>Jessie J - THREW IT AWAY (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Rick Astley - Raindrops (Official Video)</v>
+        <v>The Takes - Ain't Love (Lyric Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
+        <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-15</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Rick Astley</v>
+        <v>The Takes</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Rick Astley - Raindrops (Official Video) - Rick Astley</v>
+        <v>The Takes - Ain't Love (Lyric Video) - The Takes</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Jessie J - THREW IT AWAY (Official Video)</v>
+        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary</v>
       </c>
       <c r="B53" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
+        <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-15</v>
@@ -2395,7 +2395,7 @@
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Jessie J</v>
+        <v>The Offspring</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Jessie J - THREW IT AWAY (Official Video) - Jessie J</v>
+        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary - The Offspring</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>The Takes - Ain't Love (Lyric Video)</v>
+        <v>Louis Tomlinson - Sunflowers (Official Performance Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
+        <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-15</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>The Takes</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>The Takes - Ain't Love (Lyric Video) - The Takes</v>
+        <v>Louis Tomlinson - Sunflowers (Official Performance Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary</v>
+        <v>The Beaches - Should've Known Better (Official Visualizer)</v>
       </c>
       <c r="B55" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
+        <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-15</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>The Offspring</v>
+        <v>The Beaches</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary - The Offspring</v>
+        <v>The Beaches - Should've Known Better (Official Visualizer) - The Beaches</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Louis Tomlinson - Sunflowers (Official Performance Video)</v>
+        <v>The Kiffness - Serafino (Singing Cat Song)</v>
       </c>
       <c r="B56" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
+        <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-15</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Louis Tomlinson</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Louis Tomlinson - Sunflowers (Official Performance Video) - Louis Tomlinson</v>
+        <v>The Kiffness - Serafino (Singing Cat Song) - The Kiffness</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>The Beaches - Should've Known Better (Official Visualizer)</v>
+        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer)</v>
       </c>
       <c r="B57" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
+        <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-15</v>
@@ -2547,7 +2547,7 @@
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>The Beaches</v>
+        <v>Dennis Lloyd</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>The Beaches - Should've Known Better (Official Visualizer) - The Beaches</v>
+        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer) - Dennis Lloyd</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>The Kiffness - Serafino (Singing Cat Song)</v>
+        <v>Anna Graves - Damn In Love (Official Visualizer)</v>
       </c>
       <c r="B58" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
+        <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-15</v>
@@ -2585,7 +2585,7 @@
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>The Kiffness</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>The Kiffness - Serafino (Singing Cat Song) - The Kiffness</v>
+        <v>Anna Graves - Damn In Love (Official Visualizer) - Anna Graves</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer)</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video)</v>
       </c>
       <c r="B59" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
+        <v>https://www.youtube.com/watch?v=vKzPmy3VUzY</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-15</v>
@@ -2623,7 +2623,7 @@
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Dennis Lloyd</v>
+        <v>Brandon Lake and NICK JONAS</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer) - Dennis Lloyd</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video) - Brandon Lake and NICK JONAS</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Anna Graves - Damn In Love (Official Visualizer)</v>
+        <v>Letdown. - Do It For The Love (Visualizer)</v>
       </c>
       <c r="B60" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
+        <v>https://www.youtube.com/watch?v=vCvZbTEywr8</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-15</v>
@@ -2661,7 +2661,7 @@
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Anna Graves</v>
+        <v>Letdown.</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Anna Graves - Damn In Love (Official Visualizer) - Anna Graves</v>
+        <v>Letdown. - Do It For The Love (Visualizer) - Letdown.</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video)</v>
+        <v>Maroon 5 - Heroine (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=vKzPmy3VUzY</v>
+        <v>https://www.youtube.com/watch?v=izP-4q4YtNw</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-15</v>
@@ -2699,7 +2699,7 @@
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Brandon Lake and NICK JONAS</v>
+        <v>Maroon 5</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video) - Brandon Lake and NICK JONAS</v>
+        <v>Maroon 5 - Heroine (Official Lyric Video) - Maroon 5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Letdown. - Do It For The Love (Visualizer)</v>
+        <v>Olivia O'Brien - I'm Perfect (Official Visualizer)</v>
       </c>
       <c r="B62" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=vCvZbTEywr8</v>
+        <v>https://www.youtube.com/watch?v=leHb8CowDSw</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-15</v>
@@ -2737,7 +2737,7 @@
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Letdown.</v>
+        <v>Olivia O'Brien</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Letdown. - Do It For The Love (Visualizer) - Letdown.</v>
+        <v>Olivia O'Brien - I'm Perfect (Official Visualizer) - Olivia O'Brien</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Maroon 5 - Heroine (Official Lyric Video)</v>
+        <v>ERNEST - What's A Little Rain (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=izP-4q4YtNw</v>
+        <v>https://www.youtube.com/watch?v=U-3AGDH3mf4</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-15</v>
@@ -2775,7 +2775,7 @@
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Maroon 5</v>
+        <v>ERNEST</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Maroon 5 - Heroine (Official Lyric Video) - Maroon 5</v>
+        <v>ERNEST - What's A Little Rain (Official Music Video) - ERNEST</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Olivia O'Brien - I'm Perfect (Official Visualizer)</v>
+        <v>Claire Rosinkranz - Just A Man (Official Audio)</v>
       </c>
       <c r="B64" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=leHb8CowDSw</v>
+        <v>https://www.youtube.com/watch?v=Ta2I3EHXaDI</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-15</v>
@@ -2813,7 +2813,7 @@
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Olivia O'Brien</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Olivia O'Brien - I'm Perfect (Official Visualizer) - Olivia O'Brien</v>
+        <v>Claire Rosinkranz - Just A Man (Official Audio) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>ERNEST - What's A Little Rain (Official Music Video)</v>
+        <v>Halsey - Nothing! (Official Audio)</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=U-3AGDH3mf4</v>
+        <v>https://www.youtube.com/watch?v=PBv71KbKvHA</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-15</v>
@@ -2851,7 +2851,7 @@
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>ERNEST</v>
+        <v>Halsey</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>ERNEST - What's A Little Rain (Official Music Video) - ERNEST</v>
+        <v>Halsey - Nothing! (Official Audio) - Halsey</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Claire Rosinkranz - Just A Man (Official Audio)</v>
+        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=Ta2I3EHXaDI</v>
+        <v>https://www.youtube.com/watch?v=5-f07ca1Zfg</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-15</v>
@@ -2889,7 +2889,7 @@
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Claire Rosinkranz - Just A Man (Official Audio) - Claire Rosinkranz</v>
+        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer) - Zara Larsson</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Halsey - Nothing! (Official Audio)</v>
+        <v>Halsey - Carry the Weight (Official Audio)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=PBv71KbKvHA</v>
+        <v>https://www.youtube.com/watch?v=6MewHp8BX0w</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-15</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Halsey - Nothing! (Official Audio) - Halsey</v>
+        <v>Halsey - Carry the Weight (Official Audio) - Halsey</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer)</v>
+        <v>Bishop Briggs - Blood From A Stone (Official)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=5-f07ca1Zfg</v>
+        <v>https://www.youtube.com/watch?v=3CK6Zbdk-Nw</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-15</v>
@@ -2965,7 +2965,7 @@
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Zara Larsson</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer) - Zara Larsson</v>
+        <v>Bishop Briggs - Blood From A Stone (Official) - Bishop Briggs</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Halsey - Carry the Weight (Official Audio)</v>
+        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=6MewHp8BX0w</v>
+        <v>https://www.youtube.com/watch?v=6-AWBV5FCN4</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-15</v>
@@ -3003,7 +3003,7 @@
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Halsey</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Halsey - Carry the Weight (Official Audio) - Halsey</v>
+        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Bishop Briggs - Blood From A Stone (Official)</v>
+        <v>almost monday - no more regrets (official video)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=3CK6Zbdk-Nw</v>
+        <v>https://www.youtube.com/watch?v=iczsZVZxHKs</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-15</v>
@@ -3041,7 +3041,7 @@
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Bishop Briggs</v>
+        <v>almost monday</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Bishop Briggs - Blood From A Stone (Official) - Bishop Briggs</v>
+        <v>almost monday - no more regrets (official video) - almost monday</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio)</v>
+        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=6-AWBV5FCN4</v>
+        <v>https://www.youtube.com/watch?v=lJM-z0ohbkc</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-15</v>
@@ -3079,7 +3079,7 @@
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Louis Tomlinson</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio) - Louis Tomlinson</v>
+        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>almost monday - no more regrets (official video)</v>
+        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=iczsZVZxHKs</v>
+        <v>https://www.youtube.com/watch?v=6AjhDPwpoLI</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-15</v>
@@ -3117,7 +3117,7 @@
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>almost monday</v>
+        <v>★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>almost monday - no more regrets (official video) - almost monday</v>
+        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video) - ★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video)</v>
+        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=lJM-z0ohbkc</v>
+        <v>https://www.youtube.com/watch?v=F4ndJUCsHKg</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-15</v>
@@ -3155,7 +3155,7 @@
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>NIGHTLY and Fly By Midnight</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video) - FULL CIRCLE BOYS</v>
+        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video) - NIGHTLY and Fly By Midnight</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video)</v>
+        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=6AjhDPwpoLI</v>
+        <v>https://www.youtube.com/watch?v=-IEb-ym7VeQ</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-15</v>
@@ -3193,7 +3193,7 @@
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video) - ★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
+        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer) - Zara Larsson</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video)</v>
+        <v>JORDANA BRYANT - Truth Is (Official Video)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=F4ndJUCsHKg</v>
+        <v>https://www.youtube.com/watch?v=D4meCyyV7SQ</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-15</v>
@@ -3231,7 +3231,7 @@
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>NIGHTLY and Fly By Midnight</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video) - NIGHTLY and Fly By Midnight</v>
+        <v>JORDANA BRYANT - Truth Is (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer)</v>
+        <v>Leanna Crawford - Thank God (Lyric Video)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=-IEb-ym7VeQ</v>
+        <v>https://www.youtube.com/watch?v=QqcSoUft03s</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-15</v>
@@ -3269,7 +3269,7 @@
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Zara Larsson</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer) - Zara Larsson</v>
+        <v>Leanna Crawford - Thank God (Lyric Video) - Leanna Crawford</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>JORDANA BRYANT - Truth Is (Official Video)</v>
+        <v>Girl Tones - Stubborn Mouth (Official Music Video)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=D4meCyyV7SQ</v>
+        <v>https://www.youtube.com/watch?v=_-PyPUWZTDY</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-15</v>
@@ -3307,7 +3307,7 @@
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Jordana Bryant</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>JORDANA BRYANT - Truth Is (Official Video) - Jordana Bryant</v>
+        <v>Girl Tones - Stubborn Mouth (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Leanna Crawford - Thank God (Lyric Video)</v>
+        <v>Tauren Wells - What A Miracle Feels Like (Official Audio)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=QqcSoUft03s</v>
+        <v>https://www.youtube.com/watch?v=ZojFIe4Swmk</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-15</v>
@@ -3345,7 +3345,7 @@
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Leanna Crawford</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Leanna Crawford - Thank God (Lyric Video) - Leanna Crawford</v>
+        <v>Tauren Wells - What A Miracle Feels Like (Official Audio) - Tauren Wells</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Girl Tones - Stubborn Mouth (Official Music Video)</v>
+        <v>Matthew Ifield - Thinking (Official Video)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=_-PyPUWZTDY</v>
+        <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-15</v>
@@ -3383,7 +3383,7 @@
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Girl Tones</v>
+        <v>Matthew Ifield</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Girl Tones - Stubborn Mouth (Official Music Video) - Girl Tones</v>
+        <v>Matthew Ifield - Thinking (Official Video) - Matthew Ifield</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Tauren Wells - What A Miracle Feels Like (Official Audio)</v>
+        <v>Dons - Is There Something</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=ZojFIe4Swmk</v>
+        <v>https://www.youtube.com/watch?v=AgWIjvD-i0E</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-15</v>
@@ -3421,7 +3421,7 @@
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Tauren Wells</v>
+        <v>Dons</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Tauren Wells - What A Miracle Feels Like (Official Audio) - Tauren Wells</v>
+        <v>Dons - Is There Something - Dons</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Matthew Ifield - Thinking (Official Video)</v>
+        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
+        <v>https://www.youtube.com/watch?v=JXW3SOr7C4w</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-15</v>
@@ -3459,7 +3459,7 @@
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Matthew Ifield</v>
+        <v>Recording Academy / GRAMMYs and 3 more</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Matthew Ifield - Thinking (Official Video) - Matthew Ifield</v>
+        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris - Recording Academy / GRAMMYs and 3 more</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Dons - Is There Something</v>
+        <v>Maya Hawke - Lioness (Official Audio)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=AgWIjvD-i0E</v>
+        <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-15</v>
@@ -3497,7 +3497,7 @@
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Dons</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Dons - Is There Something - Dons</v>
+        <v>Maya Hawke - Lioness (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris</v>
+        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=JXW3SOr7C4w</v>
+        <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-15</v>
@@ -3535,7 +3535,7 @@
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Recording Academy / GRAMMYs and 3 more</v>
+        <v>Laufey</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris - Recording Academy / GRAMMYs and 3 more</v>
+        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance - Laufey</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Maya Hawke - Lioness (Official Audio)</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
+        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-15</v>
@@ -3573,7 +3573,7 @@
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Maya Hawke</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Maya Hawke - Lioness (Official Audio) - Maya Hawke</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance</v>
+        <v>DANNA - AGAIN</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
+        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-15</v>
@@ -3611,7 +3611,7 @@
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Laufey</v>
+        <v>Danna</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance - Laufey</v>
+        <v>DANNA - AGAIN - Danna</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
+        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-15</v>
@@ -3649,7 +3649,7 @@
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Keith Urban</v>
+        <v>Armik</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>DANNA - AGAIN</v>
+        <v>EUROPE - One on One (Official Video)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
+        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-15</v>
@@ -3687,7 +3687,7 @@
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Danna</v>
+        <v>Europe</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>DANNA - AGAIN - Danna</v>
+        <v>EUROPE - One on One (Official Video) - Europe</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
+        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-15</v>
@@ -3725,7 +3725,7 @@
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Armik</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>EUROPE - One on One (Official Video)</v>
+        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
+        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-15</v>
@@ -3763,7 +3763,7 @@
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Europe</v>
+        <v>Lady Gaga and Doechii</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>EUROPE - One on One (Official Video) - Europe</v>
+        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video) - Lady Gaga and Doechii</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
+        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-15</v>
@@ -3801,7 +3801,7 @@
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Foo Fighters</v>
+        <v>Muse</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video)</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
+        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-15</v>
@@ -3839,7 +3839,7 @@
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Lady Gaga and Doechii</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video) - Lady Gaga and Doechii</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
+        <v>Shaboozey - Born To Die (Official Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
+        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-15</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Muse</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
+        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
+        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-15</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Scorpions</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Shaboozey - Born To Die (Official Video)</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
+        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-15</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Shaboozey</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
+        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-15</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Scorpions</v>
+        <v>Lolo Zouaï</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
+        <v>Bonnie Tyler - One World One Home</v>
       </c>
       <c r="B96" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
+        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-15</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Meghan Trainor</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
+        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
+        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-15</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Lolo Zouaï</v>
+        <v>Jacob Gurevitsch and Prisma Music Group</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Bonnie Tyler - One World One Home</v>
+        <v>Icona Pop - Dance To This (Official Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
+        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-15</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Bonnie Tyler</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
+        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
+        <v>Michael Jackson - Human Nature (Official Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
+        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-15</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Michael Jackson</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Icona Pop - Dance To This (Official Video)</v>
+        <v>The All-American Rejects - King Kong</v>
       </c>
       <c r="B100" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
+        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-15</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Icona Pop</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
+        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Michael Jackson - Human Nature (Official Video)</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
       </c>
       <c r="B101" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
+        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-15</v>
@@ -4219,7 +4219,7 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Michael Jackson</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>The All-American Rejects - King Kong</v>
+        <v>Hit the Wall</v>
       </c>
       <c r="B102" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
+        <v>https://music.apple.com/us/song/hit-the-wall/6766750846</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-15</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>3 weeks ago</v>
+        <v>Daughter from Hell</v>
       </c>
       <c r="G102" t="str">
-        <v/>
+        <v>3:14</v>
       </c>
       <c r="H102" t="str">
-        <v>The All-American Rejects</v>
+        <v>Gracie Abrams</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/gracie-abrams/1450554836</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/hit-the-wall/6766750836</v>
       </c>
       <c r="L102" t="str">
-        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
+        <v>Hit the Wall - Gracie Abrams</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
+        <v>Ran To Atlanta</v>
       </c>
       <c r="B103" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
+        <v>https://music.apple.com/us/song/ran-to-atlanta/6769568597</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-15</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>3 weeks ago</v>
+        <v>ICEMAN</v>
       </c>
       <c r="G103" t="str">
-        <v/>
+        <v>4:07</v>
       </c>
       <c r="H103" t="str">
-        <v>Ringo Starr</v>
+        <v>Drake</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/ran-to-atlanta/6769568449</v>
       </c>
       <c r="L103" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
+        <v>Ran To Atlanta - Drake</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Hit the Wall</v>
+        <v>Hoe Phase</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/hit-the-wall/6766750846</v>
+        <v>https://music.apple.com/us/song/hoe-phase/6769556949</v>
       </c>
       <c r="D104" t="str">
         <v>2026-05-15</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Daughter from Hell</v>
+        <v>MAID OF HONOUR</v>
       </c>
       <c r="G104" t="str">
-        <v>3:14</v>
+        <v>3:23</v>
       </c>
       <c r="H104" t="str">
-        <v>Gracie Abrams</v>
+        <v>Drake</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/gracie-abrams/1450554836</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/hit-the-wall/6766750836</v>
+        <v>https://music.apple.com/us/album/hoe-phase/6769556940</v>
       </c>
       <c r="L104" t="str">
-        <v>Hit the Wall - Gracie Abrams</v>
+        <v>Hoe Phase - Drake</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Ran To Atlanta</v>
+        <v>I’m Spent</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/ran-to-atlanta/6769568597</v>
+        <v>https://music.apple.com/us/song/im-spent/6769551476</v>
       </c>
       <c r="D105" t="str">
         <v>2026-05-15</v>
@@ -4365,10 +4365,10 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>ICEMAN</v>
+        <v>HABIBTI</v>
       </c>
       <c r="G105" t="str">
-        <v>4:07</v>
+        <v>2:24</v>
       </c>
       <c r="H105" t="str">
         <v>Drake</v>
@@ -4380,21 +4380,21 @@
         <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/ran-to-atlanta/6769568449</v>
+        <v>https://music.apple.com/us/album/im-spent/6769551464</v>
       </c>
       <c r="L105" t="str">
-        <v>Ran To Atlanta - Drake</v>
+        <v>I’m Spent - Drake</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Hoe Phase</v>
+        <v>Abracadabra (Apple Music Live)</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/hoe-phase/6769556949</v>
+        <v>https://music.apple.com/us/song/abracadabra-apple-music-live/6768201780</v>
       </c>
       <c r="D106" t="str">
         <v>2026-05-15</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>MAID OF HONOUR</v>
+        <v>Apple Music Live: MAYHEM Requiem</v>
       </c>
       <c r="G106" t="str">
-        <v>3:23</v>
+        <v>4:04</v>
       </c>
       <c r="H106" t="str">
-        <v>Drake</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/drake/271256</v>
+        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/hoe-phase/6769556940</v>
+        <v>https://music.apple.com/us/album/abracadabra-apple-music-live/6768201775</v>
       </c>
       <c r="L106" t="str">
-        <v>Hoe Phase - Drake</v>
+        <v>Abracadabra (Apple Music Live) - Lady Gaga</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>I’m Spent</v>
+        <v>Falling out of Love</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/im-spent/6769551476</v>
+        <v>https://music.apple.com/us/song/falling-out-of-love/1891161448</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-15</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>HABIBTI</v>
+        <v>Reality Awaits</v>
       </c>
       <c r="G107" t="str">
-        <v>2:24</v>
+        <v>6:21</v>
       </c>
       <c r="H107" t="str">
-        <v>Drake</v>
+        <v>The Strokes</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/drake/271256</v>
+        <v>https://music.apple.com/us/artist/the-strokes/560289</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/im-spent/6769551464</v>
+        <v>https://music.apple.com/us/album/falling-out-of-love/1891161441</v>
       </c>
       <c r="L107" t="str">
-        <v>I’m Spent - Drake</v>
+        <v>Falling out of Love - The Strokes</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Abracadabra (Apple Music Live)</v>
+        <v>Dai Dai</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/abracadabra-apple-music-live/6768201780</v>
+        <v>https://music.apple.com/us/song/dai-dai/6768469976</v>
       </c>
       <c r="D108" t="str">
         <v>2026-05-15</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Apple Music Live: MAYHEM Requiem</v>
+        <v>Dai Dai - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>4:04</v>
+        <v>3:43</v>
       </c>
       <c r="H108" t="str">
-        <v>Lady Gaga</v>
+        <v>Shakira</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
+        <v>https://music.apple.com/us/artist/shakira/889327</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/abracadabra-apple-music-live/6768201775</v>
+        <v>https://music.apple.com/us/album/dai-dai/6768469975</v>
       </c>
       <c r="L108" t="str">
-        <v>Abracadabra (Apple Music Live) - Lady Gaga</v>
+        <v>Dai Dai - Shakira</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Falling out of Love</v>
+        <v>Tu recuerdo</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/falling-out-of-love/1891161448</v>
+        <v>https://music.apple.com/us/song/tu-recuerdo/6763660843</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-15</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Reality Awaits</v>
+        <v>Loco X Volver</v>
       </c>
       <c r="G109" t="str">
-        <v>6:21</v>
+        <v>3:55</v>
       </c>
       <c r="H109" t="str">
-        <v>The Strokes</v>
+        <v>Maluma</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/the-strokes/560289</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/falling-out-of-love/1891161441</v>
+        <v>https://music.apple.com/us/album/tu-recuerdo/1895423065</v>
       </c>
       <c r="L109" t="str">
-        <v>Falling out of Love - The Strokes</v>
+        <v>Tu recuerdo - Maluma</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Dai Dai</v>
+        <v>Traitor (Roles Reversed)</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/dai-dai/6768469976</v>
+        <v>https://music.apple.com/us/song/traitor-roles-reversed/6767665959</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-15</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Dai Dai - Single</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G110" t="str">
-        <v>3:43</v>
+        <v>3:27</v>
       </c>
       <c r="H110" t="str">
-        <v>Shakira</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/shakira/889327</v>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/dai-dai/6768469975</v>
+        <v>https://music.apple.com/us/album/traitor-roles-reversed/6767665713</v>
       </c>
       <c r="L110" t="str">
-        <v>Dai Dai - Shakira</v>
+        <v>Traitor (Roles Reversed) - Megan Moroney</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Tu recuerdo</v>
+        <v>Dirty Rosie</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/tu-recuerdo/6763660843</v>
+        <v>https://music.apple.com/us/song/dirty-rosie/6767044374</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-15</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Loco X Volver</v>
+        <v>Little Miss Twain</v>
       </c>
       <c r="G111" t="str">
-        <v>3:55</v>
+        <v>2:46</v>
       </c>
       <c r="H111" t="str">
-        <v>Maluma</v>
+        <v>Shania Twain</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/shania-twain/129974</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/tu-recuerdo/1895423065</v>
+        <v>https://music.apple.com/us/album/dirty-rosie/1896356105</v>
       </c>
       <c r="L111" t="str">
-        <v>Tu recuerdo - Maluma</v>
+        <v>Dirty Rosie - Shania Twain</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Traitor (Roles Reversed)</v>
+        <v>Like you mean it</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/traitor-roles-reversed/6767665959</v>
+        <v>https://music.apple.com/us/song/like-you-mean-it/6767024693</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-15</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Cloud 9</v>
+        <v>When the lights turn on</v>
       </c>
       <c r="G112" t="str">
-        <v>3:27</v>
+        <v>2:27</v>
       </c>
       <c r="H112" t="str">
-        <v>Megan Moroney</v>
+        <v>MICO</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v>https://music.apple.com/us/artist/mico/1457367370</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/traitor-roles-reversed/6767665713</v>
+        <v>https://music.apple.com/us/album/like-you-mean-it/6767024688</v>
       </c>
       <c r="L112" t="str">
-        <v>Traitor (Roles Reversed) - Megan Moroney</v>
+        <v>Like you mean it - MICO</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Dirty Rosie</v>
+        <v>Hardy (feat. Clairo)</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/dirty-rosie/6767044374</v>
+        <v>https://music.apple.com/us/song/hardy-feat-clairo/1876953073</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-15</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Little Miss Twain</v>
+        <v>American Stories</v>
       </c>
       <c r="G113" t="str">
-        <v>2:46</v>
+        <v>3:53</v>
       </c>
       <c r="H113" t="str">
-        <v>Shania Twain</v>
+        <v>Rostam</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/shania-twain/129974</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/dirty-rosie/1896356105</v>
+        <v>https://music.apple.com/us/album/hardy-feat-clairo/1876952750</v>
       </c>
       <c r="L113" t="str">
-        <v>Dirty Rosie - Shania Twain</v>
+        <v>Hardy (feat. Clairo) - Rostam</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Like you mean it</v>
+        <v>2 Hard 4 The Radio</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/like-you-mean-it/6767024693</v>
+        <v>https://music.apple.com/us/song/2-hard-4-the-radio/6769568610</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-15</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>When the lights turn on</v>
+        <v>ICEMAN</v>
       </c>
       <c r="G114" t="str">
-        <v>2:27</v>
+        <v>3:03</v>
       </c>
       <c r="H114" t="str">
-        <v>MICO</v>
+        <v>Drake</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/mico/1457367370</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/like-you-mean-it/6767024688</v>
+        <v>https://music.apple.com/us/album/2-hard-4-the-radio/6769568449</v>
       </c>
       <c r="L114" t="str">
-        <v>Like you mean it - MICO</v>
+        <v>2 Hard 4 The Radio - Drake</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Hardy (feat. Clairo)</v>
+        <v>Cheetah Print</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/hardy-feat-clairo/1876953073</v>
+        <v>https://music.apple.com/us/song/cheetah-print/6769557055</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-15</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>American Stories</v>
+        <v>MAID OF HONOUR</v>
       </c>
       <c r="G115" t="str">
-        <v>3:53</v>
+        <v>3:22</v>
       </c>
       <c r="H115" t="str">
-        <v>Rostam</v>
+        <v>Drake</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/hardy-feat-clairo/1876952750</v>
+        <v>https://music.apple.com/us/album/cheetah-print/6769556940</v>
       </c>
       <c r="L115" t="str">
-        <v>Hardy (feat. Clairo) - Rostam</v>
+        <v>Cheetah Print - Drake</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>2 Hard 4 The Radio</v>
+        <v>WNBA</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/2-hard-4-the-radio/6769568610</v>
+        <v>https://music.apple.com/us/song/wnba/6769551471</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-15</v>
@@ -4783,10 +4783,10 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>ICEMAN</v>
+        <v>HABIBTI</v>
       </c>
       <c r="G116" t="str">
-        <v>3:03</v>
+        <v>2:58</v>
       </c>
       <c r="H116" t="str">
         <v>Drake</v>
@@ -4798,21 +4798,21 @@
         <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/2-hard-4-the-radio/6769568449</v>
+        <v>https://music.apple.com/us/album/wnba/6769551464</v>
       </c>
       <c r="L116" t="str">
-        <v>2 Hard 4 The Radio - Drake</v>
+        <v>WNBA - Drake</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Cheetah Print</v>
+        <v>Shadow Of A Man (Apple Music Live)</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/cheetah-print/6769557055</v>
+        <v>https://music.apple.com/us/song/shadow-of-a-man-apple-music-live/6768201925</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-15</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>MAID OF HONOUR</v>
+        <v>Apple Music Live: MAYHEM Requiem</v>
       </c>
       <c r="G117" t="str">
-        <v>3:22</v>
+        <v>3:36</v>
       </c>
       <c r="H117" t="str">
-        <v>Drake</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/drake/271256</v>
+        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/cheetah-print/6769556940</v>
+        <v>https://music.apple.com/us/album/shadow-of-a-man-apple-music-live/6768201775</v>
       </c>
       <c r="L117" t="str">
-        <v>Cheetah Print - Drake</v>
+        <v>Shadow Of A Man (Apple Music Live) - Lady Gaga</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>WNBA</v>
+        <v>EPA</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/wnba/6769551471</v>
+        <v>https://music.apple.com/us/song/epa/6768420253</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-15</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>HABIBTI</v>
+        <v>EPA - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>2:58</v>
+        <v>3:22</v>
       </c>
       <c r="H118" t="str">
-        <v>Drake</v>
+        <v>Becky G</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/drake/271256</v>
+        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/wnba/6769551464</v>
+        <v>https://music.apple.com/us/album/epa/6768420251</v>
       </c>
       <c r="L118" t="str">
-        <v>WNBA - Drake</v>
+        <v>EPA - Becky G</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Shadow Of A Man (Apple Music Live)</v>
+        <v>I’m your girl right?</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/shadow-of-a-man-apple-music-live/6768201925</v>
+        <v>https://music.apple.com/us/song/im-your-girl-right/6766440186</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-15</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Apple Music Live: MAYHEM Requiem</v>
+        <v>ESTRUS</v>
       </c>
       <c r="G119" t="str">
-        <v>3:36</v>
+        <v>2:49</v>
       </c>
       <c r="H119" t="str">
-        <v>Lady Gaga</v>
+        <v>Tove Lo</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
+        <v>https://music.apple.com/us/artist/tove-lo/570136838</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/shadow-of-a-man-apple-music-live/6768201775</v>
+        <v>https://music.apple.com/us/album/im-your-girl-right/6766440172</v>
       </c>
       <c r="L119" t="str">
-        <v>Shadow Of A Man (Apple Music Live) - Lady Gaga</v>
+        <v>I’m your girl right? - Tove Lo</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>EPA</v>
+        <v>fuëgo</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/epa/6768420253</v>
+        <v>https://music.apple.com/us/song/fu%C3%ABgo/6767661766</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-15</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>EPA - Single</v>
+        <v>fuëgo - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:22</v>
+        <v>3:46</v>
       </c>
       <c r="H120" t="str">
-        <v>Becky G</v>
+        <v>BNYX®</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
+        <v>https://music.apple.com/us/artist/bnyx/1438325287</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/epa/6768420251</v>
+        <v>https://music.apple.com/us/album/fu%C3%ABgo/6767661604</v>
       </c>
       <c r="L120" t="str">
-        <v>EPA - Becky G</v>
+        <v>fuëgo - BNYX®</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>I’m your girl right?</v>
+        <v>jajaja</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/im-your-girl-right/6766440186</v>
+        <v>https://music.apple.com/us/song/jajaja/6766341319</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-15</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>ESTRUS</v>
+        <v>jajaja - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>2:49</v>
+        <v>2:45</v>
       </c>
       <c r="H121" t="str">
-        <v>Tove Lo</v>
+        <v>Chino Pacas</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/tove-lo/570136838</v>
+        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/im-your-girl-right/6766440172</v>
+        <v>https://music.apple.com/us/album/jajaja/6766341318</v>
       </c>
       <c r="L121" t="str">
-        <v>I’m your girl right? - Tove Lo</v>
+        <v>jajaja - Chino Pacas</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>fuëgo</v>
+        <v>FIND GOD (feat. Dominic Fike)</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/fu%C3%ABgo/6767661766</v>
+        <v>https://music.apple.com/us/song/find-god-feat-dominic-fike/1894315529</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-15</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>fuëgo - Single</v>
+        <v>BULLDAWG</v>
       </c>
       <c r="G122" t="str">
-        <v>3:46</v>
+        <v>3:59</v>
       </c>
       <c r="H122" t="str">
-        <v>BNYX®</v>
+        <v>Kenny Mason</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/bnyx/1438325287</v>
+        <v>https://music.apple.com/us/artist/kenny-mason/79382206</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/fu%C3%ABgo/6767661604</v>
+        <v>https://music.apple.com/us/album/find-god-feat-dominic-fike/1894315301</v>
       </c>
       <c r="L122" t="str">
-        <v>fuëgo - BNYX®</v>
+        <v>FIND GOD (feat. Dominic Fike) - Kenny Mason</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>jajaja</v>
+        <v>FOOL ME ONCE (feat. Leon Thomas)</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/jajaja/6766341319</v>
+        <v>https://music.apple.com/us/song/fool-me-once-feat-leon-thomas/1891467239</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-15</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>jajaja - Single</v>
+        <v>BELOVED: ACT II</v>
       </c>
       <c r="G123" t="str">
-        <v>2:45</v>
+        <v>3:18</v>
       </c>
       <c r="H123" t="str">
-        <v>Chino Pacas</v>
+        <v>GIVĒON</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
+        <v>https://music.apple.com/us/artist/giv%C4%93on/1070668868</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/jajaja/6766341318</v>
+        <v>https://music.apple.com/us/album/fool-me-once-feat-leon-thomas/1891467233</v>
       </c>
       <c r="L123" t="str">
-        <v>jajaja - Chino Pacas</v>
+        <v>FOOL ME ONCE (feat. Leon Thomas) - GIVĒON</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>FIND GOD (feat. Dominic Fike)</v>
+        <v>Shabang</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/find-god-feat-dominic-fike/1894315529</v>
+        <v>https://music.apple.com/us/song/shabang/6769568598</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-15</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>BULLDAWG</v>
+        <v>ICEMAN</v>
       </c>
       <c r="G124" t="str">
-        <v>3:59</v>
+        <v>3:08</v>
       </c>
       <c r="H124" t="str">
-        <v>Kenny Mason</v>
+        <v>Drake</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/kenny-mason/79382206</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/find-god-feat-dominic-fike/1894315301</v>
+        <v>https://music.apple.com/us/album/shabang/6769568449</v>
       </c>
       <c r="L124" t="str">
-        <v>FIND GOD (feat. Dominic Fike) - Kenny Mason</v>
+        <v>Shabang - Drake</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>FOOL ME ONCE (feat. Leon Thomas)</v>
+        <v>Road Trips</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/fool-me-once-feat-leon-thomas/1891467239</v>
+        <v>https://music.apple.com/us/song/road-trips/6769557053</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-15</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>BELOVED: ACT II</v>
+        <v>MAID OF HONOUR</v>
       </c>
       <c r="G125" t="str">
-        <v>3:18</v>
+        <v>4:03</v>
       </c>
       <c r="H125" t="str">
-        <v>GIVĒON</v>
+        <v>Drake</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/giv%C4%93on/1070668868</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/fool-me-once-feat-leon-thomas/1891467233</v>
+        <v>https://music.apple.com/us/album/road-trips/6769556940</v>
       </c>
       <c r="L125" t="str">
-        <v>FOOL ME ONCE (feat. Leon Thomas) - GIVĒON</v>
+        <v>Road Trips - Drake</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Shabang</v>
+        <v>Fortworth</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/shabang/6769568598</v>
+        <v>https://music.apple.com/us/song/fortworth/6769551482</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-15</v>
@@ -5163,10 +5163,10 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>ICEMAN</v>
+        <v>HABIBTI</v>
       </c>
       <c r="G126" t="str">
-        <v>3:08</v>
+        <v>3:51</v>
       </c>
       <c r="H126" t="str">
         <v>Drake</v>
@@ -5178,21 +5178,21 @@
         <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/shabang/6769568449</v>
+        <v>https://music.apple.com/us/album/fortworth/6769551464</v>
       </c>
       <c r="L126" t="str">
-        <v>Shabang - Drake</v>
+        <v>Fortworth - Drake</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Road Trips</v>
+        <v>Repeat It</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/road-trips/6769557053</v>
+        <v>https://music.apple.com/us/song/repeat-it/6764277864</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-15</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>MAID OF HONOUR</v>
+        <v>Repeat It - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>4:03</v>
+        <v>3:11</v>
       </c>
       <c r="H127" t="str">
-        <v>Drake</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/drake/271256</v>
+        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/road-trips/6769556940</v>
+        <v>https://music.apple.com/us/album/repeat-it/1895713789</v>
       </c>
       <c r="L127" t="str">
-        <v>Road Trips - Drake</v>
+        <v>Repeat It - Martin Garrix</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Fortworth</v>
+        <v>Fool Proof</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/fortworth/6769551482</v>
+        <v>https://music.apple.com/us/song/fool-proof/1892466004</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-15</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>HABIBTI</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G128" t="str">
-        <v>3:51</v>
+        <v>2:36</v>
       </c>
       <c r="H128" t="str">
-        <v>Drake</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/drake/271256</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/fortworth/6769551464</v>
+        <v>https://music.apple.com/us/album/fool-proof/1892465981</v>
       </c>
       <c r="L128" t="str">
-        <v>Fortworth - Drake</v>
+        <v>Fool Proof - Cody Johnson</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Repeat It</v>
+        <v>Crisco</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/repeat-it/6764277864</v>
+        <v>https://music.apple.com/us/song/crisco/6763369506</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-15</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Repeat It - Single</v>
+        <v>Crisco - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:11</v>
+        <v>2:56</v>
       </c>
       <c r="H129" t="str">
-        <v>Martin Garrix</v>
+        <v>Miranda Lambert</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
+        <v>https://music.apple.com/us/artist/miranda-lambert/18732261</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/repeat-it/1895713789</v>
+        <v>https://music.apple.com/us/album/crisco/1895284236</v>
       </c>
       <c r="L129" t="str">
-        <v>Repeat It - Martin Garrix</v>
+        <v>Crisco - Miranda Lambert</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Fool Proof</v>
+        <v>Absolution</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/fool-proof/1892466004</v>
+        <v>https://music.apple.com/us/song/absolution/1884987651</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-15</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>Forever Now</v>
       </c>
       <c r="G130" t="str">
-        <v>2:36</v>
+        <v>4:05</v>
       </c>
       <c r="H130" t="str">
-        <v>Cody Johnson</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/fool-proof/1892465981</v>
+        <v>https://music.apple.com/us/album/absolution/1884987638</v>
       </c>
       <c r="L130" t="str">
-        <v>Fool Proof - Cody Johnson</v>
+        <v>Absolution - Switchfoot</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Crisco</v>
+        <v>JESUS IS ALIVE</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/crisco/6763369506</v>
+        <v>https://music.apple.com/us/song/jesus-is-alive/6767694896</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-15</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Crisco - Single</v>
+        <v>JESUS IS ALIVE - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>2:56</v>
+        <v>2:08</v>
       </c>
       <c r="H131" t="str">
-        <v>Miranda Lambert</v>
+        <v>Forrest Frank</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/miranda-lambert/18732261</v>
+        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/crisco/1895284236</v>
+        <v>https://music.apple.com/us/album/jesus-is-alive/6767694895</v>
       </c>
       <c r="L131" t="str">
-        <v>Crisco - Miranda Lambert</v>
+        <v>JESUS IS ALIVE - Forrest Frank</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Absolution</v>
+        <v>Something To Lose</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/absolution/1884987651</v>
+        <v>https://music.apple.com/us/song/something-to-lose/6766964605</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-15</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Forever Now</v>
+        <v>Is This Heaven? - EP</v>
       </c>
       <c r="G132" t="str">
-        <v>4:05</v>
+        <v>2:55</v>
       </c>
       <c r="H132" t="str">
-        <v>Switchfoot</v>
+        <v>STELLA LEFTY</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
+        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/absolution/1884987638</v>
+        <v>https://music.apple.com/us/album/something-to-lose/6766964604</v>
       </c>
       <c r="L132" t="str">
-        <v>Absolution - Switchfoot</v>
+        <v>Something To Lose - STELLA LEFTY</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>JESUS IS ALIVE</v>
+        <v>Too Busy Missing You</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/jesus-is-alive/6767694896</v>
+        <v>https://music.apple.com/us/song/too-busy-missing-you/6766604915</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-15</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>JESUS IS ALIVE - Single</v>
+        <v>Off Campus: The Mixtape</v>
       </c>
       <c r="G133" t="str">
-        <v>2:08</v>
+        <v>3:25</v>
       </c>
       <c r="H133" t="str">
-        <v>Forrest Frank</v>
+        <v>Asha Banks</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
+        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/jesus-is-alive/6767694895</v>
+        <v>https://music.apple.com/us/album/too-busy-missing-you/6766604455</v>
       </c>
       <c r="L133" t="str">
-        <v>JESUS IS ALIVE - Forrest Frank</v>
+        <v>Too Busy Missing You - Asha Banks</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Something To Lose</v>
+        <v>F-Stop Blues (4-track)</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/something-to-lose/6766964605</v>
+        <v>https://music.apple.com/us/song/f-stop-blues-4-track/1883173173</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-15</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Is This Heaven? - EP</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G134" t="str">
-        <v>2:55</v>
+        <v>3:00</v>
       </c>
       <c r="H134" t="str">
-        <v>STELLA LEFTY</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/something-to-lose/6766964604</v>
+        <v>https://music.apple.com/us/album/f-stop-blues-4-track/1883172879</v>
       </c>
       <c r="L134" t="str">
-        <v>Something To Lose - STELLA LEFTY</v>
+        <v>F-Stop Blues (4-track) - Jack Johnson</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Too Busy Missing You</v>
+        <v>PA' LO BONITO</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/too-busy-missing-you/6766604915</v>
+        <v>https://music.apple.com/us/song/pa-lo-bonito/1886496944</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-15</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Off Campus: The Mixtape</v>
+        <v>PA' LO BONITO - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:25</v>
+        <v>3:04</v>
       </c>
       <c r="H135" t="str">
-        <v>Asha Banks</v>
+        <v>Lenny Tavárez</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
+        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/too-busy-missing-you/6766604455</v>
+        <v>https://music.apple.com/us/album/pa-lo-bonito/1886496943</v>
       </c>
       <c r="L135" t="str">
-        <v>Too Busy Missing You - Asha Banks</v>
+        <v>PA' LO BONITO - Lenny Tavárez</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>F-Stop Blues (4-track)</v>
+        <v>LONELY</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/f-stop-blues-4-track/1883173173</v>
+        <v>https://music.apple.com/us/song/lonely/6768757857</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-15</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>DESEO</v>
       </c>
       <c r="G136" t="str">
-        <v>3:00</v>
+        <v>2:58</v>
       </c>
       <c r="H136" t="str">
-        <v>Jack Johnson</v>
+        <v>Katteyes</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/katteyes/1648818255</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/f-stop-blues-4-track/1883172879</v>
+        <v>https://music.apple.com/us/album/lonely/6768757414</v>
       </c>
       <c r="L136" t="str">
-        <v>F-Stop Blues (4-track) - Jack Johnson</v>
+        <v>LONELY - Katteyes</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>PA' LO BONITO</v>
+        <v>Lockup</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/pa-lo-bonito/1886496944</v>
+        <v>https://music.apple.com/us/song/lockup/1894298102</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-15</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>PA' LO BONITO - Single</v>
+        <v>Pure Devotion</v>
       </c>
       <c r="G137" t="str">
-        <v>3:04</v>
+        <v>4:31</v>
       </c>
       <c r="H137" t="str">
-        <v>Lenny Tavárez</v>
+        <v>Overmono</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
+        <v>https://music.apple.com/us/artist/overmono/1129806758</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/pa-lo-bonito/1886496943</v>
+        <v>https://music.apple.com/us/album/lockup/1894298100</v>
       </c>
       <c r="L137" t="str">
-        <v>PA' LO BONITO - Lenny Tavárez</v>
+        <v>Lockup - Overmono</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>LONELY</v>
+        <v>Young</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/lonely/6768757857</v>
+        <v>https://music.apple.com/us/song/young/6767698952</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-15</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>DESEO</v>
+        <v>Young</v>
       </c>
       <c r="G138" t="str">
-        <v>2:58</v>
+        <v>2:46</v>
       </c>
       <c r="H138" t="str">
-        <v>Katteyes</v>
+        <v>Dan + Shay</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/katteyes/1648818255</v>
+        <v>https://music.apple.com/us/artist/dan-shay/690319057</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/lonely/6768757414</v>
+        <v>https://music.apple.com/us/album/young/6767698951</v>
       </c>
       <c r="L138" t="str">
-        <v>LONELY - Katteyes</v>
+        <v>Young - Dan + Shay</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Lockup</v>
+        <v>Parachute</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/lockup/1894298102</v>
+        <v>https://music.apple.com/us/song/parachute/6764119241</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-15</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Pure Devotion</v>
+        <v>Parachute - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>4:31</v>
+        <v>2:52</v>
       </c>
       <c r="H139" t="str">
-        <v>Overmono</v>
+        <v>Maren Morris</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/overmono/1129806758</v>
+        <v>https://music.apple.com/us/artist/maren-morris/262260873</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/lockup/1894298100</v>
+        <v>https://music.apple.com/us/album/parachute/1895648983</v>
       </c>
       <c r="L139" t="str">
-        <v>Lockup - Overmono</v>
+        <v>Parachute - Maren Morris</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Young</v>
+        <v>Little Things</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/young/6767698952</v>
+        <v>https://music.apple.com/us/song/little-things/6766351153</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-15</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Young</v>
+        <v>Little Things - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:46</v>
+        <v>2:55</v>
       </c>
       <c r="H140" t="str">
-        <v>Dan + Shay</v>
+        <v>Kevin Jonas</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/dan-shay/690319057</v>
+        <v>https://music.apple.com/us/artist/kevin-jonas/21138190</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/young/6767698951</v>
+        <v>https://music.apple.com/us/album/little-things/6766350882</v>
       </c>
       <c r="L140" t="str">
-        <v>Young - Dan + Shay</v>
+        <v>Little Things - Kevin Jonas</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Parachute</v>
+        <v>Fish Hunt Golf Drink</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/parachute/6764119241</v>
+        <v>https://music.apple.com/us/song/fish-hunt-golf-drink/6766651884</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-15</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Parachute - Single</v>
+        <v>Signs</v>
       </c>
       <c r="G141" t="str">
-        <v>2:52</v>
+        <v>2:34</v>
       </c>
       <c r="H141" t="str">
-        <v>Maren Morris</v>
+        <v>Luke Bryan</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/maren-morris/262260873</v>
+        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/parachute/1895648983</v>
+        <v>https://music.apple.com/us/album/fish-hunt-golf-drink/6766651878</v>
       </c>
       <c r="L141" t="str">
-        <v>Parachute - Maren Morris</v>
+        <v>Fish Hunt Golf Drink - Luke Bryan</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Little Things</v>
+        <v>PAGEANT STAGE</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/little-things/6766351153</v>
+        <v>https://music.apple.com/us/song/pageant-stage/6764125889</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-15</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Little Things - Single</v>
+        <v>THE EDGE</v>
       </c>
       <c r="G142" t="str">
-        <v>2:55</v>
+        <v>2:52</v>
       </c>
       <c r="H142" t="str">
-        <v>Kevin Jonas</v>
+        <v>Tone Stith</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/kevin-jonas/21138190</v>
+        <v>https://music.apple.com/us/artist/tone-stith/1167717310</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/little-things/6766350882</v>
+        <v>https://music.apple.com/us/album/pageant-stage/1895651504</v>
       </c>
       <c r="L142" t="str">
-        <v>Little Things - Kevin Jonas</v>
+        <v>PAGEANT STAGE - Tone Stith</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Fish Hunt Golf Drink</v>
+        <v>Firestorm</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/fish-hunt-golf-drink/6766651884</v>
+        <v>https://music.apple.com/us/song/firestorm/1868827004</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-15</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Signs</v>
+        <v>Of Earth &amp; Wires</v>
       </c>
       <c r="G143" t="str">
-        <v>2:34</v>
+        <v>2:29</v>
       </c>
       <c r="H143" t="str">
-        <v>Luke Bryan</v>
+        <v>Dua Saleh</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
+        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/fish-hunt-golf-drink/6766651878</v>
+        <v>https://music.apple.com/us/album/firestorm/1868826829</v>
       </c>
       <c r="L143" t="str">
-        <v>Fish Hunt Golf Drink - Luke Bryan</v>
+        <v>Firestorm - Dua Saleh</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>PAGEANT STAGE</v>
+        <v>girl next door</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/pageant-stage/6764125889</v>
+        <v>https://music.apple.com/us/song/girl-next-door/6768077610</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-15</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>THE EDGE</v>
+        <v>girl next door - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>2:52</v>
+        <v>3:18</v>
       </c>
       <c r="H144" t="str">
-        <v>Tone Stith</v>
+        <v>mgk</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/tone-stith/1167717310</v>
+        <v>https://music.apple.com/us/artist/mgk/465954501</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/pageant-stage/1895651504</v>
+        <v>https://music.apple.com/us/album/girl-next-door/6768077609</v>
       </c>
       <c r="L144" t="str">
-        <v>PAGEANT STAGE - Tone Stith</v>
+        <v>girl next door - mgk</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Firestorm</v>
+        <v>BIG DOG</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/firestorm/1868827004</v>
+        <v>https://music.apple.com/us/song/big-dog/1887197046</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-15</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Of Earth &amp; Wires</v>
+        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
       </c>
       <c r="G145" t="str">
-        <v>2:29</v>
+        <v>3:36</v>
       </c>
       <c r="H145" t="str">
-        <v>Dua Saleh</v>
+        <v>Genesis Owusu</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
+        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/firestorm/1868826829</v>
+        <v>https://music.apple.com/us/album/big-dog/1887196431</v>
       </c>
       <c r="L145" t="str">
-        <v>Firestorm - Dua Saleh</v>
+        <v>BIG DOG - Genesis Owusu</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>girl next door</v>
+        <v>idea of love - A COLORS SHOW</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/girl-next-door/6768077610</v>
+        <v>https://music.apple.com/us/song/idea-of-love-a-colors-show/6767667046</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-15</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>girl next door - Single</v>
+        <v>idea of love - A COLORS SHOW - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:18</v>
+        <v>2:34</v>
       </c>
       <c r="H146" t="str">
-        <v>mgk</v>
+        <v>kwn</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/mgk/465954501</v>
+        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/girl-next-door/6768077609</v>
+        <v>https://music.apple.com/us/album/idea-of-love-a-colors-show/6767666835</v>
       </c>
       <c r="L146" t="str">
-        <v>girl next door - mgk</v>
+        <v>idea of love - A COLORS SHOW - kwn</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>BIG DOG</v>
+        <v>Heavy Serenade</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/big-dog/1887197046</v>
+        <v>https://music.apple.com/us/song/heavy-serenade/1892154309</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-15</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
+        <v>Heavy Serenade - EP</v>
       </c>
       <c r="G147" t="str">
-        <v>3:36</v>
+        <v>3:00</v>
       </c>
       <c r="H147" t="str">
-        <v>Genesis Owusu</v>
+        <v>NMIXX</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
+        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/big-dog/1887196431</v>
+        <v>https://music.apple.com/us/album/heavy-serenade/1892154305</v>
       </c>
       <c r="L147" t="str">
-        <v>BIG DOG - Genesis Owusu</v>
+        <v>Heavy Serenade - NMIXX</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>idea of love - A COLORS SHOW</v>
+        <v>ddok ddok ddok</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/idea-of-love-a-colors-show/6767667046</v>
+        <v>https://music.apple.com/us/song/ddok-ddok-ddok/6764203482</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-15</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>idea of love - A COLORS SHOW - Single</v>
+        <v>ddok ddok ddok - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>2:34</v>
+        <v>2:35</v>
       </c>
       <c r="H148" t="str">
-        <v>kwn</v>
+        <v>BOYNEXTDOOR</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
+        <v>https://music.apple.com/us/artist/boynextdoor/1687612559</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/idea-of-love-a-colors-show/6767666835</v>
+        <v>https://music.apple.com/us/album/ddok-ddok-ddok/6764203481</v>
       </c>
       <c r="L148" t="str">
-        <v>idea of love - A COLORS SHOW - kwn</v>
+        <v>ddok ddok ddok - BOYNEXTDOOR</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Heavy Serenade</v>
+        <v>Shut It Down</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/heavy-serenade/1892154309</v>
+        <v>https://music.apple.com/us/song/shut-it-down/6763631128</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-15</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Heavy Serenade - EP</v>
+        <v>Shut It Down - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:00</v>
+        <v>3:32</v>
       </c>
       <c r="H149" t="str">
-        <v>NMIXX</v>
+        <v>Boys Noize</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
+        <v>https://music.apple.com/us/artist/boys-noize/60393190</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/heavy-serenade/1892154305</v>
+        <v>https://music.apple.com/us/album/shut-it-down/1895408470</v>
       </c>
       <c r="L149" t="str">
-        <v>Heavy Serenade - NMIXX</v>
+        <v>Shut It Down - Boys Noize</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>ddok ddok ddok</v>
+        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss)</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/ddok-ddok-ddok/6764203482</v>
+        <v>https://music.apple.com/us/song/together-feat-nikki-nair-jessy-lanza-prentiss/6763207821</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-15</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>ddok ddok ddok - Single</v>
+        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss) - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:35</v>
+        <v>3:18</v>
       </c>
       <c r="H150" t="str">
-        <v>BOYNEXTDOOR</v>
+        <v>The Avalanches</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/boynextdoor/1687612559</v>
+        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/ddok-ddok-ddok/6764203481</v>
+        <v>https://music.apple.com/us/album/together-feat-nikki-nair-jessy-lanza-prentiss/1895215105</v>
       </c>
       <c r="L150" t="str">
-        <v>ddok ddok ddok - BOYNEXTDOOR</v>
+        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss) - The Avalanches</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Shut It Down</v>
+        <v>Can’t Miss You</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/shut-it-down/6763631128</v>
+        <v>https://music.apple.com/us/song/cant-miss-you/1886810999</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-15</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Shut It Down - Single</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="G151" t="str">
-        <v>3:32</v>
+        <v>2:32</v>
       </c>
       <c r="H151" t="str">
-        <v>Boys Noize</v>
+        <v>Sublime</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/boys-noize/60393190</v>
+        <v>https://music.apple.com/us/artist/sublime/63480</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/shut-it-down/1895408470</v>
+        <v>https://music.apple.com/us/album/cant-miss-you/1886810990</v>
       </c>
       <c r="L151" t="str">
-        <v>Shut It Down - Boys Noize</v>
+        <v>Can’t Miss You - Sublime</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss)</v>
+        <v>Razorblades And Runways</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/together-feat-nikki-nair-jessy-lanza-prentiss/6763207821</v>
+        <v>https://music.apple.com/us/song/razorblades-and-runways/1888004809</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-15</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss) - Single</v>
+        <v>Get It Honest</v>
       </c>
       <c r="G152" t="str">
-        <v>3:18</v>
+        <v>3:33</v>
       </c>
       <c r="H152" t="str">
-        <v>The Avalanches</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
+        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/together-feat-nikki-nair-jessy-lanza-prentiss/1895215105</v>
+        <v>https://music.apple.com/us/album/razorblades-and-runways/1888004802</v>
       </c>
       <c r="L152" t="str">
-        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss) - The Avalanches</v>
+        <v>Razorblades And Runways - The Revivalists</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Can’t Miss You</v>
+        <v>Massacre</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/cant-miss-you/1886810999</v>
+        <v>https://music.apple.com/us/song/massacre/1892127745</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-15</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>Massacre - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:32</v>
+        <v>2:55</v>
       </c>
       <c r="H153" t="str">
-        <v>Sublime</v>
+        <v>Murex</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/sublime/63480</v>
+        <v>https://music.apple.com/us/artist/murex/1607430925</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/cant-miss-you/1886810990</v>
+        <v>https://music.apple.com/us/album/massacre/1892127742</v>
       </c>
       <c r="L153" t="str">
-        <v>Can’t Miss You - Sublime</v>
+        <v>Massacre - Murex</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Razorblades And Runways</v>
+        <v>Better That Way</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/razorblades-and-runways/1888004809</v>
+        <v>https://music.apple.com/us/song/better-that-way/6766273199</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-15</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Get It Honest</v>
+        <v>Christian Name</v>
       </c>
       <c r="G154" t="str">
-        <v>3:33</v>
+        <v>3:45</v>
       </c>
       <c r="H154" t="str">
-        <v>The Revivalists</v>
+        <v>Charles Wesley Godwin</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
+        <v>https://music.apple.com/us/artist/charles-wesley-godwin/1441994025</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/razorblades-and-runways/1888004802</v>
+        <v>https://music.apple.com/us/album/better-that-way/1896261802</v>
       </c>
       <c r="L154" t="str">
-        <v>Razorblades And Runways - The Revivalists</v>
+        <v>Better That Way - Charles Wesley Godwin</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Massacre</v>
+        <v>Apollo</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/massacre/1892127745</v>
+        <v>https://music.apple.com/us/song/apollo/6765602431</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-15</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Massacre - Single</v>
+        <v>Apollo - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>2:55</v>
+        <v>3:35</v>
       </c>
       <c r="H155" t="str">
-        <v>Murex</v>
+        <v>Bryant Barnes</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/murex/1607430925</v>
+        <v>https://music.apple.com/us/artist/bryant-barnes/1579668433</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/massacre/1892127742</v>
+        <v>https://music.apple.com/us/album/apollo/6765602369</v>
       </c>
       <c r="L155" t="str">
-        <v>Massacre - Murex</v>
+        <v>Apollo - Bryant Barnes</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Better That Way</v>
+        <v>Infinity (123)</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/better-that-way/6766273199</v>
+        <v>https://music.apple.com/us/song/infinity-123/6763447312</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-15</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Christian Name</v>
+        <v>Infinity (123) - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:45</v>
+        <v>2:19</v>
       </c>
       <c r="H156" t="str">
-        <v>Charles Wesley Godwin</v>
+        <v>December 10</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/charles-wesley-godwin/1441994025</v>
+        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/better-that-way/1896261802</v>
+        <v>https://music.apple.com/us/album/infinity-123/1895320456</v>
       </c>
       <c r="L156" t="str">
-        <v>Better That Way - Charles Wesley Godwin</v>
+        <v>Infinity (123) - December 10</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Apollo</v>
+        <v>Ain't Over Me Yet</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/apollo/6765602431</v>
+        <v>https://music.apple.com/us/song/aint-over-me-yet/6767283811</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-15</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Apollo - Single</v>
+        <v>Cherry Valley Forever</v>
       </c>
       <c r="G157" t="str">
-        <v>3:35</v>
+        <v>3:24</v>
       </c>
       <c r="H157" t="str">
-        <v>Bryant Barnes</v>
+        <v>Carter Faith</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/bryant-barnes/1579668433</v>
+        <v>https://music.apple.com/us/artist/carter-faith/1489205896</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/apollo/6765602369</v>
+        <v>https://music.apple.com/us/album/aint-over-me-yet/1896458169</v>
       </c>
       <c r="L157" t="str">
-        <v>Apollo - Bryant Barnes</v>
+        <v>Ain't Over Me Yet - Carter Faith</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Infinity (123)</v>
+        <v>Where Did You Go</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/infinity-123/6763447312</v>
+        <v>https://music.apple.com/us/song/where-did-you-go/1877958504</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-15</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Infinity (123) - Single</v>
+        <v>Growing Pains (Deluxe)</v>
       </c>
       <c r="G158" t="str">
-        <v>2:19</v>
+        <v>2:47</v>
       </c>
       <c r="H158" t="str">
-        <v>December 10</v>
+        <v>Trousdale</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/infinity-123/1895320456</v>
+        <v>https://music.apple.com/us/album/where-did-you-go/1877958112</v>
       </c>
       <c r="L158" t="str">
-        <v>Infinity (123) - December 10</v>
+        <v>Where Did You Go - Trousdale</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Ain't Over Me Yet</v>
+        <v>I LOVE YOU</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/aint-over-me-yet/6767283811</v>
+        <v>https://music.apple.com/us/song/i-love-you/6766999950</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-15</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Cherry Valley Forever</v>
+        <v>I LOVE YOU - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:24</v>
+        <v>3:11</v>
       </c>
       <c r="H159" t="str">
-        <v>Carter Faith</v>
+        <v>Noga Erez</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/carter-faith/1489205896</v>
+        <v>https://music.apple.com/us/artist/noga-erez/1166657901</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/aint-over-me-yet/1896458169</v>
+        <v>https://music.apple.com/us/album/i-love-you/6766999949</v>
       </c>
       <c r="L159" t="str">
-        <v>Ain't Over Me Yet - Carter Faith</v>
+        <v>I LOVE YOU - Noga Erez</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Where Did You Go</v>
+        <v>Housekeeping</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/where-did-you-go/1877958504</v>
+        <v>https://music.apple.com/us/song/housekeeping/6766290834</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-15</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Growing Pains (Deluxe)</v>
+        <v>Housekeeping - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>2:47</v>
+        <v>3:25</v>
       </c>
       <c r="H160" t="str">
-        <v>Trousdale</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/where-did-you-go/1877958112</v>
+        <v>https://music.apple.com/us/album/housekeeping/6766290823</v>
       </c>
       <c r="L160" t="str">
-        <v>Where Did You Go - Trousdale</v>
+        <v>Housekeeping - Ally Salort</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>I LOVE YOU</v>
+        <v>Surprise Surprise</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/i-love-you/6766999950</v>
+        <v>https://music.apple.com/us/song/surprise-surprise/6764842119</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-15</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>I LOVE YOU - Single</v>
+        <v>Surprise Surprise - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:11</v>
+        <v>2:55</v>
       </c>
       <c r="H161" t="str">
-        <v>Noga Erez</v>
+        <v>Chloe Qisha</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/noga-erez/1166657901</v>
+        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/i-love-you/6766999949</v>
+        <v>https://music.apple.com/us/album/surprise-surprise/1895934408</v>
       </c>
       <c r="L161" t="str">
-        <v>I LOVE YOU - Noga Erez</v>
+        <v>Surprise Surprise - Chloe Qisha</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Housekeeping</v>
+        <v>Dog</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/housekeeping/6766290834</v>
+        <v>https://music.apple.com/us/song/dog/1885967384</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-15</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Housekeeping - Single</v>
+        <v>Gentleman</v>
       </c>
       <c r="G162" t="str">
-        <v>3:25</v>
+        <v>3:08</v>
       </c>
       <c r="H162" t="str">
-        <v>Ally Salort</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
+        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/housekeeping/6766290823</v>
+        <v>https://music.apple.com/us/album/dog/1885967368</v>
       </c>
       <c r="L162" t="str">
-        <v>Housekeeping - Ally Salort</v>
+        <v>Dog - Towa Bird</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Surprise Surprise</v>
+        <v>I Never See Her</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/surprise-surprise/6764842119</v>
+        <v>https://music.apple.com/us/song/i-never-see-her/6764149225</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-15</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Surprise Surprise - Single</v>
+        <v>I Never See Her - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>2:55</v>
+        <v>3:04</v>
       </c>
       <c r="H163" t="str">
-        <v>Chloe Qisha</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
+        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/surprise-surprise/1895934408</v>
+        <v>https://music.apple.com/us/album/i-never-see-her/1895660748</v>
       </c>
       <c r="L163" t="str">
-        <v>Surprise Surprise - Chloe Qisha</v>
+        <v>I Never See Her - Spacey Jane</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Dog</v>
+        <v>No God</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/dog/1885967384</v>
+        <v>https://music.apple.com/us/song/no-god/1891187414</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-15</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Gentleman</v>
+        <v>Alone Together</v>
       </c>
       <c r="G164" t="str">
-        <v>3:08</v>
+        <v>2:45</v>
       </c>
       <c r="H164" t="str">
-        <v>Towa Bird</v>
+        <v>Show Me the Body</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
+        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/dog/1885967368</v>
+        <v>https://music.apple.com/us/album/no-god/1891187411</v>
       </c>
       <c r="L164" t="str">
-        <v>Dog - Towa Bird</v>
+        <v>No God - Show Me the Body</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>I Never See Her</v>
+        <v>burden</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/i-never-see-her/6764149225</v>
+        <v>https://music.apple.com/us/song/burden/6767688180</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-15</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>I Never See Her - Single</v>
+        <v>burden - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:04</v>
+        <v>3:24</v>
       </c>
       <c r="H165" t="str">
-        <v>Spacey Jane</v>
+        <v>Abe Parker</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
+        <v>https://music.apple.com/us/artist/abe-parker/490444584</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/i-never-see-her/1895660748</v>
+        <v>https://music.apple.com/us/album/burden/6767688179</v>
       </c>
       <c r="L165" t="str">
-        <v>I Never See Her - Spacey Jane</v>
+        <v>burden - Abe Parker</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>No God</v>
+        <v>Chico Raro</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/no-god/1891187414</v>
+        <v>https://music.apple.com/us/song/chico-raro/6767713536</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-15</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Alone Together</v>
+        <v>Chico Raro - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>2:45</v>
+        <v>3:17</v>
       </c>
       <c r="H166" t="str">
-        <v>Show Me the Body</v>
+        <v>Arón Piper</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
+        <v>https://music.apple.com/us/artist/ar%C3%B3n-piper/691972942</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/no-god/1891187411</v>
+        <v>https://music.apple.com/us/album/chico-raro/6767713527</v>
       </c>
       <c r="L166" t="str">
-        <v>No God - Show Me the Body</v>
+        <v>Chico Raro - Arón Piper</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>burden</v>
+        <v>What's Done Is Done</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/burden/6767688180</v>
+        <v>https://music.apple.com/us/song/whats-done-is-done/6763088629</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-15</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>burden - Single</v>
+        <v>What's Done Is Done - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:24</v>
+        <v>2:53</v>
       </c>
       <c r="H167" t="str">
-        <v>Abe Parker</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/abe-parker/490444584</v>
+        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/burden/6767688179</v>
+        <v>https://music.apple.com/us/album/whats-done-is-done/1895156626</v>
       </c>
       <c r="L167" t="str">
-        <v>burden - Abe Parker</v>
+        <v>What's Done Is Done - Jorja Smith</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Chico Raro</v>
+        <v>round and round</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/chico-raro/6767713536</v>
+        <v>https://music.apple.com/us/song/round-and-round/1885665987</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-15</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Chico Raro - Single</v>
+        <v>round and round - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:17</v>
+        <v>2:47</v>
       </c>
       <c r="H168" t="str">
-        <v>Arón Piper</v>
+        <v>bbno$</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/ar%C3%B3n-piper/691972942</v>
+        <v>https://music.apple.com/us/artist/bbno%24/1161580951</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/chico-raro/6767713527</v>
+        <v>https://music.apple.com/us/album/round-and-round/1885665982</v>
       </c>
       <c r="L168" t="str">
-        <v>Chico Raro - Arón Piper</v>
+        <v>round and round - bbno$</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>What's Done Is Done</v>
+        <v>Ain’t That Deep</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/whats-done-is-done/6763088629</v>
+        <v>https://music.apple.com/us/song/aint-that-deep/1882831449</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-15</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>What's Done Is Done - Single</v>
+        <v>The Last Balloon</v>
       </c>
       <c r="G169" t="str">
-        <v>2:53</v>
+        <v>2:39</v>
       </c>
       <c r="H169" t="str">
-        <v>Jorja Smith</v>
+        <v>Tank and the Bangas</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
+        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/whats-done-is-done/1895156626</v>
+        <v>https://music.apple.com/us/album/aint-that-deep/1882831446</v>
       </c>
       <c r="L169" t="str">
-        <v>What's Done Is Done - Jorja Smith</v>
+        <v>Ain’t That Deep - Tank and the Bangas</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>round and round</v>
+        <v>Emily</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/round-and-round/1885665987</v>
+        <v>https://music.apple.com/us/song/emily/1893405442</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-15</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>round and round - Single</v>
+        <v>So Much To Say - EP</v>
       </c>
       <c r="G170" t="str">
-        <v>2:47</v>
+        <v>2:35</v>
       </c>
       <c r="H170" t="str">
-        <v>bbno$</v>
+        <v>Daisy Grenade</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/bbno%24/1161580951</v>
+        <v>https://music.apple.com/us/artist/daisy-grenade/1611437131</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/round-and-round/1885665982</v>
+        <v>https://music.apple.com/us/album/emily/1893405440</v>
       </c>
       <c r="L170" t="str">
-        <v>round and round - bbno$</v>
+        <v>Emily - Daisy Grenade</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Ain’t That Deep</v>
+        <v>Hold</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/aint-that-deep/1882831449</v>
+        <v>https://music.apple.com/us/song/hold/6767296480</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-15</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>The Last Balloon</v>
+        <v>Hold - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:39</v>
+        <v>4:07</v>
       </c>
       <c r="H171" t="str">
-        <v>Tank and the Bangas</v>
+        <v>Sabrina Sterling</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
+        <v>https://music.apple.com/us/artist/sabrina-sterling/1577892147</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/aint-that-deep/1882831446</v>
+        <v>https://music.apple.com/us/album/hold/1896462063</v>
       </c>
       <c r="L171" t="str">
-        <v>Ain’t That Deep - Tank and the Bangas</v>
+        <v>Hold - Sabrina Sterling</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Emily</v>
+        <v>Flying Monkey</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/emily/1893405442</v>
+        <v>https://music.apple.com/us/song/flying-monkey/1894351228</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-15</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>So Much To Say - EP</v>
+        <v>Flying Monkey - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:35</v>
+        <v>4:09</v>
       </c>
       <c r="H172" t="str">
-        <v>Daisy Grenade</v>
+        <v>Blue Medusa</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/daisy-grenade/1611437131</v>
+        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/emily/1893405440</v>
+        <v>https://music.apple.com/us/album/flying-monkey/1894351227</v>
       </c>
       <c r="L172" t="str">
-        <v>Emily - Daisy Grenade</v>
+        <v>Flying Monkey - Blue Medusa</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Hold</v>
+        <v>Anything Goes</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/hold/6767296480</v>
+        <v>https://music.apple.com/us/song/anything-goes/1891118972</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-15</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Hold - Single</v>
+        <v>Anything Goes</v>
       </c>
       <c r="G173" t="str">
-        <v>4:07</v>
+        <v>3:00</v>
       </c>
       <c r="H173" t="str">
-        <v>Sabrina Sterling</v>
+        <v>Kaleena Zanders</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/sabrina-sterling/1577892147</v>
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/hold/1896462063</v>
+        <v>https://music.apple.com/us/album/anything-goes/1891118971</v>
       </c>
       <c r="L173" t="str">
-        <v>Hold - Sabrina Sterling</v>
+        <v>Anything Goes - Kaleena Zanders</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Flying Monkey</v>
+        <v>We Are</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/flying-monkey/1894351228</v>
+        <v>https://music.apple.com/us/song/we-are/1894252873</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-15</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Flying Monkey - Single</v>
+        <v>We Are - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>4:09</v>
+        <v>3:33</v>
       </c>
       <c r="H174" t="str">
-        <v>Blue Medusa</v>
+        <v>Adam Ten</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
+        <v>https://music.apple.com/us/artist/adam-ten/1472226854</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/flying-monkey/1894351227</v>
+        <v>https://music.apple.com/us/album/we-are/1894252870</v>
       </c>
       <c r="L174" t="str">
-        <v>Flying Monkey - Blue Medusa</v>
+        <v>We Are - Adam Ten</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Anything Goes</v>
+        <v>It's For the Kids</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/anything-goes/1891118972</v>
+        <v>https://music.apple.com/us/song/its-for-the-kids/1867327679</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-15</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Anything Goes</v>
+        <v>Cursum Perficio</v>
       </c>
       <c r="G175" t="str">
-        <v>3:00</v>
+        <v>4:20</v>
       </c>
       <c r="H175" t="str">
-        <v>Kaleena Zanders</v>
+        <v>Anthrax</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+        <v>https://music.apple.com/us/artist/anthrax/80417</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/anything-goes/1891118971</v>
+        <v>https://music.apple.com/us/album/its-for-the-kids/1867327673</v>
       </c>
       <c r="L175" t="str">
-        <v>Anything Goes - Kaleena Zanders</v>
+        <v>It's For the Kids - Anthrax</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>We Are</v>
+        <v>Pure Ecstasy</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/we-are/1894252873</v>
+        <v>https://music.apple.com/us/song/pure-ecstasy/6762228978</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-15</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>We Are - Single</v>
+        <v>Pure Ecstasy</v>
       </c>
       <c r="G176" t="str">
-        <v>3:33</v>
+        <v>3:05</v>
       </c>
       <c r="H176" t="str">
-        <v>Adam Ten</v>
+        <v>Beartooth</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/adam-ten/1472226854</v>
+        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/we-are/1894252870</v>
+        <v>https://music.apple.com/us/album/pure-ecstasy/1893453878</v>
       </c>
       <c r="L176" t="str">
-        <v>We Are - Adam Ten</v>
+        <v>Pure Ecstasy - Beartooth</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>It's For the Kids</v>
+        <v>Something Wicked</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/its-for-the-kids/1867327679</v>
+        <v>https://music.apple.com/us/song/something-wicked/6766252959</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-15</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Cursum Perficio</v>
+        <v>Something Wicked - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>4:20</v>
+        <v>3:28</v>
       </c>
       <c r="H177" t="str">
-        <v>Anthrax</v>
+        <v>Breaking Benjamin</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/anthrax/80417</v>
+        <v>https://music.apple.com/us/artist/breaking-benjamin/3299379</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/its-for-the-kids/1867327673</v>
+        <v>https://music.apple.com/us/album/something-wicked/1896253678</v>
       </c>
       <c r="L177" t="str">
-        <v>It's For the Kids - Anthrax</v>
+        <v>Something Wicked - Breaking Benjamin</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Pure Ecstasy</v>
+        <v>Feel The Funk</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/pure-ecstasy/6762228978</v>
+        <v>https://music.apple.com/us/song/feel-the-funk/6763294007</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-15</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Pure Ecstasy</v>
+        <v>The Funk EP - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:05</v>
+        <v>3:26</v>
       </c>
       <c r="H178" t="str">
-        <v>Beartooth</v>
+        <v>Riordan</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
+        <v>https://music.apple.com/us/artist/riordan/1517575029</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/pure-ecstasy/1893453878</v>
+        <v>https://music.apple.com/us/album/feel-the-funk/1895251685</v>
       </c>
       <c r="L178" t="str">
-        <v>Pure Ecstasy - Beartooth</v>
+        <v>Feel The Funk - Riordan</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Something Wicked</v>
+        <v>Everglades (Remix)</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/something-wicked/6766252959</v>
+        <v>https://music.apple.com/us/song/everglades-remix/6767719584</v>
       </c>
       <c r="D179" t="str">
         <v>2026-05-15</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Something Wicked - Single</v>
+        <v>Everglades (Remix) - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:28</v>
+        <v>2:42</v>
       </c>
       <c r="H179" t="str">
-        <v>Breaking Benjamin</v>
+        <v>Aziedoesntexist</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/breaking-benjamin/3299379</v>
+        <v>https://music.apple.com/us/artist/aziedoesntexist/1831152556</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/something-wicked/1896253678</v>
+        <v>https://music.apple.com/us/album/everglades-remix/6767719577</v>
       </c>
       <c r="L179" t="str">
-        <v>Something Wicked - Breaking Benjamin</v>
+        <v>Everglades (Remix) - Aziedoesntexist</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Feel The Funk</v>
+        <v>Walk</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/feel-the-funk/6763294007</v>
+        <v>https://music.apple.com/us/song/walk/1892180098</v>
       </c>
       <c r="D180" t="str">
         <v>2026-05-15</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>The Funk EP - Single</v>
+        <v>Walk - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:26</v>
+        <v>2:25</v>
       </c>
       <c r="H180" t="str">
-        <v>Riordan</v>
+        <v>Melodicb</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/riordan/1517575029</v>
+        <v>https://music.apple.com/us/artist/melodicb/1440206517</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/feel-the-funk/1895251685</v>
+        <v>https://music.apple.com/us/album/walk/1892180097</v>
       </c>
       <c r="L180" t="str">
-        <v>Feel The Funk - Riordan</v>
+        <v>Walk - Melodicb</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Everglades (Remix)</v>
+        <v>Volver a Ti</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/everglades-remix/6767719584</v>
+        <v>https://music.apple.com/us/song/volver-a-ti/6766258204</v>
       </c>
       <c r="D181" t="str">
         <v>2026-05-15</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Everglades (Remix) - Single</v>
+        <v>Norteña</v>
       </c>
       <c r="G181" t="str">
-        <v>2:42</v>
+        <v>3:47</v>
       </c>
       <c r="H181" t="str">
-        <v>Aziedoesntexist</v>
+        <v>Julieta Venegas</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/aziedoesntexist/1831152556</v>
+        <v>https://music.apple.com/us/artist/julieta-venegas/302960</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/everglades-remix/6767719577</v>
+        <v>https://music.apple.com/us/album/volver-a-ti/1896255736</v>
       </c>
       <c r="L181" t="str">
-        <v>Everglades (Remix) - Aziedoesntexist</v>
+        <v>Volver a Ti - Julieta Venegas</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Walk</v>
+        <v>Bahamas</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/walk/1892180098</v>
+        <v>https://music.apple.com/us/song/bahamas/6764695848</v>
       </c>
       <c r="D182" t="str">
         <v>2026-05-15</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Walk - Single</v>
+        <v>Bahamas - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:25</v>
+        <v>2:06</v>
       </c>
       <c r="H182" t="str">
-        <v>Melodicb</v>
+        <v>LENCHO</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/melodicb/1440206517</v>
+        <v>https://music.apple.com/us/artist/lencho/1854923384</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/walk/1892180097</v>
+        <v>https://music.apple.com/us/album/bahamas/6764695847</v>
       </c>
       <c r="L182" t="str">
-        <v>Walk - Melodicb</v>
+        <v>Bahamas - LENCHO</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Volver a Ti</v>
+        <v>Same Old Song</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/volver-a-ti/6766258204</v>
+        <v>https://music.apple.com/us/song/same-old-song/6762860685</v>
       </c>
       <c r="D183" t="str">
         <v>2026-05-15</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Norteña</v>
+        <v>Same Old Song - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:47</v>
+        <v>4:12</v>
       </c>
       <c r="H183" t="str">
-        <v>Julieta Venegas</v>
+        <v>Lila Drew</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/julieta-venegas/302960</v>
+        <v>https://music.apple.com/us/artist/lila-drew/1439482732</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/volver-a-ti/1896255736</v>
+        <v>https://music.apple.com/us/album/same-old-song/1895047985</v>
       </c>
       <c r="L183" t="str">
-        <v>Volver a Ti - Julieta Venegas</v>
+        <v>Same Old Song - Lila Drew</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Bahamas</v>
+        <v>gentle</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/bahamas/6764695848</v>
+        <v>https://music.apple.com/us/song/gentle/6762828356</v>
       </c>
       <c r="D184" t="str">
         <v>2026-05-15</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Bahamas - Single</v>
+        <v>gentle - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:06</v>
+        <v>2:48</v>
       </c>
       <c r="H184" t="str">
-        <v>LENCHO</v>
+        <v>Venus Anon</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/lencho/1854923384</v>
+        <v>https://music.apple.com/us/artist/venus-anon/1635970130</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/bahamas/6764695847</v>
+        <v>https://music.apple.com/us/album/gentle/1895031896</v>
       </c>
       <c r="L184" t="str">
-        <v>Bahamas - LENCHO</v>
+        <v>gentle - Venus Anon</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Same Old Song</v>
+        <v>Letters of Your Name</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/same-old-song/6762860685</v>
+        <v>https://music.apple.com/us/song/letters-of-your-name/1892919741</v>
       </c>
       <c r="D185" t="str">
         <v>2026-05-15</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Same Old Song - Single</v>
+        <v>Congratulations</v>
       </c>
       <c r="G185" t="str">
-        <v>4:12</v>
+        <v>3:21</v>
       </c>
       <c r="H185" t="str">
-        <v>Lila Drew</v>
+        <v>Jacob Ungerleider</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/lila-drew/1439482732</v>
+        <v>https://music.apple.com/us/artist/jacob-ungerleider/1460845591</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/same-old-song/1895047985</v>
+        <v>https://music.apple.com/us/album/letters-of-your-name/1892919737</v>
       </c>
       <c r="L185" t="str">
-        <v>Same Old Song - Lila Drew</v>
+        <v>Letters of Your Name - Jacob Ungerleider</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>gentle</v>
+        <v>Seratonin</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/gentle/6762828356</v>
+        <v>https://music.apple.com/us/song/seratonin/6763447428</v>
       </c>
       <c r="D186" t="str">
         <v>2026-05-15</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>gentle - Single</v>
+        <v>Seratonin - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:48</v>
+        <v>1:55</v>
       </c>
       <c r="H186" t="str">
-        <v>Venus Anon</v>
+        <v>James Hype</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/venus-anon/1635970130</v>
+        <v>https://music.apple.com/us/artist/james-hype/925734064</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/gentle/1895031896</v>
+        <v>https://music.apple.com/us/album/seratonin/1895320367</v>
       </c>
       <c r="L186" t="str">
-        <v>gentle - Venus Anon</v>
+        <v>Seratonin - James Hype</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Letters of Your Name</v>
+        <v>A Digital Touch</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/letters-of-your-name/1892919741</v>
+        <v>https://music.apple.com/us/song/a-digital-touch/6765592539</v>
       </c>
       <c r="D187" t="str">
         <v>2026-05-15</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Congratulations</v>
+        <v>A Digital Touch - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:21</v>
+        <v>2:53</v>
       </c>
       <c r="H187" t="str">
-        <v>Jacob Ungerleider</v>
+        <v>Evening Elephants</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/jacob-ungerleider/1460845591</v>
+        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/letters-of-your-name/1892919737</v>
+        <v>https://music.apple.com/us/album/a-digital-touch/1896003252</v>
       </c>
       <c r="L187" t="str">
-        <v>Letters of Your Name - Jacob Ungerleider</v>
+        <v>A Digital Touch - Evening Elephants</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Seratonin</v>
+        <v>Dead Man's Dog</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/seratonin/6763447428</v>
+        <v>https://music.apple.com/us/song/dead-mans-dog/6763447424</v>
       </c>
       <c r="D188" t="str">
         <v>2026-05-15</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Seratonin - Single</v>
+        <v>Aiming Torches At The Sun - EP</v>
       </c>
       <c r="G188" t="str">
-        <v>1:55</v>
+        <v>4:33</v>
       </c>
       <c r="H188" t="str">
-        <v>James Hype</v>
+        <v>Dermot Henry</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/james-hype/925734064</v>
+        <v>https://music.apple.com/us/artist/dermot-henry/1704074611</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/seratonin/1895320367</v>
+        <v>https://music.apple.com/us/album/dead-mans-dog/1895320369</v>
       </c>
       <c r="L188" t="str">
-        <v>Seratonin - James Hype</v>
+        <v>Dead Man's Dog - Dermot Henry</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>A Digital Touch</v>
+        <v>Fault of God</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/a-digital-touch/6765592539</v>
+        <v>https://music.apple.com/us/song/fault-of-god/1887702403</v>
       </c>
       <c r="D189" t="str">
         <v>2026-05-15</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>A Digital Touch - Single</v>
+        <v>Active Child</v>
       </c>
       <c r="G189" t="str">
-        <v>2:53</v>
+        <v>4:13</v>
       </c>
       <c r="H189" t="str">
-        <v>Evening Elephants</v>
+        <v>Active Child</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
+        <v>https://music.apple.com/us/artist/active-child/355288617</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/a-digital-touch/1896003252</v>
+        <v>https://music.apple.com/us/album/fault-of-god/1887701924</v>
       </c>
       <c r="L189" t="str">
-        <v>A Digital Touch - Evening Elephants</v>
+        <v>Fault of God - Active Child</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Dead Man's Dog</v>
+        <v>Zone (feat. Poppy Baskcomb)</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/dead-mans-dog/6763447424</v>
+        <v>https://music.apple.com/us/song/zone-feat-poppy-baskcomb/6763982867</v>
       </c>
       <c r="D190" t="str">
         <v>2026-05-15</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Aiming Torches At The Sun - EP</v>
+        <v>Zone (feat. Poppy Baskcomb) - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>4:33</v>
+        <v>2:56</v>
       </c>
       <c r="H190" t="str">
-        <v>Dermot Henry</v>
+        <v>MK</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/dermot-henry/1704074611</v>
+        <v>https://music.apple.com/us/artist/mk/63097617</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/dead-mans-dog/1895320369</v>
+        <v>https://music.apple.com/us/album/zone-feat-poppy-baskcomb/1895585800</v>
       </c>
       <c r="L190" t="str">
-        <v>Dead Man's Dog - Dermot Henry</v>
+        <v>Zone (feat. Poppy Baskcomb) - MK</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Fault of God</v>
+        <v>Word Vomit</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/fault-of-god/1887702403</v>
+        <v>https://music.apple.com/us/song/word-vomit/1887315297</v>
       </c>
       <c r="D191" t="str">
         <v>2026-05-15</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Active Child</v>
+        <v>Word Vomit - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>4:13</v>
+        <v>2:46</v>
       </c>
       <c r="H191" t="str">
-        <v>Active Child</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/active-child/355288617</v>
+        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/fault-of-god/1887701924</v>
+        <v>https://music.apple.com/us/album/word-vomit/1887315294</v>
       </c>
       <c r="L191" t="str">
-        <v>Fault of God - Active Child</v>
+        <v>Word Vomit - Baby Queen</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Zone (feat. Poppy Baskcomb)</v>
+        <v>Evil in this House</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/zone-feat-poppy-baskcomb/6763982867</v>
+        <v>https://music.apple.com/us/song/evil-in-this-house/1892398371</v>
       </c>
       <c r="D192" t="str">
         <v>2026-05-15</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Zone (feat. Poppy Baskcomb) - Single</v>
+        <v>Necropolitan</v>
       </c>
       <c r="G192" t="str">
-        <v>2:56</v>
+        <v>4:21</v>
       </c>
       <c r="H192" t="str">
-        <v>MK</v>
+        <v>Green Lung</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/mk/63097617</v>
+        <v>https://music.apple.com/us/artist/green-lung/1244071662</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/zone-feat-poppy-baskcomb/1895585800</v>
+        <v>https://music.apple.com/us/album/evil-in-this-house/1892398281</v>
       </c>
       <c r="L192" t="str">
-        <v>Zone (feat. Poppy Baskcomb) - MK</v>
+        <v>Evil in this House - Green Lung</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Word Vomit</v>
+        <v>Heaven on High</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/word-vomit/1887315297</v>
+        <v>https://music.apple.com/us/song/heaven-on-high/1881724153</v>
       </c>
       <c r="D193" t="str">
         <v>2026-05-15</v>
@@ -7709,106 +7709,30 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Word Vomit - Single</v>
+        <v>A Pale White Dot</v>
       </c>
       <c r="G193" t="str">
-        <v>2:46</v>
+        <v>4:19</v>
       </c>
       <c r="H193" t="str">
-        <v>Baby Queen</v>
+        <v>Periphery</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
+        <v>https://music.apple.com/us/artist/periphery/187683869</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/word-vomit/1887315294</v>
+        <v>https://music.apple.com/us/album/heaven-on-high/1881724003</v>
       </c>
       <c r="L193" t="str">
-        <v>Word Vomit - Baby Queen</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="str">
-        <v>Evil in this House</v>
-      </c>
-      <c r="B194" t="str">
-        <v/>
-      </c>
-      <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/evil-in-this-house/1892398371</v>
-      </c>
-      <c r="D194" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E194" t="str">
-        <v/>
-      </c>
-      <c r="F194" t="str">
-        <v>Necropolitan</v>
-      </c>
-      <c r="G194" t="str">
-        <v>4:21</v>
-      </c>
-      <c r="H194" t="str">
-        <v>Green Lung</v>
-      </c>
-      <c r="I194" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/green-lung/1244071662</v>
-      </c>
-      <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/evil-in-this-house/1892398281</v>
-      </c>
-      <c r="L194" t="str">
-        <v>Evil in this House - Green Lung</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="str">
-        <v>Heaven on High</v>
-      </c>
-      <c r="B195" t="str">
-        <v/>
-      </c>
-      <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/heaven-on-high/1881724153</v>
-      </c>
-      <c r="D195" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E195" t="str">
-        <v/>
-      </c>
-      <c r="F195" t="str">
-        <v>A Pale White Dot</v>
-      </c>
-      <c r="G195" t="str">
-        <v>4:19</v>
-      </c>
-      <c r="H195" t="str">
-        <v>Periphery</v>
-      </c>
-      <c r="I195" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/periphery/187683869</v>
-      </c>
-      <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/heaven-on-high/1881724003</v>
-      </c>
-      <c r="L195" t="str">
         <v>Heaven on High - Periphery</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L195"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L193"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-05-week03/titles.xlsx
+++ b/data/global/2026-05-week03/titles.xlsx
@@ -667,7 +667,7 @@
         <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Paris Paloma - Stem the Flow [Official Music Video]</v>
       </c>
       <c r="B41" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>

--- a/data/global/2026-05-week03/titles.xlsx
+++ b/data/global/2026-05-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B4" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B5" t="str">
-        <v>2 months ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 months ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B6" t="str">
-        <v>2 months ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 months ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
       </c>
       <c r="B7" t="str">
-        <v>2 months ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 months ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B9" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Ellise - Liplock (Official Music Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Tori Kelly - Dive (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
       </c>
       <c r="B13" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
       </c>
       <c r="B14" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Michael Schulte - Lovesick (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Caity Baser - Holiday Song (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
       </c>
       <c r="B18" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Porches- HABIT (Official Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Charli xcx - Rock Music (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>Jon Batiste - Alla Blues (Audio)</v>
       </c>
       <c r="B21" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
       </c>
       <c r="B24" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Tori Kelly - Control (Official Visualizer)</v>
       </c>
       <c r="B25" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Bea Miller - depressed on the internet (Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
       </c>
       <c r="B27" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Madison Beer - free (Official Audio)</v>
       </c>
       <c r="B28" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Tori Kelly - Dive (Official Audio)</v>
       </c>
       <c r="B29" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Jeremy Camp - Reflector (Official Audio)</v>
       </c>
       <c r="B30" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
       </c>
       <c r="B31" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Ashley Cooke - high school sweetheart</v>
       </c>
       <c r="B32" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Ari Abdul - Ego (Visualizer)</v>
       </c>
       <c r="B33" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=L0FjVr6LpVU</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Quinn XCII - HOOPLA (Official Music Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=eNbGA1pgmFk</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Madison Beer - lovergirl (Official Music Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=q4lU1N3oqYQ</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>David J - WHAT IF I'M IN LOVE (Official Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=-SF7Hm_ikaY</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>The Last Dinner Party - Big Dog (On The Road)</v>
       </c>
       <c r="B37" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>OCEAN ALLEY - HOLD ON (Official Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Dagny - Closet Disco Queen (Lyric Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>Purple Disco Machine - Disco Cherry (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Paris Paloma - Stem the Flow [Official Music Video]</v>
       </c>
       <c r="B41" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Lucy Blue - Who you love (Visualiser)</v>
       </c>
       <c r="B42" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026)</v>
       </c>
       <c r="B43" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Aaron Frazer - It's A Shame (Official Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Holly Humberstone - White Noise (Live) | Presented By Spotify</v>
       </c>
       <c r="B45" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>DANNA - OUT OF MY BODY</v>
       </c>
       <c r="B46" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=uW_Ye0kQ9Ac</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>The Rolling Stones - In The Stars (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser)</v>
       </c>
       <c r="B48" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
       </c>
       <c r="B49" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Rick Astley - Raindrops (Official Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>Jessie J - THREW IT AWAY (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>The Takes - Ain't Love (Lyric Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary</v>
       </c>
       <c r="B53" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Louis Tomlinson - Sunflowers (Official Performance Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>The Beaches - Should've Known Better (Official Visualizer)</v>
       </c>
       <c r="B55" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>The Kiffness - Serafino (Singing Cat Song)</v>
       </c>
       <c r="B56" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer)</v>
       </c>
       <c r="B57" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Anna Graves - Damn In Love (Official Visualizer)</v>
       </c>
       <c r="B58" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>Brandon Lake, Nick Jonas - The Author (Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=vKzPmy3VUzY</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Letdown. - Do It For The Love (Visualizer)</v>
       </c>
       <c r="B60" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=vCvZbTEywr8</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>Maroon 5 - Heroine (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=izP-4q4YtNw</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Olivia O'Brien - I'm Perfect (Official Visualizer)</v>
       </c>
       <c r="B62" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=leHb8CowDSw</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>ERNEST - What's A Little Rain (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=U-3AGDH3mf4</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Claire Rosinkranz - Just A Man (Official Audio)</v>
       </c>
       <c r="B64" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=Ta2I3EHXaDI</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Halsey - Nothing! (Official Audio)</v>
       </c>
       <c r="B65" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=PBv71KbKvHA</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B66" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=5-f07ca1Zfg</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Halsey - Carry the Weight (Official Audio)</v>
       </c>
       <c r="B67" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=6MewHp8BX0w</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Bishop Briggs - Blood From A Stone (Official)</v>
       </c>
       <c r="B68" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=3CK6Zbdk-Nw</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio)</v>
       </c>
       <c r="B69" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=6-AWBV5FCN4</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>almost monday - no more regrets (official video)</v>
       </c>
       <c r="B70" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=iczsZVZxHKs</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=lJM-z0ohbkc</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=6AjhDPwpoLI</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=F4ndJUCsHKg</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=-IEb-ym7VeQ</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>JORDANA BRYANT - Truth Is (Official Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=D4meCyyV7SQ</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>Leanna Crawford - Thank God (Lyric Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=QqcSoUft03s</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Girl Tones - Stubborn Mouth (Official Music Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=_-PyPUWZTDY</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Tauren Wells - What A Miracle Feels Like (Official Audio)</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=ZojFIe4Swmk</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>Matthew Ifield - Thinking (Official Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Dons - Is There Something</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=AgWIjvD-i0E</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=JXW3SOr7C4w</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Maya Hawke - Lioness (Official Audio)</v>
       </c>
       <c r="B82" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>DANNA - AGAIN</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>EUROPE - One on One (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Lady Gaga, Doechii - RUNWAY (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>Shaboozey - Born To Die (Official Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
       </c>
       <c r="B93" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>Meghan Trainor - Shimmer (Official Music Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Bonnie Tyler - One World One Home</v>
       </c>
       <c r="B96" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
       </c>
       <c r="B97" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>Icona Pop - Dance To This (Official Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>Michael Jackson - Human Nature (Official Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>The All-American Rejects - King Kong</v>
       </c>
       <c r="B100" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Ringo Starr - Long Long Road (Official Music Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/global/2026-05-week03/titles.xlsx
+++ b/data/global/2026-05-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B4" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B5" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B6" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
       </c>
       <c r="B7" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B9" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Ellise - Liplock (Official Music Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Tori Kelly - Dive (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
       </c>
       <c r="B13" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
       </c>
       <c r="B14" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Michael Schulte - Lovesick (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Caity Baser - Holiday Song (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
       </c>
       <c r="B18" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Porches- HABIT (Official Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Charli xcx - Rock Music (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>Jon Batiste - Alla Blues (Audio)</v>
       </c>
       <c r="B21" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
       </c>
       <c r="B24" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Tori Kelly - Control (Official Visualizer)</v>
       </c>
       <c r="B25" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Bea Miller - depressed on the internet (Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
       </c>
       <c r="B27" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Madison Beer - free (Official Audio)</v>
       </c>
       <c r="B28" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Tori Kelly - Dive (Official Audio)</v>
       </c>
       <c r="B29" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Jeremy Camp - Reflector (Official Audio)</v>
       </c>
       <c r="B30" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
       </c>
       <c r="B31" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Ashley Cooke - high school sweetheart</v>
       </c>
       <c r="B32" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Ari Abdul - Ego (Visualizer)</v>
       </c>
       <c r="B33" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=L0FjVr6LpVU</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Quinn XCII - HOOPLA (Official Music Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=eNbGA1pgmFk</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Madison Beer - lovergirl (Official Music Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=q4lU1N3oqYQ</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>David J - WHAT IF I'M IN LOVE (Official Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=-SF7Hm_ikaY</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>The Last Dinner Party - Big Dog (On The Road)</v>
       </c>
       <c r="B37" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>OCEAN ALLEY - HOLD ON (Official Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Dagny - Closet Disco Queen (Lyric Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>Purple Disco Machine - Disco Cherry (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Paris Paloma - Stem the Flow [Official Music Video]</v>
       </c>
       <c r="B41" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Lucy Blue - Who you love (Visualiser)</v>
       </c>
       <c r="B42" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026)</v>
       </c>
       <c r="B43" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Aaron Frazer - It's A Shame (Official Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Holly Humberstone - White Noise (Live) | Presented By Spotify</v>
       </c>
       <c r="B45" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>DANNA - OUT OF MY BODY</v>
       </c>
       <c r="B46" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=uW_Ye0kQ9Ac</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>The Rolling Stones - In The Stars (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser)</v>
       </c>
       <c r="B48" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
       </c>
       <c r="B49" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Rick Astley - Raindrops (Official Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>Jessie J - THREW IT AWAY (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>The Takes - Ain't Love (Lyric Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary</v>
       </c>
       <c r="B53" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Louis Tomlinson - Sunflowers (Official Performance Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>The Beaches - Should've Known Better (Official Visualizer)</v>
       </c>
       <c r="B55" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>The Kiffness - Serafino (Singing Cat Song)</v>
       </c>
       <c r="B56" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer)</v>
       </c>
       <c r="B57" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Anna Graves - Damn In Love (Official Visualizer)</v>
       </c>
       <c r="B58" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>Brandon Lake, Nick Jonas - The Author (Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=vKzPmy3VUzY</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Letdown. - Do It For The Love (Visualizer)</v>
       </c>
       <c r="B60" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=vCvZbTEywr8</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>Maroon 5 - Heroine (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=izP-4q4YtNw</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Olivia O'Brien - I'm Perfect (Official Visualizer)</v>
       </c>
       <c r="B62" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=leHb8CowDSw</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>ERNEST - What's A Little Rain (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=U-3AGDH3mf4</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Claire Rosinkranz - Just A Man (Official Audio)</v>
       </c>
       <c r="B64" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=Ta2I3EHXaDI</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Halsey - Nothing! (Official Audio)</v>
       </c>
       <c r="B65" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=PBv71KbKvHA</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B66" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=5-f07ca1Zfg</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Halsey - Carry the Weight (Official Audio)</v>
       </c>
       <c r="B67" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=6MewHp8BX0w</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Bishop Briggs - Blood From A Stone (Official)</v>
       </c>
       <c r="B68" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=3CK6Zbdk-Nw</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio)</v>
       </c>
       <c r="B69" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=6-AWBV5FCN4</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>almost monday - no more regrets (official video)</v>
       </c>
       <c r="B70" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=iczsZVZxHKs</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=lJM-z0ohbkc</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=6AjhDPwpoLI</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=F4ndJUCsHKg</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=-IEb-ym7VeQ</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>JORDANA BRYANT - Truth Is (Official Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=D4meCyyV7SQ</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>Leanna Crawford - Thank God (Lyric Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=QqcSoUft03s</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Girl Tones - Stubborn Mouth (Official Music Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=_-PyPUWZTDY</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Tauren Wells - What A Miracle Feels Like (Official Audio)</v>
       </c>
       <c r="B78" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=ZojFIe4Swmk</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>Matthew Ifield - Thinking (Official Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Dons - Is There Something</v>
       </c>
       <c r="B80" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=AgWIjvD-i0E</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris</v>
       </c>
       <c r="B81" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=JXW3SOr7C4w</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Maya Hawke - Lioness (Official Audio)</v>
       </c>
       <c r="B82" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance</v>
       </c>
       <c r="B83" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>DANNA - AGAIN</v>
       </c>
       <c r="B85" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>EUROPE - One on One (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
       </c>
       <c r="B88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Lady Gaga, Doechii - RUNWAY (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
       </c>
       <c r="B90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
       </c>
       <c r="B91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>Shaboozey - Born To Die (Official Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
       </c>
       <c r="B93" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>Meghan Trainor - Shimmer (Official Music Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Bonnie Tyler - One World One Home</v>
       </c>
       <c r="B96" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
       </c>
       <c r="B97" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>Icona Pop - Dance To This (Official Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>Michael Jackson - Human Nature (Official Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>The All-American Rejects - King Kong</v>
       </c>
       <c r="B100" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Ringo Starr - Long Long Road (Official Music Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/global/2026-05-week03/titles.xlsx
+++ b/data/global/2026-05-week03/titles.xlsx
@@ -1769,7 +1769,7 @@
         <v>The Last Dinner Party - Big Dog (On The Road)</v>
       </c>
       <c r="B37" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>

--- a/data/global/2026-05-week03/titles.xlsx
+++ b/data/global/2026-05-week03/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1085,19 +1085,19 @@
         <v>Porches- HABIT (Official Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,19 +1123,19 @@
         <v>Charli xcx - Rock Music (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,19 +1161,19 @@
         <v>Jon Batiste - Alla Blues (Audio)</v>
       </c>
       <c r="B21" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,19 +1199,19 @@
         <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,19 +1237,19 @@
         <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,19 +1275,19 @@
         <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
       </c>
       <c r="B24" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,19 +1313,19 @@
         <v>Tori Kelly - Control (Official Visualizer)</v>
       </c>
       <c r="B25" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,19 +1351,19 @@
         <v>Bea Miller - depressed on the internet (Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,19 +1389,19 @@
         <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
       </c>
       <c r="B27" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,19 +1427,19 @@
         <v>Madison Beer - free (Official Audio)</v>
       </c>
       <c r="B28" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,19 +1465,19 @@
         <v>Tori Kelly - Dive (Official Audio)</v>
       </c>
       <c r="B29" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,19 +1503,19 @@
         <v>Jeremy Camp - Reflector (Official Audio)</v>
       </c>
       <c r="B30" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,19 +1541,19 @@
         <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
       </c>
       <c r="B31" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,19 +1579,19 @@
         <v>Ashley Cooke - high school sweetheart</v>
       </c>
       <c r="B32" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,19 +1617,19 @@
         <v>Ari Abdul - Ego (Visualizer)</v>
       </c>
       <c r="B33" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=L0FjVr6LpVU</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,19 +1655,19 @@
         <v>Quinn XCII - HOOPLA (Official Music Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=eNbGA1pgmFk</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,19 +1693,19 @@
         <v>Madison Beer - lovergirl (Official Music Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=q4lU1N3oqYQ</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,19 +1731,19 @@
         <v>David J - WHAT IF I'M IN LOVE (Official Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=-SF7Hm_ikaY</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2111,19 +2111,19 @@
         <v>DANNA - OUT OF MY BODY</v>
       </c>
       <c r="B46" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=uW_Ye0kQ9Ac</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=vKzPmy3VUzY</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=vCvZbTEywr8</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=izP-4q4YtNw</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=leHb8CowDSw</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=U-3AGDH3mf4</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=Ta2I3EHXaDI</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=PBv71KbKvHA</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=5-f07ca1Zfg</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=6MewHp8BX0w</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=3CK6Zbdk-Nw</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=6-AWBV5FCN4</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=iczsZVZxHKs</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=lJM-z0ohbkc</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=6AjhDPwpoLI</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=F4ndJUCsHKg</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=-IEb-ym7VeQ</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=D4meCyyV7SQ</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=QqcSoUft03s</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=_-PyPUWZTDY</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=ZojFIe4Swmk</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=AgWIjvD-i0E</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=JXW3SOr7C4w</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/hit-the-wall/6766750846</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/ran-to-atlanta/6769568597</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/hoe-phase/6769556949</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/im-spent/6769551476</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/abracadabra-apple-music-live/6768201780</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/falling-out-of-love/1891161448</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/dai-dai/6768469976</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/tu-recuerdo/6763660843</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/traitor-roles-reversed/6767665959</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/dirty-rosie/6767044374</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/like-you-mean-it/6767024693</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/hardy-feat-clairo/1876953073</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/2-hard-4-the-radio/6769568610</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/cheetah-print/6769557055</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/wnba/6769551471</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/shadow-of-a-man-apple-music-live/6768201925</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/epa/6768420253</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/im-your-girl-right/6766440186</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/fu%C3%ABgo/6767661766</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/jajaja/6766341319</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/find-god-feat-dominic-fike/1894315529</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/fool-me-once-feat-leon-thomas/1891467239</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/shabang/6769568598</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/road-trips/6769557053</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/fortworth/6769551482</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/repeat-it/6764277864</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/fool-proof/1892466004</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/crisco/6763369506</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/absolution/1884987651</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/jesus-is-alive/6767694896</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/something-to-lose/6766964605</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/too-busy-missing-you/6766604915</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/f-stop-blues-4-track/1883173173</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/pa-lo-bonito/1886496944</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/lonely/6768757857</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/lockup/1894298102</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/young/6767698952</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/parachute/6764119241</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/little-things/6766351153</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/fish-hunt-golf-drink/6766651884</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/pageant-stage/6764125889</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/firestorm/1868827004</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/girl-next-door/6768077610</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/big-dog/1887197046</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/idea-of-love-a-colors-show/6767667046</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/heavy-serenade/1892154309</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/ddok-ddok-ddok/6764203482</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/shut-it-down/6763631128</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/together-feat-nikki-nair-jessy-lanza-prentiss/6763207821</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/cant-miss-you/1886810999</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/razorblades-and-runways/1888004809</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/massacre/1892127745</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/better-that-way/6766273199</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/apollo/6765602431</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/infinity-123/6763447312</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/aint-over-me-yet/6767283811</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/where-did-you-go/1877958504</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/i-love-you/6766999950</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/housekeeping/6766290834</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/surprise-surprise/6764842119</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/dog/1885967384</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/i-never-see-her/6764149225</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/no-god/1891187414</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/burden/6767688180</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/chico-raro/6767713536</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/whats-done-is-done/6763088629</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/round-and-round/1885665987</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/aint-that-deep/1882831449</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/emily/1893405442</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/hold/6767296480</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/flying-monkey/1894351228</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/anything-goes/1891118972</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/we-are/1894252873</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/its-for-the-kids/1867327679</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/pure-ecstasy/6762228978</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/something-wicked/6766252959</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/feel-the-funk/6763294007</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/everglades-remix/6767719584</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/walk/1892180098</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/volver-a-ti/6766258204</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/bahamas/6764695848</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/same-old-song/6762860685</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/gentle/6762828356</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/letters-of-your-name/1892919741</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/seratonin/6763447428</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/a-digital-touch/6765592539</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/dead-mans-dog/6763447424</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/fault-of-god/1887702403</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/zone-feat-poppy-baskcomb/6763982867</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/word-vomit/1887315297</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/evil-in-this-house/1892398371</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/heaven-on-high/1881724153</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E193" t="str">
         <v/>

--- a/data/global/2026-05-week03/titles.xlsx
+++ b/data/global/2026-05-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L193"/>
+  <dimension ref="A1:L194"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Harry Styles - Dance No More (Official Video)</v>
+        <v>קרולינה ואורי בראונר כנרות – תפילה</v>
       </c>
       <c r="B2" t="str">
-        <v>8 days ago</v>
+        <v>2026-05-16</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
+        <v>https://yosmusic.com/%d7%a7%d7%a8%d7%95%d7%9c%d7%99%d7%a0%d7%94-%d7%95%d7%90%d7%95%d7%a8%d7%99-%d7%91%d7%a8%d7%90%d7%95%d7%a0%d7%a8-%d7%9b%d7%a0%d7%a8%d7%95%d7%aa-%d7%aa%d7%a4%d7%99%d7%9c%d7%94/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-16</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>8 days ago</v>
+        <v>השיר "תפילה” של קרולינה הוא מהסוג שלא מנסה להרשים בכוח אלא לחלחל לאט. זוהי בלדת פופ־גרוב עדינה ואינטימית, שנשענת פחות על דרמה גדולה ויותר על אמת רגשית חשופה. קרולינה נשארת כאן מאוד “היא”: סאונד חם, אנושי, מלא נשימה ונוכחות, עם</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Harry Styles</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
+        <v>קרולינה ואורי בראונר כנרות – תפילה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
+        <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
+        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-16</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Eagles</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
+        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>6 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
+        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-16</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>6 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Nora Fatehi</v>
+        <v>Eagles</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B5" t="str">
-        <v>2 months ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
+        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-16</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 months ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Nora Fatehi</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B6" t="str">
-        <v>2 months ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
+        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-16</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 months ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Eurovision Song Contest and Alis</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B7" t="str">
-        <v>2 months ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
+        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-16</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 months ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Eurovision Song Contest and Alis</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video)</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
       </c>
       <c r="B8" t="str">
-        <v>7 days ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
+        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-16</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>7 days ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>The Head And The Heart</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
+        <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>9 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
+        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-16</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>9 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Simply Red</v>
+        <v>The Head And The Heart</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
+        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video)</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B10" t="str">
-        <v>5 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
+        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-16</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>5 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Talking Heads</v>
+        <v>Simply Red</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Ellise - Liplock (Official Music Video)</v>
+        <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>7 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
+        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-16</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>7 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Ellise</v>
+        <v>Talking Heads</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
+        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Tori Kelly - Dive (Official Music Video)</v>
+        <v>Ellise - Liplock (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
+        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-16</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Tori Kelly</v>
+        <v>Ellise</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
+        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
+        <v>Tori Kelly - Dive (Official Music Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
+        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-16</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>David Gilmour</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024) - David Gilmour</v>
+        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
+        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
       </c>
       <c r="B14" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
+        <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-16</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Scorpions</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022) - Scorpions</v>
+        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024) - David Gilmour</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
+        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
       </c>
       <c r="B15" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
+        <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-16</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Claire Leslie</v>
+        <v>Scorpions</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Claire Leslie - Passenger Seat (Official Music Video) - Claire Leslie</v>
+        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Michael Schulte - Lovesick (Official Video)</v>
+        <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
+        <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-16</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Michael Schulte</v>
+        <v>Claire Leslie</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Michael Schulte - Lovesick (Official Video) - Michael Schulte</v>
+        <v>Claire Leslie - Passenger Seat (Official Music Video) - Claire Leslie</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Caity Baser - Holiday Song (Official Video)</v>
+        <v>Michael Schulte - Lovesick (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
+        <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-16</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Caity Baser</v>
+        <v>Michael Schulte</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Caity Baser - Holiday Song (Official Video) - Caity Baser</v>
+        <v>Michael Schulte - Lovesick (Official Video) - Michael Schulte</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
+        <v>Caity Baser - Holiday Song (Official Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
+        <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-16</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Sam Fischer</v>
+        <v>Caity Baser</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser) - Sam Fischer</v>
+        <v>Caity Baser - Holiday Song (Official Video) - Caity Baser</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Porches- HABIT (Official Video)</v>
+        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
       </c>
       <c r="B19" t="str">
-        <v>8 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
+        <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-16</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>8 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Porches</v>
+        <v>Sam Fischer</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Porches- HABIT (Official Video) - Porches</v>
+        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser) - Sam Fischer</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Charli xcx - Rock Music (Official Video)</v>
+        <v>Porches- HABIT (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
+        <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-16</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Charli xcx</v>
+        <v>Porches</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Charli xcx - Rock Music (Official Video) - Charli xcx</v>
+        <v>Porches- HABIT (Official Video) - Porches</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Jon Batiste - Alla Blues (Audio)</v>
+        <v>Charli xcx - Rock Music (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
+        <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-16</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Jon Batiste</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Jon Batiste - Alla Blues (Audio) - Jon Batiste</v>
+        <v>Charli xcx - Rock Music (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
+        <v>Jon Batiste - Alla Blues (Audio)</v>
       </c>
       <c r="B22" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
+        <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-16</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Tigirlily Gold</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Tigirlily Gold - I Do or Die (Official Music Video) - Tigirlily Gold</v>
+        <v>Jon Batiste - Alla Blues (Audio) - Jon Batiste</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
+        <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
+        <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-16</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Tigirlily Gold</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video) - PAUL McCARTNEY</v>
+        <v>Tigirlily Gold - I Do or Die (Official Music Video) - Tigirlily Gold</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
+        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
+        <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-16</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Bruno Mars</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video] - Bruno Mars</v>
+        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Tori Kelly - Control (Official Visualizer)</v>
+        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
       </c>
       <c r="B25" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
+        <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-16</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Tori Kelly</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Tori Kelly - Control (Official Visualizer) - Tori Kelly</v>
+        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Bea Miller - depressed on the internet (Lyric Video)</v>
+        <v>Tori Kelly - Control (Official Visualizer)</v>
       </c>
       <c r="B26" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
+        <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-16</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>bea miller</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Bea Miller - depressed on the internet (Lyric Video) - bea miller</v>
+        <v>Tori Kelly - Control (Official Visualizer) - Tori Kelly</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
+        <v>Bea Miller - depressed on the internet (Lyric Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
+        <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-16</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>The Chainsmokers</v>
+        <v>bea miller</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer) - The Chainsmokers</v>
+        <v>Bea Miller - depressed on the internet (Lyric Video) - bea miller</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Madison Beer - free (Official Audio)</v>
+        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
       </c>
       <c r="B28" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
+        <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-16</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Madison Beer</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Madison Beer - free (Official Audio) - Madison Beer</v>
+        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Tori Kelly - Dive (Official Audio)</v>
+        <v>Madison Beer - free (Official Audio)</v>
       </c>
       <c r="B29" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
+        <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-16</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Tori Kelly</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Tori Kelly - Dive (Official Audio) - Tori Kelly</v>
+        <v>Madison Beer - free (Official Audio) - Madison Beer</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Jeremy Camp - Reflector (Official Audio)</v>
+        <v>Tori Kelly - Dive (Official Audio)</v>
       </c>
       <c r="B30" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
+        <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-16</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>JeremyCampMusic</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Jeremy Camp - Reflector (Official Audio) - JeremyCampMusic</v>
+        <v>Tori Kelly - Dive (Official Audio) - Tori Kelly</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
+        <v>Jeremy Camp - Reflector (Official Audio)</v>
       </c>
       <c r="B31" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
+        <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-16</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>The Chainsmokers</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer) - The Chainsmokers</v>
+        <v>Jeremy Camp - Reflector (Official Audio) - JeremyCampMusic</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Ashley Cooke - high school sweetheart</v>
+        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
       </c>
       <c r="B32" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
+        <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-16</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Ashley Cooke</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Ashley Cooke - high school sweetheart - Ashley Cooke</v>
+        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Ari Abdul - Ego (Visualizer)</v>
+        <v>Ashley Cooke - high school sweetheart</v>
       </c>
       <c r="B33" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=L0FjVr6LpVU</v>
+        <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-16</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Ari Abdul</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Ari Abdul - Ego (Visualizer) - Ari Abdul</v>
+        <v>Ashley Cooke - high school sweetheart - Ashley Cooke</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Quinn XCII - HOOPLA (Official Music Video)</v>
+        <v>Ari Abdul - Ego (Visualizer)</v>
       </c>
       <c r="B34" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=eNbGA1pgmFk</v>
+        <v>https://www.youtube.com/watch?v=L0FjVr6LpVU</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-16</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Quinn XCII</v>
+        <v>Ari Abdul</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Quinn XCII - HOOPLA (Official Music Video) - Quinn XCII</v>
+        <v>Ari Abdul - Ego (Visualizer) - Ari Abdul</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Madison Beer - lovergirl (Official Music Video)</v>
+        <v>Quinn XCII - HOOPLA (Official Music Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=q4lU1N3oqYQ</v>
+        <v>https://www.youtube.com/watch?v=eNbGA1pgmFk</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-16</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Madison Beer</v>
+        <v>Quinn XCII</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Madison Beer - lovergirl (Official Music Video) - Madison Beer</v>
+        <v>Quinn XCII - HOOPLA (Official Music Video) - Quinn XCII</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>David J - WHAT IF I'M IN LOVE (Official Video)</v>
+        <v>Madison Beer - lovergirl (Official Music Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=-SF7Hm_ikaY</v>
+        <v>https://www.youtube.com/watch?v=q4lU1N3oqYQ</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-16</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>David J</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>David J - WHAT IF I'M IN LOVE (Official Video) - David J</v>
+        <v>Madison Beer - lovergirl (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>The Last Dinner Party - Big Dog (On The Road)</v>
+        <v>David J - WHAT IF I'M IN LOVE (Official Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
+        <v>https://www.youtube.com/watch?v=-SF7Hm_ikaY</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-16</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>The Last Dinner Party</v>
+        <v>David J</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>The Last Dinner Party - Big Dog (On The Road) - The Last Dinner Party</v>
+        <v>David J - WHAT IF I'M IN LOVE (Official Video) - David J</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>OCEAN ALLEY - HOLD ON (Official Video)</v>
+        <v>The Last Dinner Party - Big Dog (On The Road)</v>
       </c>
       <c r="B38" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
+        <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-16</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Ocean Alley</v>
+        <v>The Last Dinner Party</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>OCEAN ALLEY - HOLD ON (Official Video) - Ocean Alley</v>
+        <v>The Last Dinner Party - Big Dog (On The Road) - The Last Dinner Party</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Dagny - Closet Disco Queen (Lyric Video)</v>
+        <v>OCEAN ALLEY - HOLD ON (Official Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
+        <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-16</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Dagny</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Dagny - Closet Disco Queen (Lyric Video) - Dagny</v>
+        <v>OCEAN ALLEY - HOLD ON (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Purple Disco Machine - Disco Cherry (Official Video)</v>
+        <v>Dagny - Closet Disco Queen (Lyric Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
+        <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-16</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Dagny</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Purple Disco Machine - Disco Cherry (Official Video) - Purple Disco Machine</v>
+        <v>Dagny - Closet Disco Queen (Lyric Video) - Dagny</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Paris Paloma - Stem the Flow [Official Music Video]</v>
+        <v>Purple Disco Machine - Disco Cherry (Official Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>9 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
+        <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-16</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>9 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Paris Paloma</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Paris Paloma - Stem the Flow [Official Music Video] - Paris Paloma</v>
+        <v>Purple Disco Machine - Disco Cherry (Official Video) - Purple Disco Machine</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Lucy Blue - Who you love (Visualiser)</v>
+        <v>Paris Paloma - Stem the Flow [Official Music Video]</v>
       </c>
       <c r="B42" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
+        <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-16</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Lucy Blue</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Lucy Blue - Who you love (Visualiser) - Lucy Blue</v>
+        <v>Paris Paloma - Stem the Flow [Official Music Video] - Paris Paloma</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026)</v>
+        <v>Lucy Blue - Who you love (Visualiser)</v>
       </c>
       <c r="B43" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
+        <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-16</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Olivia Dean</v>
+        <v>Lucy Blue</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026) - Olivia Dean</v>
+        <v>Lucy Blue - Who you love (Visualiser) - Lucy Blue</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Aaron Frazer - It's A Shame (Official Video)</v>
+        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026)</v>
       </c>
       <c r="B44" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
+        <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-16</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Aaron Frazer</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Aaron Frazer - It's A Shame (Official Video) - Aaron Frazer</v>
+        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026) - Olivia Dean</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify</v>
+        <v>Aaron Frazer - It's A Shame (Official Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
+        <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-16</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Holly Humberstone</v>
+        <v>Aaron Frazer</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>Aaron Frazer - It's A Shame (Official Video) - Aaron Frazer</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>DANNA - OUT OF MY BODY</v>
+        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify</v>
       </c>
       <c r="B46" t="str">
-        <v>10 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=uW_Ye0kQ9Ac</v>
+        <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-16</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>10 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Danna</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>DANNA - OUT OF MY BODY - Danna</v>
+        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>The Rolling Stones - In The Stars (Official Lyric Video)</v>
+        <v>DANNA - OUT OF MY BODY</v>
       </c>
       <c r="B47" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
+        <v>https://www.youtube.com/watch?v=uW_Ye0kQ9Ac</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-16</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>The Rolling Stones</v>
+        <v>Danna</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>The Rolling Stones - In The Stars (Official Lyric Video) - The Rolling Stones</v>
+        <v>DANNA - OUT OF MY BODY - Danna</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser)</v>
+        <v>The Rolling Stones - In The Stars (Official Lyric Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
+        <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-16</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Dermot Kennedy</v>
+        <v>The Rolling Stones</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser) - Dermot Kennedy</v>
+        <v>The Rolling Stones - In The Stars (Official Lyric Video) - The Rolling Stones</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
+        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser)</v>
       </c>
       <c r="B49" t="str">
-        <v>2 weeks ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
+        <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-16</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>2 weeks ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2) - SIENNA SPIRO</v>
+        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Rick Astley - Raindrops (Official Video)</v>
+        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
       </c>
       <c r="B50" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
+        <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-16</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Rick Astley</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Rick Astley - Raindrops (Official Video) - Rick Astley</v>
+        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Jessie J - THREW IT AWAY (Official Video)</v>
+        <v>Rick Astley - Raindrops (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
+        <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-16</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Jessie J</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Jessie J - THREW IT AWAY (Official Video) - Jessie J</v>
+        <v>Rick Astley - Raindrops (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>The Takes - Ain't Love (Lyric Video)</v>
+        <v>Jessie J - THREW IT AWAY (Official Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
+        <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-16</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>The Takes</v>
+        <v>Jessie J</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>The Takes - Ain't Love (Lyric Video) - The Takes</v>
+        <v>Jessie J - THREW IT AWAY (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary</v>
+        <v>The Takes - Ain't Love (Lyric Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
+        <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-16</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>The Offspring</v>
+        <v>The Takes</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary - The Offspring</v>
+        <v>The Takes - Ain't Love (Lyric Video) - The Takes</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Louis Tomlinson - Sunflowers (Official Performance Video)</v>
+        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary</v>
       </c>
       <c r="B54" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
+        <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-16</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Louis Tomlinson</v>
+        <v>The Offspring</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Louis Tomlinson - Sunflowers (Official Performance Video) - Louis Tomlinson</v>
+        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary - The Offspring</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>The Beaches - Should've Known Better (Official Visualizer)</v>
+        <v>Louis Tomlinson - Sunflowers (Official Performance Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
+        <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-16</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>The Beaches</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>The Beaches - Should've Known Better (Official Visualizer) - The Beaches</v>
+        <v>Louis Tomlinson - Sunflowers (Official Performance Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>The Kiffness - Serafino (Singing Cat Song)</v>
+        <v>The Beaches - Should've Known Better (Official Visualizer)</v>
       </c>
       <c r="B56" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
+        <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-16</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>The Kiffness</v>
+        <v>The Beaches</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>The Kiffness - Serafino (Singing Cat Song) - The Kiffness</v>
+        <v>The Beaches - Should've Known Better (Official Visualizer) - The Beaches</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer)</v>
+        <v>The Kiffness - Serafino (Singing Cat Song)</v>
       </c>
       <c r="B57" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
+        <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-16</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Dennis Lloyd</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer) - Dennis Lloyd</v>
+        <v>The Kiffness - Serafino (Singing Cat Song) - The Kiffness</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Anna Graves - Damn In Love (Official Visualizer)</v>
+        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer)</v>
       </c>
       <c r="B58" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
+        <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-16</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Anna Graves</v>
+        <v>Dennis Lloyd</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Anna Graves - Damn In Love (Official Visualizer) - Anna Graves</v>
+        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer) - Dennis Lloyd</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video)</v>
+        <v>Anna Graves - Damn In Love (Official Visualizer)</v>
       </c>
       <c r="B59" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=vKzPmy3VUzY</v>
+        <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-16</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Brandon Lake and NICK JONAS</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video) - Brandon Lake and NICK JONAS</v>
+        <v>Anna Graves - Damn In Love (Official Visualizer) - Anna Graves</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Letdown. - Do It For The Love (Visualizer)</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=vCvZbTEywr8</v>
+        <v>https://www.youtube.com/watch?v=vKzPmy3VUzY</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-16</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Letdown.</v>
+        <v>Brandon Lake and NICK JONAS</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Letdown. - Do It For The Love (Visualizer) - Letdown.</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video) - Brandon Lake and NICK JONAS</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Maroon 5 - Heroine (Official Lyric Video)</v>
+        <v>Letdown. - Do It For The Love (Visualizer)</v>
       </c>
       <c r="B61" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=izP-4q4YtNw</v>
+        <v>https://www.youtube.com/watch?v=vCvZbTEywr8</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-16</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Maroon 5</v>
+        <v>Letdown.</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Maroon 5 - Heroine (Official Lyric Video) - Maroon 5</v>
+        <v>Letdown. - Do It For The Love (Visualizer) - Letdown.</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Olivia O'Brien - I'm Perfect (Official Visualizer)</v>
+        <v>Maroon 5 - Heroine (Official Lyric Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=leHb8CowDSw</v>
+        <v>https://www.youtube.com/watch?v=izP-4q4YtNw</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-16</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Olivia O'Brien</v>
+        <v>Maroon 5</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Olivia O'Brien - I'm Perfect (Official Visualizer) - Olivia O'Brien</v>
+        <v>Maroon 5 - Heroine (Official Lyric Video) - Maroon 5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>ERNEST - What's A Little Rain (Official Music Video)</v>
+        <v>Olivia O'Brien - I'm Perfect (Official Visualizer)</v>
       </c>
       <c r="B63" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=U-3AGDH3mf4</v>
+        <v>https://www.youtube.com/watch?v=leHb8CowDSw</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-16</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>ERNEST</v>
+        <v>Olivia O'Brien</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>ERNEST - What's A Little Rain (Official Music Video) - ERNEST</v>
+        <v>Olivia O'Brien - I'm Perfect (Official Visualizer) - Olivia O'Brien</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Claire Rosinkranz - Just A Man (Official Audio)</v>
+        <v>ERNEST - What's A Little Rain (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=Ta2I3EHXaDI</v>
+        <v>https://www.youtube.com/watch?v=U-3AGDH3mf4</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-16</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>ERNEST</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Claire Rosinkranz - Just A Man (Official Audio) - Claire Rosinkranz</v>
+        <v>ERNEST - What's A Little Rain (Official Music Video) - ERNEST</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Halsey - Nothing! (Official Audio)</v>
+        <v>Claire Rosinkranz - Just A Man (Official Audio)</v>
       </c>
       <c r="B65" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=PBv71KbKvHA</v>
+        <v>https://www.youtube.com/watch?v=Ta2I3EHXaDI</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-16</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Halsey</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Halsey - Nothing! (Official Audio) - Halsey</v>
+        <v>Claire Rosinkranz - Just A Man (Official Audio) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer)</v>
+        <v>Halsey - Nothing! (Official Audio)</v>
       </c>
       <c r="B66" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=5-f07ca1Zfg</v>
+        <v>https://www.youtube.com/watch?v=PBv71KbKvHA</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-16</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Zara Larsson</v>
+        <v>Halsey</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer) - Zara Larsson</v>
+        <v>Halsey - Nothing! (Official Audio) - Halsey</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Halsey - Carry the Weight (Official Audio)</v>
+        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B67" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=6MewHp8BX0w</v>
+        <v>https://www.youtube.com/watch?v=5-f07ca1Zfg</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-16</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Halsey</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Halsey - Carry the Weight (Official Audio) - Halsey</v>
+        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer) - Zara Larsson</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Bishop Briggs - Blood From A Stone (Official)</v>
+        <v>Halsey - Carry the Weight (Official Audio)</v>
       </c>
       <c r="B68" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=3CK6Zbdk-Nw</v>
+        <v>https://www.youtube.com/watch?v=6MewHp8BX0w</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-16</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Bishop Briggs</v>
+        <v>Halsey</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Bishop Briggs - Blood From A Stone (Official) - Bishop Briggs</v>
+        <v>Halsey - Carry the Weight (Official Audio) - Halsey</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio)</v>
+        <v>Bishop Briggs - Blood From A Stone (Official)</v>
       </c>
       <c r="B69" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=6-AWBV5FCN4</v>
+        <v>https://www.youtube.com/watch?v=3CK6Zbdk-Nw</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-16</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio) - Louis Tomlinson</v>
+        <v>Bishop Briggs - Blood From A Stone (Official) - Bishop Briggs</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>almost monday - no more regrets (official video)</v>
+        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio)</v>
       </c>
       <c r="B70" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=iczsZVZxHKs</v>
+        <v>https://www.youtube.com/watch?v=6-AWBV5FCN4</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-16</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>almost monday</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>almost monday - no more regrets (official video) - almost monday</v>
+        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video)</v>
+        <v>almost monday - no more regrets (official video)</v>
       </c>
       <c r="B71" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=lJM-z0ohbkc</v>
+        <v>https://www.youtube.com/watch?v=iczsZVZxHKs</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-16</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>almost monday</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video) - FULL CIRCLE BOYS</v>
+        <v>almost monday - no more regrets (official video) - almost monday</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video)</v>
+        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=6AjhDPwpoLI</v>
+        <v>https://www.youtube.com/watch?v=lJM-z0ohbkc</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-16</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video) - ★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
+        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video)</v>
+        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=F4ndJUCsHKg</v>
+        <v>https://www.youtube.com/watch?v=6AjhDPwpoLI</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-16</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>NIGHTLY and Fly By Midnight</v>
+        <v>★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video) - NIGHTLY and Fly By Midnight</v>
+        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video) - ★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer)</v>
+        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=-IEb-ym7VeQ</v>
+        <v>https://www.youtube.com/watch?v=F4ndJUCsHKg</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-16</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Zara Larsson</v>
+        <v>NIGHTLY and Fly By Midnight</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer) - Zara Larsson</v>
+        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video) - NIGHTLY and Fly By Midnight</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>JORDANA BRYANT - Truth Is (Official Video)</v>
+        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B75" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=D4meCyyV7SQ</v>
+        <v>https://www.youtube.com/watch?v=-IEb-ym7VeQ</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-16</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Jordana Bryant</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>JORDANA BRYANT - Truth Is (Official Video) - Jordana Bryant</v>
+        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer) - Zara Larsson</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Leanna Crawford - Thank God (Lyric Video)</v>
+        <v>JORDANA BRYANT - Truth Is (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=QqcSoUft03s</v>
+        <v>https://www.youtube.com/watch?v=D4meCyyV7SQ</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-16</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Leanna Crawford</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Leanna Crawford - Thank God (Lyric Video) - Leanna Crawford</v>
+        <v>JORDANA BRYANT - Truth Is (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Girl Tones - Stubborn Mouth (Official Music Video)</v>
+        <v>Leanna Crawford - Thank God (Lyric Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=_-PyPUWZTDY</v>
+        <v>https://www.youtube.com/watch?v=QqcSoUft03s</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-16</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Girl Tones</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Girl Tones - Stubborn Mouth (Official Music Video) - Girl Tones</v>
+        <v>Leanna Crawford - Thank God (Lyric Video) - Leanna Crawford</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Tauren Wells - What A Miracle Feels Like (Official Audio)</v>
+        <v>Girl Tones - Stubborn Mouth (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=ZojFIe4Swmk</v>
+        <v>https://www.youtube.com/watch?v=_-PyPUWZTDY</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-16</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Tauren Wells</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Tauren Wells - What A Miracle Feels Like (Official Audio) - Tauren Wells</v>
+        <v>Girl Tones - Stubborn Mouth (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Matthew Ifield - Thinking (Official Video)</v>
+        <v>Tauren Wells - What A Miracle Feels Like (Official Audio)</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
+        <v>https://www.youtube.com/watch?v=ZojFIe4Swmk</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-16</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Matthew Ifield</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Matthew Ifield - Thinking (Official Video) - Matthew Ifield</v>
+        <v>Tauren Wells - What A Miracle Feels Like (Official Audio) - Tauren Wells</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Dons - Is There Something</v>
+        <v>Matthew Ifield - Thinking (Official Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=AgWIjvD-i0E</v>
+        <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-16</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Dons</v>
+        <v>Matthew Ifield</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Dons - Is There Something - Dons</v>
+        <v>Matthew Ifield - Thinking (Official Video) - Matthew Ifield</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris</v>
+        <v>Dons - Is There Something</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=JXW3SOr7C4w</v>
+        <v>https://www.youtube.com/watch?v=AgWIjvD-i0E</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-16</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Recording Academy / GRAMMYs and 3 more</v>
+        <v>Dons</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris - Recording Academy / GRAMMYs and 3 more</v>
+        <v>Dons - Is There Something - Dons</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Maya Hawke - Lioness (Official Audio)</v>
+        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris</v>
       </c>
       <c r="B82" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
+        <v>https://www.youtube.com/watch?v=JXW3SOr7C4w</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-16</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Maya Hawke</v>
+        <v>Recording Academy / GRAMMYs and 3 more</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Maya Hawke - Lioness (Official Audio) - Maya Hawke</v>
+        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris - Recording Academy / GRAMMYs and 3 more</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance</v>
+        <v>Maya Hawke - Lioness (Official Audio)</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
+        <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-16</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Laufey</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance - Laufey</v>
+        <v>Maya Hawke - Lioness (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
+        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
+        <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-16</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Keith Urban</v>
+        <v>Laufey</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
+        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance - Laufey</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>DANNA - AGAIN</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
+        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-16</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Danna</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>DANNA - AGAIN - Danna</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>DANNA - AGAIN</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
+        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-16</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Armik</v>
+        <v>Danna</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>DANNA - AGAIN - Danna</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>EUROPE - One on One (Official Video)</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
+        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-16</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Europe</v>
+        <v>Armik</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>EUROPE - One on One (Official Video) - Europe</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
+        <v>EUROPE - One on One (Official Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
+        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-16</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Foo Fighters</v>
+        <v>Europe</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
+        <v>EUROPE - One on One (Official Video) - Europe</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video)</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
+        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-16</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Lady Gaga and Doechii</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video) - Lady Gaga and Doechii</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
+        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
+        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-16</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Muse</v>
+        <v>Lady Gaga and Doechii</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
+        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video) - Lady Gaga and Doechii</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
+        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-16</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Muse</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Shaboozey - Born To Die (Official Video)</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
       </c>
       <c r="B92" t="str">
-        <v>3 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
+        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-16</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>3 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Shaboozey</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
+        <v>Shaboozey - Born To Die (Official Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
+        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-16</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Scorpions</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
+        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
       </c>
       <c r="B94" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
+        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-16</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Meghan Trainor</v>
+        <v>Scorpions</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
+        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-16</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Lolo Zouaï</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Bonnie Tyler - One World One Home</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
+        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-16</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Bonnie Tyler</v>
+        <v>Lolo Zouaï</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
+        <v>Bonnie Tyler - One World One Home</v>
       </c>
       <c r="B97" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
+        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-16</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Icona Pop - Dance To This (Official Video)</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
       </c>
       <c r="B98" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
+        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-16</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Icona Pop</v>
+        <v>Jacob Gurevitsch and Prisma Music Group</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Michael Jackson - Human Nature (Official Video)</v>
+        <v>Icona Pop - Dance To This (Official Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
+        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-16</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Michael Jackson</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
+        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>The All-American Rejects - King Kong</v>
+        <v>Michael Jackson - Human Nature (Official Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
+        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-16</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>The All-American Rejects</v>
+        <v>Michael Jackson</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
+        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
+        <v>The All-American Rejects - King Kong</v>
       </c>
       <c r="B101" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
+        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-16</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Ringo Starr</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
+        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Hit the Wall</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>3w ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/hit-the-wall/6766750846</v>
+        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-16</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Daughter from Hell</v>
+        <v>3w ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:14</v>
+        <v/>
       </c>
       <c r="H102" t="str">
-        <v>Gracie Abrams</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/gracie-abrams/1450554836</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/hit-the-wall/6766750836</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Hit the Wall - Gracie Abrams</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Ran To Atlanta</v>
+        <v>Hit the Wall</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/ran-to-atlanta/6769568597</v>
+        <v>https://music.apple.com/us/song/hit-the-wall/6766750846</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-16</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>ICEMAN</v>
+        <v>Daughter from Hell</v>
       </c>
       <c r="G103" t="str">
-        <v>4:07</v>
+        <v>3:14</v>
       </c>
       <c r="H103" t="str">
-        <v>Drake</v>
+        <v>Gracie Abrams</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/drake/271256</v>
+        <v>https://music.apple.com/us/artist/gracie-abrams/1450554836</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/ran-to-atlanta/6769568449</v>
+        <v>https://music.apple.com/us/album/hit-the-wall/6766750836</v>
       </c>
       <c r="L103" t="str">
-        <v>Ran To Atlanta - Drake</v>
+        <v>Hit the Wall - Gracie Abrams</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Hoe Phase</v>
+        <v>Ran To Atlanta</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/hoe-phase/6769556949</v>
+        <v>https://music.apple.com/us/song/ran-to-atlanta/6769568597</v>
       </c>
       <c r="D104" t="str">
         <v>2026-05-16</v>
@@ -4327,10 +4327,10 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>MAID OF HONOUR</v>
+        <v>ICEMAN</v>
       </c>
       <c r="G104" t="str">
-        <v>3:23</v>
+        <v>4:07</v>
       </c>
       <c r="H104" t="str">
         <v>Drake</v>
@@ -4342,21 +4342,21 @@
         <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/hoe-phase/6769556940</v>
+        <v>https://music.apple.com/us/album/ran-to-atlanta/6769568449</v>
       </c>
       <c r="L104" t="str">
-        <v>Hoe Phase - Drake</v>
+        <v>Ran To Atlanta - Drake</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>I’m Spent</v>
+        <v>Hoe Phase</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/im-spent/6769551476</v>
+        <v>https://music.apple.com/us/song/hoe-phase/6769556949</v>
       </c>
       <c r="D105" t="str">
         <v>2026-05-16</v>
@@ -4365,10 +4365,10 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>HABIBTI</v>
+        <v>MAID OF HONOUR</v>
       </c>
       <c r="G105" t="str">
-        <v>2:24</v>
+        <v>3:23</v>
       </c>
       <c r="H105" t="str">
         <v>Drake</v>
@@ -4380,21 +4380,21 @@
         <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/im-spent/6769551464</v>
+        <v>https://music.apple.com/us/album/hoe-phase/6769556940</v>
       </c>
       <c r="L105" t="str">
-        <v>I’m Spent - Drake</v>
+        <v>Hoe Phase - Drake</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Abracadabra (Apple Music Live)</v>
+        <v>I’m Spent</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/abracadabra-apple-music-live/6768201780</v>
+        <v>https://music.apple.com/us/song/im-spent/6769551476</v>
       </c>
       <c r="D106" t="str">
         <v>2026-05-16</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Apple Music Live: MAYHEM Requiem</v>
+        <v>HABIBTI</v>
       </c>
       <c r="G106" t="str">
-        <v>4:04</v>
+        <v>2:24</v>
       </c>
       <c r="H106" t="str">
-        <v>Lady Gaga</v>
+        <v>Drake</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/abracadabra-apple-music-live/6768201775</v>
+        <v>https://music.apple.com/us/album/im-spent/6769551464</v>
       </c>
       <c r="L106" t="str">
-        <v>Abracadabra (Apple Music Live) - Lady Gaga</v>
+        <v>I’m Spent - Drake</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Falling out of Love</v>
+        <v>Abracadabra (Apple Music Live)</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/falling-out-of-love/1891161448</v>
+        <v>https://music.apple.com/us/song/abracadabra-apple-music-live/6768201780</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-16</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Reality Awaits</v>
+        <v>Apple Music Live: MAYHEM Requiem</v>
       </c>
       <c r="G107" t="str">
-        <v>6:21</v>
+        <v>4:04</v>
       </c>
       <c r="H107" t="str">
-        <v>The Strokes</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/the-strokes/560289</v>
+        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/falling-out-of-love/1891161441</v>
+        <v>https://music.apple.com/us/album/abracadabra-apple-music-live/6768201775</v>
       </c>
       <c r="L107" t="str">
-        <v>Falling out of Love - The Strokes</v>
+        <v>Abracadabra (Apple Music Live) - Lady Gaga</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Dai Dai</v>
+        <v>Falling out of Love</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/dai-dai/6768469976</v>
+        <v>https://music.apple.com/us/song/falling-out-of-love/1891161448</v>
       </c>
       <c r="D108" t="str">
         <v>2026-05-16</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Dai Dai - Single</v>
+        <v>Reality Awaits</v>
       </c>
       <c r="G108" t="str">
-        <v>3:43</v>
+        <v>6:21</v>
       </c>
       <c r="H108" t="str">
-        <v>Shakira</v>
+        <v>The Strokes</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/shakira/889327</v>
+        <v>https://music.apple.com/us/artist/the-strokes/560289</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/dai-dai/6768469975</v>
+        <v>https://music.apple.com/us/album/falling-out-of-love/1891161441</v>
       </c>
       <c r="L108" t="str">
-        <v>Dai Dai - Shakira</v>
+        <v>Falling out of Love - The Strokes</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Tu recuerdo</v>
+        <v>Dai Dai</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/tu-recuerdo/6763660843</v>
+        <v>https://music.apple.com/us/song/dai-dai/6768469976</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-16</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Loco X Volver</v>
+        <v>Dai Dai - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>3:55</v>
+        <v>3:43</v>
       </c>
       <c r="H109" t="str">
-        <v>Maluma</v>
+        <v>Shakira</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/shakira/889327</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/tu-recuerdo/1895423065</v>
+        <v>https://music.apple.com/us/album/dai-dai/6768469975</v>
       </c>
       <c r="L109" t="str">
-        <v>Tu recuerdo - Maluma</v>
+        <v>Dai Dai - Shakira</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Traitor (Roles Reversed)</v>
+        <v>Tu recuerdo</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/traitor-roles-reversed/6767665959</v>
+        <v>https://music.apple.com/us/song/tu-recuerdo/6763660843</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-16</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Cloud 9</v>
+        <v>Loco X Volver</v>
       </c>
       <c r="G110" t="str">
-        <v>3:27</v>
+        <v>3:55</v>
       </c>
       <c r="H110" t="str">
-        <v>Megan Moroney</v>
+        <v>Maluma</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/traitor-roles-reversed/6767665713</v>
+        <v>https://music.apple.com/us/album/tu-recuerdo/1895423065</v>
       </c>
       <c r="L110" t="str">
-        <v>Traitor (Roles Reversed) - Megan Moroney</v>
+        <v>Tu recuerdo - Maluma</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Dirty Rosie</v>
+        <v>Traitor (Roles Reversed)</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/dirty-rosie/6767044374</v>
+        <v>https://music.apple.com/us/song/traitor-roles-reversed/6767665959</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-16</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Little Miss Twain</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G111" t="str">
-        <v>2:46</v>
+        <v>3:27</v>
       </c>
       <c r="H111" t="str">
-        <v>Shania Twain</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/shania-twain/129974</v>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/dirty-rosie/1896356105</v>
+        <v>https://music.apple.com/us/album/traitor-roles-reversed/6767665713</v>
       </c>
       <c r="L111" t="str">
-        <v>Dirty Rosie - Shania Twain</v>
+        <v>Traitor (Roles Reversed) - Megan Moroney</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Like you mean it</v>
+        <v>Dirty Rosie</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/like-you-mean-it/6767024693</v>
+        <v>https://music.apple.com/us/song/dirty-rosie/6767044374</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-16</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>When the lights turn on</v>
+        <v>Little Miss Twain</v>
       </c>
       <c r="G112" t="str">
-        <v>2:27</v>
+        <v>2:46</v>
       </c>
       <c r="H112" t="str">
-        <v>MICO</v>
+        <v>Shania Twain</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/mico/1457367370</v>
+        <v>https://music.apple.com/us/artist/shania-twain/129974</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/like-you-mean-it/6767024688</v>
+        <v>https://music.apple.com/us/album/dirty-rosie/1896356105</v>
       </c>
       <c r="L112" t="str">
-        <v>Like you mean it - MICO</v>
+        <v>Dirty Rosie - Shania Twain</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Hardy (feat. Clairo)</v>
+        <v>Like you mean it</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/hardy-feat-clairo/1876953073</v>
+        <v>https://music.apple.com/us/song/like-you-mean-it/6767024693</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-16</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>American Stories</v>
+        <v>When the lights turn on</v>
       </c>
       <c r="G113" t="str">
-        <v>3:53</v>
+        <v>2:27</v>
       </c>
       <c r="H113" t="str">
-        <v>Rostam</v>
+        <v>MICO</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/mico/1457367370</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/hardy-feat-clairo/1876952750</v>
+        <v>https://music.apple.com/us/album/like-you-mean-it/6767024688</v>
       </c>
       <c r="L113" t="str">
-        <v>Hardy (feat. Clairo) - Rostam</v>
+        <v>Like you mean it - MICO</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>2 Hard 4 The Radio</v>
+        <v>Hardy (feat. Clairo)</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/2-hard-4-the-radio/6769568610</v>
+        <v>https://music.apple.com/us/song/hardy-feat-clairo/1876953073</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-16</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>ICEMAN</v>
+        <v>American Stories</v>
       </c>
       <c r="G114" t="str">
-        <v>3:03</v>
+        <v>3:53</v>
       </c>
       <c r="H114" t="str">
-        <v>Drake</v>
+        <v>Rostam</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/drake/271256</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/2-hard-4-the-radio/6769568449</v>
+        <v>https://music.apple.com/us/album/hardy-feat-clairo/1876952750</v>
       </c>
       <c r="L114" t="str">
-        <v>2 Hard 4 The Radio - Drake</v>
+        <v>Hardy (feat. Clairo) - Rostam</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Cheetah Print</v>
+        <v>2 Hard 4 The Radio</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/cheetah-print/6769557055</v>
+        <v>https://music.apple.com/us/song/2-hard-4-the-radio/6769568610</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-16</v>
@@ -4745,10 +4745,10 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>MAID OF HONOUR</v>
+        <v>ICEMAN</v>
       </c>
       <c r="G115" t="str">
-        <v>3:22</v>
+        <v>3:03</v>
       </c>
       <c r="H115" t="str">
         <v>Drake</v>
@@ -4760,21 +4760,21 @@
         <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/cheetah-print/6769556940</v>
+        <v>https://music.apple.com/us/album/2-hard-4-the-radio/6769568449</v>
       </c>
       <c r="L115" t="str">
-        <v>Cheetah Print - Drake</v>
+        <v>2 Hard 4 The Radio - Drake</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>WNBA</v>
+        <v>Cheetah Print</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/wnba/6769551471</v>
+        <v>https://music.apple.com/us/song/cheetah-print/6769557055</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-16</v>
@@ -4783,10 +4783,10 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>HABIBTI</v>
+        <v>MAID OF HONOUR</v>
       </c>
       <c r="G116" t="str">
-        <v>2:58</v>
+        <v>3:22</v>
       </c>
       <c r="H116" t="str">
         <v>Drake</v>
@@ -4798,21 +4798,21 @@
         <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/wnba/6769551464</v>
+        <v>https://music.apple.com/us/album/cheetah-print/6769556940</v>
       </c>
       <c r="L116" t="str">
-        <v>WNBA - Drake</v>
+        <v>Cheetah Print - Drake</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Shadow Of A Man (Apple Music Live)</v>
+        <v>WNBA</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/shadow-of-a-man-apple-music-live/6768201925</v>
+        <v>https://music.apple.com/us/song/wnba/6769551471</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-16</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Apple Music Live: MAYHEM Requiem</v>
+        <v>HABIBTI</v>
       </c>
       <c r="G117" t="str">
-        <v>3:36</v>
+        <v>2:58</v>
       </c>
       <c r="H117" t="str">
-        <v>Lady Gaga</v>
+        <v>Drake</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/shadow-of-a-man-apple-music-live/6768201775</v>
+        <v>https://music.apple.com/us/album/wnba/6769551464</v>
       </c>
       <c r="L117" t="str">
-        <v>Shadow Of A Man (Apple Music Live) - Lady Gaga</v>
+        <v>WNBA - Drake</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>EPA</v>
+        <v>Shadow Of A Man (Apple Music Live)</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/epa/6768420253</v>
+        <v>https://music.apple.com/us/song/shadow-of-a-man-apple-music-live/6768201925</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-16</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>EPA - Single</v>
+        <v>Apple Music Live: MAYHEM Requiem</v>
       </c>
       <c r="G118" t="str">
-        <v>3:22</v>
+        <v>3:36</v>
       </c>
       <c r="H118" t="str">
-        <v>Becky G</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
+        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/epa/6768420251</v>
+        <v>https://music.apple.com/us/album/shadow-of-a-man-apple-music-live/6768201775</v>
       </c>
       <c r="L118" t="str">
-        <v>EPA - Becky G</v>
+        <v>Shadow Of A Man (Apple Music Live) - Lady Gaga</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>I’m your girl right?</v>
+        <v>EPA</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/im-your-girl-right/6766440186</v>
+        <v>https://music.apple.com/us/song/epa/6768420253</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-16</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>ESTRUS</v>
+        <v>EPA - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>2:49</v>
+        <v>3:22</v>
       </c>
       <c r="H119" t="str">
-        <v>Tove Lo</v>
+        <v>Becky G</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/tove-lo/570136838</v>
+        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/im-your-girl-right/6766440172</v>
+        <v>https://music.apple.com/us/album/epa/6768420251</v>
       </c>
       <c r="L119" t="str">
-        <v>I’m your girl right? - Tove Lo</v>
+        <v>EPA - Becky G</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>fuëgo</v>
+        <v>I’m your girl right?</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/fu%C3%ABgo/6767661766</v>
+        <v>https://music.apple.com/us/song/im-your-girl-right/6766440186</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-16</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>fuëgo - Single</v>
+        <v>ESTRUS</v>
       </c>
       <c r="G120" t="str">
-        <v>3:46</v>
+        <v>2:49</v>
       </c>
       <c r="H120" t="str">
-        <v>BNYX®</v>
+        <v>Tove Lo</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/bnyx/1438325287</v>
+        <v>https://music.apple.com/us/artist/tove-lo/570136838</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/fu%C3%ABgo/6767661604</v>
+        <v>https://music.apple.com/us/album/im-your-girl-right/6766440172</v>
       </c>
       <c r="L120" t="str">
-        <v>fuëgo - BNYX®</v>
+        <v>I’m your girl right? - Tove Lo</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>jajaja</v>
+        <v>fuëgo</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/jajaja/6766341319</v>
+        <v>https://music.apple.com/us/song/fu%C3%ABgo/6767661766</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-16</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>jajaja - Single</v>
+        <v>fuëgo - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>2:45</v>
+        <v>3:46</v>
       </c>
       <c r="H121" t="str">
-        <v>Chino Pacas</v>
+        <v>BNYX®</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
+        <v>https://music.apple.com/us/artist/bnyx/1438325287</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/jajaja/6766341318</v>
+        <v>https://music.apple.com/us/album/fu%C3%ABgo/6767661604</v>
       </c>
       <c r="L121" t="str">
-        <v>jajaja - Chino Pacas</v>
+        <v>fuëgo - BNYX®</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>FIND GOD (feat. Dominic Fike)</v>
+        <v>jajaja</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/find-god-feat-dominic-fike/1894315529</v>
+        <v>https://music.apple.com/us/song/jajaja/6766341319</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-16</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>BULLDAWG</v>
+        <v>jajaja - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:59</v>
+        <v>2:45</v>
       </c>
       <c r="H122" t="str">
-        <v>Kenny Mason</v>
+        <v>Chino Pacas</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/kenny-mason/79382206</v>
+        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/find-god-feat-dominic-fike/1894315301</v>
+        <v>https://music.apple.com/us/album/jajaja/6766341318</v>
       </c>
       <c r="L122" t="str">
-        <v>FIND GOD (feat. Dominic Fike) - Kenny Mason</v>
+        <v>jajaja - Chino Pacas</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>FOOL ME ONCE (feat. Leon Thomas)</v>
+        <v>FIND GOD (feat. Dominic Fike)</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/fool-me-once-feat-leon-thomas/1891467239</v>
+        <v>https://music.apple.com/us/song/find-god-feat-dominic-fike/1894315529</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-16</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>BELOVED: ACT II</v>
+        <v>BULLDAWG</v>
       </c>
       <c r="G123" t="str">
-        <v>3:18</v>
+        <v>3:59</v>
       </c>
       <c r="H123" t="str">
-        <v>GIVĒON</v>
+        <v>Kenny Mason</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/giv%C4%93on/1070668868</v>
+        <v>https://music.apple.com/us/artist/kenny-mason/79382206</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/fool-me-once-feat-leon-thomas/1891467233</v>
+        <v>https://music.apple.com/us/album/find-god-feat-dominic-fike/1894315301</v>
       </c>
       <c r="L123" t="str">
-        <v>FOOL ME ONCE (feat. Leon Thomas) - GIVĒON</v>
+        <v>FIND GOD (feat. Dominic Fike) - Kenny Mason</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Shabang</v>
+        <v>FOOL ME ONCE (feat. Leon Thomas)</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/shabang/6769568598</v>
+        <v>https://music.apple.com/us/song/fool-me-once-feat-leon-thomas/1891467239</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-16</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>ICEMAN</v>
+        <v>BELOVED: ACT II</v>
       </c>
       <c r="G124" t="str">
-        <v>3:08</v>
+        <v>3:18</v>
       </c>
       <c r="H124" t="str">
-        <v>Drake</v>
+        <v>GIVĒON</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/drake/271256</v>
+        <v>https://music.apple.com/us/artist/giv%C4%93on/1070668868</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/shabang/6769568449</v>
+        <v>https://music.apple.com/us/album/fool-me-once-feat-leon-thomas/1891467233</v>
       </c>
       <c r="L124" t="str">
-        <v>Shabang - Drake</v>
+        <v>FOOL ME ONCE (feat. Leon Thomas) - GIVĒON</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Road Trips</v>
+        <v>Shabang</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/road-trips/6769557053</v>
+        <v>https://music.apple.com/us/song/shabang/6769568598</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-16</v>
@@ -5125,10 +5125,10 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>MAID OF HONOUR</v>
+        <v>ICEMAN</v>
       </c>
       <c r="G125" t="str">
-        <v>4:03</v>
+        <v>3:08</v>
       </c>
       <c r="H125" t="str">
         <v>Drake</v>
@@ -5140,21 +5140,21 @@
         <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/road-trips/6769556940</v>
+        <v>https://music.apple.com/us/album/shabang/6769568449</v>
       </c>
       <c r="L125" t="str">
-        <v>Road Trips - Drake</v>
+        <v>Shabang - Drake</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Fortworth</v>
+        <v>Road Trips</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/fortworth/6769551482</v>
+        <v>https://music.apple.com/us/song/road-trips/6769557053</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-16</v>
@@ -5163,10 +5163,10 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>HABIBTI</v>
+        <v>MAID OF HONOUR</v>
       </c>
       <c r="G126" t="str">
-        <v>3:51</v>
+        <v>4:03</v>
       </c>
       <c r="H126" t="str">
         <v>Drake</v>
@@ -5178,21 +5178,21 @@
         <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/fortworth/6769551464</v>
+        <v>https://music.apple.com/us/album/road-trips/6769556940</v>
       </c>
       <c r="L126" t="str">
-        <v>Fortworth - Drake</v>
+        <v>Road Trips - Drake</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Repeat It</v>
+        <v>Fortworth</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/repeat-it/6764277864</v>
+        <v>https://music.apple.com/us/song/fortworth/6769551482</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-16</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Repeat It - Single</v>
+        <v>HABIBTI</v>
       </c>
       <c r="G127" t="str">
-        <v>3:11</v>
+        <v>3:51</v>
       </c>
       <c r="H127" t="str">
-        <v>Martin Garrix</v>
+        <v>Drake</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/repeat-it/1895713789</v>
+        <v>https://music.apple.com/us/album/fortworth/6769551464</v>
       </c>
       <c r="L127" t="str">
-        <v>Repeat It - Martin Garrix</v>
+        <v>Fortworth - Drake</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Fool Proof</v>
+        <v>Repeat It</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/fool-proof/1892466004</v>
+        <v>https://music.apple.com/us/song/repeat-it/6764277864</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-16</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>Repeat It - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:36</v>
+        <v>3:11</v>
       </c>
       <c r="H128" t="str">
-        <v>Cody Johnson</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/fool-proof/1892465981</v>
+        <v>https://music.apple.com/us/album/repeat-it/1895713789</v>
       </c>
       <c r="L128" t="str">
-        <v>Fool Proof - Cody Johnson</v>
+        <v>Repeat It - Martin Garrix</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Crisco</v>
+        <v>Fool Proof</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/crisco/6763369506</v>
+        <v>https://music.apple.com/us/song/fool-proof/1892466004</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-16</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Crisco - Single</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G129" t="str">
-        <v>2:56</v>
+        <v>2:36</v>
       </c>
       <c r="H129" t="str">
-        <v>Miranda Lambert</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/miranda-lambert/18732261</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/crisco/1895284236</v>
+        <v>https://music.apple.com/us/album/fool-proof/1892465981</v>
       </c>
       <c r="L129" t="str">
-        <v>Crisco - Miranda Lambert</v>
+        <v>Fool Proof - Cody Johnson</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Absolution</v>
+        <v>Crisco</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/absolution/1884987651</v>
+        <v>https://music.apple.com/us/song/crisco/6763369506</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-16</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Forever Now</v>
+        <v>Crisco - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>4:05</v>
+        <v>2:56</v>
       </c>
       <c r="H130" t="str">
-        <v>Switchfoot</v>
+        <v>Miranda Lambert</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
+        <v>https://music.apple.com/us/artist/miranda-lambert/18732261</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/absolution/1884987638</v>
+        <v>https://music.apple.com/us/album/crisco/1895284236</v>
       </c>
       <c r="L130" t="str">
-        <v>Absolution - Switchfoot</v>
+        <v>Crisco - Miranda Lambert</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>JESUS IS ALIVE</v>
+        <v>Absolution</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/jesus-is-alive/6767694896</v>
+        <v>https://music.apple.com/us/song/absolution/1884987651</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-16</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>JESUS IS ALIVE - Single</v>
+        <v>Forever Now</v>
       </c>
       <c r="G131" t="str">
-        <v>2:08</v>
+        <v>4:05</v>
       </c>
       <c r="H131" t="str">
-        <v>Forrest Frank</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
+        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/jesus-is-alive/6767694895</v>
+        <v>https://music.apple.com/us/album/absolution/1884987638</v>
       </c>
       <c r="L131" t="str">
-        <v>JESUS IS ALIVE - Forrest Frank</v>
+        <v>Absolution - Switchfoot</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Something To Lose</v>
+        <v>JESUS IS ALIVE</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/something-to-lose/6766964605</v>
+        <v>https://music.apple.com/us/song/jesus-is-alive/6767694896</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-16</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Is This Heaven? - EP</v>
+        <v>JESUS IS ALIVE - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>2:55</v>
+        <v>2:08</v>
       </c>
       <c r="H132" t="str">
-        <v>STELLA LEFTY</v>
+        <v>Forrest Frank</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
+        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/something-to-lose/6766964604</v>
+        <v>https://music.apple.com/us/album/jesus-is-alive/6767694895</v>
       </c>
       <c r="L132" t="str">
-        <v>Something To Lose - STELLA LEFTY</v>
+        <v>JESUS IS ALIVE - Forrest Frank</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Too Busy Missing You</v>
+        <v>Something To Lose</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/too-busy-missing-you/6766604915</v>
+        <v>https://music.apple.com/us/song/something-to-lose/6766964605</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-16</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Off Campus: The Mixtape</v>
+        <v>Is This Heaven? - EP</v>
       </c>
       <c r="G133" t="str">
-        <v>3:25</v>
+        <v>2:55</v>
       </c>
       <c r="H133" t="str">
-        <v>Asha Banks</v>
+        <v>STELLA LEFTY</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
+        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/too-busy-missing-you/6766604455</v>
+        <v>https://music.apple.com/us/album/something-to-lose/6766964604</v>
       </c>
       <c r="L133" t="str">
-        <v>Too Busy Missing You - Asha Banks</v>
+        <v>Something To Lose - STELLA LEFTY</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>F-Stop Blues (4-track)</v>
+        <v>Too Busy Missing You</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/f-stop-blues-4-track/1883173173</v>
+        <v>https://music.apple.com/us/song/too-busy-missing-you/6766604915</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-16</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>Off Campus: The Mixtape</v>
       </c>
       <c r="G134" t="str">
-        <v>3:00</v>
+        <v>3:25</v>
       </c>
       <c r="H134" t="str">
-        <v>Jack Johnson</v>
+        <v>Asha Banks</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/f-stop-blues-4-track/1883172879</v>
+        <v>https://music.apple.com/us/album/too-busy-missing-you/6766604455</v>
       </c>
       <c r="L134" t="str">
-        <v>F-Stop Blues (4-track) - Jack Johnson</v>
+        <v>Too Busy Missing You - Asha Banks</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>PA' LO BONITO</v>
+        <v>F-Stop Blues (4-track)</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/pa-lo-bonito/1886496944</v>
+        <v>https://music.apple.com/us/song/f-stop-blues-4-track/1883173173</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-16</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>PA' LO BONITO - Single</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G135" t="str">
-        <v>3:04</v>
+        <v>3:00</v>
       </c>
       <c r="H135" t="str">
-        <v>Lenny Tavárez</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/pa-lo-bonito/1886496943</v>
+        <v>https://music.apple.com/us/album/f-stop-blues-4-track/1883172879</v>
       </c>
       <c r="L135" t="str">
-        <v>PA' LO BONITO - Lenny Tavárez</v>
+        <v>F-Stop Blues (4-track) - Jack Johnson</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>LONELY</v>
+        <v>PA' LO BONITO</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/lonely/6768757857</v>
+        <v>https://music.apple.com/us/song/pa-lo-bonito/1886496944</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-16</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>DESEO</v>
+        <v>PA' LO BONITO - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:58</v>
+        <v>3:04</v>
       </c>
       <c r="H136" t="str">
-        <v>Katteyes</v>
+        <v>Lenny Tavárez</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/katteyes/1648818255</v>
+        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/lonely/6768757414</v>
+        <v>https://music.apple.com/us/album/pa-lo-bonito/1886496943</v>
       </c>
       <c r="L136" t="str">
-        <v>LONELY - Katteyes</v>
+        <v>PA' LO BONITO - Lenny Tavárez</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Lockup</v>
+        <v>LONELY</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/lockup/1894298102</v>
+        <v>https://music.apple.com/us/song/lonely/6768757857</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-16</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Pure Devotion</v>
+        <v>DESEO</v>
       </c>
       <c r="G137" t="str">
-        <v>4:31</v>
+        <v>2:58</v>
       </c>
       <c r="H137" t="str">
-        <v>Overmono</v>
+        <v>Katteyes</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/overmono/1129806758</v>
+        <v>https://music.apple.com/us/artist/katteyes/1648818255</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/lockup/1894298100</v>
+        <v>https://music.apple.com/us/album/lonely/6768757414</v>
       </c>
       <c r="L137" t="str">
-        <v>Lockup - Overmono</v>
+        <v>LONELY - Katteyes</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Young</v>
+        <v>Lockup</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/young/6767698952</v>
+        <v>https://music.apple.com/us/song/lockup/1894298102</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-16</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Young</v>
+        <v>Pure Devotion</v>
       </c>
       <c r="G138" t="str">
-        <v>2:46</v>
+        <v>4:31</v>
       </c>
       <c r="H138" t="str">
-        <v>Dan + Shay</v>
+        <v>Overmono</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/dan-shay/690319057</v>
+        <v>https://music.apple.com/us/artist/overmono/1129806758</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/young/6767698951</v>
+        <v>https://music.apple.com/us/album/lockup/1894298100</v>
       </c>
       <c r="L138" t="str">
-        <v>Young - Dan + Shay</v>
+        <v>Lockup - Overmono</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Parachute</v>
+        <v>Young</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/parachute/6764119241</v>
+        <v>https://music.apple.com/us/song/young/6767698952</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-16</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Parachute - Single</v>
+        <v>Young</v>
       </c>
       <c r="G139" t="str">
-        <v>2:52</v>
+        <v>2:46</v>
       </c>
       <c r="H139" t="str">
-        <v>Maren Morris</v>
+        <v>Dan + Shay</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/maren-morris/262260873</v>
+        <v>https://music.apple.com/us/artist/dan-shay/690319057</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/parachute/1895648983</v>
+        <v>https://music.apple.com/us/album/young/6767698951</v>
       </c>
       <c r="L139" t="str">
-        <v>Parachute - Maren Morris</v>
+        <v>Young - Dan + Shay</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Little Things</v>
+        <v>Parachute</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/little-things/6766351153</v>
+        <v>https://music.apple.com/us/song/parachute/6764119241</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-16</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Little Things - Single</v>
+        <v>Parachute - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:55</v>
+        <v>2:52</v>
       </c>
       <c r="H140" t="str">
-        <v>Kevin Jonas</v>
+        <v>Maren Morris</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/kevin-jonas/21138190</v>
+        <v>https://music.apple.com/us/artist/maren-morris/262260873</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/little-things/6766350882</v>
+        <v>https://music.apple.com/us/album/parachute/1895648983</v>
       </c>
       <c r="L140" t="str">
-        <v>Little Things - Kevin Jonas</v>
+        <v>Parachute - Maren Morris</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Fish Hunt Golf Drink</v>
+        <v>Little Things</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/fish-hunt-golf-drink/6766651884</v>
+        <v>https://music.apple.com/us/song/little-things/6766351153</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-16</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Signs</v>
+        <v>Little Things - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:34</v>
+        <v>2:55</v>
       </c>
       <c r="H141" t="str">
-        <v>Luke Bryan</v>
+        <v>Kevin Jonas</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
+        <v>https://music.apple.com/us/artist/kevin-jonas/21138190</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/fish-hunt-golf-drink/6766651878</v>
+        <v>https://music.apple.com/us/album/little-things/6766350882</v>
       </c>
       <c r="L141" t="str">
-        <v>Fish Hunt Golf Drink - Luke Bryan</v>
+        <v>Little Things - Kevin Jonas</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>PAGEANT STAGE</v>
+        <v>Fish Hunt Golf Drink</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/pageant-stage/6764125889</v>
+        <v>https://music.apple.com/us/song/fish-hunt-golf-drink/6766651884</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-16</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>THE EDGE</v>
+        <v>Signs</v>
       </c>
       <c r="G142" t="str">
-        <v>2:52</v>
+        <v>2:34</v>
       </c>
       <c r="H142" t="str">
-        <v>Tone Stith</v>
+        <v>Luke Bryan</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/tone-stith/1167717310</v>
+        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/pageant-stage/1895651504</v>
+        <v>https://music.apple.com/us/album/fish-hunt-golf-drink/6766651878</v>
       </c>
       <c r="L142" t="str">
-        <v>PAGEANT STAGE - Tone Stith</v>
+        <v>Fish Hunt Golf Drink - Luke Bryan</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Firestorm</v>
+        <v>PAGEANT STAGE</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/firestorm/1868827004</v>
+        <v>https://music.apple.com/us/song/pageant-stage/6764125889</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-16</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Of Earth &amp; Wires</v>
+        <v>THE EDGE</v>
       </c>
       <c r="G143" t="str">
-        <v>2:29</v>
+        <v>2:52</v>
       </c>
       <c r="H143" t="str">
-        <v>Dua Saleh</v>
+        <v>Tone Stith</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
+        <v>https://music.apple.com/us/artist/tone-stith/1167717310</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/firestorm/1868826829</v>
+        <v>https://music.apple.com/us/album/pageant-stage/1895651504</v>
       </c>
       <c r="L143" t="str">
-        <v>Firestorm - Dua Saleh</v>
+        <v>PAGEANT STAGE - Tone Stith</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>girl next door</v>
+        <v>Firestorm</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/girl-next-door/6768077610</v>
+        <v>https://music.apple.com/us/song/firestorm/1868827004</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-16</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>girl next door - Single</v>
+        <v>Of Earth &amp; Wires</v>
       </c>
       <c r="G144" t="str">
-        <v>3:18</v>
+        <v>2:29</v>
       </c>
       <c r="H144" t="str">
-        <v>mgk</v>
+        <v>Dua Saleh</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/mgk/465954501</v>
+        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/girl-next-door/6768077609</v>
+        <v>https://music.apple.com/us/album/firestorm/1868826829</v>
       </c>
       <c r="L144" t="str">
-        <v>girl next door - mgk</v>
+        <v>Firestorm - Dua Saleh</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>BIG DOG</v>
+        <v>girl next door</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/big-dog/1887197046</v>
+        <v>https://music.apple.com/us/song/girl-next-door/6768077610</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-16</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
+        <v>girl next door - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:36</v>
+        <v>3:18</v>
       </c>
       <c r="H145" t="str">
-        <v>Genesis Owusu</v>
+        <v>mgk</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
+        <v>https://music.apple.com/us/artist/mgk/465954501</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/big-dog/1887196431</v>
+        <v>https://music.apple.com/us/album/girl-next-door/6768077609</v>
       </c>
       <c r="L145" t="str">
-        <v>BIG DOG - Genesis Owusu</v>
+        <v>girl next door - mgk</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>idea of love - A COLORS SHOW</v>
+        <v>BIG DOG</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/idea-of-love-a-colors-show/6767667046</v>
+        <v>https://music.apple.com/us/song/big-dog/1887197046</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-16</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>idea of love - A COLORS SHOW - Single</v>
+        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
       </c>
       <c r="G146" t="str">
-        <v>2:34</v>
+        <v>3:36</v>
       </c>
       <c r="H146" t="str">
-        <v>kwn</v>
+        <v>Genesis Owusu</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
+        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/idea-of-love-a-colors-show/6767666835</v>
+        <v>https://music.apple.com/us/album/big-dog/1887196431</v>
       </c>
       <c r="L146" t="str">
-        <v>idea of love - A COLORS SHOW - kwn</v>
+        <v>BIG DOG - Genesis Owusu</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Heavy Serenade</v>
+        <v>idea of love - A COLORS SHOW</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/heavy-serenade/1892154309</v>
+        <v>https://music.apple.com/us/song/idea-of-love-a-colors-show/6767667046</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-16</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Heavy Serenade - EP</v>
+        <v>idea of love - A COLORS SHOW - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:00</v>
+        <v>2:34</v>
       </c>
       <c r="H147" t="str">
-        <v>NMIXX</v>
+        <v>kwn</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
+        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/heavy-serenade/1892154305</v>
+        <v>https://music.apple.com/us/album/idea-of-love-a-colors-show/6767666835</v>
       </c>
       <c r="L147" t="str">
-        <v>Heavy Serenade - NMIXX</v>
+        <v>idea of love - A COLORS SHOW - kwn</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>ddok ddok ddok</v>
+        <v>Heavy Serenade</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/ddok-ddok-ddok/6764203482</v>
+        <v>https://music.apple.com/us/song/heavy-serenade/1892154309</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-16</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>ddok ddok ddok - Single</v>
+        <v>Heavy Serenade - EP</v>
       </c>
       <c r="G148" t="str">
-        <v>2:35</v>
+        <v>3:00</v>
       </c>
       <c r="H148" t="str">
-        <v>BOYNEXTDOOR</v>
+        <v>NMIXX</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/boynextdoor/1687612559</v>
+        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/ddok-ddok-ddok/6764203481</v>
+        <v>https://music.apple.com/us/album/heavy-serenade/1892154305</v>
       </c>
       <c r="L148" t="str">
-        <v>ddok ddok ddok - BOYNEXTDOOR</v>
+        <v>Heavy Serenade - NMIXX</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Shut It Down</v>
+        <v>ddok ddok ddok</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/shut-it-down/6763631128</v>
+        <v>https://music.apple.com/us/song/ddok-ddok-ddok/6764203482</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-16</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Shut It Down - Single</v>
+        <v>ddok ddok ddok - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:32</v>
+        <v>2:35</v>
       </c>
       <c r="H149" t="str">
-        <v>Boys Noize</v>
+        <v>BOYNEXTDOOR</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/boys-noize/60393190</v>
+        <v>https://music.apple.com/us/artist/boynextdoor/1687612559</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/shut-it-down/1895408470</v>
+        <v>https://music.apple.com/us/album/ddok-ddok-ddok/6764203481</v>
       </c>
       <c r="L149" t="str">
-        <v>Shut It Down - Boys Noize</v>
+        <v>ddok ddok ddok - BOYNEXTDOOR</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss)</v>
+        <v>Shut It Down</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/together-feat-nikki-nair-jessy-lanza-prentiss/6763207821</v>
+        <v>https://music.apple.com/us/song/shut-it-down/6763631128</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-16</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss) - Single</v>
+        <v>Shut It Down - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:18</v>
+        <v>3:32</v>
       </c>
       <c r="H150" t="str">
-        <v>The Avalanches</v>
+        <v>Boys Noize</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
+        <v>https://music.apple.com/us/artist/boys-noize/60393190</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/together-feat-nikki-nair-jessy-lanza-prentiss/1895215105</v>
+        <v>https://music.apple.com/us/album/shut-it-down/1895408470</v>
       </c>
       <c r="L150" t="str">
-        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss) - The Avalanches</v>
+        <v>Shut It Down - Boys Noize</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Can’t Miss You</v>
+        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss)</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/cant-miss-you/1886810999</v>
+        <v>https://music.apple.com/us/song/together-feat-nikki-nair-jessy-lanza-prentiss/6763207821</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-16</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss) - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:32</v>
+        <v>3:18</v>
       </c>
       <c r="H151" t="str">
-        <v>Sublime</v>
+        <v>The Avalanches</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/sublime/63480</v>
+        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/cant-miss-you/1886810990</v>
+        <v>https://music.apple.com/us/album/together-feat-nikki-nair-jessy-lanza-prentiss/1895215105</v>
       </c>
       <c r="L151" t="str">
-        <v>Can’t Miss You - Sublime</v>
+        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss) - The Avalanches</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Razorblades And Runways</v>
+        <v>Can’t Miss You</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/razorblades-and-runways/1888004809</v>
+        <v>https://music.apple.com/us/song/cant-miss-you/1886810999</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-16</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Get It Honest</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="G152" t="str">
-        <v>3:33</v>
+        <v>2:32</v>
       </c>
       <c r="H152" t="str">
-        <v>The Revivalists</v>
+        <v>Sublime</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
+        <v>https://music.apple.com/us/artist/sublime/63480</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/razorblades-and-runways/1888004802</v>
+        <v>https://music.apple.com/us/album/cant-miss-you/1886810990</v>
       </c>
       <c r="L152" t="str">
-        <v>Razorblades And Runways - The Revivalists</v>
+        <v>Can’t Miss You - Sublime</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Massacre</v>
+        <v>Razorblades And Runways</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/massacre/1892127745</v>
+        <v>https://music.apple.com/us/song/razorblades-and-runways/1888004809</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-16</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Massacre - Single</v>
+        <v>Get It Honest</v>
       </c>
       <c r="G153" t="str">
-        <v>2:55</v>
+        <v>3:33</v>
       </c>
       <c r="H153" t="str">
-        <v>Murex</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/murex/1607430925</v>
+        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/massacre/1892127742</v>
+        <v>https://music.apple.com/us/album/razorblades-and-runways/1888004802</v>
       </c>
       <c r="L153" t="str">
-        <v>Massacre - Murex</v>
+        <v>Razorblades And Runways - The Revivalists</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Better That Way</v>
+        <v>Massacre</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/better-that-way/6766273199</v>
+        <v>https://music.apple.com/us/song/massacre/1892127745</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-16</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Christian Name</v>
+        <v>Massacre - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>3:45</v>
+        <v>2:55</v>
       </c>
       <c r="H154" t="str">
-        <v>Charles Wesley Godwin</v>
+        <v>Murex</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/charles-wesley-godwin/1441994025</v>
+        <v>https://music.apple.com/us/artist/murex/1607430925</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/better-that-way/1896261802</v>
+        <v>https://music.apple.com/us/album/massacre/1892127742</v>
       </c>
       <c r="L154" t="str">
-        <v>Better That Way - Charles Wesley Godwin</v>
+        <v>Massacre - Murex</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Apollo</v>
+        <v>Better That Way</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/apollo/6765602431</v>
+        <v>https://music.apple.com/us/song/better-that-way/6766273199</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-16</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Apollo - Single</v>
+        <v>Christian Name</v>
       </c>
       <c r="G155" t="str">
-        <v>3:35</v>
+        <v>3:45</v>
       </c>
       <c r="H155" t="str">
-        <v>Bryant Barnes</v>
+        <v>Charles Wesley Godwin</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/bryant-barnes/1579668433</v>
+        <v>https://music.apple.com/us/artist/charles-wesley-godwin/1441994025</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/apollo/6765602369</v>
+        <v>https://music.apple.com/us/album/better-that-way/1896261802</v>
       </c>
       <c r="L155" t="str">
-        <v>Apollo - Bryant Barnes</v>
+        <v>Better That Way - Charles Wesley Godwin</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Infinity (123)</v>
+        <v>Apollo</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/infinity-123/6763447312</v>
+        <v>https://music.apple.com/us/song/apollo/6765602431</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-16</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Infinity (123) - Single</v>
+        <v>Apollo - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>2:19</v>
+        <v>3:35</v>
       </c>
       <c r="H156" t="str">
-        <v>December 10</v>
+        <v>Bryant Barnes</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
+        <v>https://music.apple.com/us/artist/bryant-barnes/1579668433</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/infinity-123/1895320456</v>
+        <v>https://music.apple.com/us/album/apollo/6765602369</v>
       </c>
       <c r="L156" t="str">
-        <v>Infinity (123) - December 10</v>
+        <v>Apollo - Bryant Barnes</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Ain't Over Me Yet</v>
+        <v>Infinity (123)</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/aint-over-me-yet/6767283811</v>
+        <v>https://music.apple.com/us/song/infinity-123/6763447312</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-16</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Cherry Valley Forever</v>
+        <v>Infinity (123) - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>3:24</v>
+        <v>2:19</v>
       </c>
       <c r="H157" t="str">
-        <v>Carter Faith</v>
+        <v>December 10</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/carter-faith/1489205896</v>
+        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/aint-over-me-yet/1896458169</v>
+        <v>https://music.apple.com/us/album/infinity-123/1895320456</v>
       </c>
       <c r="L157" t="str">
-        <v>Ain't Over Me Yet - Carter Faith</v>
+        <v>Infinity (123) - December 10</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Where Did You Go</v>
+        <v>Ain't Over Me Yet</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/where-did-you-go/1877958504</v>
+        <v>https://music.apple.com/us/song/aint-over-me-yet/6767283811</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-16</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Growing Pains (Deluxe)</v>
+        <v>Cherry Valley Forever</v>
       </c>
       <c r="G158" t="str">
-        <v>2:47</v>
+        <v>3:24</v>
       </c>
       <c r="H158" t="str">
-        <v>Trousdale</v>
+        <v>Carter Faith</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/carter-faith/1489205896</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/where-did-you-go/1877958112</v>
+        <v>https://music.apple.com/us/album/aint-over-me-yet/1896458169</v>
       </c>
       <c r="L158" t="str">
-        <v>Where Did You Go - Trousdale</v>
+        <v>Ain't Over Me Yet - Carter Faith</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>I LOVE YOU</v>
+        <v>Where Did You Go</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/i-love-you/6766999950</v>
+        <v>https://music.apple.com/us/song/where-did-you-go/1877958504</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-16</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>I LOVE YOU - Single</v>
+        <v>Growing Pains (Deluxe)</v>
       </c>
       <c r="G159" t="str">
-        <v>3:11</v>
+        <v>2:47</v>
       </c>
       <c r="H159" t="str">
-        <v>Noga Erez</v>
+        <v>Trousdale</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/noga-erez/1166657901</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/i-love-you/6766999949</v>
+        <v>https://music.apple.com/us/album/where-did-you-go/1877958112</v>
       </c>
       <c r="L159" t="str">
-        <v>I LOVE YOU - Noga Erez</v>
+        <v>Where Did You Go - Trousdale</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Housekeeping</v>
+        <v>I LOVE YOU</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/housekeeping/6766290834</v>
+        <v>https://music.apple.com/us/song/i-love-you/6766999950</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-16</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Housekeeping - Single</v>
+        <v>I LOVE YOU - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:25</v>
+        <v>3:11</v>
       </c>
       <c r="H160" t="str">
-        <v>Ally Salort</v>
+        <v>Noga Erez</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
+        <v>https://music.apple.com/us/artist/noga-erez/1166657901</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/housekeeping/6766290823</v>
+        <v>https://music.apple.com/us/album/i-love-you/6766999949</v>
       </c>
       <c r="L160" t="str">
-        <v>Housekeeping - Ally Salort</v>
+        <v>I LOVE YOU - Noga Erez</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Surprise Surprise</v>
+        <v>Housekeeping</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/surprise-surprise/6764842119</v>
+        <v>https://music.apple.com/us/song/housekeeping/6766290834</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-16</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Surprise Surprise - Single</v>
+        <v>Housekeeping - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:55</v>
+        <v>3:25</v>
       </c>
       <c r="H161" t="str">
-        <v>Chloe Qisha</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
+        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/surprise-surprise/1895934408</v>
+        <v>https://music.apple.com/us/album/housekeeping/6766290823</v>
       </c>
       <c r="L161" t="str">
-        <v>Surprise Surprise - Chloe Qisha</v>
+        <v>Housekeeping - Ally Salort</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Dog</v>
+        <v>Surprise Surprise</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/dog/1885967384</v>
+        <v>https://music.apple.com/us/song/surprise-surprise/6764842119</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-16</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Gentleman</v>
+        <v>Surprise Surprise - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:08</v>
+        <v>2:55</v>
       </c>
       <c r="H162" t="str">
-        <v>Towa Bird</v>
+        <v>Chloe Qisha</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
+        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/dog/1885967368</v>
+        <v>https://music.apple.com/us/album/surprise-surprise/1895934408</v>
       </c>
       <c r="L162" t="str">
-        <v>Dog - Towa Bird</v>
+        <v>Surprise Surprise - Chloe Qisha</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>I Never See Her</v>
+        <v>Dog</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/i-never-see-her/6764149225</v>
+        <v>https://music.apple.com/us/song/dog/1885967384</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-16</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>I Never See Her - Single</v>
+        <v>Gentleman</v>
       </c>
       <c r="G163" t="str">
-        <v>3:04</v>
+        <v>3:08</v>
       </c>
       <c r="H163" t="str">
-        <v>Spacey Jane</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
+        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/i-never-see-her/1895660748</v>
+        <v>https://music.apple.com/us/album/dog/1885967368</v>
       </c>
       <c r="L163" t="str">
-        <v>I Never See Her - Spacey Jane</v>
+        <v>Dog - Towa Bird</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>No God</v>
+        <v>I Never See Her</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/no-god/1891187414</v>
+        <v>https://music.apple.com/us/song/i-never-see-her/6764149225</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-16</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Alone Together</v>
+        <v>I Never See Her - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:45</v>
+        <v>3:04</v>
       </c>
       <c r="H164" t="str">
-        <v>Show Me the Body</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
+        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/no-god/1891187411</v>
+        <v>https://music.apple.com/us/album/i-never-see-her/1895660748</v>
       </c>
       <c r="L164" t="str">
-        <v>No God - Show Me the Body</v>
+        <v>I Never See Her - Spacey Jane</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>burden</v>
+        <v>No God</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/burden/6767688180</v>
+        <v>https://music.apple.com/us/song/no-god/1891187414</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-16</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>burden - Single</v>
+        <v>Alone Together</v>
       </c>
       <c r="G165" t="str">
-        <v>3:24</v>
+        <v>2:45</v>
       </c>
       <c r="H165" t="str">
-        <v>Abe Parker</v>
+        <v>Show Me the Body</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/abe-parker/490444584</v>
+        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/burden/6767688179</v>
+        <v>https://music.apple.com/us/album/no-god/1891187411</v>
       </c>
       <c r="L165" t="str">
-        <v>burden - Abe Parker</v>
+        <v>No God - Show Me the Body</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Chico Raro</v>
+        <v>burden</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/chico-raro/6767713536</v>
+        <v>https://music.apple.com/us/song/burden/6767688180</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-16</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Chico Raro - Single</v>
+        <v>burden - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:17</v>
+        <v>3:24</v>
       </c>
       <c r="H166" t="str">
-        <v>Arón Piper</v>
+        <v>Abe Parker</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/ar%C3%B3n-piper/691972942</v>
+        <v>https://music.apple.com/us/artist/abe-parker/490444584</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/chico-raro/6767713527</v>
+        <v>https://music.apple.com/us/album/burden/6767688179</v>
       </c>
       <c r="L166" t="str">
-        <v>Chico Raro - Arón Piper</v>
+        <v>burden - Abe Parker</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>What's Done Is Done</v>
+        <v>Chico Raro</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/whats-done-is-done/6763088629</v>
+        <v>https://music.apple.com/us/song/chico-raro/6767713536</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-16</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>What's Done Is Done - Single</v>
+        <v>Chico Raro - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:53</v>
+        <v>3:17</v>
       </c>
       <c r="H167" t="str">
-        <v>Jorja Smith</v>
+        <v>Arón Piper</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
+        <v>https://music.apple.com/us/artist/ar%C3%B3n-piper/691972942</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/whats-done-is-done/1895156626</v>
+        <v>https://music.apple.com/us/album/chico-raro/6767713527</v>
       </c>
       <c r="L167" t="str">
-        <v>What's Done Is Done - Jorja Smith</v>
+        <v>Chico Raro - Arón Piper</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>round and round</v>
+        <v>What's Done Is Done</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/round-and-round/1885665987</v>
+        <v>https://music.apple.com/us/song/whats-done-is-done/6763088629</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-16</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>round and round - Single</v>
+        <v>What's Done Is Done - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>2:47</v>
+        <v>2:53</v>
       </c>
       <c r="H168" t="str">
-        <v>bbno$</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/bbno%24/1161580951</v>
+        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/round-and-round/1885665982</v>
+        <v>https://music.apple.com/us/album/whats-done-is-done/1895156626</v>
       </c>
       <c r="L168" t="str">
-        <v>round and round - bbno$</v>
+        <v>What's Done Is Done - Jorja Smith</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Ain’t That Deep</v>
+        <v>round and round</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/aint-that-deep/1882831449</v>
+        <v>https://music.apple.com/us/song/round-and-round/1885665987</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-16</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>The Last Balloon</v>
+        <v>round and round - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>2:39</v>
+        <v>2:47</v>
       </c>
       <c r="H169" t="str">
-        <v>Tank and the Bangas</v>
+        <v>bbno$</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
+        <v>https://music.apple.com/us/artist/bbno%24/1161580951</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/aint-that-deep/1882831446</v>
+        <v>https://music.apple.com/us/album/round-and-round/1885665982</v>
       </c>
       <c r="L169" t="str">
-        <v>Ain’t That Deep - Tank and the Bangas</v>
+        <v>round and round - bbno$</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Emily</v>
+        <v>Ain’t That Deep</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/emily/1893405442</v>
+        <v>https://music.apple.com/us/song/aint-that-deep/1882831449</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-16</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>So Much To Say - EP</v>
+        <v>The Last Balloon</v>
       </c>
       <c r="G170" t="str">
-        <v>2:35</v>
+        <v>2:39</v>
       </c>
       <c r="H170" t="str">
-        <v>Daisy Grenade</v>
+        <v>Tank and the Bangas</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/daisy-grenade/1611437131</v>
+        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/emily/1893405440</v>
+        <v>https://music.apple.com/us/album/aint-that-deep/1882831446</v>
       </c>
       <c r="L170" t="str">
-        <v>Emily - Daisy Grenade</v>
+        <v>Ain’t That Deep - Tank and the Bangas</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Hold</v>
+        <v>Emily</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/hold/6767296480</v>
+        <v>https://music.apple.com/us/song/emily/1893405442</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-16</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Hold - Single</v>
+        <v>So Much To Say - EP</v>
       </c>
       <c r="G171" t="str">
-        <v>4:07</v>
+        <v>2:35</v>
       </c>
       <c r="H171" t="str">
-        <v>Sabrina Sterling</v>
+        <v>Daisy Grenade</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/sabrina-sterling/1577892147</v>
+        <v>https://music.apple.com/us/artist/daisy-grenade/1611437131</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/hold/1896462063</v>
+        <v>https://music.apple.com/us/album/emily/1893405440</v>
       </c>
       <c r="L171" t="str">
-        <v>Hold - Sabrina Sterling</v>
+        <v>Emily - Daisy Grenade</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Flying Monkey</v>
+        <v>Hold</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/flying-monkey/1894351228</v>
+        <v>https://music.apple.com/us/song/hold/6767296480</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-16</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Flying Monkey - Single</v>
+        <v>Hold - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>4:09</v>
+        <v>4:07</v>
       </c>
       <c r="H172" t="str">
-        <v>Blue Medusa</v>
+        <v>Sabrina Sterling</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
+        <v>https://music.apple.com/us/artist/sabrina-sterling/1577892147</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/flying-monkey/1894351227</v>
+        <v>https://music.apple.com/us/album/hold/1896462063</v>
       </c>
       <c r="L172" t="str">
-        <v>Flying Monkey - Blue Medusa</v>
+        <v>Hold - Sabrina Sterling</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Anything Goes</v>
+        <v>Flying Monkey</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/anything-goes/1891118972</v>
+        <v>https://music.apple.com/us/song/flying-monkey/1894351228</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-16</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Anything Goes</v>
+        <v>Flying Monkey - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:00</v>
+        <v>4:09</v>
       </c>
       <c r="H173" t="str">
-        <v>Kaleena Zanders</v>
+        <v>Blue Medusa</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/anything-goes/1891118971</v>
+        <v>https://music.apple.com/us/album/flying-monkey/1894351227</v>
       </c>
       <c r="L173" t="str">
-        <v>Anything Goes - Kaleena Zanders</v>
+        <v>Flying Monkey - Blue Medusa</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>We Are</v>
+        <v>Anything Goes</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/we-are/1894252873</v>
+        <v>https://music.apple.com/us/song/anything-goes/1891118972</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-16</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>We Are - Single</v>
+        <v>Anything Goes</v>
       </c>
       <c r="G174" t="str">
-        <v>3:33</v>
+        <v>3:00</v>
       </c>
       <c r="H174" t="str">
-        <v>Adam Ten</v>
+        <v>Kaleena Zanders</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/adam-ten/1472226854</v>
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/we-are/1894252870</v>
+        <v>https://music.apple.com/us/album/anything-goes/1891118971</v>
       </c>
       <c r="L174" t="str">
-        <v>We Are - Adam Ten</v>
+        <v>Anything Goes - Kaleena Zanders</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>It's For the Kids</v>
+        <v>We Are</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/its-for-the-kids/1867327679</v>
+        <v>https://music.apple.com/us/song/we-are/1894252873</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-16</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Cursum Perficio</v>
+        <v>We Are - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>4:20</v>
+        <v>3:33</v>
       </c>
       <c r="H175" t="str">
-        <v>Anthrax</v>
+        <v>Adam Ten</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/anthrax/80417</v>
+        <v>https://music.apple.com/us/artist/adam-ten/1472226854</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/its-for-the-kids/1867327673</v>
+        <v>https://music.apple.com/us/album/we-are/1894252870</v>
       </c>
       <c r="L175" t="str">
-        <v>It's For the Kids - Anthrax</v>
+        <v>We Are - Adam Ten</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Pure Ecstasy</v>
+        <v>It's For the Kids</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/pure-ecstasy/6762228978</v>
+        <v>https://music.apple.com/us/song/its-for-the-kids/1867327679</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-16</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Pure Ecstasy</v>
+        <v>Cursum Perficio</v>
       </c>
       <c r="G176" t="str">
-        <v>3:05</v>
+        <v>4:20</v>
       </c>
       <c r="H176" t="str">
-        <v>Beartooth</v>
+        <v>Anthrax</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
+        <v>https://music.apple.com/us/artist/anthrax/80417</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/pure-ecstasy/1893453878</v>
+        <v>https://music.apple.com/us/album/its-for-the-kids/1867327673</v>
       </c>
       <c r="L176" t="str">
-        <v>Pure Ecstasy - Beartooth</v>
+        <v>It's For the Kids - Anthrax</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Something Wicked</v>
+        <v>Pure Ecstasy</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/something-wicked/6766252959</v>
+        <v>https://music.apple.com/us/song/pure-ecstasy/6762228978</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-16</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Something Wicked - Single</v>
+        <v>Pure Ecstasy</v>
       </c>
       <c r="G177" t="str">
-        <v>3:28</v>
+        <v>3:05</v>
       </c>
       <c r="H177" t="str">
-        <v>Breaking Benjamin</v>
+        <v>Beartooth</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/breaking-benjamin/3299379</v>
+        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/something-wicked/1896253678</v>
+        <v>https://music.apple.com/us/album/pure-ecstasy/1893453878</v>
       </c>
       <c r="L177" t="str">
-        <v>Something Wicked - Breaking Benjamin</v>
+        <v>Pure Ecstasy - Beartooth</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Feel The Funk</v>
+        <v>Something Wicked</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/feel-the-funk/6763294007</v>
+        <v>https://music.apple.com/us/song/something-wicked/6766252959</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-16</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>The Funk EP - Single</v>
+        <v>Something Wicked - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:26</v>
+        <v>3:28</v>
       </c>
       <c r="H178" t="str">
-        <v>Riordan</v>
+        <v>Breaking Benjamin</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/riordan/1517575029</v>
+        <v>https://music.apple.com/us/artist/breaking-benjamin/3299379</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/feel-the-funk/1895251685</v>
+        <v>https://music.apple.com/us/album/something-wicked/1896253678</v>
       </c>
       <c r="L178" t="str">
-        <v>Feel The Funk - Riordan</v>
+        <v>Something Wicked - Breaking Benjamin</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Everglades (Remix)</v>
+        <v>Feel The Funk</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/everglades-remix/6767719584</v>
+        <v>https://music.apple.com/us/song/feel-the-funk/6763294007</v>
       </c>
       <c r="D179" t="str">
         <v>2026-05-16</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Everglades (Remix) - Single</v>
+        <v>The Funk EP - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:42</v>
+        <v>3:26</v>
       </c>
       <c r="H179" t="str">
-        <v>Aziedoesntexist</v>
+        <v>Riordan</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/aziedoesntexist/1831152556</v>
+        <v>https://music.apple.com/us/artist/riordan/1517575029</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/everglades-remix/6767719577</v>
+        <v>https://music.apple.com/us/album/feel-the-funk/1895251685</v>
       </c>
       <c r="L179" t="str">
-        <v>Everglades (Remix) - Aziedoesntexist</v>
+        <v>Feel The Funk - Riordan</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Walk</v>
+        <v>Everglades (Remix)</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/walk/1892180098</v>
+        <v>https://music.apple.com/us/song/everglades-remix/6767719584</v>
       </c>
       <c r="D180" t="str">
         <v>2026-05-16</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Walk - Single</v>
+        <v>Everglades (Remix) - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:25</v>
+        <v>2:42</v>
       </c>
       <c r="H180" t="str">
-        <v>Melodicb</v>
+        <v>Aziedoesntexist</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/melodicb/1440206517</v>
+        <v>https://music.apple.com/us/artist/aziedoesntexist/1831152556</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/walk/1892180097</v>
+        <v>https://music.apple.com/us/album/everglades-remix/6767719577</v>
       </c>
       <c r="L180" t="str">
-        <v>Walk - Melodicb</v>
+        <v>Everglades (Remix) - Aziedoesntexist</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Volver a Ti</v>
+        <v>Walk</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/volver-a-ti/6766258204</v>
+        <v>https://music.apple.com/us/song/walk/1892180098</v>
       </c>
       <c r="D181" t="str">
         <v>2026-05-16</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Norteña</v>
+        <v>Walk - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:47</v>
+        <v>2:25</v>
       </c>
       <c r="H181" t="str">
-        <v>Julieta Venegas</v>
+        <v>Melodicb</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/julieta-venegas/302960</v>
+        <v>https://music.apple.com/us/artist/melodicb/1440206517</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/volver-a-ti/1896255736</v>
+        <v>https://music.apple.com/us/album/walk/1892180097</v>
       </c>
       <c r="L181" t="str">
-        <v>Volver a Ti - Julieta Venegas</v>
+        <v>Walk - Melodicb</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Bahamas</v>
+        <v>Volver a Ti</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/bahamas/6764695848</v>
+        <v>https://music.apple.com/us/song/volver-a-ti/6766258204</v>
       </c>
       <c r="D182" t="str">
         <v>2026-05-16</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Bahamas - Single</v>
+        <v>Norteña</v>
       </c>
       <c r="G182" t="str">
-        <v>2:06</v>
+        <v>3:47</v>
       </c>
       <c r="H182" t="str">
-        <v>LENCHO</v>
+        <v>Julieta Venegas</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/lencho/1854923384</v>
+        <v>https://music.apple.com/us/artist/julieta-venegas/302960</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/bahamas/6764695847</v>
+        <v>https://music.apple.com/us/album/volver-a-ti/1896255736</v>
       </c>
       <c r="L182" t="str">
-        <v>Bahamas - LENCHO</v>
+        <v>Volver a Ti - Julieta Venegas</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Same Old Song</v>
+        <v>Bahamas</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/same-old-song/6762860685</v>
+        <v>https://music.apple.com/us/song/bahamas/6764695848</v>
       </c>
       <c r="D183" t="str">
         <v>2026-05-16</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Same Old Song - Single</v>
+        <v>Bahamas - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>4:12</v>
+        <v>2:06</v>
       </c>
       <c r="H183" t="str">
-        <v>Lila Drew</v>
+        <v>LENCHO</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/lila-drew/1439482732</v>
+        <v>https://music.apple.com/us/artist/lencho/1854923384</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/same-old-song/1895047985</v>
+        <v>https://music.apple.com/us/album/bahamas/6764695847</v>
       </c>
       <c r="L183" t="str">
-        <v>Same Old Song - Lila Drew</v>
+        <v>Bahamas - LENCHO</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>gentle</v>
+        <v>Same Old Song</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/gentle/6762828356</v>
+        <v>https://music.apple.com/us/song/same-old-song/6762860685</v>
       </c>
       <c r="D184" t="str">
         <v>2026-05-16</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>gentle - Single</v>
+        <v>Same Old Song - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:48</v>
+        <v>4:12</v>
       </c>
       <c r="H184" t="str">
-        <v>Venus Anon</v>
+        <v>Lila Drew</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/venus-anon/1635970130</v>
+        <v>https://music.apple.com/us/artist/lila-drew/1439482732</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/gentle/1895031896</v>
+        <v>https://music.apple.com/us/album/same-old-song/1895047985</v>
       </c>
       <c r="L184" t="str">
-        <v>gentle - Venus Anon</v>
+        <v>Same Old Song - Lila Drew</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Letters of Your Name</v>
+        <v>gentle</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/letters-of-your-name/1892919741</v>
+        <v>https://music.apple.com/us/song/gentle/6762828356</v>
       </c>
       <c r="D185" t="str">
         <v>2026-05-16</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Congratulations</v>
+        <v>gentle - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:21</v>
+        <v>2:48</v>
       </c>
       <c r="H185" t="str">
-        <v>Jacob Ungerleider</v>
+        <v>Venus Anon</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/jacob-ungerleider/1460845591</v>
+        <v>https://music.apple.com/us/artist/venus-anon/1635970130</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/letters-of-your-name/1892919737</v>
+        <v>https://music.apple.com/us/album/gentle/1895031896</v>
       </c>
       <c r="L185" t="str">
-        <v>Letters of Your Name - Jacob Ungerleider</v>
+        <v>gentle - Venus Anon</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Seratonin</v>
+        <v>Letters of Your Name</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/seratonin/6763447428</v>
+        <v>https://music.apple.com/us/song/letters-of-your-name/1892919741</v>
       </c>
       <c r="D186" t="str">
         <v>2026-05-16</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Seratonin - Single</v>
+        <v>Congratulations</v>
       </c>
       <c r="G186" t="str">
-        <v>1:55</v>
+        <v>3:21</v>
       </c>
       <c r="H186" t="str">
-        <v>James Hype</v>
+        <v>Jacob Ungerleider</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/james-hype/925734064</v>
+        <v>https://music.apple.com/us/artist/jacob-ungerleider/1460845591</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/seratonin/1895320367</v>
+        <v>https://music.apple.com/us/album/letters-of-your-name/1892919737</v>
       </c>
       <c r="L186" t="str">
-        <v>Seratonin - James Hype</v>
+        <v>Letters of Your Name - Jacob Ungerleider</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>A Digital Touch</v>
+        <v>Seratonin</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/a-digital-touch/6765592539</v>
+        <v>https://music.apple.com/us/song/seratonin/6763447428</v>
       </c>
       <c r="D187" t="str">
         <v>2026-05-16</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>A Digital Touch - Single</v>
+        <v>Seratonin - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:53</v>
+        <v>1:55</v>
       </c>
       <c r="H187" t="str">
-        <v>Evening Elephants</v>
+        <v>James Hype</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
+        <v>https://music.apple.com/us/artist/james-hype/925734064</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/a-digital-touch/1896003252</v>
+        <v>https://music.apple.com/us/album/seratonin/1895320367</v>
       </c>
       <c r="L187" t="str">
-        <v>A Digital Touch - Evening Elephants</v>
+        <v>Seratonin - James Hype</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Dead Man's Dog</v>
+        <v>A Digital Touch</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/dead-mans-dog/6763447424</v>
+        <v>https://music.apple.com/us/song/a-digital-touch/6765592539</v>
       </c>
       <c r="D188" t="str">
         <v>2026-05-16</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Aiming Torches At The Sun - EP</v>
+        <v>A Digital Touch - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>4:33</v>
+        <v>2:53</v>
       </c>
       <c r="H188" t="str">
-        <v>Dermot Henry</v>
+        <v>Evening Elephants</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/dermot-henry/1704074611</v>
+        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/dead-mans-dog/1895320369</v>
+        <v>https://music.apple.com/us/album/a-digital-touch/1896003252</v>
       </c>
       <c r="L188" t="str">
-        <v>Dead Man's Dog - Dermot Henry</v>
+        <v>A Digital Touch - Evening Elephants</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Fault of God</v>
+        <v>Dead Man's Dog</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/fault-of-god/1887702403</v>
+        <v>https://music.apple.com/us/song/dead-mans-dog/6763447424</v>
       </c>
       <c r="D189" t="str">
         <v>2026-05-16</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Active Child</v>
+        <v>Aiming Torches At The Sun - EP</v>
       </c>
       <c r="G189" t="str">
-        <v>4:13</v>
+        <v>4:33</v>
       </c>
       <c r="H189" t="str">
-        <v>Active Child</v>
+        <v>Dermot Henry</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/active-child/355288617</v>
+        <v>https://music.apple.com/us/artist/dermot-henry/1704074611</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/fault-of-god/1887701924</v>
+        <v>https://music.apple.com/us/album/dead-mans-dog/1895320369</v>
       </c>
       <c r="L189" t="str">
-        <v>Fault of God - Active Child</v>
+        <v>Dead Man's Dog - Dermot Henry</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Zone (feat. Poppy Baskcomb)</v>
+        <v>Fault of God</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/zone-feat-poppy-baskcomb/6763982867</v>
+        <v>https://music.apple.com/us/song/fault-of-god/1887702403</v>
       </c>
       <c r="D190" t="str">
         <v>2026-05-16</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Zone (feat. Poppy Baskcomb) - Single</v>
+        <v>Active Child</v>
       </c>
       <c r="G190" t="str">
-        <v>2:56</v>
+        <v>4:13</v>
       </c>
       <c r="H190" t="str">
-        <v>MK</v>
+        <v>Active Child</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/mk/63097617</v>
+        <v>https://music.apple.com/us/artist/active-child/355288617</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/zone-feat-poppy-baskcomb/1895585800</v>
+        <v>https://music.apple.com/us/album/fault-of-god/1887701924</v>
       </c>
       <c r="L190" t="str">
-        <v>Zone (feat. Poppy Baskcomb) - MK</v>
+        <v>Fault of God - Active Child</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Word Vomit</v>
+        <v>Zone (feat. Poppy Baskcomb)</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/word-vomit/1887315297</v>
+        <v>https://music.apple.com/us/song/zone-feat-poppy-baskcomb/6763982867</v>
       </c>
       <c r="D191" t="str">
         <v>2026-05-16</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Word Vomit - Single</v>
+        <v>Zone (feat. Poppy Baskcomb) - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>2:46</v>
+        <v>2:56</v>
       </c>
       <c r="H191" t="str">
-        <v>Baby Queen</v>
+        <v>MK</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
+        <v>https://music.apple.com/us/artist/mk/63097617</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/word-vomit/1887315294</v>
+        <v>https://music.apple.com/us/album/zone-feat-poppy-baskcomb/1895585800</v>
       </c>
       <c r="L191" t="str">
-        <v>Word Vomit - Baby Queen</v>
+        <v>Zone (feat. Poppy Baskcomb) - MK</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Evil in this House</v>
+        <v>Word Vomit</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/evil-in-this-house/1892398371</v>
+        <v>https://music.apple.com/us/song/word-vomit/1887315297</v>
       </c>
       <c r="D192" t="str">
         <v>2026-05-16</v>
@@ -7671,68 +7671,106 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Necropolitan</v>
+        <v>Word Vomit - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>4:21</v>
+        <v>2:46</v>
       </c>
       <c r="H192" t="str">
-        <v>Green Lung</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/green-lung/1244071662</v>
+        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/evil-in-this-house/1892398281</v>
+        <v>https://music.apple.com/us/album/word-vomit/1887315294</v>
       </c>
       <c r="L192" t="str">
-        <v>Evil in this House - Green Lung</v>
+        <v>Word Vomit - Baby Queen</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
+        <v>Evil in this House</v>
+      </c>
+      <c r="B193" t="str">
+        <v/>
+      </c>
+      <c r="C193" t="str">
+        <v>https://music.apple.com/us/song/evil-in-this-house/1892398371</v>
+      </c>
+      <c r="D193" t="str">
+        <v>2026-05-16</v>
+      </c>
+      <c r="E193" t="str">
+        <v/>
+      </c>
+      <c r="F193" t="str">
+        <v>Necropolitan</v>
+      </c>
+      <c r="G193" t="str">
+        <v>4:21</v>
+      </c>
+      <c r="H193" t="str">
+        <v>Green Lung</v>
+      </c>
+      <c r="I193" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J193" t="str">
+        <v>https://music.apple.com/us/artist/green-lung/1244071662</v>
+      </c>
+      <c r="K193" t="str">
+        <v>https://music.apple.com/us/album/evil-in-this-house/1892398281</v>
+      </c>
+      <c r="L193" t="str">
+        <v>Evil in this House - Green Lung</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
         <v>Heaven on High</v>
       </c>
-      <c r="B193" t="str">
-        <v/>
-      </c>
-      <c r="C193" t="str">
+      <c r="B194" t="str">
+        <v/>
+      </c>
+      <c r="C194" t="str">
         <v>https://music.apple.com/us/song/heaven-on-high/1881724153</v>
       </c>
-      <c r="D193" t="str">
-        <v>2026-05-16</v>
-      </c>
-      <c r="E193" t="str">
-        <v/>
-      </c>
-      <c r="F193" t="str">
+      <c r="D194" t="str">
+        <v>2026-05-16</v>
+      </c>
+      <c r="E194" t="str">
+        <v/>
+      </c>
+      <c r="F194" t="str">
         <v>A Pale White Dot</v>
       </c>
-      <c r="G193" t="str">
+      <c r="G194" t="str">
         <v>4:19</v>
       </c>
-      <c r="H193" t="str">
+      <c r="H194" t="str">
         <v>Periphery</v>
       </c>
-      <c r="I193" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J193" t="str">
+      <c r="I194" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J194" t="str">
         <v>https://music.apple.com/us/artist/periphery/187683869</v>
       </c>
-      <c r="K193" t="str">
+      <c r="K194" t="str">
         <v>https://music.apple.com/us/album/heaven-on-high/1881724003</v>
       </c>
-      <c r="L193" t="str">
+      <c r="L194" t="str">
         <v>Heaven on High - Periphery</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L193"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L194"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-05-week03/titles.xlsx
+++ b/data/global/2026-05-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L194"/>
+  <dimension ref="A1:L193"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>קרולינה ואורי בראונר כנרות – תפילה</v>
+        <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-16</v>
+        <v>8 days ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a7%d7%a8%d7%95%d7%9c%d7%99%d7%a0%d7%94-%d7%95%d7%90%d7%95%d7%a8%d7%99-%d7%91%d7%a8%d7%90%d7%95%d7%a0%d7%a8-%d7%9b%d7%a0%d7%a8%d7%95%d7%aa-%d7%aa%d7%a4%d7%99%d7%9c%d7%94/</v>
+        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-16</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "תפילה” של קרולינה הוא מהסוג שלא מנסה להרשים בכוח אלא לחלחל לאט. זוהי בלדת פופ־גרוב עדינה ואינטימית, שנשענת פחות על דרמה גדולה ויותר על אמת רגשית חשופה. קרולינה נשארת כאן מאוד “היא”: סאונד חם, אנושי, מלא נשימה ונוכחות, עם</v>
+        <v>8 days ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Harry Styles</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>קרולינה ואורי בראונר כנרות – תפילה</v>
+        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Harry Styles - Dance No More (Official Video)</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
+        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-16</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Harry Styles</v>
+        <v>Eagles</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B4" t="str">
-        <v>8d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
+        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-16</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>8d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Eagles</v>
+        <v>Nora Fatehi</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B5" t="str">
-        <v>6d ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
+        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-16</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>6d ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Nora Fatehi</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B6" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
+        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-16</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Eurovision Song Contest and Alis</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
       </c>
       <c r="B7" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
+        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-16</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Eurovision Song Contest and Alis</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
+        <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>2mo ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
+        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-16</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2mo ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>The Head And The Heart</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
+        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video)</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B9" t="str">
-        <v>7d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
+        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-16</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>7d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>The Head And The Heart</v>
+        <v>Simply Red</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
+        <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>9d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
+        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-16</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>9d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Simply Red</v>
+        <v>Talking Heads</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
+        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video)</v>
+        <v>Ellise - Liplock (Official Music Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>5d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
+        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-16</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>5d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Talking Heads</v>
+        <v>Ellise</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
+        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Ellise - Liplock (Official Music Video)</v>
+        <v>Tori Kelly - Dive (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
+        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-16</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Ellise</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
+        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Tori Kelly - Dive (Official Music Video)</v>
+        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
       </c>
       <c r="B13" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
+        <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-16</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Tori Kelly</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
+        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024) - David Gilmour</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
+        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
       </c>
       <c r="B14" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
+        <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-16</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>David Gilmour</v>
+        <v>Scorpions</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024) - David Gilmour</v>
+        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
+        <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
+        <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-16</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Scorpions</v>
+        <v>Claire Leslie</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022) - Scorpions</v>
+        <v>Claire Leslie - Passenger Seat (Official Music Video) - Claire Leslie</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
+        <v>Michael Schulte - Lovesick (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
+        <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-16</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Claire Leslie</v>
+        <v>Michael Schulte</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Claire Leslie - Passenger Seat (Official Music Video) - Claire Leslie</v>
+        <v>Michael Schulte - Lovesick (Official Video) - Michael Schulte</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Michael Schulte - Lovesick (Official Video)</v>
+        <v>Caity Baser - Holiday Song (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
+        <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-16</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Michael Schulte</v>
+        <v>Caity Baser</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Michael Schulte - Lovesick (Official Video) - Michael Schulte</v>
+        <v>Caity Baser - Holiday Song (Official Video) - Caity Baser</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Caity Baser - Holiday Song (Official Video)</v>
+        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
       </c>
       <c r="B18" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
+        <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-16</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Caity Baser</v>
+        <v>Sam Fischer</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Caity Baser - Holiday Song (Official Video) - Caity Baser</v>
+        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser) - Sam Fischer</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
+        <v>Porches- HABIT (Official Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
+        <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-16</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Sam Fischer</v>
+        <v>Porches</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser) - Sam Fischer</v>
+        <v>Porches- HABIT (Official Video) - Porches</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Porches- HABIT (Official Video)</v>
+        <v>Charli xcx - Rock Music (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
+        <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-16</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Porches</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Porches- HABIT (Official Video) - Porches</v>
+        <v>Charli xcx - Rock Music (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Charli xcx - Rock Music (Official Video)</v>
+        <v>Jon Batiste - Alla Blues (Audio)</v>
       </c>
       <c r="B21" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
+        <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-16</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Charli xcx</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Charli xcx - Rock Music (Official Video) - Charli xcx</v>
+        <v>Jon Batiste - Alla Blues (Audio) - Jon Batiste</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Jon Batiste - Alla Blues (Audio)</v>
+        <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
+        <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-16</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Jon Batiste</v>
+        <v>Tigirlily Gold</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Jon Batiste - Alla Blues (Audio) - Jon Batiste</v>
+        <v>Tigirlily Gold - I Do or Die (Official Music Video) - Tigirlily Gold</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
+        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
+        <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-16</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Tigirlily Gold</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Tigirlily Gold - I Do or Die (Official Music Video) - Tigirlily Gold</v>
+        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
+        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
       </c>
       <c r="B24" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
+        <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-16</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video) - PAUL McCARTNEY</v>
+        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
+        <v>Tori Kelly - Control (Official Visualizer)</v>
       </c>
       <c r="B25" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
+        <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-16</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Bruno Mars</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video] - Bruno Mars</v>
+        <v>Tori Kelly - Control (Official Visualizer) - Tori Kelly</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Tori Kelly - Control (Official Visualizer)</v>
+        <v>Bea Miller - depressed on the internet (Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
+        <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-16</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Tori Kelly</v>
+        <v>bea miller</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Tori Kelly - Control (Official Visualizer) - Tori Kelly</v>
+        <v>Bea Miller - depressed on the internet (Lyric Video) - bea miller</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Bea Miller - depressed on the internet (Lyric Video)</v>
+        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
       </c>
       <c r="B27" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
+        <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-16</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>bea miller</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Bea Miller - depressed on the internet (Lyric Video) - bea miller</v>
+        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
+        <v>Madison Beer - free (Official Audio)</v>
       </c>
       <c r="B28" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
+        <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-16</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>The Chainsmokers</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer) - The Chainsmokers</v>
+        <v>Madison Beer - free (Official Audio) - Madison Beer</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Madison Beer - free (Official Audio)</v>
+        <v>Tori Kelly - Dive (Official Audio)</v>
       </c>
       <c r="B29" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
+        <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-16</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Madison Beer</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Madison Beer - free (Official Audio) - Madison Beer</v>
+        <v>Tori Kelly - Dive (Official Audio) - Tori Kelly</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Tori Kelly - Dive (Official Audio)</v>
+        <v>Jeremy Camp - Reflector (Official Audio)</v>
       </c>
       <c r="B30" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
+        <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-16</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Tori Kelly</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Tori Kelly - Dive (Official Audio) - Tori Kelly</v>
+        <v>Jeremy Camp - Reflector (Official Audio) - JeremyCampMusic</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Jeremy Camp - Reflector (Official Audio)</v>
+        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
       </c>
       <c r="B31" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
+        <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-16</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>JeremyCampMusic</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Jeremy Camp - Reflector (Official Audio) - JeremyCampMusic</v>
+        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
+        <v>Ashley Cooke - high school sweetheart</v>
       </c>
       <c r="B32" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
+        <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-16</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>The Chainsmokers</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer) - The Chainsmokers</v>
+        <v>Ashley Cooke - high school sweetheart - Ashley Cooke</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Ashley Cooke - high school sweetheart</v>
+        <v>Ari Abdul - Ego (Visualizer)</v>
       </c>
       <c r="B33" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
+        <v>https://www.youtube.com/watch?v=L0FjVr6LpVU</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-16</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Ashley Cooke</v>
+        <v>Ari Abdul</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Ashley Cooke - high school sweetheart - Ashley Cooke</v>
+        <v>Ari Abdul - Ego (Visualizer) - Ari Abdul</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Ari Abdul - Ego (Visualizer)</v>
+        <v>Quinn XCII - HOOPLA (Official Music Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=L0FjVr6LpVU</v>
+        <v>https://www.youtube.com/watch?v=eNbGA1pgmFk</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-16</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Ari Abdul</v>
+        <v>Quinn XCII</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Ari Abdul - Ego (Visualizer) - Ari Abdul</v>
+        <v>Quinn XCII - HOOPLA (Official Music Video) - Quinn XCII</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Quinn XCII - HOOPLA (Official Music Video)</v>
+        <v>Madison Beer - lovergirl (Official Music Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=eNbGA1pgmFk</v>
+        <v>https://www.youtube.com/watch?v=q4lU1N3oqYQ</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-16</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Quinn XCII</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Quinn XCII - HOOPLA (Official Music Video) - Quinn XCII</v>
+        <v>Madison Beer - lovergirl (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Madison Beer - lovergirl (Official Music Video)</v>
+        <v>David J - WHAT IF I'M IN LOVE (Official Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=q4lU1N3oqYQ</v>
+        <v>https://www.youtube.com/watch?v=-SF7Hm_ikaY</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-16</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Madison Beer</v>
+        <v>David J</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Madison Beer - lovergirl (Official Music Video) - Madison Beer</v>
+        <v>David J - WHAT IF I'M IN LOVE (Official Video) - David J</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>David J - WHAT IF I'M IN LOVE (Official Video)</v>
+        <v>The Last Dinner Party - Big Dog (On The Road)</v>
       </c>
       <c r="B37" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=-SF7Hm_ikaY</v>
+        <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-16</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>David J</v>
+        <v>The Last Dinner Party</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>David J - WHAT IF I'M IN LOVE (Official Video) - David J</v>
+        <v>The Last Dinner Party - Big Dog (On The Road) - The Last Dinner Party</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>The Last Dinner Party - Big Dog (On The Road)</v>
+        <v>OCEAN ALLEY - HOLD ON (Official Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
+        <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-16</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>The Last Dinner Party</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>The Last Dinner Party - Big Dog (On The Road) - The Last Dinner Party</v>
+        <v>OCEAN ALLEY - HOLD ON (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>OCEAN ALLEY - HOLD ON (Official Video)</v>
+        <v>Dagny - Closet Disco Queen (Lyric Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
+        <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-16</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Ocean Alley</v>
+        <v>Dagny</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>OCEAN ALLEY - HOLD ON (Official Video) - Ocean Alley</v>
+        <v>Dagny - Closet Disco Queen (Lyric Video) - Dagny</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Dagny - Closet Disco Queen (Lyric Video)</v>
+        <v>Purple Disco Machine - Disco Cherry (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
+        <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-16</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Dagny</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Dagny - Closet Disco Queen (Lyric Video) - Dagny</v>
+        <v>Purple Disco Machine - Disco Cherry (Official Video) - Purple Disco Machine</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Purple Disco Machine - Disco Cherry (Official Video)</v>
+        <v>Paris Paloma - Stem the Flow [Official Music Video]</v>
       </c>
       <c r="B41" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
+        <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-16</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Purple Disco Machine - Disco Cherry (Official Video) - Purple Disco Machine</v>
+        <v>Paris Paloma - Stem the Flow [Official Music Video] - Paris Paloma</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Paris Paloma - Stem the Flow [Official Music Video]</v>
+        <v>Lucy Blue - Who you love (Visualiser)</v>
       </c>
       <c r="B42" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
+        <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-16</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Paris Paloma</v>
+        <v>Lucy Blue</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Paris Paloma - Stem the Flow [Official Music Video] - Paris Paloma</v>
+        <v>Lucy Blue - Who you love (Visualiser) - Lucy Blue</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Lucy Blue - Who you love (Visualiser)</v>
+        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026)</v>
       </c>
       <c r="B43" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
+        <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-16</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Lucy Blue</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Lucy Blue - Who you love (Visualiser) - Lucy Blue</v>
+        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026) - Olivia Dean</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026)</v>
+        <v>Aaron Frazer - It's A Shame (Official Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
+        <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-16</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Olivia Dean</v>
+        <v>Aaron Frazer</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026) - Olivia Dean</v>
+        <v>Aaron Frazer - It's A Shame (Official Video) - Aaron Frazer</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Aaron Frazer - It's A Shame (Official Video)</v>
+        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify</v>
       </c>
       <c r="B45" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
+        <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-16</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Aaron Frazer</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Aaron Frazer - It's A Shame (Official Video) - Aaron Frazer</v>
+        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify</v>
+        <v>DANNA - OUT OF MY BODY</v>
       </c>
       <c r="B46" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
+        <v>https://www.youtube.com/watch?v=uW_Ye0kQ9Ac</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-16</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Holly Humberstone</v>
+        <v>Danna</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>DANNA - OUT OF MY BODY - Danna</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>DANNA - OUT OF MY BODY</v>
+        <v>The Rolling Stones - In The Stars (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=uW_Ye0kQ9Ac</v>
+        <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-16</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Danna</v>
+        <v>The Rolling Stones</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>DANNA - OUT OF MY BODY - Danna</v>
+        <v>The Rolling Stones - In The Stars (Official Lyric Video) - The Rolling Stones</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>The Rolling Stones - In The Stars (Official Lyric Video)</v>
+        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser)</v>
       </c>
       <c r="B48" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
+        <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-16</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>The Rolling Stones</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>The Rolling Stones - In The Stars (Official Lyric Video) - The Rolling Stones</v>
+        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser)</v>
+        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
       </c>
       <c r="B49" t="str">
-        <v>10d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
+        <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-16</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>10d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Dermot Kennedy</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser) - Dermot Kennedy</v>
+        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
+        <v>Rick Astley - Raindrops (Official Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
+        <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-16</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2) - SIENNA SPIRO</v>
+        <v>Rick Astley - Raindrops (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Rick Astley - Raindrops (Official Video)</v>
+        <v>Jessie J - THREW IT AWAY (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
+        <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-16</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Rick Astley</v>
+        <v>Jessie J</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Rick Astley - Raindrops (Official Video) - Rick Astley</v>
+        <v>Jessie J - THREW IT AWAY (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Jessie J - THREW IT AWAY (Official Video)</v>
+        <v>The Takes - Ain't Love (Lyric Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
+        <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-16</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Jessie J</v>
+        <v>The Takes</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Jessie J - THREW IT AWAY (Official Video) - Jessie J</v>
+        <v>The Takes - Ain't Love (Lyric Video) - The Takes</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>The Takes - Ain't Love (Lyric Video)</v>
+        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary</v>
       </c>
       <c r="B53" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
+        <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-16</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>The Takes</v>
+        <v>The Offspring</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>The Takes - Ain't Love (Lyric Video) - The Takes</v>
+        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary - The Offspring</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary</v>
+        <v>Louis Tomlinson - Sunflowers (Official Performance Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
+        <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-16</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>The Offspring</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary - The Offspring</v>
+        <v>Louis Tomlinson - Sunflowers (Official Performance Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Louis Tomlinson - Sunflowers (Official Performance Video)</v>
+        <v>The Beaches - Should've Known Better (Official Visualizer)</v>
       </c>
       <c r="B55" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
+        <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-16</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Louis Tomlinson</v>
+        <v>The Beaches</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Louis Tomlinson - Sunflowers (Official Performance Video) - Louis Tomlinson</v>
+        <v>The Beaches - Should've Known Better (Official Visualizer) - The Beaches</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>The Beaches - Should've Known Better (Official Visualizer)</v>
+        <v>The Kiffness - Serafino (Singing Cat Song)</v>
       </c>
       <c r="B56" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
+        <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-16</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>The Beaches</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>The Beaches - Should've Known Better (Official Visualizer) - The Beaches</v>
+        <v>The Kiffness - Serafino (Singing Cat Song) - The Kiffness</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>The Kiffness - Serafino (Singing Cat Song)</v>
+        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer)</v>
       </c>
       <c r="B57" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
+        <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-16</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>The Kiffness</v>
+        <v>Dennis Lloyd</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>The Kiffness - Serafino (Singing Cat Song) - The Kiffness</v>
+        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer) - Dennis Lloyd</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer)</v>
+        <v>Anna Graves - Damn In Love (Official Visualizer)</v>
       </c>
       <c r="B58" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
+        <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-16</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Dennis Lloyd</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer) - Dennis Lloyd</v>
+        <v>Anna Graves - Damn In Love (Official Visualizer) - Anna Graves</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Anna Graves - Damn In Love (Official Visualizer)</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
+        <v>https://www.youtube.com/watch?v=vKzPmy3VUzY</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-16</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Anna Graves</v>
+        <v>Brandon Lake and NICK JONAS</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Anna Graves - Damn In Love (Official Visualizer) - Anna Graves</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video) - Brandon Lake and NICK JONAS</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video)</v>
+        <v>Letdown. - Do It For The Love (Visualizer)</v>
       </c>
       <c r="B60" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=vKzPmy3VUzY</v>
+        <v>https://www.youtube.com/watch?v=vCvZbTEywr8</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-16</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Brandon Lake and NICK JONAS</v>
+        <v>Letdown.</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video) - Brandon Lake and NICK JONAS</v>
+        <v>Letdown. - Do It For The Love (Visualizer) - Letdown.</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Letdown. - Do It For The Love (Visualizer)</v>
+        <v>Maroon 5 - Heroine (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=vCvZbTEywr8</v>
+        <v>https://www.youtube.com/watch?v=izP-4q4YtNw</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-16</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Letdown.</v>
+        <v>Maroon 5</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Letdown. - Do It For The Love (Visualizer) - Letdown.</v>
+        <v>Maroon 5 - Heroine (Official Lyric Video) - Maroon 5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Maroon 5 - Heroine (Official Lyric Video)</v>
+        <v>Olivia O'Brien - I'm Perfect (Official Visualizer)</v>
       </c>
       <c r="B62" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=izP-4q4YtNw</v>
+        <v>https://www.youtube.com/watch?v=leHb8CowDSw</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-16</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Maroon 5</v>
+        <v>Olivia O'Brien</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Maroon 5 - Heroine (Official Lyric Video) - Maroon 5</v>
+        <v>Olivia O'Brien - I'm Perfect (Official Visualizer) - Olivia O'Brien</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Olivia O'Brien - I'm Perfect (Official Visualizer)</v>
+        <v>ERNEST - What's A Little Rain (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=leHb8CowDSw</v>
+        <v>https://www.youtube.com/watch?v=U-3AGDH3mf4</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-16</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Olivia O'Brien</v>
+        <v>ERNEST</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Olivia O'Brien - I'm Perfect (Official Visualizer) - Olivia O'Brien</v>
+        <v>ERNEST - What's A Little Rain (Official Music Video) - ERNEST</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>ERNEST - What's A Little Rain (Official Music Video)</v>
+        <v>Claire Rosinkranz - Just A Man (Official Audio)</v>
       </c>
       <c r="B64" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=U-3AGDH3mf4</v>
+        <v>https://www.youtube.com/watch?v=Ta2I3EHXaDI</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-16</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>ERNEST</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>ERNEST - What's A Little Rain (Official Music Video) - ERNEST</v>
+        <v>Claire Rosinkranz - Just A Man (Official Audio) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Claire Rosinkranz - Just A Man (Official Audio)</v>
+        <v>Halsey - Nothing! (Official Audio)</v>
       </c>
       <c r="B65" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=Ta2I3EHXaDI</v>
+        <v>https://www.youtube.com/watch?v=PBv71KbKvHA</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-16</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Halsey</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Claire Rosinkranz - Just A Man (Official Audio) - Claire Rosinkranz</v>
+        <v>Halsey - Nothing! (Official Audio) - Halsey</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Halsey - Nothing! (Official Audio)</v>
+        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B66" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=PBv71KbKvHA</v>
+        <v>https://www.youtube.com/watch?v=5-f07ca1Zfg</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-16</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Halsey</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Halsey - Nothing! (Official Audio) - Halsey</v>
+        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer) - Zara Larsson</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer)</v>
+        <v>Halsey - Carry the Weight (Official Audio)</v>
       </c>
       <c r="B67" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=5-f07ca1Zfg</v>
+        <v>https://www.youtube.com/watch?v=6MewHp8BX0w</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-16</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Zara Larsson</v>
+        <v>Halsey</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer) - Zara Larsson</v>
+        <v>Halsey - Carry the Weight (Official Audio) - Halsey</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Halsey - Carry the Weight (Official Audio)</v>
+        <v>Bishop Briggs - Blood From A Stone (Official)</v>
       </c>
       <c r="B68" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=6MewHp8BX0w</v>
+        <v>https://www.youtube.com/watch?v=3CK6Zbdk-Nw</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-16</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Halsey</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Halsey - Carry the Weight (Official Audio) - Halsey</v>
+        <v>Bishop Briggs - Blood From A Stone (Official) - Bishop Briggs</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Bishop Briggs - Blood From A Stone (Official)</v>
+        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio)</v>
       </c>
       <c r="B69" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=3CK6Zbdk-Nw</v>
+        <v>https://www.youtube.com/watch?v=6-AWBV5FCN4</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-16</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Bishop Briggs</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Bishop Briggs - Blood From A Stone (Official) - Bishop Briggs</v>
+        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio)</v>
+        <v>almost monday - no more regrets (official video)</v>
       </c>
       <c r="B70" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=6-AWBV5FCN4</v>
+        <v>https://www.youtube.com/watch?v=iczsZVZxHKs</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-16</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Louis Tomlinson</v>
+        <v>almost monday</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio) - Louis Tomlinson</v>
+        <v>almost monday - no more regrets (official video) - almost monday</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>almost monday - no more regrets (official video)</v>
+        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=iczsZVZxHKs</v>
+        <v>https://www.youtube.com/watch?v=lJM-z0ohbkc</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-16</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>almost monday</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>almost monday - no more regrets (official video) - almost monday</v>
+        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video)</v>
+        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=lJM-z0ohbkc</v>
+        <v>https://www.youtube.com/watch?v=6AjhDPwpoLI</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-16</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video) - FULL CIRCLE BOYS</v>
+        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video) - ★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video)</v>
+        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=6AjhDPwpoLI</v>
+        <v>https://www.youtube.com/watch?v=F4ndJUCsHKg</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-16</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
+        <v>NIGHTLY and Fly By Midnight</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video) - ★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
+        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video) - NIGHTLY and Fly By Midnight</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video)</v>
+        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=F4ndJUCsHKg</v>
+        <v>https://www.youtube.com/watch?v=-IEb-ym7VeQ</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-16</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>NIGHTLY and Fly By Midnight</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video) - NIGHTLY and Fly By Midnight</v>
+        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer) - Zara Larsson</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer)</v>
+        <v>JORDANA BRYANT - Truth Is (Official Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=-IEb-ym7VeQ</v>
+        <v>https://www.youtube.com/watch?v=D4meCyyV7SQ</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-16</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Zara Larsson</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer) - Zara Larsson</v>
+        <v>JORDANA BRYANT - Truth Is (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>JORDANA BRYANT - Truth Is (Official Video)</v>
+        <v>Leanna Crawford - Thank God (Lyric Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=D4meCyyV7SQ</v>
+        <v>https://www.youtube.com/watch?v=QqcSoUft03s</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-16</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Jordana Bryant</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>JORDANA BRYANT - Truth Is (Official Video) - Jordana Bryant</v>
+        <v>Leanna Crawford - Thank God (Lyric Video) - Leanna Crawford</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Leanna Crawford - Thank God (Lyric Video)</v>
+        <v>Girl Tones - Stubborn Mouth (Official Music Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=QqcSoUft03s</v>
+        <v>https://www.youtube.com/watch?v=_-PyPUWZTDY</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-16</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Leanna Crawford</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Leanna Crawford - Thank God (Lyric Video) - Leanna Crawford</v>
+        <v>Girl Tones - Stubborn Mouth (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Girl Tones - Stubborn Mouth (Official Music Video)</v>
+        <v>Tauren Wells - What A Miracle Feels Like (Official Audio)</v>
       </c>
       <c r="B78" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=_-PyPUWZTDY</v>
+        <v>https://www.youtube.com/watch?v=ZojFIe4Swmk</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-16</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Girl Tones</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Girl Tones - Stubborn Mouth (Official Music Video) - Girl Tones</v>
+        <v>Tauren Wells - What A Miracle Feels Like (Official Audio) - Tauren Wells</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Tauren Wells - What A Miracle Feels Like (Official Audio)</v>
+        <v>Matthew Ifield - Thinking (Official Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=ZojFIe4Swmk</v>
+        <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-16</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Tauren Wells</v>
+        <v>Matthew Ifield</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Tauren Wells - What A Miracle Feels Like (Official Audio) - Tauren Wells</v>
+        <v>Matthew Ifield - Thinking (Official Video) - Matthew Ifield</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Matthew Ifield - Thinking (Official Video)</v>
+        <v>Dons - Is There Something</v>
       </c>
       <c r="B80" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
+        <v>https://www.youtube.com/watch?v=AgWIjvD-i0E</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-16</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Matthew Ifield</v>
+        <v>Dons</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Matthew Ifield - Thinking (Official Video) - Matthew Ifield</v>
+        <v>Dons - Is There Something - Dons</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Dons - Is There Something</v>
+        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris</v>
       </c>
       <c r="B81" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=AgWIjvD-i0E</v>
+        <v>https://www.youtube.com/watch?v=JXW3SOr7C4w</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-16</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Dons</v>
+        <v>Recording Academy / GRAMMYs and 3 more</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Dons - Is There Something - Dons</v>
+        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris - Recording Academy / GRAMMYs and 3 more</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris</v>
+        <v>Maya Hawke - Lioness (Official Audio)</v>
       </c>
       <c r="B82" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=JXW3SOr7C4w</v>
+        <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-16</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Recording Academy / GRAMMYs and 3 more</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris - Recording Academy / GRAMMYs and 3 more</v>
+        <v>Maya Hawke - Lioness (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Maya Hawke - Lioness (Official Audio)</v>
+        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance</v>
       </c>
       <c r="B83" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
+        <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-16</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Maya Hawke</v>
+        <v>Laufey</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Maya Hawke - Lioness (Official Audio) - Maya Hawke</v>
+        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance - Laufey</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
+        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-16</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Laufey</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance - Laufey</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
+        <v>DANNA - AGAIN</v>
       </c>
       <c r="B85" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
+        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-16</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Keith Urban</v>
+        <v>Danna</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
+        <v>DANNA - AGAIN - Danna</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>DANNA - AGAIN</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
+        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-16</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Danna</v>
+        <v>Armik</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>DANNA - AGAIN - Danna</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>EUROPE - One on One (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
+        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-16</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Armik</v>
+        <v>Europe</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>EUROPE - One on One (Official Video) - Europe</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>EUROPE - One on One (Official Video)</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
       </c>
       <c r="B88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
+        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-16</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Europe</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>EUROPE - One on One (Official Video) - Europe</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
+        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
+        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-16</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Foo Fighters</v>
+        <v>Lady Gaga and Doechii</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
+        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video) - Lady Gaga and Doechii</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video)</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
       </c>
       <c r="B90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
+        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-16</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Lady Gaga and Doechii</v>
+        <v>Muse</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video) - Lady Gaga and Doechii</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
       </c>
       <c r="B91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
+        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-16</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Muse</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
+        <v>Shaboozey - Born To Die (Official Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>2w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
+        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-16</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
+        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Shaboozey - Born To Die (Official Video)</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
       </c>
       <c r="B93" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
+        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-16</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Shaboozey</v>
+        <v>Scorpions</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
+        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-16</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Scorpions</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
+        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-16</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Meghan Trainor</v>
+        <v>Lolo Zouaï</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
+        <v>Bonnie Tyler - One World One Home</v>
       </c>
       <c r="B96" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
+        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-16</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Lolo Zouaï</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
+        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Bonnie Tyler - One World One Home</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
       </c>
       <c r="B97" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
+        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-16</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Bonnie Tyler</v>
+        <v>Jacob Gurevitsch and Prisma Music Group</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
+        <v>Icona Pop - Dance To This (Official Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
+        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-16</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Icona Pop - Dance To This (Official Video)</v>
+        <v>Michael Jackson - Human Nature (Official Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
+        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-16</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Icona Pop</v>
+        <v>Michael Jackson</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
+        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Michael Jackson - Human Nature (Official Video)</v>
+        <v>The All-American Rejects - King Kong</v>
       </c>
       <c r="B100" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
+        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-16</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Michael Jackson</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
+        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>The All-American Rejects - King Kong</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
+        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-16</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>The All-American Rejects</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
+        <v>Hit the Wall</v>
       </c>
       <c r="B102" t="str">
-        <v>3w ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
+        <v>https://music.apple.com/us/song/hit-the-wall/6766750846</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-16</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>3w ago</v>
+        <v>Daughter from Hell</v>
       </c>
       <c r="G102" t="str">
-        <v/>
+        <v>3:14</v>
       </c>
       <c r="H102" t="str">
-        <v>Ringo Starr</v>
+        <v>Gracie Abrams</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/gracie-abrams/1450554836</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/hit-the-wall/6766750836</v>
       </c>
       <c r="L102" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
+        <v>Hit the Wall - Gracie Abrams</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Hit the Wall</v>
+        <v>Ran To Atlanta</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/hit-the-wall/6766750846</v>
+        <v>https://music.apple.com/us/song/ran-to-atlanta/6769568597</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-16</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Daughter from Hell</v>
+        <v>ICEMAN</v>
       </c>
       <c r="G103" t="str">
-        <v>3:14</v>
+        <v>4:07</v>
       </c>
       <c r="H103" t="str">
-        <v>Gracie Abrams</v>
+        <v>Drake</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/gracie-abrams/1450554836</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/hit-the-wall/6766750836</v>
+        <v>https://music.apple.com/us/album/ran-to-atlanta/6769568449</v>
       </c>
       <c r="L103" t="str">
-        <v>Hit the Wall - Gracie Abrams</v>
+        <v>Ran To Atlanta - Drake</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Ran To Atlanta</v>
+        <v>Hoe Phase</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/ran-to-atlanta/6769568597</v>
+        <v>https://music.apple.com/us/song/hoe-phase/6769556949</v>
       </c>
       <c r="D104" t="str">
         <v>2026-05-16</v>
@@ -4327,10 +4327,10 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>ICEMAN</v>
+        <v>MAID OF HONOUR</v>
       </c>
       <c r="G104" t="str">
-        <v>4:07</v>
+        <v>3:23</v>
       </c>
       <c r="H104" t="str">
         <v>Drake</v>
@@ -4342,21 +4342,21 @@
         <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/ran-to-atlanta/6769568449</v>
+        <v>https://music.apple.com/us/album/hoe-phase/6769556940</v>
       </c>
       <c r="L104" t="str">
-        <v>Ran To Atlanta - Drake</v>
+        <v>Hoe Phase - Drake</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Hoe Phase</v>
+        <v>I’m Spent</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/hoe-phase/6769556949</v>
+        <v>https://music.apple.com/us/song/im-spent/6769551476</v>
       </c>
       <c r="D105" t="str">
         <v>2026-05-16</v>
@@ -4365,10 +4365,10 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>MAID OF HONOUR</v>
+        <v>HABIBTI</v>
       </c>
       <c r="G105" t="str">
-        <v>3:23</v>
+        <v>2:24</v>
       </c>
       <c r="H105" t="str">
         <v>Drake</v>
@@ -4380,21 +4380,21 @@
         <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/hoe-phase/6769556940</v>
+        <v>https://music.apple.com/us/album/im-spent/6769551464</v>
       </c>
       <c r="L105" t="str">
-        <v>Hoe Phase - Drake</v>
+        <v>I’m Spent - Drake</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>I’m Spent</v>
+        <v>Abracadabra (Apple Music Live)</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/im-spent/6769551476</v>
+        <v>https://music.apple.com/us/song/abracadabra-apple-music-live/6768201780</v>
       </c>
       <c r="D106" t="str">
         <v>2026-05-16</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>HABIBTI</v>
+        <v>Apple Music Live: MAYHEM Requiem</v>
       </c>
       <c r="G106" t="str">
-        <v>2:24</v>
+        <v>4:04</v>
       </c>
       <c r="H106" t="str">
-        <v>Drake</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/drake/271256</v>
+        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/im-spent/6769551464</v>
+        <v>https://music.apple.com/us/album/abracadabra-apple-music-live/6768201775</v>
       </c>
       <c r="L106" t="str">
-        <v>I’m Spent - Drake</v>
+        <v>Abracadabra (Apple Music Live) - Lady Gaga</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Abracadabra (Apple Music Live)</v>
+        <v>Falling out of Love</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/abracadabra-apple-music-live/6768201780</v>
+        <v>https://music.apple.com/us/song/falling-out-of-love/1891161448</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-16</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Apple Music Live: MAYHEM Requiem</v>
+        <v>Reality Awaits</v>
       </c>
       <c r="G107" t="str">
-        <v>4:04</v>
+        <v>6:21</v>
       </c>
       <c r="H107" t="str">
-        <v>Lady Gaga</v>
+        <v>The Strokes</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
+        <v>https://music.apple.com/us/artist/the-strokes/560289</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/abracadabra-apple-music-live/6768201775</v>
+        <v>https://music.apple.com/us/album/falling-out-of-love/1891161441</v>
       </c>
       <c r="L107" t="str">
-        <v>Abracadabra (Apple Music Live) - Lady Gaga</v>
+        <v>Falling out of Love - The Strokes</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Falling out of Love</v>
+        <v>Dai Dai</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/falling-out-of-love/1891161448</v>
+        <v>https://music.apple.com/us/song/dai-dai/6768469976</v>
       </c>
       <c r="D108" t="str">
         <v>2026-05-16</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Reality Awaits</v>
+        <v>Dai Dai - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>6:21</v>
+        <v>3:43</v>
       </c>
       <c r="H108" t="str">
-        <v>The Strokes</v>
+        <v>Shakira</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/the-strokes/560289</v>
+        <v>https://music.apple.com/us/artist/shakira/889327</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/falling-out-of-love/1891161441</v>
+        <v>https://music.apple.com/us/album/dai-dai/6768469975</v>
       </c>
       <c r="L108" t="str">
-        <v>Falling out of Love - The Strokes</v>
+        <v>Dai Dai - Shakira</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Dai Dai</v>
+        <v>Tu recuerdo</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/dai-dai/6768469976</v>
+        <v>https://music.apple.com/us/song/tu-recuerdo/6763660843</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-16</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Dai Dai - Single</v>
+        <v>Loco X Volver</v>
       </c>
       <c r="G109" t="str">
-        <v>3:43</v>
+        <v>3:55</v>
       </c>
       <c r="H109" t="str">
-        <v>Shakira</v>
+        <v>Maluma</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/shakira/889327</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/dai-dai/6768469975</v>
+        <v>https://music.apple.com/us/album/tu-recuerdo/1895423065</v>
       </c>
       <c r="L109" t="str">
-        <v>Dai Dai - Shakira</v>
+        <v>Tu recuerdo - Maluma</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Tu recuerdo</v>
+        <v>Traitor (Roles Reversed)</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/tu-recuerdo/6763660843</v>
+        <v>https://music.apple.com/us/song/traitor-roles-reversed/6767665959</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-16</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Loco X Volver</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G110" t="str">
-        <v>3:55</v>
+        <v>3:27</v>
       </c>
       <c r="H110" t="str">
-        <v>Maluma</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/tu-recuerdo/1895423065</v>
+        <v>https://music.apple.com/us/album/traitor-roles-reversed/6767665713</v>
       </c>
       <c r="L110" t="str">
-        <v>Tu recuerdo - Maluma</v>
+        <v>Traitor (Roles Reversed) - Megan Moroney</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Traitor (Roles Reversed)</v>
+        <v>Dirty Rosie</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/traitor-roles-reversed/6767665959</v>
+        <v>https://music.apple.com/us/song/dirty-rosie/6767044374</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-16</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Cloud 9</v>
+        <v>Little Miss Twain</v>
       </c>
       <c r="G111" t="str">
-        <v>3:27</v>
+        <v>2:46</v>
       </c>
       <c r="H111" t="str">
-        <v>Megan Moroney</v>
+        <v>Shania Twain</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v>https://music.apple.com/us/artist/shania-twain/129974</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/traitor-roles-reversed/6767665713</v>
+        <v>https://music.apple.com/us/album/dirty-rosie/1896356105</v>
       </c>
       <c r="L111" t="str">
-        <v>Traitor (Roles Reversed) - Megan Moroney</v>
+        <v>Dirty Rosie - Shania Twain</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Dirty Rosie</v>
+        <v>Like you mean it</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/dirty-rosie/6767044374</v>
+        <v>https://music.apple.com/us/song/like-you-mean-it/6767024693</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-16</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Little Miss Twain</v>
+        <v>When the lights turn on</v>
       </c>
       <c r="G112" t="str">
-        <v>2:46</v>
+        <v>2:27</v>
       </c>
       <c r="H112" t="str">
-        <v>Shania Twain</v>
+        <v>MICO</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/shania-twain/129974</v>
+        <v>https://music.apple.com/us/artist/mico/1457367370</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/dirty-rosie/1896356105</v>
+        <v>https://music.apple.com/us/album/like-you-mean-it/6767024688</v>
       </c>
       <c r="L112" t="str">
-        <v>Dirty Rosie - Shania Twain</v>
+        <v>Like you mean it - MICO</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Like you mean it</v>
+        <v>Hardy (feat. Clairo)</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/like-you-mean-it/6767024693</v>
+        <v>https://music.apple.com/us/song/hardy-feat-clairo/1876953073</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-16</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>When the lights turn on</v>
+        <v>American Stories</v>
       </c>
       <c r="G113" t="str">
-        <v>2:27</v>
+        <v>3:53</v>
       </c>
       <c r="H113" t="str">
-        <v>MICO</v>
+        <v>Rostam</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/mico/1457367370</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/like-you-mean-it/6767024688</v>
+        <v>https://music.apple.com/us/album/hardy-feat-clairo/1876952750</v>
       </c>
       <c r="L113" t="str">
-        <v>Like you mean it - MICO</v>
+        <v>Hardy (feat. Clairo) - Rostam</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Hardy (feat. Clairo)</v>
+        <v>2 Hard 4 The Radio</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/hardy-feat-clairo/1876953073</v>
+        <v>https://music.apple.com/us/song/2-hard-4-the-radio/6769568610</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-16</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>American Stories</v>
+        <v>ICEMAN</v>
       </c>
       <c r="G114" t="str">
-        <v>3:53</v>
+        <v>3:03</v>
       </c>
       <c r="H114" t="str">
-        <v>Rostam</v>
+        <v>Drake</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/hardy-feat-clairo/1876952750</v>
+        <v>https://music.apple.com/us/album/2-hard-4-the-radio/6769568449</v>
       </c>
       <c r="L114" t="str">
-        <v>Hardy (feat. Clairo) - Rostam</v>
+        <v>2 Hard 4 The Radio - Drake</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>2 Hard 4 The Radio</v>
+        <v>Cheetah Print</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/2-hard-4-the-radio/6769568610</v>
+        <v>https://music.apple.com/us/song/cheetah-print/6769557055</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-16</v>
@@ -4745,10 +4745,10 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>ICEMAN</v>
+        <v>MAID OF HONOUR</v>
       </c>
       <c r="G115" t="str">
-        <v>3:03</v>
+        <v>3:22</v>
       </c>
       <c r="H115" t="str">
         <v>Drake</v>
@@ -4760,21 +4760,21 @@
         <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/2-hard-4-the-radio/6769568449</v>
+        <v>https://music.apple.com/us/album/cheetah-print/6769556940</v>
       </c>
       <c r="L115" t="str">
-        <v>2 Hard 4 The Radio - Drake</v>
+        <v>Cheetah Print - Drake</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Cheetah Print</v>
+        <v>WNBA</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/cheetah-print/6769557055</v>
+        <v>https://music.apple.com/us/song/wnba/6769551471</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-16</v>
@@ -4783,10 +4783,10 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>MAID OF HONOUR</v>
+        <v>HABIBTI</v>
       </c>
       <c r="G116" t="str">
-        <v>3:22</v>
+        <v>2:58</v>
       </c>
       <c r="H116" t="str">
         <v>Drake</v>
@@ -4798,21 +4798,21 @@
         <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/cheetah-print/6769556940</v>
+        <v>https://music.apple.com/us/album/wnba/6769551464</v>
       </c>
       <c r="L116" t="str">
-        <v>Cheetah Print - Drake</v>
+        <v>WNBA - Drake</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>WNBA</v>
+        <v>Shadow Of A Man (Apple Music Live)</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/wnba/6769551471</v>
+        <v>https://music.apple.com/us/song/shadow-of-a-man-apple-music-live/6768201925</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-16</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>HABIBTI</v>
+        <v>Apple Music Live: MAYHEM Requiem</v>
       </c>
       <c r="G117" t="str">
-        <v>2:58</v>
+        <v>3:36</v>
       </c>
       <c r="H117" t="str">
-        <v>Drake</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/drake/271256</v>
+        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/wnba/6769551464</v>
+        <v>https://music.apple.com/us/album/shadow-of-a-man-apple-music-live/6768201775</v>
       </c>
       <c r="L117" t="str">
-        <v>WNBA - Drake</v>
+        <v>Shadow Of A Man (Apple Music Live) - Lady Gaga</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Shadow Of A Man (Apple Music Live)</v>
+        <v>EPA</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/shadow-of-a-man-apple-music-live/6768201925</v>
+        <v>https://music.apple.com/us/song/epa/6768420253</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-16</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Apple Music Live: MAYHEM Requiem</v>
+        <v>EPA - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:36</v>
+        <v>3:22</v>
       </c>
       <c r="H118" t="str">
-        <v>Lady Gaga</v>
+        <v>Becky G</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
+        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/shadow-of-a-man-apple-music-live/6768201775</v>
+        <v>https://music.apple.com/us/album/epa/6768420251</v>
       </c>
       <c r="L118" t="str">
-        <v>Shadow Of A Man (Apple Music Live) - Lady Gaga</v>
+        <v>EPA - Becky G</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>EPA</v>
+        <v>I’m your girl right?</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/epa/6768420253</v>
+        <v>https://music.apple.com/us/song/im-your-girl-right/6766440186</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-16</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>EPA - Single</v>
+        <v>ESTRUS</v>
       </c>
       <c r="G119" t="str">
-        <v>3:22</v>
+        <v>2:49</v>
       </c>
       <c r="H119" t="str">
-        <v>Becky G</v>
+        <v>Tove Lo</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
+        <v>https://music.apple.com/us/artist/tove-lo/570136838</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/epa/6768420251</v>
+        <v>https://music.apple.com/us/album/im-your-girl-right/6766440172</v>
       </c>
       <c r="L119" t="str">
-        <v>EPA - Becky G</v>
+        <v>I’m your girl right? - Tove Lo</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>I’m your girl right?</v>
+        <v>fuëgo</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/im-your-girl-right/6766440186</v>
+        <v>https://music.apple.com/us/song/fu%C3%ABgo/6767661766</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-16</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>ESTRUS</v>
+        <v>fuëgo - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>2:49</v>
+        <v>3:46</v>
       </c>
       <c r="H120" t="str">
-        <v>Tove Lo</v>
+        <v>BNYX®</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/tove-lo/570136838</v>
+        <v>https://music.apple.com/us/artist/bnyx/1438325287</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/im-your-girl-right/6766440172</v>
+        <v>https://music.apple.com/us/album/fu%C3%ABgo/6767661604</v>
       </c>
       <c r="L120" t="str">
-        <v>I’m your girl right? - Tove Lo</v>
+        <v>fuëgo - BNYX®</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>fuëgo</v>
+        <v>jajaja</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/fu%C3%ABgo/6767661766</v>
+        <v>https://music.apple.com/us/song/jajaja/6766341319</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-16</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>fuëgo - Single</v>
+        <v>jajaja - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:46</v>
+        <v>2:45</v>
       </c>
       <c r="H121" t="str">
-        <v>BNYX®</v>
+        <v>Chino Pacas</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/bnyx/1438325287</v>
+        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/fu%C3%ABgo/6767661604</v>
+        <v>https://music.apple.com/us/album/jajaja/6766341318</v>
       </c>
       <c r="L121" t="str">
-        <v>fuëgo - BNYX®</v>
+        <v>jajaja - Chino Pacas</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>jajaja</v>
+        <v>FIND GOD (feat. Dominic Fike)</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/jajaja/6766341319</v>
+        <v>https://music.apple.com/us/song/find-god-feat-dominic-fike/1894315529</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-16</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>jajaja - Single</v>
+        <v>BULLDAWG</v>
       </c>
       <c r="G122" t="str">
-        <v>2:45</v>
+        <v>3:59</v>
       </c>
       <c r="H122" t="str">
-        <v>Chino Pacas</v>
+        <v>Kenny Mason</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
+        <v>https://music.apple.com/us/artist/kenny-mason/79382206</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/jajaja/6766341318</v>
+        <v>https://music.apple.com/us/album/find-god-feat-dominic-fike/1894315301</v>
       </c>
       <c r="L122" t="str">
-        <v>jajaja - Chino Pacas</v>
+        <v>FIND GOD (feat. Dominic Fike) - Kenny Mason</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>FIND GOD (feat. Dominic Fike)</v>
+        <v>FOOL ME ONCE (feat. Leon Thomas)</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/find-god-feat-dominic-fike/1894315529</v>
+        <v>https://music.apple.com/us/song/fool-me-once-feat-leon-thomas/1891467239</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-16</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>BULLDAWG</v>
+        <v>BELOVED: ACT II</v>
       </c>
       <c r="G123" t="str">
-        <v>3:59</v>
+        <v>3:18</v>
       </c>
       <c r="H123" t="str">
-        <v>Kenny Mason</v>
+        <v>GIVĒON</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/kenny-mason/79382206</v>
+        <v>https://music.apple.com/us/artist/giv%C4%93on/1070668868</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/find-god-feat-dominic-fike/1894315301</v>
+        <v>https://music.apple.com/us/album/fool-me-once-feat-leon-thomas/1891467233</v>
       </c>
       <c r="L123" t="str">
-        <v>FIND GOD (feat. Dominic Fike) - Kenny Mason</v>
+        <v>FOOL ME ONCE (feat. Leon Thomas) - GIVĒON</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>FOOL ME ONCE (feat. Leon Thomas)</v>
+        <v>Shabang</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/fool-me-once-feat-leon-thomas/1891467239</v>
+        <v>https://music.apple.com/us/song/shabang/6769568598</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-16</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>BELOVED: ACT II</v>
+        <v>ICEMAN</v>
       </c>
       <c r="G124" t="str">
-        <v>3:18</v>
+        <v>3:08</v>
       </c>
       <c r="H124" t="str">
-        <v>GIVĒON</v>
+        <v>Drake</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/giv%C4%93on/1070668868</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/fool-me-once-feat-leon-thomas/1891467233</v>
+        <v>https://music.apple.com/us/album/shabang/6769568449</v>
       </c>
       <c r="L124" t="str">
-        <v>FOOL ME ONCE (feat. Leon Thomas) - GIVĒON</v>
+        <v>Shabang - Drake</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Shabang</v>
+        <v>Road Trips</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/shabang/6769568598</v>
+        <v>https://music.apple.com/us/song/road-trips/6769557053</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-16</v>
@@ -5125,10 +5125,10 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>ICEMAN</v>
+        <v>MAID OF HONOUR</v>
       </c>
       <c r="G125" t="str">
-        <v>3:08</v>
+        <v>4:03</v>
       </c>
       <c r="H125" t="str">
         <v>Drake</v>
@@ -5140,21 +5140,21 @@
         <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/shabang/6769568449</v>
+        <v>https://music.apple.com/us/album/road-trips/6769556940</v>
       </c>
       <c r="L125" t="str">
-        <v>Shabang - Drake</v>
+        <v>Road Trips - Drake</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Road Trips</v>
+        <v>Fortworth</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/road-trips/6769557053</v>
+        <v>https://music.apple.com/us/song/fortworth/6769551482</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-16</v>
@@ -5163,10 +5163,10 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>MAID OF HONOUR</v>
+        <v>HABIBTI</v>
       </c>
       <c r="G126" t="str">
-        <v>4:03</v>
+        <v>3:51</v>
       </c>
       <c r="H126" t="str">
         <v>Drake</v>
@@ -5178,21 +5178,21 @@
         <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/road-trips/6769556940</v>
+        <v>https://music.apple.com/us/album/fortworth/6769551464</v>
       </c>
       <c r="L126" t="str">
-        <v>Road Trips - Drake</v>
+        <v>Fortworth - Drake</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Fortworth</v>
+        <v>Repeat It</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/fortworth/6769551482</v>
+        <v>https://music.apple.com/us/song/repeat-it/6764277864</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-16</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>HABIBTI</v>
+        <v>Repeat It - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:51</v>
+        <v>3:11</v>
       </c>
       <c r="H127" t="str">
-        <v>Drake</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/drake/271256</v>
+        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/fortworth/6769551464</v>
+        <v>https://music.apple.com/us/album/repeat-it/1895713789</v>
       </c>
       <c r="L127" t="str">
-        <v>Fortworth - Drake</v>
+        <v>Repeat It - Martin Garrix</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Repeat It</v>
+        <v>Fool Proof</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/repeat-it/6764277864</v>
+        <v>https://music.apple.com/us/song/fool-proof/1892466004</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-16</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Repeat It - Single</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G128" t="str">
-        <v>3:11</v>
+        <v>2:36</v>
       </c>
       <c r="H128" t="str">
-        <v>Martin Garrix</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/repeat-it/1895713789</v>
+        <v>https://music.apple.com/us/album/fool-proof/1892465981</v>
       </c>
       <c r="L128" t="str">
-        <v>Repeat It - Martin Garrix</v>
+        <v>Fool Proof - Cody Johnson</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Fool Proof</v>
+        <v>Crisco</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/fool-proof/1892466004</v>
+        <v>https://music.apple.com/us/song/crisco/6763369506</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-16</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>Crisco - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>2:36</v>
+        <v>2:56</v>
       </c>
       <c r="H129" t="str">
-        <v>Cody Johnson</v>
+        <v>Miranda Lambert</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/miranda-lambert/18732261</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/fool-proof/1892465981</v>
+        <v>https://music.apple.com/us/album/crisco/1895284236</v>
       </c>
       <c r="L129" t="str">
-        <v>Fool Proof - Cody Johnson</v>
+        <v>Crisco - Miranda Lambert</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Crisco</v>
+        <v>Absolution</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/crisco/6763369506</v>
+        <v>https://music.apple.com/us/song/absolution/1884987651</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-16</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Crisco - Single</v>
+        <v>Forever Now</v>
       </c>
       <c r="G130" t="str">
-        <v>2:56</v>
+        <v>4:05</v>
       </c>
       <c r="H130" t="str">
-        <v>Miranda Lambert</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/miranda-lambert/18732261</v>
+        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/crisco/1895284236</v>
+        <v>https://music.apple.com/us/album/absolution/1884987638</v>
       </c>
       <c r="L130" t="str">
-        <v>Crisco - Miranda Lambert</v>
+        <v>Absolution - Switchfoot</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Absolution</v>
+        <v>JESUS IS ALIVE</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/absolution/1884987651</v>
+        <v>https://music.apple.com/us/song/jesus-is-alive/6767694896</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-16</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Forever Now</v>
+        <v>JESUS IS ALIVE - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>4:05</v>
+        <v>2:08</v>
       </c>
       <c r="H131" t="str">
-        <v>Switchfoot</v>
+        <v>Forrest Frank</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
+        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/absolution/1884987638</v>
+        <v>https://music.apple.com/us/album/jesus-is-alive/6767694895</v>
       </c>
       <c r="L131" t="str">
-        <v>Absolution - Switchfoot</v>
+        <v>JESUS IS ALIVE - Forrest Frank</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>JESUS IS ALIVE</v>
+        <v>Something To Lose</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/jesus-is-alive/6767694896</v>
+        <v>https://music.apple.com/us/song/something-to-lose/6766964605</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-16</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>JESUS IS ALIVE - Single</v>
+        <v>Is This Heaven? - EP</v>
       </c>
       <c r="G132" t="str">
-        <v>2:08</v>
+        <v>2:55</v>
       </c>
       <c r="H132" t="str">
-        <v>Forrest Frank</v>
+        <v>STELLA LEFTY</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
+        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/jesus-is-alive/6767694895</v>
+        <v>https://music.apple.com/us/album/something-to-lose/6766964604</v>
       </c>
       <c r="L132" t="str">
-        <v>JESUS IS ALIVE - Forrest Frank</v>
+        <v>Something To Lose - STELLA LEFTY</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Something To Lose</v>
+        <v>Too Busy Missing You</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/something-to-lose/6766964605</v>
+        <v>https://music.apple.com/us/song/too-busy-missing-you/6766604915</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-16</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Is This Heaven? - EP</v>
+        <v>Off Campus: The Mixtape</v>
       </c>
       <c r="G133" t="str">
-        <v>2:55</v>
+        <v>3:25</v>
       </c>
       <c r="H133" t="str">
-        <v>STELLA LEFTY</v>
+        <v>Asha Banks</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
+        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/something-to-lose/6766964604</v>
+        <v>https://music.apple.com/us/album/too-busy-missing-you/6766604455</v>
       </c>
       <c r="L133" t="str">
-        <v>Something To Lose - STELLA LEFTY</v>
+        <v>Too Busy Missing You - Asha Banks</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Too Busy Missing You</v>
+        <v>F-Stop Blues (4-track)</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/too-busy-missing-you/6766604915</v>
+        <v>https://music.apple.com/us/song/f-stop-blues-4-track/1883173173</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-16</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Off Campus: The Mixtape</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G134" t="str">
-        <v>3:25</v>
+        <v>3:00</v>
       </c>
       <c r="H134" t="str">
-        <v>Asha Banks</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/too-busy-missing-you/6766604455</v>
+        <v>https://music.apple.com/us/album/f-stop-blues-4-track/1883172879</v>
       </c>
       <c r="L134" t="str">
-        <v>Too Busy Missing You - Asha Banks</v>
+        <v>F-Stop Blues (4-track) - Jack Johnson</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>F-Stop Blues (4-track)</v>
+        <v>PA' LO BONITO</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/f-stop-blues-4-track/1883173173</v>
+        <v>https://music.apple.com/us/song/pa-lo-bonito/1886496944</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-16</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>PA' LO BONITO - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:00</v>
+        <v>3:04</v>
       </c>
       <c r="H135" t="str">
-        <v>Jack Johnson</v>
+        <v>Lenny Tavárez</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/f-stop-blues-4-track/1883172879</v>
+        <v>https://music.apple.com/us/album/pa-lo-bonito/1886496943</v>
       </c>
       <c r="L135" t="str">
-        <v>F-Stop Blues (4-track) - Jack Johnson</v>
+        <v>PA' LO BONITO - Lenny Tavárez</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>PA' LO BONITO</v>
+        <v>LONELY</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/pa-lo-bonito/1886496944</v>
+        <v>https://music.apple.com/us/song/lonely/6768757857</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-16</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>PA' LO BONITO - Single</v>
+        <v>DESEO</v>
       </c>
       <c r="G136" t="str">
-        <v>3:04</v>
+        <v>2:58</v>
       </c>
       <c r="H136" t="str">
-        <v>Lenny Tavárez</v>
+        <v>Katteyes</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
+        <v>https://music.apple.com/us/artist/katteyes/1648818255</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/pa-lo-bonito/1886496943</v>
+        <v>https://music.apple.com/us/album/lonely/6768757414</v>
       </c>
       <c r="L136" t="str">
-        <v>PA' LO BONITO - Lenny Tavárez</v>
+        <v>LONELY - Katteyes</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>LONELY</v>
+        <v>Lockup</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/lonely/6768757857</v>
+        <v>https://music.apple.com/us/song/lockup/1894298102</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-16</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>DESEO</v>
+        <v>Pure Devotion</v>
       </c>
       <c r="G137" t="str">
-        <v>2:58</v>
+        <v>4:31</v>
       </c>
       <c r="H137" t="str">
-        <v>Katteyes</v>
+        <v>Overmono</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/katteyes/1648818255</v>
+        <v>https://music.apple.com/us/artist/overmono/1129806758</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/lonely/6768757414</v>
+        <v>https://music.apple.com/us/album/lockup/1894298100</v>
       </c>
       <c r="L137" t="str">
-        <v>LONELY - Katteyes</v>
+        <v>Lockup - Overmono</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Lockup</v>
+        <v>Young</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/lockup/1894298102</v>
+        <v>https://music.apple.com/us/song/young/6767698952</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-16</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Pure Devotion</v>
+        <v>Young</v>
       </c>
       <c r="G138" t="str">
-        <v>4:31</v>
+        <v>2:46</v>
       </c>
       <c r="H138" t="str">
-        <v>Overmono</v>
+        <v>Dan + Shay</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/overmono/1129806758</v>
+        <v>https://music.apple.com/us/artist/dan-shay/690319057</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/lockup/1894298100</v>
+        <v>https://music.apple.com/us/album/young/6767698951</v>
       </c>
       <c r="L138" t="str">
-        <v>Lockup - Overmono</v>
+        <v>Young - Dan + Shay</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Young</v>
+        <v>Parachute</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/young/6767698952</v>
+        <v>https://music.apple.com/us/song/parachute/6764119241</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-16</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Young</v>
+        <v>Parachute - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>2:46</v>
+        <v>2:52</v>
       </c>
       <c r="H139" t="str">
-        <v>Dan + Shay</v>
+        <v>Maren Morris</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/dan-shay/690319057</v>
+        <v>https://music.apple.com/us/artist/maren-morris/262260873</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/young/6767698951</v>
+        <v>https://music.apple.com/us/album/parachute/1895648983</v>
       </c>
       <c r="L139" t="str">
-        <v>Young - Dan + Shay</v>
+        <v>Parachute - Maren Morris</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Parachute</v>
+        <v>Little Things</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/parachute/6764119241</v>
+        <v>https://music.apple.com/us/song/little-things/6766351153</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-16</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Parachute - Single</v>
+        <v>Little Things - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:52</v>
+        <v>2:55</v>
       </c>
       <c r="H140" t="str">
-        <v>Maren Morris</v>
+        <v>Kevin Jonas</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/maren-morris/262260873</v>
+        <v>https://music.apple.com/us/artist/kevin-jonas/21138190</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/parachute/1895648983</v>
+        <v>https://music.apple.com/us/album/little-things/6766350882</v>
       </c>
       <c r="L140" t="str">
-        <v>Parachute - Maren Morris</v>
+        <v>Little Things - Kevin Jonas</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Little Things</v>
+        <v>Fish Hunt Golf Drink</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/little-things/6766351153</v>
+        <v>https://music.apple.com/us/song/fish-hunt-golf-drink/6766651884</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-16</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Little Things - Single</v>
+        <v>Signs</v>
       </c>
       <c r="G141" t="str">
-        <v>2:55</v>
+        <v>2:34</v>
       </c>
       <c r="H141" t="str">
-        <v>Kevin Jonas</v>
+        <v>Luke Bryan</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/kevin-jonas/21138190</v>
+        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/little-things/6766350882</v>
+        <v>https://music.apple.com/us/album/fish-hunt-golf-drink/6766651878</v>
       </c>
       <c r="L141" t="str">
-        <v>Little Things - Kevin Jonas</v>
+        <v>Fish Hunt Golf Drink - Luke Bryan</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Fish Hunt Golf Drink</v>
+        <v>PAGEANT STAGE</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/fish-hunt-golf-drink/6766651884</v>
+        <v>https://music.apple.com/us/song/pageant-stage/6764125889</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-16</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Signs</v>
+        <v>THE EDGE</v>
       </c>
       <c r="G142" t="str">
-        <v>2:34</v>
+        <v>2:52</v>
       </c>
       <c r="H142" t="str">
-        <v>Luke Bryan</v>
+        <v>Tone Stith</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
+        <v>https://music.apple.com/us/artist/tone-stith/1167717310</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/fish-hunt-golf-drink/6766651878</v>
+        <v>https://music.apple.com/us/album/pageant-stage/1895651504</v>
       </c>
       <c r="L142" t="str">
-        <v>Fish Hunt Golf Drink - Luke Bryan</v>
+        <v>PAGEANT STAGE - Tone Stith</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>PAGEANT STAGE</v>
+        <v>Firestorm</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/pageant-stage/6764125889</v>
+        <v>https://music.apple.com/us/song/firestorm/1868827004</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-16</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>THE EDGE</v>
+        <v>Of Earth &amp; Wires</v>
       </c>
       <c r="G143" t="str">
-        <v>2:52</v>
+        <v>2:29</v>
       </c>
       <c r="H143" t="str">
-        <v>Tone Stith</v>
+        <v>Dua Saleh</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/tone-stith/1167717310</v>
+        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/pageant-stage/1895651504</v>
+        <v>https://music.apple.com/us/album/firestorm/1868826829</v>
       </c>
       <c r="L143" t="str">
-        <v>PAGEANT STAGE - Tone Stith</v>
+        <v>Firestorm - Dua Saleh</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Firestorm</v>
+        <v>girl next door</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/firestorm/1868827004</v>
+        <v>https://music.apple.com/us/song/girl-next-door/6768077610</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-16</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Of Earth &amp; Wires</v>
+        <v>girl next door - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>2:29</v>
+        <v>3:18</v>
       </c>
       <c r="H144" t="str">
-        <v>Dua Saleh</v>
+        <v>mgk</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
+        <v>https://music.apple.com/us/artist/mgk/465954501</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/firestorm/1868826829</v>
+        <v>https://music.apple.com/us/album/girl-next-door/6768077609</v>
       </c>
       <c r="L144" t="str">
-        <v>Firestorm - Dua Saleh</v>
+        <v>girl next door - mgk</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>girl next door</v>
+        <v>BIG DOG</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/girl-next-door/6768077610</v>
+        <v>https://music.apple.com/us/song/big-dog/1887197046</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-16</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>girl next door - Single</v>
+        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
       </c>
       <c r="G145" t="str">
-        <v>3:18</v>
+        <v>3:36</v>
       </c>
       <c r="H145" t="str">
-        <v>mgk</v>
+        <v>Genesis Owusu</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/mgk/465954501</v>
+        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/girl-next-door/6768077609</v>
+        <v>https://music.apple.com/us/album/big-dog/1887196431</v>
       </c>
       <c r="L145" t="str">
-        <v>girl next door - mgk</v>
+        <v>BIG DOG - Genesis Owusu</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>BIG DOG</v>
+        <v>idea of love - A COLORS SHOW</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/big-dog/1887197046</v>
+        <v>https://music.apple.com/us/song/idea-of-love-a-colors-show/6767667046</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-16</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
+        <v>idea of love - A COLORS SHOW - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:36</v>
+        <v>2:34</v>
       </c>
       <c r="H146" t="str">
-        <v>Genesis Owusu</v>
+        <v>kwn</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
+        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/big-dog/1887196431</v>
+        <v>https://music.apple.com/us/album/idea-of-love-a-colors-show/6767666835</v>
       </c>
       <c r="L146" t="str">
-        <v>BIG DOG - Genesis Owusu</v>
+        <v>idea of love - A COLORS SHOW - kwn</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>idea of love - A COLORS SHOW</v>
+        <v>Heavy Serenade</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/idea-of-love-a-colors-show/6767667046</v>
+        <v>https://music.apple.com/us/song/heavy-serenade/1892154309</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-16</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>idea of love - A COLORS SHOW - Single</v>
+        <v>Heavy Serenade - EP</v>
       </c>
       <c r="G147" t="str">
-        <v>2:34</v>
+        <v>3:00</v>
       </c>
       <c r="H147" t="str">
-        <v>kwn</v>
+        <v>NMIXX</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
+        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/idea-of-love-a-colors-show/6767666835</v>
+        <v>https://music.apple.com/us/album/heavy-serenade/1892154305</v>
       </c>
       <c r="L147" t="str">
-        <v>idea of love - A COLORS SHOW - kwn</v>
+        <v>Heavy Serenade - NMIXX</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Heavy Serenade</v>
+        <v>ddok ddok ddok</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/heavy-serenade/1892154309</v>
+        <v>https://music.apple.com/us/song/ddok-ddok-ddok/6764203482</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-16</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Heavy Serenade - EP</v>
+        <v>ddok ddok ddok - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:00</v>
+        <v>2:35</v>
       </c>
       <c r="H148" t="str">
-        <v>NMIXX</v>
+        <v>BOYNEXTDOOR</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
+        <v>https://music.apple.com/us/artist/boynextdoor/1687612559</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/heavy-serenade/1892154305</v>
+        <v>https://music.apple.com/us/album/ddok-ddok-ddok/6764203481</v>
       </c>
       <c r="L148" t="str">
-        <v>Heavy Serenade - NMIXX</v>
+        <v>ddok ddok ddok - BOYNEXTDOOR</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>ddok ddok ddok</v>
+        <v>Shut It Down</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/ddok-ddok-ddok/6764203482</v>
+        <v>https://music.apple.com/us/song/shut-it-down/6763631128</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-16</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>ddok ddok ddok - Single</v>
+        <v>Shut It Down - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>2:35</v>
+        <v>3:32</v>
       </c>
       <c r="H149" t="str">
-        <v>BOYNEXTDOOR</v>
+        <v>Boys Noize</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/boynextdoor/1687612559</v>
+        <v>https://music.apple.com/us/artist/boys-noize/60393190</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/ddok-ddok-ddok/6764203481</v>
+        <v>https://music.apple.com/us/album/shut-it-down/1895408470</v>
       </c>
       <c r="L149" t="str">
-        <v>ddok ddok ddok - BOYNEXTDOOR</v>
+        <v>Shut It Down - Boys Noize</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Shut It Down</v>
+        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss)</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/shut-it-down/6763631128</v>
+        <v>https://music.apple.com/us/song/together-feat-nikki-nair-jessy-lanza-prentiss/6763207821</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-16</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Shut It Down - Single</v>
+        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss) - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:32</v>
+        <v>3:18</v>
       </c>
       <c r="H150" t="str">
-        <v>Boys Noize</v>
+        <v>The Avalanches</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/boys-noize/60393190</v>
+        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/shut-it-down/1895408470</v>
+        <v>https://music.apple.com/us/album/together-feat-nikki-nair-jessy-lanza-prentiss/1895215105</v>
       </c>
       <c r="L150" t="str">
-        <v>Shut It Down - Boys Noize</v>
+        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss) - The Avalanches</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss)</v>
+        <v>Can’t Miss You</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/together-feat-nikki-nair-jessy-lanza-prentiss/6763207821</v>
+        <v>https://music.apple.com/us/song/cant-miss-you/1886810999</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-16</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss) - Single</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="G151" t="str">
-        <v>3:18</v>
+        <v>2:32</v>
       </c>
       <c r="H151" t="str">
-        <v>The Avalanches</v>
+        <v>Sublime</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
+        <v>https://music.apple.com/us/artist/sublime/63480</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/together-feat-nikki-nair-jessy-lanza-prentiss/1895215105</v>
+        <v>https://music.apple.com/us/album/cant-miss-you/1886810990</v>
       </c>
       <c r="L151" t="str">
-        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss) - The Avalanches</v>
+        <v>Can’t Miss You - Sublime</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Can’t Miss You</v>
+        <v>Razorblades And Runways</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/cant-miss-you/1886810999</v>
+        <v>https://music.apple.com/us/song/razorblades-and-runways/1888004809</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-16</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>Get It Honest</v>
       </c>
       <c r="G152" t="str">
-        <v>2:32</v>
+        <v>3:33</v>
       </c>
       <c r="H152" t="str">
-        <v>Sublime</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/sublime/63480</v>
+        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/cant-miss-you/1886810990</v>
+        <v>https://music.apple.com/us/album/razorblades-and-runways/1888004802</v>
       </c>
       <c r="L152" t="str">
-        <v>Can’t Miss You - Sublime</v>
+        <v>Razorblades And Runways - The Revivalists</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Razorblades And Runways</v>
+        <v>Massacre</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/razorblades-and-runways/1888004809</v>
+        <v>https://music.apple.com/us/song/massacre/1892127745</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-16</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Get It Honest</v>
+        <v>Massacre - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>3:33</v>
+        <v>2:55</v>
       </c>
       <c r="H153" t="str">
-        <v>The Revivalists</v>
+        <v>Murex</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
+        <v>https://music.apple.com/us/artist/murex/1607430925</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/razorblades-and-runways/1888004802</v>
+        <v>https://music.apple.com/us/album/massacre/1892127742</v>
       </c>
       <c r="L153" t="str">
-        <v>Razorblades And Runways - The Revivalists</v>
+        <v>Massacre - Murex</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Massacre</v>
+        <v>Better That Way</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/massacre/1892127745</v>
+        <v>https://music.apple.com/us/song/better-that-way/6766273199</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-16</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Massacre - Single</v>
+        <v>Christian Name</v>
       </c>
       <c r="G154" t="str">
-        <v>2:55</v>
+        <v>3:45</v>
       </c>
       <c r="H154" t="str">
-        <v>Murex</v>
+        <v>Charles Wesley Godwin</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/murex/1607430925</v>
+        <v>https://music.apple.com/us/artist/charles-wesley-godwin/1441994025</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/massacre/1892127742</v>
+        <v>https://music.apple.com/us/album/better-that-way/1896261802</v>
       </c>
       <c r="L154" t="str">
-        <v>Massacre - Murex</v>
+        <v>Better That Way - Charles Wesley Godwin</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Better That Way</v>
+        <v>Apollo</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/better-that-way/6766273199</v>
+        <v>https://music.apple.com/us/song/apollo/6765602431</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-16</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Christian Name</v>
+        <v>Apollo - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:45</v>
+        <v>3:35</v>
       </c>
       <c r="H155" t="str">
-        <v>Charles Wesley Godwin</v>
+        <v>Bryant Barnes</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/charles-wesley-godwin/1441994025</v>
+        <v>https://music.apple.com/us/artist/bryant-barnes/1579668433</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/better-that-way/1896261802</v>
+        <v>https://music.apple.com/us/album/apollo/6765602369</v>
       </c>
       <c r="L155" t="str">
-        <v>Better That Way - Charles Wesley Godwin</v>
+        <v>Apollo - Bryant Barnes</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Apollo</v>
+        <v>Infinity (123)</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/apollo/6765602431</v>
+        <v>https://music.apple.com/us/song/infinity-123/6763447312</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-16</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Apollo - Single</v>
+        <v>Infinity (123) - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:35</v>
+        <v>2:19</v>
       </c>
       <c r="H156" t="str">
-        <v>Bryant Barnes</v>
+        <v>December 10</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/bryant-barnes/1579668433</v>
+        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/apollo/6765602369</v>
+        <v>https://music.apple.com/us/album/infinity-123/1895320456</v>
       </c>
       <c r="L156" t="str">
-        <v>Apollo - Bryant Barnes</v>
+        <v>Infinity (123) - December 10</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Infinity (123)</v>
+        <v>Ain't Over Me Yet</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/infinity-123/6763447312</v>
+        <v>https://music.apple.com/us/song/aint-over-me-yet/6767283811</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-16</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Infinity (123) - Single</v>
+        <v>Cherry Valley Forever</v>
       </c>
       <c r="G157" t="str">
-        <v>2:19</v>
+        <v>3:24</v>
       </c>
       <c r="H157" t="str">
-        <v>December 10</v>
+        <v>Carter Faith</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
+        <v>https://music.apple.com/us/artist/carter-faith/1489205896</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/infinity-123/1895320456</v>
+        <v>https://music.apple.com/us/album/aint-over-me-yet/1896458169</v>
       </c>
       <c r="L157" t="str">
-        <v>Infinity (123) - December 10</v>
+        <v>Ain't Over Me Yet - Carter Faith</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Ain't Over Me Yet</v>
+        <v>Where Did You Go</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/aint-over-me-yet/6767283811</v>
+        <v>https://music.apple.com/us/song/where-did-you-go/1877958504</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-16</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Cherry Valley Forever</v>
+        <v>Growing Pains (Deluxe)</v>
       </c>
       <c r="G158" t="str">
-        <v>3:24</v>
+        <v>2:47</v>
       </c>
       <c r="H158" t="str">
-        <v>Carter Faith</v>
+        <v>Trousdale</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/carter-faith/1489205896</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/aint-over-me-yet/1896458169</v>
+        <v>https://music.apple.com/us/album/where-did-you-go/1877958112</v>
       </c>
       <c r="L158" t="str">
-        <v>Ain't Over Me Yet - Carter Faith</v>
+        <v>Where Did You Go - Trousdale</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Where Did You Go</v>
+        <v>I LOVE YOU</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/where-did-you-go/1877958504</v>
+        <v>https://music.apple.com/us/song/i-love-you/6766999950</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-16</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Growing Pains (Deluxe)</v>
+        <v>I LOVE YOU - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:47</v>
+        <v>3:11</v>
       </c>
       <c r="H159" t="str">
-        <v>Trousdale</v>
+        <v>Noga Erez</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/noga-erez/1166657901</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/where-did-you-go/1877958112</v>
+        <v>https://music.apple.com/us/album/i-love-you/6766999949</v>
       </c>
       <c r="L159" t="str">
-        <v>Where Did You Go - Trousdale</v>
+        <v>I LOVE YOU - Noga Erez</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>I LOVE YOU</v>
+        <v>Housekeeping</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/i-love-you/6766999950</v>
+        <v>https://music.apple.com/us/song/housekeeping/6766290834</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-16</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>I LOVE YOU - Single</v>
+        <v>Housekeeping - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:11</v>
+        <v>3:25</v>
       </c>
       <c r="H160" t="str">
-        <v>Noga Erez</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/noga-erez/1166657901</v>
+        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/i-love-you/6766999949</v>
+        <v>https://music.apple.com/us/album/housekeeping/6766290823</v>
       </c>
       <c r="L160" t="str">
-        <v>I LOVE YOU - Noga Erez</v>
+        <v>Housekeeping - Ally Salort</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Housekeeping</v>
+        <v>Surprise Surprise</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/housekeeping/6766290834</v>
+        <v>https://music.apple.com/us/song/surprise-surprise/6764842119</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-16</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Housekeeping - Single</v>
+        <v>Surprise Surprise - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:25</v>
+        <v>2:55</v>
       </c>
       <c r="H161" t="str">
-        <v>Ally Salort</v>
+        <v>Chloe Qisha</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
+        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/housekeeping/6766290823</v>
+        <v>https://music.apple.com/us/album/surprise-surprise/1895934408</v>
       </c>
       <c r="L161" t="str">
-        <v>Housekeeping - Ally Salort</v>
+        <v>Surprise Surprise - Chloe Qisha</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Surprise Surprise</v>
+        <v>Dog</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/surprise-surprise/6764842119</v>
+        <v>https://music.apple.com/us/song/dog/1885967384</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-16</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Surprise Surprise - Single</v>
+        <v>Gentleman</v>
       </c>
       <c r="G162" t="str">
-        <v>2:55</v>
+        <v>3:08</v>
       </c>
       <c r="H162" t="str">
-        <v>Chloe Qisha</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
+        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/surprise-surprise/1895934408</v>
+        <v>https://music.apple.com/us/album/dog/1885967368</v>
       </c>
       <c r="L162" t="str">
-        <v>Surprise Surprise - Chloe Qisha</v>
+        <v>Dog - Towa Bird</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Dog</v>
+        <v>I Never See Her</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/dog/1885967384</v>
+        <v>https://music.apple.com/us/song/i-never-see-her/6764149225</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-16</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Gentleman</v>
+        <v>I Never See Her - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:08</v>
+        <v>3:04</v>
       </c>
       <c r="H163" t="str">
-        <v>Towa Bird</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
+        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/dog/1885967368</v>
+        <v>https://music.apple.com/us/album/i-never-see-her/1895660748</v>
       </c>
       <c r="L163" t="str">
-        <v>Dog - Towa Bird</v>
+        <v>I Never See Her - Spacey Jane</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>I Never See Her</v>
+        <v>No God</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/i-never-see-her/6764149225</v>
+        <v>https://music.apple.com/us/song/no-god/1891187414</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-16</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>I Never See Her - Single</v>
+        <v>Alone Together</v>
       </c>
       <c r="G164" t="str">
-        <v>3:04</v>
+        <v>2:45</v>
       </c>
       <c r="H164" t="str">
-        <v>Spacey Jane</v>
+        <v>Show Me the Body</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
+        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/i-never-see-her/1895660748</v>
+        <v>https://music.apple.com/us/album/no-god/1891187411</v>
       </c>
       <c r="L164" t="str">
-        <v>I Never See Her - Spacey Jane</v>
+        <v>No God - Show Me the Body</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>No God</v>
+        <v>burden</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/no-god/1891187414</v>
+        <v>https://music.apple.com/us/song/burden/6767688180</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-16</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Alone Together</v>
+        <v>burden - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>2:45</v>
+        <v>3:24</v>
       </c>
       <c r="H165" t="str">
-        <v>Show Me the Body</v>
+        <v>Abe Parker</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
+        <v>https://music.apple.com/us/artist/abe-parker/490444584</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/no-god/1891187411</v>
+        <v>https://music.apple.com/us/album/burden/6767688179</v>
       </c>
       <c r="L165" t="str">
-        <v>No God - Show Me the Body</v>
+        <v>burden - Abe Parker</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>burden</v>
+        <v>Chico Raro</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/burden/6767688180</v>
+        <v>https://music.apple.com/us/song/chico-raro/6767713536</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-16</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>burden - Single</v>
+        <v>Chico Raro - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:24</v>
+        <v>3:17</v>
       </c>
       <c r="H166" t="str">
-        <v>Abe Parker</v>
+        <v>Arón Piper</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/abe-parker/490444584</v>
+        <v>https://music.apple.com/us/artist/ar%C3%B3n-piper/691972942</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/burden/6767688179</v>
+        <v>https://music.apple.com/us/album/chico-raro/6767713527</v>
       </c>
       <c r="L166" t="str">
-        <v>burden - Abe Parker</v>
+        <v>Chico Raro - Arón Piper</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Chico Raro</v>
+        <v>What's Done Is Done</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/chico-raro/6767713536</v>
+        <v>https://music.apple.com/us/song/whats-done-is-done/6763088629</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-16</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Chico Raro - Single</v>
+        <v>What's Done Is Done - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:17</v>
+        <v>2:53</v>
       </c>
       <c r="H167" t="str">
-        <v>Arón Piper</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/ar%C3%B3n-piper/691972942</v>
+        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/chico-raro/6767713527</v>
+        <v>https://music.apple.com/us/album/whats-done-is-done/1895156626</v>
       </c>
       <c r="L167" t="str">
-        <v>Chico Raro - Arón Piper</v>
+        <v>What's Done Is Done - Jorja Smith</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>What's Done Is Done</v>
+        <v>round and round</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/whats-done-is-done/6763088629</v>
+        <v>https://music.apple.com/us/song/round-and-round/1885665987</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-16</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>What's Done Is Done - Single</v>
+        <v>round and round - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>2:53</v>
+        <v>2:47</v>
       </c>
       <c r="H168" t="str">
-        <v>Jorja Smith</v>
+        <v>bbno$</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
+        <v>https://music.apple.com/us/artist/bbno%24/1161580951</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/whats-done-is-done/1895156626</v>
+        <v>https://music.apple.com/us/album/round-and-round/1885665982</v>
       </c>
       <c r="L168" t="str">
-        <v>What's Done Is Done - Jorja Smith</v>
+        <v>round and round - bbno$</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>round and round</v>
+        <v>Ain’t That Deep</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/round-and-round/1885665987</v>
+        <v>https://music.apple.com/us/song/aint-that-deep/1882831449</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-16</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>round and round - Single</v>
+        <v>The Last Balloon</v>
       </c>
       <c r="G169" t="str">
-        <v>2:47</v>
+        <v>2:39</v>
       </c>
       <c r="H169" t="str">
-        <v>bbno$</v>
+        <v>Tank and the Bangas</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/bbno%24/1161580951</v>
+        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/round-and-round/1885665982</v>
+        <v>https://music.apple.com/us/album/aint-that-deep/1882831446</v>
       </c>
       <c r="L169" t="str">
-        <v>round and round - bbno$</v>
+        <v>Ain’t That Deep - Tank and the Bangas</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Ain’t That Deep</v>
+        <v>Emily</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/aint-that-deep/1882831449</v>
+        <v>https://music.apple.com/us/song/emily/1893405442</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-16</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>The Last Balloon</v>
+        <v>So Much To Say - EP</v>
       </c>
       <c r="G170" t="str">
-        <v>2:39</v>
+        <v>2:35</v>
       </c>
       <c r="H170" t="str">
-        <v>Tank and the Bangas</v>
+        <v>Daisy Grenade</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
+        <v>https://music.apple.com/us/artist/daisy-grenade/1611437131</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/aint-that-deep/1882831446</v>
+        <v>https://music.apple.com/us/album/emily/1893405440</v>
       </c>
       <c r="L170" t="str">
-        <v>Ain’t That Deep - Tank and the Bangas</v>
+        <v>Emily - Daisy Grenade</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Emily</v>
+        <v>Hold</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/emily/1893405442</v>
+        <v>https://music.apple.com/us/song/hold/6767296480</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-16</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>So Much To Say - EP</v>
+        <v>Hold - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:35</v>
+        <v>4:07</v>
       </c>
       <c r="H171" t="str">
-        <v>Daisy Grenade</v>
+        <v>Sabrina Sterling</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/daisy-grenade/1611437131</v>
+        <v>https://music.apple.com/us/artist/sabrina-sterling/1577892147</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/emily/1893405440</v>
+        <v>https://music.apple.com/us/album/hold/1896462063</v>
       </c>
       <c r="L171" t="str">
-        <v>Emily - Daisy Grenade</v>
+        <v>Hold - Sabrina Sterling</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Hold</v>
+        <v>Flying Monkey</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/hold/6767296480</v>
+        <v>https://music.apple.com/us/song/flying-monkey/1894351228</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-16</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Hold - Single</v>
+        <v>Flying Monkey - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>4:07</v>
+        <v>4:09</v>
       </c>
       <c r="H172" t="str">
-        <v>Sabrina Sterling</v>
+        <v>Blue Medusa</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/sabrina-sterling/1577892147</v>
+        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/hold/1896462063</v>
+        <v>https://music.apple.com/us/album/flying-monkey/1894351227</v>
       </c>
       <c r="L172" t="str">
-        <v>Hold - Sabrina Sterling</v>
+        <v>Flying Monkey - Blue Medusa</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Flying Monkey</v>
+        <v>Anything Goes</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/flying-monkey/1894351228</v>
+        <v>https://music.apple.com/us/song/anything-goes/1891118972</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-16</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Flying Monkey - Single</v>
+        <v>Anything Goes</v>
       </c>
       <c r="G173" t="str">
-        <v>4:09</v>
+        <v>3:00</v>
       </c>
       <c r="H173" t="str">
-        <v>Blue Medusa</v>
+        <v>Kaleena Zanders</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/flying-monkey/1894351227</v>
+        <v>https://music.apple.com/us/album/anything-goes/1891118971</v>
       </c>
       <c r="L173" t="str">
-        <v>Flying Monkey - Blue Medusa</v>
+        <v>Anything Goes - Kaleena Zanders</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Anything Goes</v>
+        <v>We Are</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/anything-goes/1891118972</v>
+        <v>https://music.apple.com/us/song/we-are/1894252873</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-16</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Anything Goes</v>
+        <v>We Are - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:00</v>
+        <v>3:33</v>
       </c>
       <c r="H174" t="str">
-        <v>Kaleena Zanders</v>
+        <v>Adam Ten</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+        <v>https://music.apple.com/us/artist/adam-ten/1472226854</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/anything-goes/1891118971</v>
+        <v>https://music.apple.com/us/album/we-are/1894252870</v>
       </c>
       <c r="L174" t="str">
-        <v>Anything Goes - Kaleena Zanders</v>
+        <v>We Are - Adam Ten</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>We Are</v>
+        <v>It's For the Kids</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/we-are/1894252873</v>
+        <v>https://music.apple.com/us/song/its-for-the-kids/1867327679</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-16</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>We Are - Single</v>
+        <v>Cursum Perficio</v>
       </c>
       <c r="G175" t="str">
-        <v>3:33</v>
+        <v>4:20</v>
       </c>
       <c r="H175" t="str">
-        <v>Adam Ten</v>
+        <v>Anthrax</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/adam-ten/1472226854</v>
+        <v>https://music.apple.com/us/artist/anthrax/80417</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/we-are/1894252870</v>
+        <v>https://music.apple.com/us/album/its-for-the-kids/1867327673</v>
       </c>
       <c r="L175" t="str">
-        <v>We Are - Adam Ten</v>
+        <v>It's For the Kids - Anthrax</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>It's For the Kids</v>
+        <v>Pure Ecstasy</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/its-for-the-kids/1867327679</v>
+        <v>https://music.apple.com/us/song/pure-ecstasy/6762228978</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-16</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Cursum Perficio</v>
+        <v>Pure Ecstasy</v>
       </c>
       <c r="G176" t="str">
-        <v>4:20</v>
+        <v>3:05</v>
       </c>
       <c r="H176" t="str">
-        <v>Anthrax</v>
+        <v>Beartooth</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/anthrax/80417</v>
+        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/its-for-the-kids/1867327673</v>
+        <v>https://music.apple.com/us/album/pure-ecstasy/1893453878</v>
       </c>
       <c r="L176" t="str">
-        <v>It's For the Kids - Anthrax</v>
+        <v>Pure Ecstasy - Beartooth</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Pure Ecstasy</v>
+        <v>Something Wicked</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/pure-ecstasy/6762228978</v>
+        <v>https://music.apple.com/us/song/something-wicked/6766252959</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-16</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Pure Ecstasy</v>
+        <v>Something Wicked - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:05</v>
+        <v>3:28</v>
       </c>
       <c r="H177" t="str">
-        <v>Beartooth</v>
+        <v>Breaking Benjamin</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
+        <v>https://music.apple.com/us/artist/breaking-benjamin/3299379</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/pure-ecstasy/1893453878</v>
+        <v>https://music.apple.com/us/album/something-wicked/1896253678</v>
       </c>
       <c r="L177" t="str">
-        <v>Pure Ecstasy - Beartooth</v>
+        <v>Something Wicked - Breaking Benjamin</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Something Wicked</v>
+        <v>Feel The Funk</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/something-wicked/6766252959</v>
+        <v>https://music.apple.com/us/song/feel-the-funk/6763294007</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-16</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Something Wicked - Single</v>
+        <v>The Funk EP - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:28</v>
+        <v>3:26</v>
       </c>
       <c r="H178" t="str">
-        <v>Breaking Benjamin</v>
+        <v>Riordan</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/breaking-benjamin/3299379</v>
+        <v>https://music.apple.com/us/artist/riordan/1517575029</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/something-wicked/1896253678</v>
+        <v>https://music.apple.com/us/album/feel-the-funk/1895251685</v>
       </c>
       <c r="L178" t="str">
-        <v>Something Wicked - Breaking Benjamin</v>
+        <v>Feel The Funk - Riordan</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Feel The Funk</v>
+        <v>Everglades (Remix)</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/feel-the-funk/6763294007</v>
+        <v>https://music.apple.com/us/song/everglades-remix/6767719584</v>
       </c>
       <c r="D179" t="str">
         <v>2026-05-16</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>The Funk EP - Single</v>
+        <v>Everglades (Remix) - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:26</v>
+        <v>2:42</v>
       </c>
       <c r="H179" t="str">
-        <v>Riordan</v>
+        <v>Aziedoesntexist</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/riordan/1517575029</v>
+        <v>https://music.apple.com/us/artist/aziedoesntexist/1831152556</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/feel-the-funk/1895251685</v>
+        <v>https://music.apple.com/us/album/everglades-remix/6767719577</v>
       </c>
       <c r="L179" t="str">
-        <v>Feel The Funk - Riordan</v>
+        <v>Everglades (Remix) - Aziedoesntexist</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Everglades (Remix)</v>
+        <v>Walk</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/everglades-remix/6767719584</v>
+        <v>https://music.apple.com/us/song/walk/1892180098</v>
       </c>
       <c r="D180" t="str">
         <v>2026-05-16</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Everglades (Remix) - Single</v>
+        <v>Walk - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:42</v>
+        <v>2:25</v>
       </c>
       <c r="H180" t="str">
-        <v>Aziedoesntexist</v>
+        <v>Melodicb</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/aziedoesntexist/1831152556</v>
+        <v>https://music.apple.com/us/artist/melodicb/1440206517</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/everglades-remix/6767719577</v>
+        <v>https://music.apple.com/us/album/walk/1892180097</v>
       </c>
       <c r="L180" t="str">
-        <v>Everglades (Remix) - Aziedoesntexist</v>
+        <v>Walk - Melodicb</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Walk</v>
+        <v>Volver a Ti</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/walk/1892180098</v>
+        <v>https://music.apple.com/us/song/volver-a-ti/6766258204</v>
       </c>
       <c r="D181" t="str">
         <v>2026-05-16</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Walk - Single</v>
+        <v>Norteña</v>
       </c>
       <c r="G181" t="str">
-        <v>2:25</v>
+        <v>3:47</v>
       </c>
       <c r="H181" t="str">
-        <v>Melodicb</v>
+        <v>Julieta Venegas</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/melodicb/1440206517</v>
+        <v>https://music.apple.com/us/artist/julieta-venegas/302960</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/walk/1892180097</v>
+        <v>https://music.apple.com/us/album/volver-a-ti/1896255736</v>
       </c>
       <c r="L181" t="str">
-        <v>Walk - Melodicb</v>
+        <v>Volver a Ti - Julieta Venegas</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Volver a Ti</v>
+        <v>Bahamas</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/volver-a-ti/6766258204</v>
+        <v>https://music.apple.com/us/song/bahamas/6764695848</v>
       </c>
       <c r="D182" t="str">
         <v>2026-05-16</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Norteña</v>
+        <v>Bahamas - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:47</v>
+        <v>2:06</v>
       </c>
       <c r="H182" t="str">
-        <v>Julieta Venegas</v>
+        <v>LENCHO</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/julieta-venegas/302960</v>
+        <v>https://music.apple.com/us/artist/lencho/1854923384</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/volver-a-ti/1896255736</v>
+        <v>https://music.apple.com/us/album/bahamas/6764695847</v>
       </c>
       <c r="L182" t="str">
-        <v>Volver a Ti - Julieta Venegas</v>
+        <v>Bahamas - LENCHO</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Bahamas</v>
+        <v>Same Old Song</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/bahamas/6764695848</v>
+        <v>https://music.apple.com/us/song/same-old-song/6762860685</v>
       </c>
       <c r="D183" t="str">
         <v>2026-05-16</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Bahamas - Single</v>
+        <v>Same Old Song - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:06</v>
+        <v>4:12</v>
       </c>
       <c r="H183" t="str">
-        <v>LENCHO</v>
+        <v>Lila Drew</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/lencho/1854923384</v>
+        <v>https://music.apple.com/us/artist/lila-drew/1439482732</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/bahamas/6764695847</v>
+        <v>https://music.apple.com/us/album/same-old-song/1895047985</v>
       </c>
       <c r="L183" t="str">
-        <v>Bahamas - LENCHO</v>
+        <v>Same Old Song - Lila Drew</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Same Old Song</v>
+        <v>gentle</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/same-old-song/6762860685</v>
+        <v>https://music.apple.com/us/song/gentle/6762828356</v>
       </c>
       <c r="D184" t="str">
         <v>2026-05-16</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Same Old Song - Single</v>
+        <v>gentle - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>4:12</v>
+        <v>2:48</v>
       </c>
       <c r="H184" t="str">
-        <v>Lila Drew</v>
+        <v>Venus Anon</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/lila-drew/1439482732</v>
+        <v>https://music.apple.com/us/artist/venus-anon/1635970130</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/same-old-song/1895047985</v>
+        <v>https://music.apple.com/us/album/gentle/1895031896</v>
       </c>
       <c r="L184" t="str">
-        <v>Same Old Song - Lila Drew</v>
+        <v>gentle - Venus Anon</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>gentle</v>
+        <v>Letters of Your Name</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/gentle/6762828356</v>
+        <v>https://music.apple.com/us/song/letters-of-your-name/1892919741</v>
       </c>
       <c r="D185" t="str">
         <v>2026-05-16</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>gentle - Single</v>
+        <v>Congratulations</v>
       </c>
       <c r="G185" t="str">
-        <v>2:48</v>
+        <v>3:21</v>
       </c>
       <c r="H185" t="str">
-        <v>Venus Anon</v>
+        <v>Jacob Ungerleider</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/venus-anon/1635970130</v>
+        <v>https://music.apple.com/us/artist/jacob-ungerleider/1460845591</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/gentle/1895031896</v>
+        <v>https://music.apple.com/us/album/letters-of-your-name/1892919737</v>
       </c>
       <c r="L185" t="str">
-        <v>gentle - Venus Anon</v>
+        <v>Letters of Your Name - Jacob Ungerleider</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Letters of Your Name</v>
+        <v>Seratonin</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/letters-of-your-name/1892919741</v>
+        <v>https://music.apple.com/us/song/seratonin/6763447428</v>
       </c>
       <c r="D186" t="str">
         <v>2026-05-16</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Congratulations</v>
+        <v>Seratonin - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:21</v>
+        <v>1:55</v>
       </c>
       <c r="H186" t="str">
-        <v>Jacob Ungerleider</v>
+        <v>James Hype</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/jacob-ungerleider/1460845591</v>
+        <v>https://music.apple.com/us/artist/james-hype/925734064</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/letters-of-your-name/1892919737</v>
+        <v>https://music.apple.com/us/album/seratonin/1895320367</v>
       </c>
       <c r="L186" t="str">
-        <v>Letters of Your Name - Jacob Ungerleider</v>
+        <v>Seratonin - James Hype</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Seratonin</v>
+        <v>A Digital Touch</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/seratonin/6763447428</v>
+        <v>https://music.apple.com/us/song/a-digital-touch/6765592539</v>
       </c>
       <c r="D187" t="str">
         <v>2026-05-16</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Seratonin - Single</v>
+        <v>A Digital Touch - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>1:55</v>
+        <v>2:53</v>
       </c>
       <c r="H187" t="str">
-        <v>James Hype</v>
+        <v>Evening Elephants</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/james-hype/925734064</v>
+        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/seratonin/1895320367</v>
+        <v>https://music.apple.com/us/album/a-digital-touch/1896003252</v>
       </c>
       <c r="L187" t="str">
-        <v>Seratonin - James Hype</v>
+        <v>A Digital Touch - Evening Elephants</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>A Digital Touch</v>
+        <v>Dead Man's Dog</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/a-digital-touch/6765592539</v>
+        <v>https://music.apple.com/us/song/dead-mans-dog/6763447424</v>
       </c>
       <c r="D188" t="str">
         <v>2026-05-16</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>A Digital Touch - Single</v>
+        <v>Aiming Torches At The Sun - EP</v>
       </c>
       <c r="G188" t="str">
-        <v>2:53</v>
+        <v>4:33</v>
       </c>
       <c r="H188" t="str">
-        <v>Evening Elephants</v>
+        <v>Dermot Henry</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
+        <v>https://music.apple.com/us/artist/dermot-henry/1704074611</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/a-digital-touch/1896003252</v>
+        <v>https://music.apple.com/us/album/dead-mans-dog/1895320369</v>
       </c>
       <c r="L188" t="str">
-        <v>A Digital Touch - Evening Elephants</v>
+        <v>Dead Man's Dog - Dermot Henry</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Dead Man's Dog</v>
+        <v>Fault of God</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/dead-mans-dog/6763447424</v>
+        <v>https://music.apple.com/us/song/fault-of-god/1887702403</v>
       </c>
       <c r="D189" t="str">
         <v>2026-05-16</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Aiming Torches At The Sun - EP</v>
+        <v>Active Child</v>
       </c>
       <c r="G189" t="str">
-        <v>4:33</v>
+        <v>4:13</v>
       </c>
       <c r="H189" t="str">
-        <v>Dermot Henry</v>
+        <v>Active Child</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/dermot-henry/1704074611</v>
+        <v>https://music.apple.com/us/artist/active-child/355288617</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/dead-mans-dog/1895320369</v>
+        <v>https://music.apple.com/us/album/fault-of-god/1887701924</v>
       </c>
       <c r="L189" t="str">
-        <v>Dead Man's Dog - Dermot Henry</v>
+        <v>Fault of God - Active Child</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Fault of God</v>
+        <v>Zone (feat. Poppy Baskcomb)</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/fault-of-god/1887702403</v>
+        <v>https://music.apple.com/us/song/zone-feat-poppy-baskcomb/6763982867</v>
       </c>
       <c r="D190" t="str">
         <v>2026-05-16</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Active Child</v>
+        <v>Zone (feat. Poppy Baskcomb) - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>4:13</v>
+        <v>2:56</v>
       </c>
       <c r="H190" t="str">
-        <v>Active Child</v>
+        <v>MK</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/active-child/355288617</v>
+        <v>https://music.apple.com/us/artist/mk/63097617</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/fault-of-god/1887701924</v>
+        <v>https://music.apple.com/us/album/zone-feat-poppy-baskcomb/1895585800</v>
       </c>
       <c r="L190" t="str">
-        <v>Fault of God - Active Child</v>
+        <v>Zone (feat. Poppy Baskcomb) - MK</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Zone (feat. Poppy Baskcomb)</v>
+        <v>Word Vomit</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/zone-feat-poppy-baskcomb/6763982867</v>
+        <v>https://music.apple.com/us/song/word-vomit/1887315297</v>
       </c>
       <c r="D191" t="str">
         <v>2026-05-16</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Zone (feat. Poppy Baskcomb) - Single</v>
+        <v>Word Vomit - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>2:56</v>
+        <v>2:46</v>
       </c>
       <c r="H191" t="str">
-        <v>MK</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/mk/63097617</v>
+        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/zone-feat-poppy-baskcomb/1895585800</v>
+        <v>https://music.apple.com/us/album/word-vomit/1887315294</v>
       </c>
       <c r="L191" t="str">
-        <v>Zone (feat. Poppy Baskcomb) - MK</v>
+        <v>Word Vomit - Baby Queen</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Word Vomit</v>
+        <v>Evil in this House</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/word-vomit/1887315297</v>
+        <v>https://music.apple.com/us/song/evil-in-this-house/1892398371</v>
       </c>
       <c r="D192" t="str">
         <v>2026-05-16</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Word Vomit - Single</v>
+        <v>Necropolitan</v>
       </c>
       <c r="G192" t="str">
-        <v>2:46</v>
+        <v>4:21</v>
       </c>
       <c r="H192" t="str">
-        <v>Baby Queen</v>
+        <v>Green Lung</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
+        <v>https://music.apple.com/us/artist/green-lung/1244071662</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/word-vomit/1887315294</v>
+        <v>https://music.apple.com/us/album/evil-in-this-house/1892398281</v>
       </c>
       <c r="L192" t="str">
-        <v>Word Vomit - Baby Queen</v>
+        <v>Evil in this House - Green Lung</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Evil in this House</v>
+        <v>Heaven on High</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/evil-in-this-house/1892398371</v>
+        <v>https://music.apple.com/us/song/heaven-on-high/1881724153</v>
       </c>
       <c r="D193" t="str">
         <v>2026-05-16</v>
@@ -7709,68 +7709,30 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Necropolitan</v>
+        <v>A Pale White Dot</v>
       </c>
       <c r="G193" t="str">
-        <v>4:21</v>
+        <v>4:19</v>
       </c>
       <c r="H193" t="str">
-        <v>Green Lung</v>
+        <v>Periphery</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/green-lung/1244071662</v>
+        <v>https://music.apple.com/us/artist/periphery/187683869</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/evil-in-this-house/1892398281</v>
+        <v>https://music.apple.com/us/album/heaven-on-high/1881724003</v>
       </c>
       <c r="L193" t="str">
-        <v>Evil in this House - Green Lung</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="str">
-        <v>Heaven on High</v>
-      </c>
-      <c r="B194" t="str">
-        <v/>
-      </c>
-      <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/heaven-on-high/1881724153</v>
-      </c>
-      <c r="D194" t="str">
-        <v>2026-05-16</v>
-      </c>
-      <c r="E194" t="str">
-        <v/>
-      </c>
-      <c r="F194" t="str">
-        <v>A Pale White Dot</v>
-      </c>
-      <c r="G194" t="str">
-        <v>4:19</v>
-      </c>
-      <c r="H194" t="str">
-        <v>Periphery</v>
-      </c>
-      <c r="I194" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/periphery/187683869</v>
-      </c>
-      <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/heaven-on-high/1881724003</v>
-      </c>
-      <c r="L194" t="str">
         <v>Heaven on High - Periphery</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L194"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L193"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-05-week03/titles.xlsx
+++ b/data/global/2026-05-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B4" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B9" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Ellise - Liplock (Official Music Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Tori Kelly - Dive (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
       </c>
       <c r="B13" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
       </c>
       <c r="B14" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Michael Schulte - Lovesick (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Lucy Blue - Who you love (Visualiser)</v>
       </c>
       <c r="B42" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026)</v>
       </c>
       <c r="B43" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Aaron Frazer - It's A Shame (Official Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Holly Humberstone - White Noise (Live) | Presented By Spotify</v>
       </c>
       <c r="B45" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>The Rolling Stones - In The Stars (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser)</v>
       </c>
       <c r="B48" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>

--- a/data/global/2026-05-week03/titles.xlsx
+++ b/data/global/2026-05-week03/titles.xlsx
@@ -1921,7 +1921,7 @@
         <v>Paris Paloma - Stem the Flow [Official Music Video]</v>
       </c>
       <c r="B41" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>

--- a/data/global/2026-05-week03/titles.xlsx
+++ b/data/global/2026-05-week03/titles.xlsx
@@ -667,7 +667,7 @@
         <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>

--- a/data/global/2026-05-week03/titles.xlsx
+++ b/data/global/2026-05-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Harry Styles - Dance No More (Official Video)</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B2" t="str">
-        <v>9 days ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
+        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-16</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>9 days ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Harry Styles</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B3" t="str">
-        <v>9 days ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
+        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-16</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>9 days ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Eagles</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
+        <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
+        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-16</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Nora Fatehi</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
+        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
+        <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>2 months ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
+        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-16</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 months ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Carver Jones</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
+        <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>2 months ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
+        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-16</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 months ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Eurovision Song Contest and Alis</v>
+        <v>Jazmin bean</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
+        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B7" t="str">
-        <v>2 months ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
+        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-16</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 months ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video)</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
+        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-16</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>The Head And The Heart</v>
+        <v>Evanescence</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
+        <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B9" t="str">
-        <v>10 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
+        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-16</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>10 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Simply Red</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
+        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video)</v>
+        <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
+        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-16</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Talking Heads</v>
+        <v>Grace Potter</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
+        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Ellise - Liplock (Official Music Video)</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B11" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
+        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-16</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Ellise</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Tori Kelly - Dive (Official Music Video)</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
+        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-16</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Tori Kelly</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
+        <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B13" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
+        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-16</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>David Gilmour</v>
+        <v>Henry Moodie</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024) - David Gilmour</v>
+        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
+        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-16</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Scorpions</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022) - Scorpions</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
+        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-16</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Claire Leslie</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Claire Leslie - Passenger Seat (Official Music Video) - Claire Leslie</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Michael Schulte - Lovesick (Official Video)</v>
+        <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B16" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
+        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-16</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Michael Schulte</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Michael Schulte - Lovesick (Official Video) - Michael Schulte</v>
+        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Caity Baser - Holiday Song (Official Video)</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
+        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-16</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Caity Baser</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Caity Baser - Holiday Song (Official Video) - Caity Baser</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
+        <v>Keith Urban - Steal Away (Visualizer)</v>
       </c>
       <c r="B18" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
+        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-16</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Sam Fischer</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser) - Sam Fischer</v>
+        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Porches- HABIT (Official Video)</v>
+        <v>VALÉ - Mugshot (Official Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
+        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-16</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Porches</v>
+        <v>VALÉ</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Porches- HABIT (Official Video) - Porches</v>
+        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Charli xcx - Rock Music (Official Video)</v>
+        <v>Mackenzie Carpenter - High Pony (Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
+        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-16</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Charli xcx</v>
+        <v>Mackenzie Carpenter</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Charli xcx - Rock Music (Official Video) - Charli xcx</v>
+        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Jon Batiste - Alla Blues (Audio)</v>
+        <v>Towa Bird - Afterglow (Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
+        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-16</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Jon Batiste</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Jon Batiste - Alla Blues (Audio) - Jon Batiste</v>
+        <v>Towa Bird - Afterglow (Lyric Video) - Towa Bird</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
       </c>
       <c r="B22" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
+        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-16</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Tigirlily Gold</v>
+        <v>Sabrina Sterling</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Tigirlily Gold - I Do or Die (Official Music Video) - Tigirlily Gold</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
+        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-16</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video) - PAUL McCARTNEY</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
+        <v>Becky G - EPA (Official Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
+        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-16</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Bruno Mars</v>
+        <v>Becky G</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video] - Bruno Mars</v>
+        <v>Becky G - EPA (Official Video) - Becky G</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Tori Kelly - Control (Official Visualizer)</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
+        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-16</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Tori Kelly</v>
+        <v>Daisy the Great</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Tori Kelly - Control (Official Visualizer) - Tori Kelly</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Bea Miller - depressed on the internet (Lyric Video)</v>
+        <v>Towa Bird - Dog (Official Music Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
+        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-16</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>bea miller</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Bea Miller - depressed on the internet (Lyric Video) - bea miller</v>
+        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
       </c>
       <c r="B27" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
+        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-16</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>The Chainsmokers</v>
+        <v>Madonna</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer) - The Chainsmokers</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Madison Beer - free (Official Audio)</v>
+        <v>Ally Salort - Housekeeping (Lyric Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
+        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-16</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Madison Beer</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Madison Beer - free (Official Audio) - Madison Beer</v>
+        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Tori Kelly - Dive (Official Audio)</v>
+        <v>Bella White - Better - Official Music Video</v>
       </c>
       <c r="B29" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
+        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-16</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Tori Kelly</v>
+        <v>Bella White</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Tori Kelly - Dive (Official Audio) - Tori Kelly</v>
+        <v>Bella White - Better - Official Music Video - Bella White</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Jeremy Camp - Reflector (Official Audio)</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
+        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-16</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>JeremyCampMusic</v>
+        <v>Charles Wesley Godwin</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Jeremy Camp - Reflector (Official Audio) - JeremyCampMusic</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
+        <v>Towa Bird - All Gone (Lyric Video) ft. Kathleen Hanna</v>
       </c>
       <c r="B31" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
+        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-16</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>The Chainsmokers</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer) - The Chainsmokers</v>
+        <v>Towa Bird - All Gone (Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Ashley Cooke - high school sweetheart</v>
+        <v>Miranda Lambert - Crisco (Visualizer)</v>
       </c>
       <c r="B32" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
+        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-16</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Ashley Cooke</v>
+        <v>Miranda Lambert</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Ashley Cooke - high school sweetheart - Ashley Cooke</v>
+        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Ari Abdul - Ego (Visualizer)</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
       </c>
       <c r="B33" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=L0FjVr6LpVU</v>
+        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-16</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Ari Abdul</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Ari Abdul - Ego (Visualizer) - Ari Abdul</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Quinn XCII - HOOPLA (Official Music Video)</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=eNbGA1pgmFk</v>
+        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-16</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Quinn XCII</v>
+        <v>Gracie Abrams</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Quinn XCII - HOOPLA (Official Music Video) - Quinn XCII</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Madison Beer - lovergirl (Official Music Video)</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=q4lU1N3oqYQ</v>
+        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-16</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>8 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Madison Beer</v>
+        <v>The Last Dinner Party</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Madison Beer - lovergirl (Official Music Video) - Madison Beer</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>David J - WHAT IF I'M IN LOVE (Official Video)</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
       </c>
       <c r="B36" t="str">
-        <v>8 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=-SF7Hm_ikaY</v>
+        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-16</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>8 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>David J</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>David J - WHAT IF I'M IN LOVE (Official Video) - David J</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>The Last Dinner Party - Big Dog (On The Road)</v>
+        <v>Jorja Smith - What's Done Is Done</v>
       </c>
       <c r="B37" t="str">
-        <v>8 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
+        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-16</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>8 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>The Last Dinner Party</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>The Last Dinner Party - Big Dog (On The Road) - The Last Dinner Party</v>
+        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>OCEAN ALLEY - HOLD ON (Official Video)</v>
+        <v>LP - Shelly (Official Music Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>8 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
+        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-16</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>8 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Ocean Alley</v>
+        <v>LP</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>OCEAN ALLEY - HOLD ON (Official Video) - Ocean Alley</v>
+        <v>LP - Shelly (Official Music Video) - LP</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Dagny - Closet Disco Queen (Lyric Video)</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
       </c>
       <c r="B39" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
+        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-16</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Dagny</v>
+        <v>The Rolling Stones</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Dagny - Closet Disco Queen (Lyric Video) - Dagny</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Purple Disco Machine - Disco Cherry (Official Video)</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
       </c>
       <c r="B40" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
+        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-16</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Oasis</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Purple Disco Machine - Disco Cherry (Official Video) - Purple Disco Machine</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Paris Paloma - Stem the Flow [Official Music Video]</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
       </c>
       <c r="B41" t="str">
-        <v>10 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
+        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-16</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>10 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Paris Paloma</v>
+        <v>Breaking Benjamin</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Paris Paloma - Stem the Flow [Official Music Video] - Paris Paloma</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Lucy Blue - Who you love (Visualiser)</v>
+        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
       </c>
       <c r="B42" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
+        <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-16</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Lucy Blue</v>
+        <v>VictorBiliac</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Lucy Blue - Who you love (Visualiser) - Lucy Blue</v>
+        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit ) - VictorBiliac</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026)</v>
+        <v>From The Inside (Live in Mumbai) - Linkin Park</v>
       </c>
       <c r="B43" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
+        <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-16</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Olivia Dean</v>
+        <v>Linkin Park</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026) - Olivia Dean</v>
+        <v>From The Inside (Live in Mumbai) - Linkin Park - Linkin Park</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Aaron Frazer - It's A Shame (Official Video)</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
+        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-16</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>10 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Aaron Frazer</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Aaron Frazer - It's A Shame (Official Video) - Aaron Frazer</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify</v>
+        <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
+        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-16</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Holly Humberstone</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>DANNA - OUT OF MY BODY</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=uW_Ye0kQ9Ac</v>
+        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-16</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Danna</v>
+        <v>Eagles</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>DANNA - OUT OF MY BODY - Danna</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>The Rolling Stones - In The Stars (Official Lyric Video)</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B47" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
+        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-16</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>The Rolling Stones</v>
+        <v>Nora Fatehi</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>The Rolling Stones - In The Stars (Official Lyric Video) - The Rolling Stones</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser)</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B48" t="str">
-        <v>11 days ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
+        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-16</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>11 days ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser) - Dermot Kennedy</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B49" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
+        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-16</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Eurovision Song Contest and Alis</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2) - SIENNA SPIRO</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Rick Astley - Raindrops (Official Video)</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
       </c>
       <c r="B50" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
+        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-16</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Rick Astley</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Rick Astley - Raindrops (Official Video) - Rick Astley</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Jessie J - THREW IT AWAY (Official Video)</v>
+        <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
+        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-16</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Jessie J</v>
+        <v>The Head And The Heart</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Jessie J - THREW IT AWAY (Official Video) - Jessie J</v>
+        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>The Takes - Ain't Love (Lyric Video)</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B52" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
+        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-16</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>The Takes</v>
+        <v>Simply Red</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>The Takes - Ain't Love (Lyric Video) - The Takes</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary</v>
+        <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
+        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-16</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>The Offspring</v>
+        <v>Talking Heads</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary - The Offspring</v>
+        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Louis Tomlinson - Sunflowers (Official Performance Video)</v>
+        <v>Ellise - Liplock (Official Music Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
+        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-16</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Ellise</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Louis Tomlinson - Sunflowers (Official Performance Video) - Louis Tomlinson</v>
+        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>The Beaches - Should've Known Better (Official Visualizer)</v>
+        <v>Tori Kelly - Dive (Official Music Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
+        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-16</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>The Beaches</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>The Beaches - Should've Known Better (Official Visualizer) - The Beaches</v>
+        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>The Kiffness - Serafino (Singing Cat Song)</v>
+        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
       </c>
       <c r="B56" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
+        <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-16</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>The Kiffness</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>The Kiffness - Serafino (Singing Cat Song) - The Kiffness</v>
+        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024) - David Gilmour</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer)</v>
+        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
       </c>
       <c r="B57" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
+        <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-16</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Dennis Lloyd</v>
+        <v>Scorpions</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer) - Dennis Lloyd</v>
+        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Anna Graves - Damn In Love (Official Visualizer)</v>
+        <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
+        <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-16</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Anna Graves</v>
+        <v>Claire Leslie</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Anna Graves - Damn In Love (Official Visualizer) - Anna Graves</v>
+        <v>Claire Leslie - Passenger Seat (Official Music Video) - Claire Leslie</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video)</v>
+        <v>Michael Schulte - Lovesick (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=vKzPmy3VUzY</v>
+        <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-16</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Brandon Lake and NICK JONAS</v>
+        <v>Michael Schulte</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video) - Brandon Lake and NICK JONAS</v>
+        <v>Michael Schulte - Lovesick (Official Video) - Michael Schulte</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Letdown. - Do It For The Love (Visualizer)</v>
+        <v>Caity Baser - Holiday Song (Official Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=vCvZbTEywr8</v>
+        <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-16</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Letdown.</v>
+        <v>Caity Baser</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Letdown. - Do It For The Love (Visualizer) - Letdown.</v>
+        <v>Caity Baser - Holiday Song (Official Video) - Caity Baser</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Maroon 5 - Heroine (Official Lyric Video)</v>
+        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
       </c>
       <c r="B61" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=izP-4q4YtNw</v>
+        <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-16</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Maroon 5</v>
+        <v>Sam Fischer</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Maroon 5 - Heroine (Official Lyric Video) - Maroon 5</v>
+        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser) - Sam Fischer</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Olivia O'Brien - I'm Perfect (Official Visualizer)</v>
+        <v>Porches- HABIT (Official Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=leHb8CowDSw</v>
+        <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-16</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Olivia O'Brien</v>
+        <v>Porches</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Olivia O'Brien - I'm Perfect (Official Visualizer) - Olivia O'Brien</v>
+        <v>Porches- HABIT (Official Video) - Porches</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>ERNEST - What's A Little Rain (Official Music Video)</v>
+        <v>Charli xcx - Rock Music (Official Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=U-3AGDH3mf4</v>
+        <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-16</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>ERNEST</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>ERNEST - What's A Little Rain (Official Music Video) - ERNEST</v>
+        <v>Charli xcx - Rock Music (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Claire Rosinkranz - Just A Man (Official Audio)</v>
+        <v>Jon Batiste - Alla Blues (Audio)</v>
       </c>
       <c r="B64" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=Ta2I3EHXaDI</v>
+        <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-16</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Claire Rosinkranz - Just A Man (Official Audio) - Claire Rosinkranz</v>
+        <v>Jon Batiste - Alla Blues (Audio) - Jon Batiste</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Halsey - Nothing! (Official Audio)</v>
+        <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=PBv71KbKvHA</v>
+        <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-16</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Halsey</v>
+        <v>Tigirlily Gold</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Halsey - Nothing! (Official Audio) - Halsey</v>
+        <v>Tigirlily Gold - I Do or Die (Official Music Video) - Tigirlily Gold</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer)</v>
+        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=5-f07ca1Zfg</v>
+        <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-16</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Zara Larsson</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer) - Zara Larsson</v>
+        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Halsey - Carry the Weight (Official Audio)</v>
+        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
       </c>
       <c r="B67" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=6MewHp8BX0w</v>
+        <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-16</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Halsey</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Halsey - Carry the Weight (Official Audio) - Halsey</v>
+        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Bishop Briggs - Blood From A Stone (Official)</v>
+        <v>Tori Kelly - Control (Official Visualizer)</v>
       </c>
       <c r="B68" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=3CK6Zbdk-Nw</v>
+        <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-16</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Bishop Briggs</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Bishop Briggs - Blood From A Stone (Official) - Bishop Briggs</v>
+        <v>Tori Kelly - Control (Official Visualizer) - Tori Kelly</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio)</v>
+        <v>Bea Miller - depressed on the internet (Lyric Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=6-AWBV5FCN4</v>
+        <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-16</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Louis Tomlinson</v>
+        <v>bea miller</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio) - Louis Tomlinson</v>
+        <v>Bea Miller - depressed on the internet (Lyric Video) - bea miller</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>almost monday - no more regrets (official video)</v>
+        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
       </c>
       <c r="B70" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=iczsZVZxHKs</v>
+        <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-16</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>almost monday</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>almost monday - no more regrets (official video) - almost monday</v>
+        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video)</v>
+        <v>Madison Beer - free (Official Audio)</v>
       </c>
       <c r="B71" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=lJM-z0ohbkc</v>
+        <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-16</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video) - FULL CIRCLE BOYS</v>
+        <v>Madison Beer - free (Official Audio) - Madison Beer</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video)</v>
+        <v>Tori Kelly - Dive (Official Audio)</v>
       </c>
       <c r="B72" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=6AjhDPwpoLI</v>
+        <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-16</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video) - ★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
+        <v>Tori Kelly - Dive (Official Audio) - Tori Kelly</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video)</v>
+        <v>Jeremy Camp - Reflector (Official Audio)</v>
       </c>
       <c r="B73" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=F4ndJUCsHKg</v>
+        <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-16</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>NIGHTLY and Fly By Midnight</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video) - NIGHTLY and Fly By Midnight</v>
+        <v>Jeremy Camp - Reflector (Official Audio) - JeremyCampMusic</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer)</v>
+        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=-IEb-ym7VeQ</v>
+        <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-16</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Zara Larsson</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer) - Zara Larsson</v>
+        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>JORDANA BRYANT - Truth Is (Official Video)</v>
+        <v>Ashley Cooke - high school sweetheart</v>
       </c>
       <c r="B75" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=D4meCyyV7SQ</v>
+        <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-16</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Jordana Bryant</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>JORDANA BRYANT - Truth Is (Official Video) - Jordana Bryant</v>
+        <v>Ashley Cooke - high school sweetheart - Ashley Cooke</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Leanna Crawford - Thank God (Lyric Video)</v>
+        <v>Ari Abdul - Ego (Visualizer)</v>
       </c>
       <c r="B76" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=QqcSoUft03s</v>
+        <v>https://www.youtube.com/watch?v=L0FjVr6LpVU</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-16</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Leanna Crawford</v>
+        <v>Ari Abdul</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Leanna Crawford - Thank God (Lyric Video) - Leanna Crawford</v>
+        <v>Ari Abdul - Ego (Visualizer) - Ari Abdul</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Girl Tones - Stubborn Mouth (Official Music Video)</v>
+        <v>Quinn XCII - HOOPLA (Official Music Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=_-PyPUWZTDY</v>
+        <v>https://www.youtube.com/watch?v=eNbGA1pgmFk</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-16</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Girl Tones</v>
+        <v>Quinn XCII</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Girl Tones - Stubborn Mouth (Official Music Video) - Girl Tones</v>
+        <v>Quinn XCII - HOOPLA (Official Music Video) - Quinn XCII</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Tauren Wells - What A Miracle Feels Like (Official Audio)</v>
+        <v>Madison Beer - lovergirl (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=ZojFIe4Swmk</v>
+        <v>https://www.youtube.com/watch?v=q4lU1N3oqYQ</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-16</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Tauren Wells</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Tauren Wells - What A Miracle Feels Like (Official Audio) - Tauren Wells</v>
+        <v>Madison Beer - lovergirl (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Matthew Ifield - Thinking (Official Video)</v>
+        <v>David J - WHAT IF I'M IN LOVE (Official Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
+        <v>https://www.youtube.com/watch?v=-SF7Hm_ikaY</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-16</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Matthew Ifield</v>
+        <v>David J</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Matthew Ifield - Thinking (Official Video) - Matthew Ifield</v>
+        <v>David J - WHAT IF I'M IN LOVE (Official Video) - David J</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Dons - Is There Something</v>
+        <v>The Last Dinner Party - Big Dog (On The Road)</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=AgWIjvD-i0E</v>
+        <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-16</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Dons</v>
+        <v>The Last Dinner Party</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Dons - Is There Something - Dons</v>
+        <v>The Last Dinner Party - Big Dog (On The Road) - The Last Dinner Party</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris</v>
+        <v>OCEAN ALLEY - HOLD ON (Official Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=JXW3SOr7C4w</v>
+        <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-16</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Recording Academy / GRAMMYs and 3 more</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris - Recording Academy / GRAMMYs and 3 more</v>
+        <v>OCEAN ALLEY - HOLD ON (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Maya Hawke - Lioness (Official Audio)</v>
+        <v>Dagny - Closet Disco Queen (Lyric Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
+        <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-16</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Maya Hawke</v>
+        <v>Dagny</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Maya Hawke - Lioness (Official Audio) - Maya Hawke</v>
+        <v>Dagny - Closet Disco Queen (Lyric Video) - Dagny</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance</v>
+        <v>Purple Disco Machine - Disco Cherry (Official Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
+        <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-16</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Laufey</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance - Laufey</v>
+        <v>Purple Disco Machine - Disco Cherry (Official Video) - Purple Disco Machine</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
+        <v>Paris Paloma - Stem the Flow [Official Music Video]</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
+        <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-16</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Keith Urban</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
+        <v>Paris Paloma - Stem the Flow [Official Music Video] - Paris Paloma</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>DANNA - AGAIN</v>
+        <v>Lucy Blue - Who you love (Visualiser)</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
+        <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-16</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Danna</v>
+        <v>Lucy Blue</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>DANNA - AGAIN - Danna</v>
+        <v>Lucy Blue - Who you love (Visualiser) - Lucy Blue</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026)</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
+        <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-16</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Armik</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026) - Olivia Dean</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>EUROPE - One on One (Official Video)</v>
+        <v>Aaron Frazer - It's A Shame (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
+        <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-16</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Europe</v>
+        <v>Aaron Frazer</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>EUROPE - One on One (Official Video) - Europe</v>
+        <v>Aaron Frazer - It's A Shame (Official Video) - Aaron Frazer</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
+        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
+        <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-16</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Foo Fighters</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
+        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video)</v>
+        <v>DANNA - OUT OF MY BODY</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
+        <v>https://www.youtube.com/watch?v=uW_Ye0kQ9Ac</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-16</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Lady Gaga and Doechii</v>
+        <v>Danna</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video) - Lady Gaga and Doechii</v>
+        <v>DANNA - OUT OF MY BODY - Danna</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
+        <v>The Rolling Stones - In The Stars (Official Lyric Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
+        <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-16</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Muse</v>
+        <v>The Rolling Stones</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
+        <v>The Rolling Stones - In The Stars (Official Lyric Video) - The Rolling Stones</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
+        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser)</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
+        <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-16</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
+        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Shaboozey - Born To Die (Official Video)</v>
+        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
       </c>
       <c r="B92" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
+        <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-16</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Shaboozey</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
+        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
+        <v>Rick Astley - Raindrops (Official Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
+        <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-16</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Scorpions</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
+        <v>Rick Astley - Raindrops (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
+        <v>Jessie J - THREW IT AWAY (Official Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
+        <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-16</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Meghan Trainor</v>
+        <v>Jessie J</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
+        <v>Jessie J - THREW IT AWAY (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
+        <v>The Takes - Ain't Love (Lyric Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
+        <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-16</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Lolo Zouaï</v>
+        <v>The Takes</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
+        <v>The Takes - Ain't Love (Lyric Video) - The Takes</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Bonnie Tyler - One World One Home</v>
+        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary</v>
       </c>
       <c r="B96" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
+        <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-16</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Bonnie Tyler</v>
+        <v>The Offspring</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
+        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary - The Offspring</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
+        <v>Louis Tomlinson - Sunflowers (Official Performance Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
+        <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-16</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Louis Tomlinson - Sunflowers (Official Performance Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Icona Pop - Dance To This (Official Video)</v>
+        <v>The Beaches - Should've Known Better (Official Visualizer)</v>
       </c>
       <c r="B98" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
+        <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-16</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Icona Pop</v>
+        <v>The Beaches</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
+        <v>The Beaches - Should've Known Better (Official Visualizer) - The Beaches</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Michael Jackson - Human Nature (Official Video)</v>
+        <v>The Kiffness - Serafino (Singing Cat Song)</v>
       </c>
       <c r="B99" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
+        <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-16</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Michael Jackson</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
+        <v>The Kiffness - Serafino (Singing Cat Song) - The Kiffness</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>The All-American Rejects - King Kong</v>
+        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer)</v>
       </c>
       <c r="B100" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
+        <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-16</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>The All-American Rejects</v>
+        <v>Dennis Lloyd</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
+        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer) - Dennis Lloyd</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
+        <v>Anna Graves - Damn In Love (Official Visualizer)</v>
       </c>
       <c r="B101" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
+        <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-16</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Ringo Starr</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
+        <v>Anna Graves - Damn In Love (Official Visualizer) - Anna Graves</v>
       </c>
     </row>
     <row r="102">

--- a/data/global/2026-05-week03/titles.xlsx
+++ b/data/global/2026-05-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B2" t="str">
-        <v>7 hours ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
+        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-16</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>7 hours ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Madison Cunningham</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B3" t="str">
-        <v>7 hours ago</v>
+        <v>1 hour ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
+        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-16</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>7 hours ago</v>
+        <v>1 hour ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Armin van Buuren</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video)</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
+        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-16</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Johnny Orlando</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video)</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>2 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
+        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-16</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>2 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Carver Jones</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video)</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>2 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
+        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-16</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>2 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Jazmin bean</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>1 hour ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
+        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-16</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>1 hour ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Baby Queen</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="8">
@@ -702,13 +702,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Switchfoot - Absolution (Official Audio)</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
+        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-16</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Switchfoot</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio)</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
+        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-16</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Grace Potter</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
+        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-16</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
+        <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B12" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
+        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-16</v>
@@ -837,7 +837,7 @@
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>The All-American Rejects</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
+        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser)</v>
+        <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B13" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
+        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-16</v>
@@ -875,7 +875,7 @@
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Henry Moodie</v>
+        <v>Carver Jones</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
+        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
+        <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
+        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-16</v>
@@ -913,7 +913,7 @@
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Spacey Jane</v>
+        <v>Jazmin bean</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
+        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B15" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
+        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-16</v>
@@ -951,7 +951,7 @@
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Megan Moroney</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser)</v>
+        <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B16" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
+        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-16</v>
@@ -989,7 +989,7 @@
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Matt Hansen</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
+        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
+        <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B17" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
+        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-16</v>
@@ -1027,7 +1027,7 @@
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Matt Hansen</v>
+        <v>Grace Potter</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
+        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Keith Urban - Steal Away (Visualizer)</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B18" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
+        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-16</v>
@@ -1065,7 +1065,7 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Keith Urban</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>VALÉ - Mugshot (Official Video)</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
+        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-16</v>
@@ -1103,7 +1103,7 @@
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>VALÉ</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio)</v>
+        <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B20" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
+        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-16</v>
@@ -1141,7 +1141,7 @@
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Mackenzie Carpenter</v>
+        <v>Henry Moodie</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
+        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Towa Bird - Afterglow (Lyric Video)</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B21" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
+        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-16</v>
@@ -1179,7 +1179,7 @@
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Towa Bird</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Towa Bird - Afterglow (Lyric Video) - Towa Bird</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
+        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-16</v>
@@ -1217,7 +1217,7 @@
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Sabrina Sterling</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
+        <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B23" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
+        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-16</v>
@@ -1255,7 +1255,7 @@
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Little Big Town</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
+        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Becky G - EPA (Official Video)</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
       </c>
       <c r="B24" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
+        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-16</v>
@@ -1293,7 +1293,7 @@
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Becky G</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Becky G - EPA (Official Video) - Becky G</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
+        <v>Keith Urban - Steal Away (Visualizer)</v>
       </c>
       <c r="B25" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
+        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-16</v>
@@ -1331,7 +1331,7 @@
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Daisy the Great</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
+        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Towa Bird - Dog (Official Music Video)</v>
+        <v>VALÉ - Mugshot (Official Video)</v>
       </c>
       <c r="B26" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
+        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-16</v>
@@ -1369,7 +1369,7 @@
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Towa Bird</v>
+        <v>VALÉ</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
+        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
+        <v>Mackenzie Carpenter - High Pony (Audio)</v>
       </c>
       <c r="B27" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
+        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-16</v>
@@ -1407,7 +1407,7 @@
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Madonna</v>
+        <v>Mackenzie Carpenter</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
+        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video)</v>
+        <v>Towa Bird - Afterglow (Lyric Video)</v>
       </c>
       <c r="B28" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
+        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-16</v>
@@ -1445,7 +1445,7 @@
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Ally Salort</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
+        <v>Towa Bird - Afterglow (Lyric Video) - Towa Bird</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Bella White - Better - Official Music Video</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
       </c>
       <c r="B29" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
+        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-16</v>
@@ -1483,7 +1483,7 @@
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Bella White</v>
+        <v>Sabrina Sterling</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Bella White - Better - Official Music Video - Bella White</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
+        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-16</v>
@@ -1521,7 +1521,7 @@
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Charles Wesley Godwin</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Towa Bird - All Gone (Lyric Video) ft. Kathleen Hanna</v>
+        <v>Becky G - EPA (Official Video)</v>
       </c>
       <c r="B31" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
+        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-16</v>
@@ -1559,7 +1559,7 @@
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Towa Bird</v>
+        <v>Becky G</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Towa Bird - All Gone (Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
+        <v>Becky G - EPA (Official Video) - Becky G</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer)</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
       </c>
       <c r="B32" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
+        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-16</v>
@@ -1597,7 +1597,7 @@
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Miranda Lambert</v>
+        <v>Daisy the Great</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
+        <v>Towa Bird - Dog (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
+        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-16</v>
@@ -1635,7 +1635,7 @@
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Lady Gaga</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
+        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
       </c>
       <c r="B34" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
+        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-16</v>
@@ -1673,7 +1673,7 @@
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Gracie Abrams</v>
+        <v>Madonna</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
+        <v>Ally Salort - Housekeeping (Lyric Video)</v>
       </c>
       <c r="B35" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
+        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-16</v>
@@ -1711,7 +1711,7 @@
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>The Last Dinner Party</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
+        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
+        <v>Bella White - Better - Official Music Video</v>
       </c>
       <c r="B36" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
+        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-16</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Martin Garrix</v>
+        <v>Bella White</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
+        <v>Bella White - Better - Official Music Video - Bella White</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Jorja Smith - What's Done Is Done</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
+        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-16</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Jorja Smith</v>
+        <v>Charles Wesley Godwin</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>LP - Shelly (Official Music Video)</v>
+        <v>Towa Bird - All Gone (Lyric Video) ft. Kathleen Hanna</v>
       </c>
       <c r="B38" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
+        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-16</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>LP</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>LP - Shelly (Official Music Video) - LP</v>
+        <v>Towa Bird - All Gone (Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
+        <v>Miranda Lambert - Crisco (Visualizer)</v>
       </c>
       <c r="B39" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
+        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-16</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>The Rolling Stones</v>
+        <v>Miranda Lambert</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
+        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
       </c>
       <c r="B40" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
+        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-16</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Oasis</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
+        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-16</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Breaking Benjamin</v>
+        <v>Gracie Abrams</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
+        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-16</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>VictorBiliac</v>
+        <v>The Last Dinner Party</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit ) - VictorBiliac</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>From The Inside (Live in Mumbai) - Linkin Park</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
       </c>
       <c r="B43" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
+        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-16</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Linkin Park</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>From The Inside (Live in Mumbai) - Linkin Park - Linkin Park</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
+        <v>Jorja Smith - What's Done Is Done</v>
       </c>
       <c r="B44" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
+        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-16</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Harry Styles - Dance No More (Official Video)</v>
+        <v>LP - Shelly (Official Music Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>9 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
+        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-16</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>9 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Harry Styles</v>
+        <v>LP</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
+        <v>LP - Shelly (Official Music Video) - LP</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
       </c>
       <c r="B46" t="str">
-        <v>9 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
+        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-16</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>9 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Eagles</v>
+        <v>The Rolling Stones</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
       </c>
       <c r="B47" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
+        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-16</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Nora Fatehi</v>
+        <v>Oasis</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
       </c>
       <c r="B48" t="str">
-        <v>2 months ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
+        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-16</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>2 months ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Breaking Benjamin</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
+        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
       </c>
       <c r="B49" t="str">
-        <v>2 months ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
+        <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-16</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>2 months ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Eurovision Song Contest and Alis</v>
+        <v>VictorBiliac</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
+        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit ) - VictorBiliac</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
+        <v>From The Inside (Live in Mumbai) - Linkin Park</v>
       </c>
       <c r="B50" t="str">
-        <v>2 months ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
+        <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-16</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>2 months ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Linkin Park</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
+        <v>From The Inside (Live in Mumbai) - Linkin Park - Linkin Park</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video)</v>
+        <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
+        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-16</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>The Head And The Heart</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
+        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
+        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-16</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Simply Red</v>
+        <v>Eagles</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video)</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B53" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
+        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-16</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Talking Heads</v>
+        <v>Nora Fatehi</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Ellise - Liplock (Official Music Video)</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B54" t="str">
-        <v>8 days ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
+        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-16</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8 days ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Ellise</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Tori Kelly - Dive (Official Music Video)</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B55" t="str">
-        <v>8 days ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
+        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-16</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>8 days ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Tori Kelly</v>
+        <v>Eurovision Song Contest and Alis</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
       </c>
       <c r="B56" t="str">
-        <v>8 days ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
+        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-16</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>8 days ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>David Gilmour</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024) - David Gilmour</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
+        <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B57" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
+        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-16</v>
@@ -2547,7 +2547,7 @@
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Scorpions</v>
+        <v>The Head And The Heart</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022) - Scorpions</v>
+        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B58" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
+        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-16</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Claire Leslie</v>
+        <v>Simply Red</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Claire Leslie - Passenger Seat (Official Music Video) - Claire Leslie</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Michael Schulte - Lovesick (Official Video)</v>
+        <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
+        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-16</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Michael Schulte</v>
+        <v>Talking Heads</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Michael Schulte - Lovesick (Official Video) - Michael Schulte</v>
+        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Caity Baser - Holiday Song (Official Video)</v>
+        <v>Ellise - Liplock (Official Music Video)</v>
       </c>
       <c r="B60" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
+        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-16</v>
@@ -2661,7 +2661,7 @@
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Caity Baser</v>
+        <v>Ellise</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Caity Baser - Holiday Song (Official Video) - Caity Baser</v>
+        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
+        <v>Tori Kelly - Dive (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
+        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-16</v>
@@ -2699,7 +2699,7 @@
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Sam Fischer</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser) - Sam Fischer</v>
+        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Porches- HABIT (Official Video)</v>
+        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
       </c>
       <c r="B62" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
+        <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-16</v>
@@ -2737,7 +2737,7 @@
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Porches</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Porches- HABIT (Official Video) - Porches</v>
+        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024) - David Gilmour</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Charli xcx - Rock Music (Official Video)</v>
+        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
       </c>
       <c r="B63" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
+        <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-16</v>
@@ -2775,7 +2775,7 @@
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Charli xcx</v>
+        <v>Scorpions</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Charli xcx - Rock Music (Official Video) - Charli xcx</v>
+        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Jon Batiste - Alla Blues (Audio)</v>
+        <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
+        <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-16</v>
@@ -2813,7 +2813,7 @@
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Jon Batiste</v>
+        <v>Claire Leslie</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Jon Batiste - Alla Blues (Audio) - Jon Batiste</v>
+        <v>Claire Leslie - Passenger Seat (Official Music Video) - Claire Leslie</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
+        <v>Michael Schulte - Lovesick (Official Video)</v>
       </c>
       <c r="B65" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
+        <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-16</v>
@@ -2851,7 +2851,7 @@
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Tigirlily Gold</v>
+        <v>Michael Schulte</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Tigirlily Gold - I Do or Die (Official Music Video) - Tigirlily Gold</v>
+        <v>Michael Schulte - Lovesick (Official Video) - Michael Schulte</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
+        <v>Caity Baser - Holiday Song (Official Video)</v>
       </c>
       <c r="B66" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
+        <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-16</v>
@@ -2889,7 +2889,7 @@
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Caity Baser</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video) - PAUL McCARTNEY</v>
+        <v>Caity Baser - Holiday Song (Official Video) - Caity Baser</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
+        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
       </c>
       <c r="B67" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
+        <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-16</v>
@@ -2927,7 +2927,7 @@
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Bruno Mars</v>
+        <v>Sam Fischer</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video] - Bruno Mars</v>
+        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser) - Sam Fischer</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Tori Kelly - Control (Official Visualizer)</v>
+        <v>Porches- HABIT (Official Video)</v>
       </c>
       <c r="B68" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
+        <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-16</v>
@@ -2965,7 +2965,7 @@
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Tori Kelly</v>
+        <v>Porches</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Tori Kelly - Control (Official Visualizer) - Tori Kelly</v>
+        <v>Porches- HABIT (Official Video) - Porches</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Bea Miller - depressed on the internet (Lyric Video)</v>
+        <v>Charli xcx - Rock Music (Official Video)</v>
       </c>
       <c r="B69" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
+        <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-16</v>
@@ -3003,7 +3003,7 @@
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>bea miller</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Bea Miller - depressed on the internet (Lyric Video) - bea miller</v>
+        <v>Charli xcx - Rock Music (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
+        <v>Jon Batiste - Alla Blues (Audio)</v>
       </c>
       <c r="B70" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
+        <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-16</v>
@@ -3041,7 +3041,7 @@
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>The Chainsmokers</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer) - The Chainsmokers</v>
+        <v>Jon Batiste - Alla Blues (Audio) - Jon Batiste</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Madison Beer - free (Official Audio)</v>
+        <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
+        <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-16</v>
@@ -3079,7 +3079,7 @@
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Madison Beer</v>
+        <v>Tigirlily Gold</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Madison Beer - free (Official Audio) - Madison Beer</v>
+        <v>Tigirlily Gold - I Do or Die (Official Music Video) - Tigirlily Gold</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Tori Kelly - Dive (Official Audio)</v>
+        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
       </c>
       <c r="B72" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
+        <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-16</v>
@@ -3117,7 +3117,7 @@
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Tori Kelly</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Tori Kelly - Dive (Official Audio) - Tori Kelly</v>
+        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Jeremy Camp - Reflector (Official Audio)</v>
+        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
       </c>
       <c r="B73" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
+        <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-16</v>
@@ -3155,7 +3155,7 @@
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>JeremyCampMusic</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Jeremy Camp - Reflector (Official Audio) - JeremyCampMusic</v>
+        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
+        <v>Tori Kelly - Control (Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
+        <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-16</v>
@@ -3193,7 +3193,7 @@
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>The Chainsmokers</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer) - The Chainsmokers</v>
+        <v>Tori Kelly - Control (Official Visualizer) - Tori Kelly</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Ashley Cooke - high school sweetheart</v>
+        <v>Bea Miller - depressed on the internet (Lyric Video)</v>
       </c>
       <c r="B75" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
+        <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-16</v>
@@ -3231,7 +3231,7 @@
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Ashley Cooke</v>
+        <v>bea miller</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Ashley Cooke - high school sweetheart - Ashley Cooke</v>
+        <v>Bea Miller - depressed on the internet (Lyric Video) - bea miller</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Ari Abdul - Ego (Visualizer)</v>
+        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
       </c>
       <c r="B76" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=L0FjVr6LpVU</v>
+        <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-16</v>
@@ -3269,7 +3269,7 @@
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Ari Abdul</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Ari Abdul - Ego (Visualizer) - Ari Abdul</v>
+        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Quinn XCII - HOOPLA (Official Music Video)</v>
+        <v>Madison Beer - free (Official Audio)</v>
       </c>
       <c r="B77" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=eNbGA1pgmFk</v>
+        <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-16</v>
@@ -3307,7 +3307,7 @@
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Quinn XCII</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Quinn XCII - HOOPLA (Official Music Video) - Quinn XCII</v>
+        <v>Madison Beer - free (Official Audio) - Madison Beer</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Madison Beer - lovergirl (Official Music Video)</v>
+        <v>Tori Kelly - Dive (Official Audio)</v>
       </c>
       <c r="B78" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=q4lU1N3oqYQ</v>
+        <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-16</v>
@@ -3345,7 +3345,7 @@
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Madison Beer</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Madison Beer - lovergirl (Official Music Video) - Madison Beer</v>
+        <v>Tori Kelly - Dive (Official Audio) - Tori Kelly</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>David J - WHAT IF I'M IN LOVE (Official Video)</v>
+        <v>Jeremy Camp - Reflector (Official Audio)</v>
       </c>
       <c r="B79" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=-SF7Hm_ikaY</v>
+        <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-16</v>
@@ -3383,7 +3383,7 @@
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>David J</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>David J - WHAT IF I'M IN LOVE (Official Video) - David J</v>
+        <v>Jeremy Camp - Reflector (Official Audio) - JeremyCampMusic</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>The Last Dinner Party - Big Dog (On The Road)</v>
+        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
       </c>
       <c r="B80" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
+        <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-16</v>
@@ -3421,7 +3421,7 @@
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>The Last Dinner Party</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>The Last Dinner Party - Big Dog (On The Road) - The Last Dinner Party</v>
+        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>OCEAN ALLEY - HOLD ON (Official Video)</v>
+        <v>Ashley Cooke - high school sweetheart</v>
       </c>
       <c r="B81" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
+        <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-16</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Ocean Alley</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>OCEAN ALLEY - HOLD ON (Official Video) - Ocean Alley</v>
+        <v>Ashley Cooke - high school sweetheart - Ashley Cooke</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Dagny - Closet Disco Queen (Lyric Video)</v>
+        <v>Ari Abdul - Ego (Visualizer)</v>
       </c>
       <c r="B82" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
+        <v>https://www.youtube.com/watch?v=L0FjVr6LpVU</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-16</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Dagny</v>
+        <v>Ari Abdul</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Dagny - Closet Disco Queen (Lyric Video) - Dagny</v>
+        <v>Ari Abdul - Ego (Visualizer) - Ari Abdul</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Purple Disco Machine - Disco Cherry (Official Video)</v>
+        <v>Quinn XCII - HOOPLA (Official Music Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
+        <v>https://www.youtube.com/watch?v=eNbGA1pgmFk</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-16</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Quinn XCII</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Purple Disco Machine - Disco Cherry (Official Video) - Purple Disco Machine</v>
+        <v>Quinn XCII - HOOPLA (Official Music Video) - Quinn XCII</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Paris Paloma - Stem the Flow [Official Music Video]</v>
+        <v>Madison Beer - lovergirl (Official Music Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
+        <v>https://www.youtube.com/watch?v=q4lU1N3oqYQ</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-16</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Paris Paloma</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Paris Paloma - Stem the Flow [Official Music Video] - Paris Paloma</v>
+        <v>Madison Beer - lovergirl (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Lucy Blue - Who you love (Visualiser)</v>
+        <v>David J - WHAT IF I'M IN LOVE (Official Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
+        <v>https://www.youtube.com/watch?v=-SF7Hm_ikaY</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-16</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Lucy Blue</v>
+        <v>David J</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Lucy Blue - Who you love (Visualiser) - Lucy Blue</v>
+        <v>David J - WHAT IF I'M IN LOVE (Official Video) - David J</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026)</v>
+        <v>The Last Dinner Party - Big Dog (On The Road)</v>
       </c>
       <c r="B86" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
+        <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-16</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Olivia Dean</v>
+        <v>The Last Dinner Party</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026) - Olivia Dean</v>
+        <v>The Last Dinner Party - Big Dog (On The Road) - The Last Dinner Party</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Aaron Frazer - It's A Shame (Official Video)</v>
+        <v>OCEAN ALLEY - HOLD ON (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
+        <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-16</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Aaron Frazer</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Aaron Frazer - It's A Shame (Official Video) - Aaron Frazer</v>
+        <v>OCEAN ALLEY - HOLD ON (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify</v>
+        <v>Dagny - Closet Disco Queen (Lyric Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
+        <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-16</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Holly Humberstone</v>
+        <v>Dagny</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>Dagny - Closet Disco Queen (Lyric Video) - Dagny</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>DANNA - OUT OF MY BODY</v>
+        <v>Purple Disco Machine - Disco Cherry (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=uW_Ye0kQ9Ac</v>
+        <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-16</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Danna</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>DANNA - OUT OF MY BODY - Danna</v>
+        <v>Purple Disco Machine - Disco Cherry (Official Video) - Purple Disco Machine</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>The Rolling Stones - In The Stars (Official Lyric Video)</v>
+        <v>Paris Paloma - Stem the Flow [Official Music Video]</v>
       </c>
       <c r="B90" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
+        <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-16</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>The Rolling Stones</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>The Rolling Stones - In The Stars (Official Lyric Video) - The Rolling Stones</v>
+        <v>Paris Paloma - Stem the Flow [Official Music Video] - Paris Paloma</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser)</v>
+        <v>Lucy Blue - Who you love (Visualiser)</v>
       </c>
       <c r="B91" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
+        <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-16</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Lucy Blue</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser) - Dermot Kennedy</v>
+        <v>Lucy Blue - Who you love (Visualiser) - Lucy Blue</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
+        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026)</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
+        <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-16</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2) - SIENNA SPIRO</v>
+        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026) - Olivia Dean</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Rick Astley - Raindrops (Official Video)</v>
+        <v>Aaron Frazer - It's A Shame (Official Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
+        <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-16</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Rick Astley</v>
+        <v>Aaron Frazer</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Rick Astley - Raindrops (Official Video) - Rick Astley</v>
+        <v>Aaron Frazer - It's A Shame (Official Video) - Aaron Frazer</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Jessie J - THREW IT AWAY (Official Video)</v>
+        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
+        <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-16</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Jessie J</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Jessie J - THREW IT AWAY (Official Video) - Jessie J</v>
+        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>The Takes - Ain't Love (Lyric Video)</v>
+        <v>DANNA - OUT OF MY BODY</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
+        <v>https://www.youtube.com/watch?v=uW_Ye0kQ9Ac</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-16</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>The Takes</v>
+        <v>Danna</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>The Takes - Ain't Love (Lyric Video) - The Takes</v>
+        <v>DANNA - OUT OF MY BODY - Danna</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary</v>
+        <v>The Rolling Stones - In The Stars (Official Lyric Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
+        <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-16</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>The Offspring</v>
+        <v>The Rolling Stones</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary - The Offspring</v>
+        <v>The Rolling Stones - In The Stars (Official Lyric Video) - The Rolling Stones</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Louis Tomlinson - Sunflowers (Official Performance Video)</v>
+        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser)</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
+        <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-16</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Louis Tomlinson - Sunflowers (Official Performance Video) - Louis Tomlinson</v>
+        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>The Beaches - Should've Known Better (Official Visualizer)</v>
+        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
+        <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-16</v>
@@ -4105,7 +4105,7 @@
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>The Beaches</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>The Beaches - Should've Known Better (Official Visualizer) - The Beaches</v>
+        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>The Kiffness - Serafino (Singing Cat Song)</v>
+        <v>Rick Astley - Raindrops (Official Video)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
+        <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-16</v>
@@ -4143,7 +4143,7 @@
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>The Kiffness</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>The Kiffness - Serafino (Singing Cat Song) - The Kiffness</v>
+        <v>Rick Astley - Raindrops (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer)</v>
+        <v>Jessie J - THREW IT AWAY (Official Video)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
+        <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-16</v>
@@ -4181,7 +4181,7 @@
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Dennis Lloyd</v>
+        <v>Jessie J</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer) - Dennis Lloyd</v>
+        <v>Jessie J - THREW IT AWAY (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Anna Graves - Damn In Love (Official Visualizer)</v>
+        <v>The Takes - Ain't Love (Lyric Video)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
+        <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-16</v>
@@ -4219,7 +4219,7 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Anna Graves</v>
+        <v>The Takes</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Anna Graves - Damn In Love (Official Visualizer) - Anna Graves</v>
+        <v>The Takes - Ain't Love (Lyric Video) - The Takes</v>
       </c>
     </row>
     <row r="102">

--- a/data/global/2026-05-week03/titles.xlsx
+++ b/data/global/2026-05-week03/titles.xlsx
@@ -439,19 +439,19 @@
         <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B2" t="str">
-        <v>3 hours ago</v>
+        <v>5h ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>3 hours ago</v>
+        <v>5h ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,19 +477,19 @@
         <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B3" t="str">
-        <v>1 hour ago</v>
+        <v>3h ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 hour ago</v>
+        <v>3h ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,19 +515,19 @@
         <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B4" t="str">
-        <v>3 hours ago</v>
+        <v>5h ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>3 hours ago</v>
+        <v>5h ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,19 +553,19 @@
         <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B5" t="str">
-        <v>2 hours ago</v>
+        <v>4h ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 hours ago</v>
+        <v>4h ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,19 +591,19 @@
         <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B6" t="str">
-        <v>2 hours ago</v>
+        <v>4h ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 hours ago</v>
+        <v>4h ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,19 +629,19 @@
         <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B7" t="str">
-        <v>1 hour ago</v>
+        <v>3h ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 hour ago</v>
+        <v>3h ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,19 +667,19 @@
         <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,19 +705,19 @@
         <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,19 +743,19 @@
         <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B10" t="str">
-        <v>8 hours ago</v>
+        <v>11h ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>8 hours ago</v>
+        <v>11h ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,19 +781,19 @@
         <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B11" t="str">
-        <v>8 hours ago</v>
+        <v>10h ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>8 hours ago</v>
+        <v>10h ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,19 +819,19 @@
         <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,19 +857,19 @@
         <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,19 +895,19 @@
         <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,19 +933,19 @@
         <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B15" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,19 +971,19 @@
         <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B16" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,19 +1009,19 @@
         <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B17" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,19 +1047,19 @@
         <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B18" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,19 +1085,19 @@
         <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,19 +1123,19 @@
         <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B20" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,19 +1161,19 @@
         <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,19 +1199,19 @@
         <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,19 +1237,19 @@
         <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B23" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,19 +1275,19 @@
         <v>Matt Hansen - Before We Know It (Lyric Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,19 +1313,19 @@
         <v>Keith Urban - Steal Away (Visualizer)</v>
       </c>
       <c r="B25" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,19 +1351,19 @@
         <v>VALÉ - Mugshot (Official Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,19 +1389,19 @@
         <v>Mackenzie Carpenter - High Pony (Audio)</v>
       </c>
       <c r="B27" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,19 +1427,19 @@
         <v>Towa Bird - Afterglow (Lyric Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,19 +1465,19 @@
         <v>Sabrina Sterling - Hold (Official Visualizer)</v>
       </c>
       <c r="B29" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,19 +1503,19 @@
         <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,19 +1541,19 @@
         <v>Becky G - EPA (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,19 +1579,19 @@
         <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,19 +1617,19 @@
         <v>Towa Bird - Dog (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,19 +1655,19 @@
         <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
       </c>
       <c r="B34" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,19 +1693,19 @@
         <v>Ally Salort - Housekeeping (Lyric Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,19 +1731,19 @@
         <v>Bella White - Better - Official Music Video</v>
       </c>
       <c r="B36" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,19 +1769,19 @@
         <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,19 +1807,19 @@
         <v>Towa Bird - All Gone (Lyric Video) ft. Kathleen Hanna</v>
       </c>
       <c r="B38" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,19 +1845,19 @@
         <v>Miranda Lambert - Crisco (Visualizer)</v>
       </c>
       <c r="B39" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,19 +1883,19 @@
         <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
       </c>
       <c r="B40" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,19 +1921,19 @@
         <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,19 +1959,19 @@
         <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,19 +1997,19 @@
         <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
       </c>
       <c r="B43" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,19 +2035,19 @@
         <v>Jorja Smith - What's Done Is Done</v>
       </c>
       <c r="B44" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,19 +2073,19 @@
         <v>LP - Shelly (Official Music Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,19 +2111,19 @@
         <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
       </c>
       <c r="B46" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,19 +2149,19 @@
         <v>Oasis - Champagne Supernova (Official Visualiser)</v>
       </c>
       <c r="B47" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,19 +2187,19 @@
         <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
       </c>
       <c r="B48" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,19 +2225,19 @@
         <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
       </c>
       <c r="B49" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,19 +2263,19 @@
         <v>From The Inside (Live in Mumbai) - Linkin Park</v>
       </c>
       <c r="B50" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,19 +2301,19 @@
         <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,19 +2339,19 @@
         <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,19 +2377,19 @@
         <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B53" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,19 +2415,19 @@
         <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B54" t="str">
-        <v>2 months ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2 months ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,19 +2453,19 @@
         <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B55" t="str">
-        <v>2 months ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2 months ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,19 +2491,19 @@
         <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
       </c>
       <c r="B56" t="str">
-        <v>2 months ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2 months ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,19 +2529,19 @@
         <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,19 +2567,19 @@
         <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B58" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,19 +2605,19 @@
         <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,19 +2643,19 @@
         <v>Ellise - Liplock (Official Music Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,19 +2681,19 @@
         <v>Tori Kelly - Dive (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,19 +2719,19 @@
         <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
       </c>
       <c r="B62" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,19 +2757,19 @@
         <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
       </c>
       <c r="B63" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,19 +2795,19 @@
         <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,19 +2833,19 @@
         <v>Michael Schulte - Lovesick (Official Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,19 +2871,19 @@
         <v>Caity Baser - Holiday Song (Official Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,19 +2909,19 @@
         <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
       </c>
       <c r="B67" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,19 +2947,19 @@
         <v>Porches- HABIT (Official Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,19 +2985,19 @@
         <v>Charli xcx - Rock Music (Official Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,19 +3023,19 @@
         <v>Jon Batiste - Alla Blues (Audio)</v>
       </c>
       <c r="B70" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,19 +3061,19 @@
         <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,19 +3099,19 @@
         <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,19 +3137,19 @@
         <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
       </c>
       <c r="B73" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,19 +3175,19 @@
         <v>Tori Kelly - Control (Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,19 +3213,19 @@
         <v>Bea Miller - depressed on the internet (Lyric Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,19 +3251,19 @@
         <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
       </c>
       <c r="B76" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,19 +3289,19 @@
         <v>Madison Beer - free (Official Audio)</v>
       </c>
       <c r="B77" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,19 +3327,19 @@
         <v>Tori Kelly - Dive (Official Audio)</v>
       </c>
       <c r="B78" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,19 +3365,19 @@
         <v>Jeremy Camp - Reflector (Official Audio)</v>
       </c>
       <c r="B79" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,19 +3403,19 @@
         <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
       </c>
       <c r="B80" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,19 +3441,19 @@
         <v>Ashley Cooke - high school sweetheart</v>
       </c>
       <c r="B81" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,19 +3479,19 @@
         <v>Ari Abdul - Ego (Visualizer)</v>
       </c>
       <c r="B82" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=L0FjVr6LpVU</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,19 +3517,19 @@
         <v>Quinn XCII - HOOPLA (Official Music Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=eNbGA1pgmFk</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,19 +3555,19 @@
         <v>Madison Beer - lovergirl (Official Music Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=q4lU1N3oqYQ</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,19 +3593,19 @@
         <v>David J - WHAT IF I'M IN LOVE (Official Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=-SF7Hm_ikaY</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,19 +3631,19 @@
         <v>The Last Dinner Party - Big Dog (On The Road)</v>
       </c>
       <c r="B86" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,19 +3669,19 @@
         <v>OCEAN ALLEY - HOLD ON (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,19 +3707,19 @@
         <v>Dagny - Closet Disco Queen (Lyric Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,19 +3745,19 @@
         <v>Purple Disco Machine - Disco Cherry (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,19 +3783,19 @@
         <v>Paris Paloma - Stem the Flow [Official Music Video]</v>
       </c>
       <c r="B90" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,19 +3821,19 @@
         <v>Lucy Blue - Who you love (Visualiser)</v>
       </c>
       <c r="B91" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,19 +3859,19 @@
         <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026)</v>
       </c>
       <c r="B92" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,19 +3897,19 @@
         <v>Aaron Frazer - It's A Shame (Official Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,19 +3935,19 @@
         <v>Holly Humberstone - White Noise (Live) | Presented By Spotify</v>
       </c>
       <c r="B94" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,19 +3973,19 @@
         <v>DANNA - OUT OF MY BODY</v>
       </c>
       <c r="B95" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=uW_Ye0kQ9Ac</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,19 +4011,19 @@
         <v>The Rolling Stones - In The Stars (Official Lyric Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,19 +4049,19 @@
         <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser)</v>
       </c>
       <c r="B97" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,19 +4087,19 @@
         <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
       </c>
       <c r="B98" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,19 +4125,19 @@
         <v>Rick Astley - Raindrops (Official Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,19 +4163,19 @@
         <v>Jessie J - THREW IT AWAY (Official Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,19 +4201,19 @@
         <v>The Takes - Ain't Love (Lyric Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E101" t="str">
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/hit-the-wall/6766750846</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/ran-to-atlanta/6769568597</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/hoe-phase/6769556949</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/im-spent/6769551476</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/abracadabra-apple-music-live/6768201780</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/falling-out-of-love/1891161448</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/dai-dai/6768469976</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/tu-recuerdo/6763660843</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/traitor-roles-reversed/6767665959</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/dirty-rosie/6767044374</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/like-you-mean-it/6767024693</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/hardy-feat-clairo/1876953073</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/2-hard-4-the-radio/6769568610</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/cheetah-print/6769557055</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/wnba/6769551471</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/shadow-of-a-man-apple-music-live/6768201925</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/epa/6768420253</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/im-your-girl-right/6766440186</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/fu%C3%ABgo/6767661766</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/jajaja/6766341319</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/find-god-feat-dominic-fike/1894315529</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/fool-me-once-feat-leon-thomas/1891467239</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/shabang/6769568598</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/road-trips/6769557053</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/fortworth/6769551482</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/repeat-it/6764277864</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/fool-proof/1892466004</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/crisco/6763369506</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/absolution/1884987651</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/jesus-is-alive/6767694896</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/something-to-lose/6766964605</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/too-busy-missing-you/6766604915</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/f-stop-blues-4-track/1883173173</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/pa-lo-bonito/1886496944</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/lonely/6768757857</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/lockup/1894298102</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/young/6767698952</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/parachute/6764119241</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/little-things/6766351153</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/fish-hunt-golf-drink/6766651884</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/pageant-stage/6764125889</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/firestorm/1868827004</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/girl-next-door/6768077610</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/big-dog/1887197046</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/idea-of-love-a-colors-show/6767667046</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/heavy-serenade/1892154309</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/ddok-ddok-ddok/6764203482</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/shut-it-down/6763631128</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/together-feat-nikki-nair-jessy-lanza-prentiss/6763207821</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/cant-miss-you/1886810999</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/razorblades-and-runways/1888004809</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/massacre/1892127745</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/better-that-way/6766273199</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/apollo/6765602431</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/infinity-123/6763447312</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/aint-over-me-yet/6767283811</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/where-did-you-go/1877958504</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/i-love-you/6766999950</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/housekeeping/6766290834</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/surprise-surprise/6764842119</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/dog/1885967384</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/i-never-see-her/6764149225</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/no-god/1891187414</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/burden/6767688180</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/chico-raro/6767713536</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/whats-done-is-done/6763088629</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/round-and-round/1885665987</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/aint-that-deep/1882831449</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/emily/1893405442</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/hold/6767296480</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/flying-monkey/1894351228</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/anything-goes/1891118972</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/we-are/1894252873</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/its-for-the-kids/1867327679</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/pure-ecstasy/6762228978</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/something-wicked/6766252959</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/feel-the-funk/6763294007</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/everglades-remix/6767719584</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/walk/1892180098</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/volver-a-ti/6766258204</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/bahamas/6764695848</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/same-old-song/6762860685</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/gentle/6762828356</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/letters-of-your-name/1892919741</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/seratonin/6763447428</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/a-digital-touch/6765592539</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/dead-mans-dog/6763447424</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/fault-of-god/1887702403</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/zone-feat-poppy-baskcomb/6763982867</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/word-vomit/1887315297</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/evil-in-this-house/1892398371</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/heaven-on-high/1881724153</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E193" t="str">
         <v/>

--- a/data/global/2026-05-week03/titles.xlsx
+++ b/data/global/2026-05-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L193"/>
+  <dimension ref="A1:L194"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Eurovision 2026</v>
+        <v>בן ארצי – ישראל</v>
       </c>
       <c r="B2" t="str">
-        <v>5h ago</v>
+        <v>2026-05-17</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
+        <v>https://yosmusic.com/%d7%91%d7%9f-%d7%90%d7%a8%d7%a6%d7%99-%d7%99%d7%a9%d7%a8%d7%90%d7%9c/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-17</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>5h ago</v>
+        <v>השיר "ישראל” של בן ארצי בנוי כעל פרדוקס רגשי: אהבה עמוקה למדינה לצד תחושת אכזבה קשה ממנה. זה לא שיר מחאה זועם או מהפכני, אלא שיר של אדם שמרגיש שייך – ולכן גם פגוע. דווקא בגלל הטון הפשוט והישיר שלו,</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Eurovision Song Contest</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>בן ארצי – ישראל</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B3" t="str">
-        <v>3h ago</v>
+        <v>11h ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
+        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-17</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>3h ago</v>
+        <v>11h ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B4" t="str">
-        <v>5h ago</v>
+        <v>9h ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
+        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-17</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>5h ago</v>
+        <v>9h ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B5" t="str">
-        <v>4h ago</v>
+        <v>12h ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
+        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-17</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>4h ago</v>
+        <v>12h ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B6" t="str">
-        <v>4h ago</v>
+        <v>10h ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
+        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-17</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>4h ago</v>
+        <v>10h ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B7" t="str">
-        <v>3h ago</v>
+        <v>10h ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
+        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-17</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>3h ago</v>
+        <v>10h ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B8" t="str">
-        <v>1d ago</v>
+        <v>10h ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
+        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-17</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1d ago</v>
+        <v>10h ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Evanescence</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>4d ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
+        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-17</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>4d ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Evanescence</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>11h ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
+        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-17</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>11h ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Armin van Buuren</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B11" t="str">
-        <v>10h ago</v>
+        <v>17h ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
+        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-17</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>10h ago</v>
+        <v>17h ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Madison Cunningham</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video)</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B12" t="str">
-        <v>1d ago</v>
+        <v>17h ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
+        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-17</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1d ago</v>
+        <v>17h ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Johnny Orlando</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video)</v>
+        <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B13" t="str">
         <v>1d ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
+        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-17</v>
@@ -875,7 +875,7 @@
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Carver Jones</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
+        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video)</v>
+        <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B14" t="str">
         <v>1d ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
+        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-17</v>
@@ -913,7 +913,7 @@
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Jazmin bean</v>
+        <v>Carver Jones</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
+        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
+        <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
         <v>1d ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
+        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-17</v>
@@ -951,7 +951,7 @@
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Baby Queen</v>
+        <v>Jazmin bean</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
+        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Switchfoot - Absolution (Official Audio)</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B16" t="str">
         <v>1d ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
+        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-17</v>
@@ -989,7 +989,7 @@
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Switchfoot</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio)</v>
+        <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B17" t="str">
         <v>1d ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
+        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-17</v>
@@ -1027,7 +1027,7 @@
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Grace Potter</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
+        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
+        <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B18" t="str">
         <v>1d ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
+        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-17</v>
@@ -1065,7 +1065,7 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>Grace Potter</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
+        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B19" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
+        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-17</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>The All-American Rejects</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser)</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
+        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-17</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Henry Moodie</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
+        <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B21" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
+        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-17</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Spacey Jane</v>
+        <v>Henry Moodie</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
+        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
+        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-17</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Megan Moroney</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser)</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
+        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-17</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Matt Hansen</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
+        <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B24" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
+        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-17</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
+        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Keith Urban - Steal Away (Visualizer)</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
+        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-17</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Keith Urban</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>VALÉ - Mugshot (Official Video)</v>
+        <v>Keith Urban - Steal Away (Visualizer)</v>
       </c>
       <c r="B26" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
+        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-17</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>VALÉ</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
+        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio)</v>
+        <v>VALÉ - Mugshot (Official Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
+        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-17</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Mackenzie Carpenter</v>
+        <v>VALÉ</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
+        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Towa Bird - Afterglow (Lyric Video)</v>
+        <v>Mackenzie Carpenter - High Pony (Audio)</v>
       </c>
       <c r="B28" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
+        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-17</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Towa Bird</v>
+        <v>Mackenzie Carpenter</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Towa Bird - Afterglow (Lyric Video) - Towa Bird</v>
+        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
+        <v>Towa Bird - Afterglow (Lyric Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
+        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-17</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Sabrina Sterling</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
+        <v>Towa Bird - Afterglow (Lyric Video) - Towa Bird</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
       </c>
       <c r="B30" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
+        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-17</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Little Big Town</v>
+        <v>Sabrina Sterling</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Becky G - EPA (Official Video)</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
+        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-17</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Becky G</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Becky G - EPA (Official Video) - Becky G</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
+        <v>Becky G - EPA (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
+        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-17</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Daisy the Great</v>
+        <v>Becky G</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
+        <v>Becky G - EPA (Official Video) - Becky G</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Towa Bird - Dog (Official Music Video)</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
+        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-17</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Towa Bird</v>
+        <v>Daisy the Great</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
+        <v>Towa Bird - Dog (Official Music Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
+        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-17</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Madonna</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
+        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video)</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
       </c>
       <c r="B35" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
+        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-17</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Ally Salort</v>
+        <v>Madonna</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Bella White - Better - Official Music Video</v>
+        <v>Ally Salort - Housekeeping (Lyric Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
+        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-17</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Bella White</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Bella White - Better - Official Music Video - Bella White</v>
+        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
+        <v>Bella White - Better - Official Music Video</v>
       </c>
       <c r="B37" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
+        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-17</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Charles Wesley Godwin</v>
+        <v>Bella White</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
+        <v>Bella White - Better - Official Music Video - Bella White</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Towa Bird - All Gone (Lyric Video) ft. Kathleen Hanna</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
+        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-17</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Towa Bird</v>
+        <v>Charles Wesley Godwin</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Towa Bird - All Gone (Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer)</v>
+        <v>Towa Bird - All Gone (Lyric Video) ft. Kathleen Hanna</v>
       </c>
       <c r="B39" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
+        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-17</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Miranda Lambert</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
+        <v>Towa Bird - All Gone (Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
+        <v>Miranda Lambert - Crisco (Visualizer)</v>
       </c>
       <c r="B40" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
+        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-17</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>1d ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Lady Gaga</v>
+        <v>Miranda Lambert</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
+        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
       </c>
       <c r="B41" t="str">
         <v>2d ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
+        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-17</v>
@@ -1939,7 +1939,7 @@
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Gracie Abrams</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
       </c>
       <c r="B42" t="str">
         <v>2d ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
+        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-17</v>
@@ -1977,7 +1977,7 @@
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>The Last Dinner Party</v>
+        <v>Gracie Abrams</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
       </c>
       <c r="B43" t="str">
         <v>2d ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
+        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-17</v>
@@ -2015,7 +2015,7 @@
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Martin Garrix</v>
+        <v>The Last Dinner Party</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Jorja Smith - What's Done Is Done</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
       </c>
       <c r="B44" t="str">
         <v>2d ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
+        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-17</v>
@@ -2053,7 +2053,7 @@
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Jorja Smith</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>LP - Shelly (Official Music Video)</v>
+        <v>Jorja Smith - What's Done Is Done</v>
       </c>
       <c r="B45" t="str">
         <v>2d ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
+        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-17</v>
@@ -2091,7 +2091,7 @@
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>LP</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>LP - Shelly (Official Music Video) - LP</v>
+        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
+        <v>LP - Shelly (Official Music Video)</v>
       </c>
       <c r="B46" t="str">
         <v>3d ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
+        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-17</v>
@@ -2129,7 +2129,7 @@
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>The Rolling Stones</v>
+        <v>LP</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
+        <v>LP - Shelly (Official Music Video) - LP</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
       </c>
       <c r="B47" t="str">
         <v>3d ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
+        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-17</v>
@@ -2167,7 +2167,7 @@
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Oasis</v>
+        <v>The Rolling Stones</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
       </c>
       <c r="B48" t="str">
         <v>3d ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
+        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-17</v>
@@ -2205,7 +2205,7 @@
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Breaking Benjamin</v>
+        <v>Oasis</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
       </c>
       <c r="B49" t="str">
         <v>4d ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
+        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-17</v>
@@ -2243,7 +2243,7 @@
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>VictorBiliac</v>
+        <v>Breaking Benjamin</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit ) - VictorBiliac</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>From The Inside (Live in Mumbai) - Linkin Park</v>
+        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
       </c>
       <c r="B50" t="str">
         <v>4d ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
+        <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-17</v>
@@ -2281,7 +2281,7 @@
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Linkin Park</v>
+        <v>VictorBiliac</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>From The Inside (Live in Mumbai) - Linkin Park - Linkin Park</v>
+        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit ) - VictorBiliac</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Harry Styles - Dance No More (Official Video)</v>
+        <v>From The Inside (Live in Mumbai) - Linkin Park</v>
       </c>
       <c r="B51" t="str">
-        <v>9d ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
+        <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-17</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>9d ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Harry Styles</v>
+        <v>Linkin Park</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
+        <v>From The Inside (Live in Mumbai) - Linkin Park - Linkin Park</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
+        <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B52" t="str">
         <v>9d ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
+        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-17</v>
@@ -2357,7 +2357,7 @@
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Eagles</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
+        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>7d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
+        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-17</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>7d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Nora Fatehi</v>
+        <v>Eagles</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B54" t="str">
-        <v>2mo ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
+        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-17</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2mo ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Nora Fatehi</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B55" t="str">
         <v>2mo ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
+        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-17</v>
@@ -2471,7 +2471,7 @@
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Eurovision Song Contest and Alis</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B56" t="str">
         <v>2mo ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
+        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-17</v>
@@ -2509,7 +2509,7 @@
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Eurovision Song Contest and Alis</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video)</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
       </c>
       <c r="B57" t="str">
-        <v>8d ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
+        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-17</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>8d ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>The Head And The Heart</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
+        <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>10d ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
+        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-17</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>10d ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Simply Red</v>
+        <v>The Head And The Heart</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
+        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video)</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B59" t="str">
-        <v>6d ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
+        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-17</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>6d ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Talking Heads</v>
+        <v>Simply Red</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Ellise - Liplock (Official Music Video)</v>
+        <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>8d ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
+        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-17</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>8d ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Ellise</v>
+        <v>Talking Heads</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
+        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Tori Kelly - Dive (Official Music Video)</v>
+        <v>Ellise - Liplock (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
         <v>8d ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
+        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-17</v>
@@ -2699,7 +2699,7 @@
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Tori Kelly</v>
+        <v>Ellise</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
+        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
+        <v>Tori Kelly - Dive (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
         <v>8d ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
+        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-17</v>
@@ -2737,7 +2737,7 @@
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>David Gilmour</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024) - David Gilmour</v>
+        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
+        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
       </c>
       <c r="B63" t="str">
         <v>8d ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
+        <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-17</v>
@@ -2775,7 +2775,7 @@
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Scorpions</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022) - Scorpions</v>
+        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024) - David Gilmour</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
+        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
       </c>
       <c r="B64" t="str">
         <v>8d ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
+        <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-17</v>
@@ -2813,7 +2813,7 @@
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Claire Leslie</v>
+        <v>Scorpions</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Claire Leslie - Passenger Seat (Official Music Video) - Claire Leslie</v>
+        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Michael Schulte - Lovesick (Official Video)</v>
+        <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
         <v>8d ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
+        <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-17</v>
@@ -2851,7 +2851,7 @@
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Michael Schulte</v>
+        <v>Claire Leslie</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Michael Schulte - Lovesick (Official Video) - Michael Schulte</v>
+        <v>Claire Leslie - Passenger Seat (Official Music Video) - Claire Leslie</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Caity Baser - Holiday Song (Official Video)</v>
+        <v>Michael Schulte - Lovesick (Official Video)</v>
       </c>
       <c r="B66" t="str">
         <v>8d ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
+        <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-17</v>
@@ -2889,7 +2889,7 @@
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Caity Baser</v>
+        <v>Michael Schulte</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Caity Baser - Holiday Song (Official Video) - Caity Baser</v>
+        <v>Michael Schulte - Lovesick (Official Video) - Michael Schulte</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
+        <v>Caity Baser - Holiday Song (Official Video)</v>
       </c>
       <c r="B67" t="str">
         <v>8d ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
+        <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-17</v>
@@ -2927,7 +2927,7 @@
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Sam Fischer</v>
+        <v>Caity Baser</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser) - Sam Fischer</v>
+        <v>Caity Baser - Holiday Song (Official Video) - Caity Baser</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Porches- HABIT (Official Video)</v>
+        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
       </c>
       <c r="B68" t="str">
         <v>8d ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
+        <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-17</v>
@@ -2965,7 +2965,7 @@
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Porches</v>
+        <v>Sam Fischer</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Porches- HABIT (Official Video) - Porches</v>
+        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser) - Sam Fischer</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Charli xcx - Rock Music (Official Video)</v>
+        <v>Porches- HABIT (Official Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
+        <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-17</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Charli xcx</v>
+        <v>Porches</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Charli xcx - Rock Music (Official Video) - Charli xcx</v>
+        <v>Porches- HABIT (Official Video) - Porches</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Jon Batiste - Alla Blues (Audio)</v>
+        <v>Charli xcx - Rock Music (Official Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
+        <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-17</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Jon Batiste</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Jon Batiste - Alla Blues (Audio) - Jon Batiste</v>
+        <v>Charli xcx - Rock Music (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
+        <v>Jon Batiste - Alla Blues (Audio)</v>
       </c>
       <c r="B71" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
+        <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-17</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Tigirlily Gold</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Tigirlily Gold - I Do or Die (Official Music Video) - Tigirlily Gold</v>
+        <v>Jon Batiste - Alla Blues (Audio) - Jon Batiste</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
+        <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
+        <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-17</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Tigirlily Gold</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video) - PAUL McCARTNEY</v>
+        <v>Tigirlily Gold - I Do or Die (Official Music Video) - Tigirlily Gold</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
+        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
+        <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-17</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Bruno Mars</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video] - Bruno Mars</v>
+        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Tori Kelly - Control (Official Visualizer)</v>
+        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
       </c>
       <c r="B74" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
+        <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-17</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Tori Kelly</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Tori Kelly - Control (Official Visualizer) - Tori Kelly</v>
+        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Bea Miller - depressed on the internet (Lyric Video)</v>
+        <v>Tori Kelly - Control (Official Visualizer)</v>
       </c>
       <c r="B75" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
+        <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-17</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>bea miller</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Bea Miller - depressed on the internet (Lyric Video) - bea miller</v>
+        <v>Tori Kelly - Control (Official Visualizer) - Tori Kelly</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
+        <v>Bea Miller - depressed on the internet (Lyric Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
+        <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-17</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>The Chainsmokers</v>
+        <v>bea miller</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer) - The Chainsmokers</v>
+        <v>Bea Miller - depressed on the internet (Lyric Video) - bea miller</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Madison Beer - free (Official Audio)</v>
+        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
       </c>
       <c r="B77" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
+        <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-17</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Madison Beer</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Madison Beer - free (Official Audio) - Madison Beer</v>
+        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Tori Kelly - Dive (Official Audio)</v>
+        <v>Madison Beer - free (Official Audio)</v>
       </c>
       <c r="B78" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
+        <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-17</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Tori Kelly</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Tori Kelly - Dive (Official Audio) - Tori Kelly</v>
+        <v>Madison Beer - free (Official Audio) - Madison Beer</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Jeremy Camp - Reflector (Official Audio)</v>
+        <v>Tori Kelly - Dive (Official Audio)</v>
       </c>
       <c r="B79" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
+        <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-17</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>JeremyCampMusic</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Jeremy Camp - Reflector (Official Audio) - JeremyCampMusic</v>
+        <v>Tori Kelly - Dive (Official Audio) - Tori Kelly</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
+        <v>Jeremy Camp - Reflector (Official Audio)</v>
       </c>
       <c r="B80" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
+        <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-17</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>The Chainsmokers</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer) - The Chainsmokers</v>
+        <v>Jeremy Camp - Reflector (Official Audio) - JeremyCampMusic</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Ashley Cooke - high school sweetheart</v>
+        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
       </c>
       <c r="B81" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
+        <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-17</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Ashley Cooke</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Ashley Cooke - high school sweetheart - Ashley Cooke</v>
+        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Ari Abdul - Ego (Visualizer)</v>
+        <v>Ashley Cooke - high school sweetheart</v>
       </c>
       <c r="B82" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=L0FjVr6LpVU</v>
+        <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-17</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Ari Abdul</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Ari Abdul - Ego (Visualizer) - Ari Abdul</v>
+        <v>Ashley Cooke - high school sweetheart - Ashley Cooke</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Quinn XCII - HOOPLA (Official Music Video)</v>
+        <v>Ari Abdul - Ego (Visualizer)</v>
       </c>
       <c r="B83" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=eNbGA1pgmFk</v>
+        <v>https://www.youtube.com/watch?v=L0FjVr6LpVU</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-17</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Quinn XCII</v>
+        <v>Ari Abdul</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Quinn XCII - HOOPLA (Official Music Video) - Quinn XCII</v>
+        <v>Ari Abdul - Ego (Visualizer) - Ari Abdul</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Madison Beer - lovergirl (Official Music Video)</v>
+        <v>Quinn XCII - HOOPLA (Official Music Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=q4lU1N3oqYQ</v>
+        <v>https://www.youtube.com/watch?v=eNbGA1pgmFk</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-17</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Madison Beer</v>
+        <v>Quinn XCII</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Madison Beer - lovergirl (Official Music Video) - Madison Beer</v>
+        <v>Quinn XCII - HOOPLA (Official Music Video) - Quinn XCII</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>David J - WHAT IF I'M IN LOVE (Official Video)</v>
+        <v>Madison Beer - lovergirl (Official Music Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=-SF7Hm_ikaY</v>
+        <v>https://www.youtube.com/watch?v=q4lU1N3oqYQ</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-17</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>8d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>David J</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>David J - WHAT IF I'M IN LOVE (Official Video) - David J</v>
+        <v>Madison Beer - lovergirl (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>The Last Dinner Party - Big Dog (On The Road)</v>
+        <v>David J - WHAT IF I'M IN LOVE (Official Video)</v>
       </c>
       <c r="B86" t="str">
         <v>9d ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
+        <v>https://www.youtube.com/watch?v=-SF7Hm_ikaY</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-17</v>
@@ -3649,7 +3649,7 @@
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>The Last Dinner Party</v>
+        <v>David J</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>The Last Dinner Party - Big Dog (On The Road) - The Last Dinner Party</v>
+        <v>David J - WHAT IF I'M IN LOVE (Official Video) - David J</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>OCEAN ALLEY - HOLD ON (Official Video)</v>
+        <v>The Last Dinner Party - Big Dog (On The Road)</v>
       </c>
       <c r="B87" t="str">
         <v>9d ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
+        <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-17</v>
@@ -3687,7 +3687,7 @@
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Ocean Alley</v>
+        <v>The Last Dinner Party</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>OCEAN ALLEY - HOLD ON (Official Video) - Ocean Alley</v>
+        <v>The Last Dinner Party - Big Dog (On The Road) - The Last Dinner Party</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Dagny - Closet Disco Queen (Lyric Video)</v>
+        <v>OCEAN ALLEY - HOLD ON (Official Video)</v>
       </c>
       <c r="B88" t="str">
         <v>9d ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
+        <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-17</v>
@@ -3725,7 +3725,7 @@
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Dagny</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Dagny - Closet Disco Queen (Lyric Video) - Dagny</v>
+        <v>OCEAN ALLEY - HOLD ON (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Purple Disco Machine - Disco Cherry (Official Video)</v>
+        <v>Dagny - Closet Disco Queen (Lyric Video)</v>
       </c>
       <c r="B89" t="str">
         <v>9d ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
+        <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-17</v>
@@ -3763,7 +3763,7 @@
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Dagny</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Purple Disco Machine - Disco Cherry (Official Video) - Purple Disco Machine</v>
+        <v>Dagny - Closet Disco Queen (Lyric Video) - Dagny</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Paris Paloma - Stem the Flow [Official Music Video]</v>
+        <v>Purple Disco Machine - Disco Cherry (Official Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>10d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
+        <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-17</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>10d ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Paris Paloma</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Paris Paloma - Stem the Flow [Official Music Video] - Paris Paloma</v>
+        <v>Purple Disco Machine - Disco Cherry (Official Video) - Purple Disco Machine</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Lucy Blue - Who you love (Visualiser)</v>
+        <v>Paris Paloma - Stem the Flow [Official Music Video]</v>
       </c>
       <c r="B91" t="str">
         <v>10d ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
+        <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-17</v>
@@ -3839,7 +3839,7 @@
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Lucy Blue</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Lucy Blue - Who you love (Visualiser) - Lucy Blue</v>
+        <v>Paris Paloma - Stem the Flow [Official Music Video] - Paris Paloma</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026)</v>
+        <v>Lucy Blue - Who you love (Visualiser)</v>
       </c>
       <c r="B92" t="str">
         <v>10d ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
+        <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-17</v>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Olivia Dean</v>
+        <v>Lucy Blue</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026) - Olivia Dean</v>
+        <v>Lucy Blue - Who you love (Visualiser) - Lucy Blue</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Aaron Frazer - It's A Shame (Official Video)</v>
+        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026)</v>
       </c>
       <c r="B93" t="str">
         <v>10d ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
+        <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-17</v>
@@ -3915,7 +3915,7 @@
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Aaron Frazer</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Aaron Frazer - It's A Shame (Official Video) - Aaron Frazer</v>
+        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026) - Olivia Dean</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify</v>
+        <v>Aaron Frazer - It's A Shame (Official Video)</v>
       </c>
       <c r="B94" t="str">
         <v>10d ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
+        <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-17</v>
@@ -3953,7 +3953,7 @@
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Holly Humberstone</v>
+        <v>Aaron Frazer</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>Aaron Frazer - It's A Shame (Official Video) - Aaron Frazer</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>DANNA - OUT OF MY BODY</v>
+        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify</v>
       </c>
       <c r="B95" t="str">
-        <v>11d ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=uW_Ye0kQ9Ac</v>
+        <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-17</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>11d ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Danna</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>DANNA - OUT OF MY BODY - Danna</v>
+        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>The Rolling Stones - In The Stars (Official Lyric Video)</v>
+        <v>DANNA - OUT OF MY BODY</v>
       </c>
       <c r="B96" t="str">
         <v>11d ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
+        <v>https://www.youtube.com/watch?v=uW_Ye0kQ9Ac</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-17</v>
@@ -4029,7 +4029,7 @@
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>The Rolling Stones</v>
+        <v>Danna</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>The Rolling Stones - In The Stars (Official Lyric Video) - The Rolling Stones</v>
+        <v>DANNA - OUT OF MY BODY - Danna</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser)</v>
+        <v>The Rolling Stones - In The Stars (Official Lyric Video)</v>
       </c>
       <c r="B97" t="str">
         <v>11d ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
+        <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-17</v>
@@ -4067,7 +4067,7 @@
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Dermot Kennedy</v>
+        <v>The Rolling Stones</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser) - Dermot Kennedy</v>
+        <v>The Rolling Stones - In The Stars (Official Lyric Video) - The Rolling Stones</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
+        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser)</v>
       </c>
       <c r="B98" t="str">
-        <v>2w ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
+        <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-17</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2w ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2) - SIENNA SPIRO</v>
+        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Rick Astley - Raindrops (Official Video)</v>
+        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
       </c>
       <c r="B99" t="str">
         <v>2w ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
+        <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-17</v>
@@ -4143,7 +4143,7 @@
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Rick Astley</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Rick Astley - Raindrops (Official Video) - Rick Astley</v>
+        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Jessie J - THREW IT AWAY (Official Video)</v>
+        <v>Rick Astley - Raindrops (Official Video)</v>
       </c>
       <c r="B100" t="str">
         <v>2w ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
+        <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-17</v>
@@ -4181,7 +4181,7 @@
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Jessie J</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Jessie J - THREW IT AWAY (Official Video) - Jessie J</v>
+        <v>Rick Astley - Raindrops (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>The Takes - Ain't Love (Lyric Video)</v>
+        <v>Jessie J - THREW IT AWAY (Official Video)</v>
       </c>
       <c r="B101" t="str">
         <v>2w ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
+        <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-17</v>
@@ -4219,7 +4219,7 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>The Takes</v>
+        <v>Jessie J</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>The Takes - Ain't Love (Lyric Video) - The Takes</v>
+        <v>Jessie J - THREW IT AWAY (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Hit the Wall</v>
+        <v>The Takes - Ain't Love (Lyric Video)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>2w ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/hit-the-wall/6766750846</v>
+        <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-17</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Daughter from Hell</v>
+        <v>2w ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:14</v>
+        <v/>
       </c>
       <c r="H102" t="str">
-        <v>Gracie Abrams</v>
+        <v>The Takes</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/gracie-abrams/1450554836</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/hit-the-wall/6766750836</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Hit the Wall - Gracie Abrams</v>
+        <v>The Takes - Ain't Love (Lyric Video) - The Takes</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Ran To Atlanta</v>
+        <v>Hit the Wall</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/ran-to-atlanta/6769568597</v>
+        <v>https://music.apple.com/us/song/hit-the-wall/6766750846</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-17</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>ICEMAN</v>
+        <v>Daughter from Hell</v>
       </c>
       <c r="G103" t="str">
-        <v>4:07</v>
+        <v>3:14</v>
       </c>
       <c r="H103" t="str">
-        <v>Drake</v>
+        <v>Gracie Abrams</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/drake/271256</v>
+        <v>https://music.apple.com/us/artist/gracie-abrams/1450554836</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/ran-to-atlanta/6769568449</v>
+        <v>https://music.apple.com/us/album/hit-the-wall/6766750836</v>
       </c>
       <c r="L103" t="str">
-        <v>Ran To Atlanta - Drake</v>
+        <v>Hit the Wall - Gracie Abrams</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Hoe Phase</v>
+        <v>Ran To Atlanta</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/hoe-phase/6769556949</v>
+        <v>https://music.apple.com/us/song/ran-to-atlanta/6769568597</v>
       </c>
       <c r="D104" t="str">
         <v>2026-05-17</v>
@@ -4327,10 +4327,10 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>MAID OF HONOUR</v>
+        <v>ICEMAN</v>
       </c>
       <c r="G104" t="str">
-        <v>3:23</v>
+        <v>4:07</v>
       </c>
       <c r="H104" t="str">
         <v>Drake</v>
@@ -4342,21 +4342,21 @@
         <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/hoe-phase/6769556940</v>
+        <v>https://music.apple.com/us/album/ran-to-atlanta/6769568449</v>
       </c>
       <c r="L104" t="str">
-        <v>Hoe Phase - Drake</v>
+        <v>Ran To Atlanta - Drake</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>I’m Spent</v>
+        <v>Hoe Phase</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/im-spent/6769551476</v>
+        <v>https://music.apple.com/us/song/hoe-phase/6769556949</v>
       </c>
       <c r="D105" t="str">
         <v>2026-05-17</v>
@@ -4365,10 +4365,10 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>HABIBTI</v>
+        <v>MAID OF HONOUR</v>
       </c>
       <c r="G105" t="str">
-        <v>2:24</v>
+        <v>3:23</v>
       </c>
       <c r="H105" t="str">
         <v>Drake</v>
@@ -4380,21 +4380,21 @@
         <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/im-spent/6769551464</v>
+        <v>https://music.apple.com/us/album/hoe-phase/6769556940</v>
       </c>
       <c r="L105" t="str">
-        <v>I’m Spent - Drake</v>
+        <v>Hoe Phase - Drake</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Abracadabra (Apple Music Live)</v>
+        <v>I’m Spent</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/abracadabra-apple-music-live/6768201780</v>
+        <v>https://music.apple.com/us/song/im-spent/6769551476</v>
       </c>
       <c r="D106" t="str">
         <v>2026-05-17</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Apple Music Live: MAYHEM Requiem</v>
+        <v>HABIBTI</v>
       </c>
       <c r="G106" t="str">
-        <v>4:04</v>
+        <v>2:24</v>
       </c>
       <c r="H106" t="str">
-        <v>Lady Gaga</v>
+        <v>Drake</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/abracadabra-apple-music-live/6768201775</v>
+        <v>https://music.apple.com/us/album/im-spent/6769551464</v>
       </c>
       <c r="L106" t="str">
-        <v>Abracadabra (Apple Music Live) - Lady Gaga</v>
+        <v>I’m Spent - Drake</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Falling out of Love</v>
+        <v>Abracadabra (Apple Music Live)</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/falling-out-of-love/1891161448</v>
+        <v>https://music.apple.com/us/song/abracadabra-apple-music-live/6768201780</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-17</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Reality Awaits</v>
+        <v>Apple Music Live: MAYHEM Requiem</v>
       </c>
       <c r="G107" t="str">
-        <v>6:21</v>
+        <v>4:04</v>
       </c>
       <c r="H107" t="str">
-        <v>The Strokes</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/the-strokes/560289</v>
+        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/falling-out-of-love/1891161441</v>
+        <v>https://music.apple.com/us/album/abracadabra-apple-music-live/6768201775</v>
       </c>
       <c r="L107" t="str">
-        <v>Falling out of Love - The Strokes</v>
+        <v>Abracadabra (Apple Music Live) - Lady Gaga</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Dai Dai</v>
+        <v>Falling out of Love</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/dai-dai/6768469976</v>
+        <v>https://music.apple.com/us/song/falling-out-of-love/1891161448</v>
       </c>
       <c r="D108" t="str">
         <v>2026-05-17</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Dai Dai - Single</v>
+        <v>Reality Awaits</v>
       </c>
       <c r="G108" t="str">
-        <v>3:43</v>
+        <v>6:21</v>
       </c>
       <c r="H108" t="str">
-        <v>Shakira</v>
+        <v>The Strokes</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/shakira/889327</v>
+        <v>https://music.apple.com/us/artist/the-strokes/560289</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/dai-dai/6768469975</v>
+        <v>https://music.apple.com/us/album/falling-out-of-love/1891161441</v>
       </c>
       <c r="L108" t="str">
-        <v>Dai Dai - Shakira</v>
+        <v>Falling out of Love - The Strokes</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Tu recuerdo</v>
+        <v>Dai Dai</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/tu-recuerdo/6763660843</v>
+        <v>https://music.apple.com/us/song/dai-dai/6768469976</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-17</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Loco X Volver</v>
+        <v>Dai Dai - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>3:55</v>
+        <v>3:43</v>
       </c>
       <c r="H109" t="str">
-        <v>Maluma</v>
+        <v>Shakira</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/shakira/889327</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/tu-recuerdo/1895423065</v>
+        <v>https://music.apple.com/us/album/dai-dai/6768469975</v>
       </c>
       <c r="L109" t="str">
-        <v>Tu recuerdo - Maluma</v>
+        <v>Dai Dai - Shakira</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Traitor (Roles Reversed)</v>
+        <v>Tu recuerdo</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/traitor-roles-reversed/6767665959</v>
+        <v>https://music.apple.com/us/song/tu-recuerdo/6763660843</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-17</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Cloud 9</v>
+        <v>Loco X Volver</v>
       </c>
       <c r="G110" t="str">
-        <v>3:27</v>
+        <v>3:55</v>
       </c>
       <c r="H110" t="str">
-        <v>Megan Moroney</v>
+        <v>Maluma</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/traitor-roles-reversed/6767665713</v>
+        <v>https://music.apple.com/us/album/tu-recuerdo/1895423065</v>
       </c>
       <c r="L110" t="str">
-        <v>Traitor (Roles Reversed) - Megan Moroney</v>
+        <v>Tu recuerdo - Maluma</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Dirty Rosie</v>
+        <v>Traitor (Roles Reversed)</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/dirty-rosie/6767044374</v>
+        <v>https://music.apple.com/us/song/traitor-roles-reversed/6767665959</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-17</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Little Miss Twain</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G111" t="str">
-        <v>2:46</v>
+        <v>3:27</v>
       </c>
       <c r="H111" t="str">
-        <v>Shania Twain</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/shania-twain/129974</v>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/dirty-rosie/1896356105</v>
+        <v>https://music.apple.com/us/album/traitor-roles-reversed/6767665713</v>
       </c>
       <c r="L111" t="str">
-        <v>Dirty Rosie - Shania Twain</v>
+        <v>Traitor (Roles Reversed) - Megan Moroney</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Like you mean it</v>
+        <v>Dirty Rosie</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/like-you-mean-it/6767024693</v>
+        <v>https://music.apple.com/us/song/dirty-rosie/6767044374</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-17</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>When the lights turn on</v>
+        <v>Little Miss Twain</v>
       </c>
       <c r="G112" t="str">
-        <v>2:27</v>
+        <v>2:46</v>
       </c>
       <c r="H112" t="str">
-        <v>MICO</v>
+        <v>Shania Twain</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/mico/1457367370</v>
+        <v>https://music.apple.com/us/artist/shania-twain/129974</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/like-you-mean-it/6767024688</v>
+        <v>https://music.apple.com/us/album/dirty-rosie/1896356105</v>
       </c>
       <c r="L112" t="str">
-        <v>Like you mean it - MICO</v>
+        <v>Dirty Rosie - Shania Twain</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Hardy (feat. Clairo)</v>
+        <v>Like you mean it</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/hardy-feat-clairo/1876953073</v>
+        <v>https://music.apple.com/us/song/like-you-mean-it/6767024693</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-17</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>American Stories</v>
+        <v>When the lights turn on</v>
       </c>
       <c r="G113" t="str">
-        <v>3:53</v>
+        <v>2:27</v>
       </c>
       <c r="H113" t="str">
-        <v>Rostam</v>
+        <v>MICO</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/mico/1457367370</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/hardy-feat-clairo/1876952750</v>
+        <v>https://music.apple.com/us/album/like-you-mean-it/6767024688</v>
       </c>
       <c r="L113" t="str">
-        <v>Hardy (feat. Clairo) - Rostam</v>
+        <v>Like you mean it - MICO</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>2 Hard 4 The Radio</v>
+        <v>Hardy (feat. Clairo)</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/2-hard-4-the-radio/6769568610</v>
+        <v>https://music.apple.com/us/song/hardy-feat-clairo/1876953073</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-17</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>ICEMAN</v>
+        <v>American Stories</v>
       </c>
       <c r="G114" t="str">
-        <v>3:03</v>
+        <v>3:53</v>
       </c>
       <c r="H114" t="str">
-        <v>Drake</v>
+        <v>Rostam</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/drake/271256</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/2-hard-4-the-radio/6769568449</v>
+        <v>https://music.apple.com/us/album/hardy-feat-clairo/1876952750</v>
       </c>
       <c r="L114" t="str">
-        <v>2 Hard 4 The Radio - Drake</v>
+        <v>Hardy (feat. Clairo) - Rostam</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Cheetah Print</v>
+        <v>2 Hard 4 The Radio</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/cheetah-print/6769557055</v>
+        <v>https://music.apple.com/us/song/2-hard-4-the-radio/6769568610</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-17</v>
@@ -4745,10 +4745,10 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>MAID OF HONOUR</v>
+        <v>ICEMAN</v>
       </c>
       <c r="G115" t="str">
-        <v>3:22</v>
+        <v>3:03</v>
       </c>
       <c r="H115" t="str">
         <v>Drake</v>
@@ -4760,21 +4760,21 @@
         <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/cheetah-print/6769556940</v>
+        <v>https://music.apple.com/us/album/2-hard-4-the-radio/6769568449</v>
       </c>
       <c r="L115" t="str">
-        <v>Cheetah Print - Drake</v>
+        <v>2 Hard 4 The Radio - Drake</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>WNBA</v>
+        <v>Cheetah Print</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/wnba/6769551471</v>
+        <v>https://music.apple.com/us/song/cheetah-print/6769557055</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-17</v>
@@ -4783,10 +4783,10 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>HABIBTI</v>
+        <v>MAID OF HONOUR</v>
       </c>
       <c r="G116" t="str">
-        <v>2:58</v>
+        <v>3:22</v>
       </c>
       <c r="H116" t="str">
         <v>Drake</v>
@@ -4798,21 +4798,21 @@
         <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/wnba/6769551464</v>
+        <v>https://music.apple.com/us/album/cheetah-print/6769556940</v>
       </c>
       <c r="L116" t="str">
-        <v>WNBA - Drake</v>
+        <v>Cheetah Print - Drake</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Shadow Of A Man (Apple Music Live)</v>
+        <v>WNBA</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/shadow-of-a-man-apple-music-live/6768201925</v>
+        <v>https://music.apple.com/us/song/wnba/6769551471</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-17</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Apple Music Live: MAYHEM Requiem</v>
+        <v>HABIBTI</v>
       </c>
       <c r="G117" t="str">
-        <v>3:36</v>
+        <v>2:58</v>
       </c>
       <c r="H117" t="str">
-        <v>Lady Gaga</v>
+        <v>Drake</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/shadow-of-a-man-apple-music-live/6768201775</v>
+        <v>https://music.apple.com/us/album/wnba/6769551464</v>
       </c>
       <c r="L117" t="str">
-        <v>Shadow Of A Man (Apple Music Live) - Lady Gaga</v>
+        <v>WNBA - Drake</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>EPA</v>
+        <v>Shadow Of A Man (Apple Music Live)</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/epa/6768420253</v>
+        <v>https://music.apple.com/us/song/shadow-of-a-man-apple-music-live/6768201925</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-17</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>EPA - Single</v>
+        <v>Apple Music Live: MAYHEM Requiem</v>
       </c>
       <c r="G118" t="str">
-        <v>3:22</v>
+        <v>3:36</v>
       </c>
       <c r="H118" t="str">
-        <v>Becky G</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
+        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/epa/6768420251</v>
+        <v>https://music.apple.com/us/album/shadow-of-a-man-apple-music-live/6768201775</v>
       </c>
       <c r="L118" t="str">
-        <v>EPA - Becky G</v>
+        <v>Shadow Of A Man (Apple Music Live) - Lady Gaga</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>I’m your girl right?</v>
+        <v>EPA</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/im-your-girl-right/6766440186</v>
+        <v>https://music.apple.com/us/song/epa/6768420253</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-17</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>ESTRUS</v>
+        <v>EPA - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>2:49</v>
+        <v>3:22</v>
       </c>
       <c r="H119" t="str">
-        <v>Tove Lo</v>
+        <v>Becky G</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/tove-lo/570136838</v>
+        <v>https://music.apple.com/us/artist/becky-g/550411604</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/im-your-girl-right/6766440172</v>
+        <v>https://music.apple.com/us/album/epa/6768420251</v>
       </c>
       <c r="L119" t="str">
-        <v>I’m your girl right? - Tove Lo</v>
+        <v>EPA - Becky G</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>fuëgo</v>
+        <v>I’m your girl right?</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/fu%C3%ABgo/6767661766</v>
+        <v>https://music.apple.com/us/song/im-your-girl-right/6766440186</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-17</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>fuëgo - Single</v>
+        <v>ESTRUS</v>
       </c>
       <c r="G120" t="str">
-        <v>3:46</v>
+        <v>2:49</v>
       </c>
       <c r="H120" t="str">
-        <v>BNYX®</v>
+        <v>Tove Lo</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/bnyx/1438325287</v>
+        <v>https://music.apple.com/us/artist/tove-lo/570136838</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/fu%C3%ABgo/6767661604</v>
+        <v>https://music.apple.com/us/album/im-your-girl-right/6766440172</v>
       </c>
       <c r="L120" t="str">
-        <v>fuëgo - BNYX®</v>
+        <v>I’m your girl right? - Tove Lo</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>jajaja</v>
+        <v>fuëgo</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/jajaja/6766341319</v>
+        <v>https://music.apple.com/us/song/fu%C3%ABgo/6767661766</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-17</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>jajaja - Single</v>
+        <v>fuëgo - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>2:45</v>
+        <v>3:46</v>
       </c>
       <c r="H121" t="str">
-        <v>Chino Pacas</v>
+        <v>BNYX®</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
+        <v>https://music.apple.com/us/artist/bnyx/1438325287</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/jajaja/6766341318</v>
+        <v>https://music.apple.com/us/album/fu%C3%ABgo/6767661604</v>
       </c>
       <c r="L121" t="str">
-        <v>jajaja - Chino Pacas</v>
+        <v>fuëgo - BNYX®</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>FIND GOD (feat. Dominic Fike)</v>
+        <v>jajaja</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/find-god-feat-dominic-fike/1894315529</v>
+        <v>https://music.apple.com/us/song/jajaja/6766341319</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-17</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>BULLDAWG</v>
+        <v>jajaja - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:59</v>
+        <v>2:45</v>
       </c>
       <c r="H122" t="str">
-        <v>Kenny Mason</v>
+        <v>Chino Pacas</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/kenny-mason/79382206</v>
+        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/find-god-feat-dominic-fike/1894315301</v>
+        <v>https://music.apple.com/us/album/jajaja/6766341318</v>
       </c>
       <c r="L122" t="str">
-        <v>FIND GOD (feat. Dominic Fike) - Kenny Mason</v>
+        <v>jajaja - Chino Pacas</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>FOOL ME ONCE (feat. Leon Thomas)</v>
+        <v>FIND GOD (feat. Dominic Fike)</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/fool-me-once-feat-leon-thomas/1891467239</v>
+        <v>https://music.apple.com/us/song/find-god-feat-dominic-fike/1894315529</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-17</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>BELOVED: ACT II</v>
+        <v>BULLDAWG</v>
       </c>
       <c r="G123" t="str">
-        <v>3:18</v>
+        <v>3:59</v>
       </c>
       <c r="H123" t="str">
-        <v>GIVĒON</v>
+        <v>Kenny Mason</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/giv%C4%93on/1070668868</v>
+        <v>https://music.apple.com/us/artist/kenny-mason/79382206</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/fool-me-once-feat-leon-thomas/1891467233</v>
+        <v>https://music.apple.com/us/album/find-god-feat-dominic-fike/1894315301</v>
       </c>
       <c r="L123" t="str">
-        <v>FOOL ME ONCE (feat. Leon Thomas) - GIVĒON</v>
+        <v>FIND GOD (feat. Dominic Fike) - Kenny Mason</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Shabang</v>
+        <v>FOOL ME ONCE (feat. Leon Thomas)</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/shabang/6769568598</v>
+        <v>https://music.apple.com/us/song/fool-me-once-feat-leon-thomas/1891467239</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-17</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>ICEMAN</v>
+        <v>BELOVED: ACT II</v>
       </c>
       <c r="G124" t="str">
-        <v>3:08</v>
+        <v>3:18</v>
       </c>
       <c r="H124" t="str">
-        <v>Drake</v>
+        <v>GIVĒON</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/drake/271256</v>
+        <v>https://music.apple.com/us/artist/giv%C4%93on/1070668868</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/shabang/6769568449</v>
+        <v>https://music.apple.com/us/album/fool-me-once-feat-leon-thomas/1891467233</v>
       </c>
       <c r="L124" t="str">
-        <v>Shabang - Drake</v>
+        <v>FOOL ME ONCE (feat. Leon Thomas) - GIVĒON</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Road Trips</v>
+        <v>Shabang</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/road-trips/6769557053</v>
+        <v>https://music.apple.com/us/song/shabang/6769568598</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-17</v>
@@ -5125,10 +5125,10 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>MAID OF HONOUR</v>
+        <v>ICEMAN</v>
       </c>
       <c r="G125" t="str">
-        <v>4:03</v>
+        <v>3:08</v>
       </c>
       <c r="H125" t="str">
         <v>Drake</v>
@@ -5140,21 +5140,21 @@
         <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/road-trips/6769556940</v>
+        <v>https://music.apple.com/us/album/shabang/6769568449</v>
       </c>
       <c r="L125" t="str">
-        <v>Road Trips - Drake</v>
+        <v>Shabang - Drake</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Fortworth</v>
+        <v>Road Trips</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/fortworth/6769551482</v>
+        <v>https://music.apple.com/us/song/road-trips/6769557053</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-17</v>
@@ -5163,10 +5163,10 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>HABIBTI</v>
+        <v>MAID OF HONOUR</v>
       </c>
       <c r="G126" t="str">
-        <v>3:51</v>
+        <v>4:03</v>
       </c>
       <c r="H126" t="str">
         <v>Drake</v>
@@ -5178,21 +5178,21 @@
         <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/fortworth/6769551464</v>
+        <v>https://music.apple.com/us/album/road-trips/6769556940</v>
       </c>
       <c r="L126" t="str">
-        <v>Fortworth - Drake</v>
+        <v>Road Trips - Drake</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Repeat It</v>
+        <v>Fortworth</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/repeat-it/6764277864</v>
+        <v>https://music.apple.com/us/song/fortworth/6769551482</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-17</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Repeat It - Single</v>
+        <v>HABIBTI</v>
       </c>
       <c r="G127" t="str">
-        <v>3:11</v>
+        <v>3:51</v>
       </c>
       <c r="H127" t="str">
-        <v>Martin Garrix</v>
+        <v>Drake</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/repeat-it/1895713789</v>
+        <v>https://music.apple.com/us/album/fortworth/6769551464</v>
       </c>
       <c r="L127" t="str">
-        <v>Repeat It - Martin Garrix</v>
+        <v>Fortworth - Drake</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Fool Proof</v>
+        <v>Repeat It</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/fool-proof/1892466004</v>
+        <v>https://music.apple.com/us/song/repeat-it/6764277864</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-17</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>Repeat It - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:36</v>
+        <v>3:11</v>
       </c>
       <c r="H128" t="str">
-        <v>Cody Johnson</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/fool-proof/1892465981</v>
+        <v>https://music.apple.com/us/album/repeat-it/1895713789</v>
       </c>
       <c r="L128" t="str">
-        <v>Fool Proof - Cody Johnson</v>
+        <v>Repeat It - Martin Garrix</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Crisco</v>
+        <v>Fool Proof</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/crisco/6763369506</v>
+        <v>https://music.apple.com/us/song/fool-proof/1892466004</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-17</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Crisco - Single</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G129" t="str">
-        <v>2:56</v>
+        <v>2:36</v>
       </c>
       <c r="H129" t="str">
-        <v>Miranda Lambert</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/miranda-lambert/18732261</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/crisco/1895284236</v>
+        <v>https://music.apple.com/us/album/fool-proof/1892465981</v>
       </c>
       <c r="L129" t="str">
-        <v>Crisco - Miranda Lambert</v>
+        <v>Fool Proof - Cody Johnson</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Absolution</v>
+        <v>Crisco</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/absolution/1884987651</v>
+        <v>https://music.apple.com/us/song/crisco/6763369506</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-17</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Forever Now</v>
+        <v>Crisco - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>4:05</v>
+        <v>2:56</v>
       </c>
       <c r="H130" t="str">
-        <v>Switchfoot</v>
+        <v>Miranda Lambert</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
+        <v>https://music.apple.com/us/artist/miranda-lambert/18732261</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/absolution/1884987638</v>
+        <v>https://music.apple.com/us/album/crisco/1895284236</v>
       </c>
       <c r="L130" t="str">
-        <v>Absolution - Switchfoot</v>
+        <v>Crisco - Miranda Lambert</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>JESUS IS ALIVE</v>
+        <v>Absolution</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/jesus-is-alive/6767694896</v>
+        <v>https://music.apple.com/us/song/absolution/1884987651</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-17</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>JESUS IS ALIVE - Single</v>
+        <v>Forever Now</v>
       </c>
       <c r="G131" t="str">
-        <v>2:08</v>
+        <v>4:05</v>
       </c>
       <c r="H131" t="str">
-        <v>Forrest Frank</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
+        <v>https://music.apple.com/us/artist/switchfoot/655658</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/jesus-is-alive/6767694895</v>
+        <v>https://music.apple.com/us/album/absolution/1884987638</v>
       </c>
       <c r="L131" t="str">
-        <v>JESUS IS ALIVE - Forrest Frank</v>
+        <v>Absolution - Switchfoot</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Something To Lose</v>
+        <v>JESUS IS ALIVE</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/something-to-lose/6766964605</v>
+        <v>https://music.apple.com/us/song/jesus-is-alive/6767694896</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-17</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Is This Heaven? - EP</v>
+        <v>JESUS IS ALIVE - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>2:55</v>
+        <v>2:08</v>
       </c>
       <c r="H132" t="str">
-        <v>STELLA LEFTY</v>
+        <v>Forrest Frank</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
+        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/something-to-lose/6766964604</v>
+        <v>https://music.apple.com/us/album/jesus-is-alive/6767694895</v>
       </c>
       <c r="L132" t="str">
-        <v>Something To Lose - STELLA LEFTY</v>
+        <v>JESUS IS ALIVE - Forrest Frank</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Too Busy Missing You</v>
+        <v>Something To Lose</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/too-busy-missing-you/6766604915</v>
+        <v>https://music.apple.com/us/song/something-to-lose/6766964605</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-17</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Off Campus: The Mixtape</v>
+        <v>Is This Heaven? - EP</v>
       </c>
       <c r="G133" t="str">
-        <v>3:25</v>
+        <v>2:55</v>
       </c>
       <c r="H133" t="str">
-        <v>Asha Banks</v>
+        <v>STELLA LEFTY</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
+        <v>https://music.apple.com/us/artist/stella-lefty/1641742186</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/too-busy-missing-you/6766604455</v>
+        <v>https://music.apple.com/us/album/something-to-lose/6766964604</v>
       </c>
       <c r="L133" t="str">
-        <v>Too Busy Missing You - Asha Banks</v>
+        <v>Something To Lose - STELLA LEFTY</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>F-Stop Blues (4-track)</v>
+        <v>Too Busy Missing You</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/f-stop-blues-4-track/1883173173</v>
+        <v>https://music.apple.com/us/song/too-busy-missing-you/6766604915</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-17</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>Off Campus: The Mixtape</v>
       </c>
       <c r="G134" t="str">
-        <v>3:00</v>
+        <v>3:25</v>
       </c>
       <c r="H134" t="str">
-        <v>Jack Johnson</v>
+        <v>Asha Banks</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/asha-banks/943493421</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/f-stop-blues-4-track/1883172879</v>
+        <v>https://music.apple.com/us/album/too-busy-missing-you/6766604455</v>
       </c>
       <c r="L134" t="str">
-        <v>F-Stop Blues (4-track) - Jack Johnson</v>
+        <v>Too Busy Missing You - Asha Banks</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>PA' LO BONITO</v>
+        <v>F-Stop Blues (4-track)</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/pa-lo-bonito/1886496944</v>
+        <v>https://music.apple.com/us/song/f-stop-blues-4-track/1883173173</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-17</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>PA' LO BONITO - Single</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G135" t="str">
-        <v>3:04</v>
+        <v>3:00</v>
       </c>
       <c r="H135" t="str">
-        <v>Lenny Tavárez</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/pa-lo-bonito/1886496943</v>
+        <v>https://music.apple.com/us/album/f-stop-blues-4-track/1883172879</v>
       </c>
       <c r="L135" t="str">
-        <v>PA' LO BONITO - Lenny Tavárez</v>
+        <v>F-Stop Blues (4-track) - Jack Johnson</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>LONELY</v>
+        <v>PA' LO BONITO</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/lonely/6768757857</v>
+        <v>https://music.apple.com/us/song/pa-lo-bonito/1886496944</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-17</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>DESEO</v>
+        <v>PA' LO BONITO - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:58</v>
+        <v>3:04</v>
       </c>
       <c r="H136" t="str">
-        <v>Katteyes</v>
+        <v>Lenny Tavárez</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/katteyes/1648818255</v>
+        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/lonely/6768757414</v>
+        <v>https://music.apple.com/us/album/pa-lo-bonito/1886496943</v>
       </c>
       <c r="L136" t="str">
-        <v>LONELY - Katteyes</v>
+        <v>PA' LO BONITO - Lenny Tavárez</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Lockup</v>
+        <v>LONELY</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/lockup/1894298102</v>
+        <v>https://music.apple.com/us/song/lonely/6768757857</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-17</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Pure Devotion</v>
+        <v>DESEO</v>
       </c>
       <c r="G137" t="str">
-        <v>4:31</v>
+        <v>2:58</v>
       </c>
       <c r="H137" t="str">
-        <v>Overmono</v>
+        <v>Katteyes</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/overmono/1129806758</v>
+        <v>https://music.apple.com/us/artist/katteyes/1648818255</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/lockup/1894298100</v>
+        <v>https://music.apple.com/us/album/lonely/6768757414</v>
       </c>
       <c r="L137" t="str">
-        <v>Lockup - Overmono</v>
+        <v>LONELY - Katteyes</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Young</v>
+        <v>Lockup</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/young/6767698952</v>
+        <v>https://music.apple.com/us/song/lockup/1894298102</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-17</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Young</v>
+        <v>Pure Devotion</v>
       </c>
       <c r="G138" t="str">
-        <v>2:46</v>
+        <v>4:31</v>
       </c>
       <c r="H138" t="str">
-        <v>Dan + Shay</v>
+        <v>Overmono</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/dan-shay/690319057</v>
+        <v>https://music.apple.com/us/artist/overmono/1129806758</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/young/6767698951</v>
+        <v>https://music.apple.com/us/album/lockup/1894298100</v>
       </c>
       <c r="L138" t="str">
-        <v>Young - Dan + Shay</v>
+        <v>Lockup - Overmono</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Parachute</v>
+        <v>Young</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/parachute/6764119241</v>
+        <v>https://music.apple.com/us/song/young/6767698952</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-17</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Parachute - Single</v>
+        <v>Young</v>
       </c>
       <c r="G139" t="str">
-        <v>2:52</v>
+        <v>2:46</v>
       </c>
       <c r="H139" t="str">
-        <v>Maren Morris</v>
+        <v>Dan + Shay</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/maren-morris/262260873</v>
+        <v>https://music.apple.com/us/artist/dan-shay/690319057</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/parachute/1895648983</v>
+        <v>https://music.apple.com/us/album/young/6767698951</v>
       </c>
       <c r="L139" t="str">
-        <v>Parachute - Maren Morris</v>
+        <v>Young - Dan + Shay</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Little Things</v>
+        <v>Parachute</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/little-things/6766351153</v>
+        <v>https://music.apple.com/us/song/parachute/6764119241</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-17</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Little Things - Single</v>
+        <v>Parachute - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:55</v>
+        <v>2:52</v>
       </c>
       <c r="H140" t="str">
-        <v>Kevin Jonas</v>
+        <v>Maren Morris</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/kevin-jonas/21138190</v>
+        <v>https://music.apple.com/us/artist/maren-morris/262260873</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/little-things/6766350882</v>
+        <v>https://music.apple.com/us/album/parachute/1895648983</v>
       </c>
       <c r="L140" t="str">
-        <v>Little Things - Kevin Jonas</v>
+        <v>Parachute - Maren Morris</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Fish Hunt Golf Drink</v>
+        <v>Little Things</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/fish-hunt-golf-drink/6766651884</v>
+        <v>https://music.apple.com/us/song/little-things/6766351153</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-17</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Signs</v>
+        <v>Little Things - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:34</v>
+        <v>2:55</v>
       </c>
       <c r="H141" t="str">
-        <v>Luke Bryan</v>
+        <v>Kevin Jonas</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
+        <v>https://music.apple.com/us/artist/kevin-jonas/21138190</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/fish-hunt-golf-drink/6766651878</v>
+        <v>https://music.apple.com/us/album/little-things/6766350882</v>
       </c>
       <c r="L141" t="str">
-        <v>Fish Hunt Golf Drink - Luke Bryan</v>
+        <v>Little Things - Kevin Jonas</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>PAGEANT STAGE</v>
+        <v>Fish Hunt Golf Drink</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/pageant-stage/6764125889</v>
+        <v>https://music.apple.com/us/song/fish-hunt-golf-drink/6766651884</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-17</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>THE EDGE</v>
+        <v>Signs</v>
       </c>
       <c r="G142" t="str">
-        <v>2:52</v>
+        <v>2:34</v>
       </c>
       <c r="H142" t="str">
-        <v>Tone Stith</v>
+        <v>Luke Bryan</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/tone-stith/1167717310</v>
+        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/pageant-stage/1895651504</v>
+        <v>https://music.apple.com/us/album/fish-hunt-golf-drink/6766651878</v>
       </c>
       <c r="L142" t="str">
-        <v>PAGEANT STAGE - Tone Stith</v>
+        <v>Fish Hunt Golf Drink - Luke Bryan</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Firestorm</v>
+        <v>PAGEANT STAGE</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/firestorm/1868827004</v>
+        <v>https://music.apple.com/us/song/pageant-stage/6764125889</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-17</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Of Earth &amp; Wires</v>
+        <v>THE EDGE</v>
       </c>
       <c r="G143" t="str">
-        <v>2:29</v>
+        <v>2:52</v>
       </c>
       <c r="H143" t="str">
-        <v>Dua Saleh</v>
+        <v>Tone Stith</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
+        <v>https://music.apple.com/us/artist/tone-stith/1167717310</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/firestorm/1868826829</v>
+        <v>https://music.apple.com/us/album/pageant-stage/1895651504</v>
       </c>
       <c r="L143" t="str">
-        <v>Firestorm - Dua Saleh</v>
+        <v>PAGEANT STAGE - Tone Stith</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>girl next door</v>
+        <v>Firestorm</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/girl-next-door/6768077610</v>
+        <v>https://music.apple.com/us/song/firestorm/1868827004</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-17</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>girl next door - Single</v>
+        <v>Of Earth &amp; Wires</v>
       </c>
       <c r="G144" t="str">
-        <v>3:18</v>
+        <v>2:29</v>
       </c>
       <c r="H144" t="str">
-        <v>mgk</v>
+        <v>Dua Saleh</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/mgk/465954501</v>
+        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/girl-next-door/6768077609</v>
+        <v>https://music.apple.com/us/album/firestorm/1868826829</v>
       </c>
       <c r="L144" t="str">
-        <v>girl next door - mgk</v>
+        <v>Firestorm - Dua Saleh</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>BIG DOG</v>
+        <v>girl next door</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/big-dog/1887197046</v>
+        <v>https://music.apple.com/us/song/girl-next-door/6768077610</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-17</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
+        <v>girl next door - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:36</v>
+        <v>3:18</v>
       </c>
       <c r="H145" t="str">
-        <v>Genesis Owusu</v>
+        <v>mgk</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
+        <v>https://music.apple.com/us/artist/mgk/465954501</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/big-dog/1887196431</v>
+        <v>https://music.apple.com/us/album/girl-next-door/6768077609</v>
       </c>
       <c r="L145" t="str">
-        <v>BIG DOG - Genesis Owusu</v>
+        <v>girl next door - mgk</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>idea of love - A COLORS SHOW</v>
+        <v>BIG DOG</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/idea-of-love-a-colors-show/6767667046</v>
+        <v>https://music.apple.com/us/song/big-dog/1887197046</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-17</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>idea of love - A COLORS SHOW - Single</v>
+        <v>REDSTAR WU &amp; THE WORLDWIDE SCOURGE</v>
       </c>
       <c r="G146" t="str">
-        <v>2:34</v>
+        <v>3:36</v>
       </c>
       <c r="H146" t="str">
-        <v>kwn</v>
+        <v>Genesis Owusu</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
+        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/idea-of-love-a-colors-show/6767666835</v>
+        <v>https://music.apple.com/us/album/big-dog/1887196431</v>
       </c>
       <c r="L146" t="str">
-        <v>idea of love - A COLORS SHOW - kwn</v>
+        <v>BIG DOG - Genesis Owusu</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Heavy Serenade</v>
+        <v>idea of love - A COLORS SHOW</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/heavy-serenade/1892154309</v>
+        <v>https://music.apple.com/us/song/idea-of-love-a-colors-show/6767667046</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-17</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Heavy Serenade - EP</v>
+        <v>idea of love - A COLORS SHOW - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:00</v>
+        <v>2:34</v>
       </c>
       <c r="H147" t="str">
-        <v>NMIXX</v>
+        <v>kwn</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
+        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/heavy-serenade/1892154305</v>
+        <v>https://music.apple.com/us/album/idea-of-love-a-colors-show/6767666835</v>
       </c>
       <c r="L147" t="str">
-        <v>Heavy Serenade - NMIXX</v>
+        <v>idea of love - A COLORS SHOW - kwn</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>ddok ddok ddok</v>
+        <v>Heavy Serenade</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/ddok-ddok-ddok/6764203482</v>
+        <v>https://music.apple.com/us/song/heavy-serenade/1892154309</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-17</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>ddok ddok ddok - Single</v>
+        <v>Heavy Serenade - EP</v>
       </c>
       <c r="G148" t="str">
-        <v>2:35</v>
+        <v>3:00</v>
       </c>
       <c r="H148" t="str">
-        <v>BOYNEXTDOOR</v>
+        <v>NMIXX</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/boynextdoor/1687612559</v>
+        <v>https://music.apple.com/us/artist/nmixx/1600411676</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/ddok-ddok-ddok/6764203481</v>
+        <v>https://music.apple.com/us/album/heavy-serenade/1892154305</v>
       </c>
       <c r="L148" t="str">
-        <v>ddok ddok ddok - BOYNEXTDOOR</v>
+        <v>Heavy Serenade - NMIXX</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Shut It Down</v>
+        <v>ddok ddok ddok</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/shut-it-down/6763631128</v>
+        <v>https://music.apple.com/us/song/ddok-ddok-ddok/6764203482</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-17</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Shut It Down - Single</v>
+        <v>ddok ddok ddok - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:32</v>
+        <v>2:35</v>
       </c>
       <c r="H149" t="str">
-        <v>Boys Noize</v>
+        <v>BOYNEXTDOOR</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/boys-noize/60393190</v>
+        <v>https://music.apple.com/us/artist/boynextdoor/1687612559</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/shut-it-down/1895408470</v>
+        <v>https://music.apple.com/us/album/ddok-ddok-ddok/6764203481</v>
       </c>
       <c r="L149" t="str">
-        <v>Shut It Down - Boys Noize</v>
+        <v>ddok ddok ddok - BOYNEXTDOOR</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss)</v>
+        <v>Shut It Down</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/together-feat-nikki-nair-jessy-lanza-prentiss/6763207821</v>
+        <v>https://music.apple.com/us/song/shut-it-down/6763631128</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-17</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss) - Single</v>
+        <v>Shut It Down - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:18</v>
+        <v>3:32</v>
       </c>
       <c r="H150" t="str">
-        <v>The Avalanches</v>
+        <v>Boys Noize</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
+        <v>https://music.apple.com/us/artist/boys-noize/60393190</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/together-feat-nikki-nair-jessy-lanza-prentiss/1895215105</v>
+        <v>https://music.apple.com/us/album/shut-it-down/1895408470</v>
       </c>
       <c r="L150" t="str">
-        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss) - The Avalanches</v>
+        <v>Shut It Down - Boys Noize</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Can’t Miss You</v>
+        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss)</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/cant-miss-you/1886810999</v>
+        <v>https://music.apple.com/us/song/together-feat-nikki-nair-jessy-lanza-prentiss/6763207821</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-17</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Until The Sun Explodes</v>
+        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss) - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:32</v>
+        <v>3:18</v>
       </c>
       <c r="H151" t="str">
-        <v>Sublime</v>
+        <v>The Avalanches</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/sublime/63480</v>
+        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/cant-miss-you/1886810990</v>
+        <v>https://music.apple.com/us/album/together-feat-nikki-nair-jessy-lanza-prentiss/1895215105</v>
       </c>
       <c r="L151" t="str">
-        <v>Can’t Miss You - Sublime</v>
+        <v>Together (feat. Nikki Nair, Jessy Lanza &amp; Prentiss) - The Avalanches</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Razorblades And Runways</v>
+        <v>Can’t Miss You</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/razorblades-and-runways/1888004809</v>
+        <v>https://music.apple.com/us/song/cant-miss-you/1886810999</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-17</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Get It Honest</v>
+        <v>Until The Sun Explodes</v>
       </c>
       <c r="G152" t="str">
-        <v>3:33</v>
+        <v>2:32</v>
       </c>
       <c r="H152" t="str">
-        <v>The Revivalists</v>
+        <v>Sublime</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
+        <v>https://music.apple.com/us/artist/sublime/63480</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/razorblades-and-runways/1888004802</v>
+        <v>https://music.apple.com/us/album/cant-miss-you/1886810990</v>
       </c>
       <c r="L152" t="str">
-        <v>Razorblades And Runways - The Revivalists</v>
+        <v>Can’t Miss You - Sublime</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Massacre</v>
+        <v>Razorblades And Runways</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/massacre/1892127745</v>
+        <v>https://music.apple.com/us/song/razorblades-and-runways/1888004809</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-17</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Massacre - Single</v>
+        <v>Get It Honest</v>
       </c>
       <c r="G153" t="str">
-        <v>2:55</v>
+        <v>3:33</v>
       </c>
       <c r="H153" t="str">
-        <v>Murex</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/murex/1607430925</v>
+        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/massacre/1892127742</v>
+        <v>https://music.apple.com/us/album/razorblades-and-runways/1888004802</v>
       </c>
       <c r="L153" t="str">
-        <v>Massacre - Murex</v>
+        <v>Razorblades And Runways - The Revivalists</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Better That Way</v>
+        <v>Massacre</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/better-that-way/6766273199</v>
+        <v>https://music.apple.com/us/song/massacre/1892127745</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-17</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Christian Name</v>
+        <v>Massacre - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>3:45</v>
+        <v>2:55</v>
       </c>
       <c r="H154" t="str">
-        <v>Charles Wesley Godwin</v>
+        <v>Murex</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/charles-wesley-godwin/1441994025</v>
+        <v>https://music.apple.com/us/artist/murex/1607430925</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/better-that-way/1896261802</v>
+        <v>https://music.apple.com/us/album/massacre/1892127742</v>
       </c>
       <c r="L154" t="str">
-        <v>Better That Way - Charles Wesley Godwin</v>
+        <v>Massacre - Murex</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Apollo</v>
+        <v>Better That Way</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/apollo/6765602431</v>
+        <v>https://music.apple.com/us/song/better-that-way/6766273199</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-17</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Apollo - Single</v>
+        <v>Christian Name</v>
       </c>
       <c r="G155" t="str">
-        <v>3:35</v>
+        <v>3:45</v>
       </c>
       <c r="H155" t="str">
-        <v>Bryant Barnes</v>
+        <v>Charles Wesley Godwin</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/bryant-barnes/1579668433</v>
+        <v>https://music.apple.com/us/artist/charles-wesley-godwin/1441994025</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/apollo/6765602369</v>
+        <v>https://music.apple.com/us/album/better-that-way/1896261802</v>
       </c>
       <c r="L155" t="str">
-        <v>Apollo - Bryant Barnes</v>
+        <v>Better That Way - Charles Wesley Godwin</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Infinity (123)</v>
+        <v>Apollo</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/infinity-123/6763447312</v>
+        <v>https://music.apple.com/us/song/apollo/6765602431</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-17</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Infinity (123) - Single</v>
+        <v>Apollo - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>2:19</v>
+        <v>3:35</v>
       </c>
       <c r="H156" t="str">
-        <v>December 10</v>
+        <v>Bryant Barnes</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
+        <v>https://music.apple.com/us/artist/bryant-barnes/1579668433</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/infinity-123/1895320456</v>
+        <v>https://music.apple.com/us/album/apollo/6765602369</v>
       </c>
       <c r="L156" t="str">
-        <v>Infinity (123) - December 10</v>
+        <v>Apollo - Bryant Barnes</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Ain't Over Me Yet</v>
+        <v>Infinity (123)</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/aint-over-me-yet/6767283811</v>
+        <v>https://music.apple.com/us/song/infinity-123/6763447312</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-17</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Cherry Valley Forever</v>
+        <v>Infinity (123) - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>3:24</v>
+        <v>2:19</v>
       </c>
       <c r="H157" t="str">
-        <v>Carter Faith</v>
+        <v>December 10</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/carter-faith/1489205896</v>
+        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/aint-over-me-yet/1896458169</v>
+        <v>https://music.apple.com/us/album/infinity-123/1895320456</v>
       </c>
       <c r="L157" t="str">
-        <v>Ain't Over Me Yet - Carter Faith</v>
+        <v>Infinity (123) - December 10</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Where Did You Go</v>
+        <v>Ain't Over Me Yet</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/where-did-you-go/1877958504</v>
+        <v>https://music.apple.com/us/song/aint-over-me-yet/6767283811</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-17</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Growing Pains (Deluxe)</v>
+        <v>Cherry Valley Forever</v>
       </c>
       <c r="G158" t="str">
-        <v>2:47</v>
+        <v>3:24</v>
       </c>
       <c r="H158" t="str">
-        <v>Trousdale</v>
+        <v>Carter Faith</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/carter-faith/1489205896</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/where-did-you-go/1877958112</v>
+        <v>https://music.apple.com/us/album/aint-over-me-yet/1896458169</v>
       </c>
       <c r="L158" t="str">
-        <v>Where Did You Go - Trousdale</v>
+        <v>Ain't Over Me Yet - Carter Faith</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>I LOVE YOU</v>
+        <v>Where Did You Go</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/i-love-you/6766999950</v>
+        <v>https://music.apple.com/us/song/where-did-you-go/1877958504</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-17</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>I LOVE YOU - Single</v>
+        <v>Growing Pains (Deluxe)</v>
       </c>
       <c r="G159" t="str">
-        <v>3:11</v>
+        <v>2:47</v>
       </c>
       <c r="H159" t="str">
-        <v>Noga Erez</v>
+        <v>Trousdale</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/noga-erez/1166657901</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/i-love-you/6766999949</v>
+        <v>https://music.apple.com/us/album/where-did-you-go/1877958112</v>
       </c>
       <c r="L159" t="str">
-        <v>I LOVE YOU - Noga Erez</v>
+        <v>Where Did You Go - Trousdale</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Housekeeping</v>
+        <v>I LOVE YOU</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/housekeeping/6766290834</v>
+        <v>https://music.apple.com/us/song/i-love-you/6766999950</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-17</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Housekeeping - Single</v>
+        <v>I LOVE YOU - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:25</v>
+        <v>3:11</v>
       </c>
       <c r="H160" t="str">
-        <v>Ally Salort</v>
+        <v>Noga Erez</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
+        <v>https://music.apple.com/us/artist/noga-erez/1166657901</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/housekeeping/6766290823</v>
+        <v>https://music.apple.com/us/album/i-love-you/6766999949</v>
       </c>
       <c r="L160" t="str">
-        <v>Housekeeping - Ally Salort</v>
+        <v>I LOVE YOU - Noga Erez</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Surprise Surprise</v>
+        <v>Housekeeping</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/surprise-surprise/6764842119</v>
+        <v>https://music.apple.com/us/song/housekeeping/6766290834</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-17</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Surprise Surprise - Single</v>
+        <v>Housekeeping - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:55</v>
+        <v>3:25</v>
       </c>
       <c r="H161" t="str">
-        <v>Chloe Qisha</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
+        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/surprise-surprise/1895934408</v>
+        <v>https://music.apple.com/us/album/housekeeping/6766290823</v>
       </c>
       <c r="L161" t="str">
-        <v>Surprise Surprise - Chloe Qisha</v>
+        <v>Housekeeping - Ally Salort</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Dog</v>
+        <v>Surprise Surprise</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/dog/1885967384</v>
+        <v>https://music.apple.com/us/song/surprise-surprise/6764842119</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-17</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Gentleman</v>
+        <v>Surprise Surprise - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:08</v>
+        <v>2:55</v>
       </c>
       <c r="H162" t="str">
-        <v>Towa Bird</v>
+        <v>Chloe Qisha</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
+        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/dog/1885967368</v>
+        <v>https://music.apple.com/us/album/surprise-surprise/1895934408</v>
       </c>
       <c r="L162" t="str">
-        <v>Dog - Towa Bird</v>
+        <v>Surprise Surprise - Chloe Qisha</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>I Never See Her</v>
+        <v>Dog</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/i-never-see-her/6764149225</v>
+        <v>https://music.apple.com/us/song/dog/1885967384</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-17</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>I Never See Her - Single</v>
+        <v>Gentleman</v>
       </c>
       <c r="G163" t="str">
-        <v>3:04</v>
+        <v>3:08</v>
       </c>
       <c r="H163" t="str">
-        <v>Spacey Jane</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
+        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/i-never-see-her/1895660748</v>
+        <v>https://music.apple.com/us/album/dog/1885967368</v>
       </c>
       <c r="L163" t="str">
-        <v>I Never See Her - Spacey Jane</v>
+        <v>Dog - Towa Bird</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>No God</v>
+        <v>I Never See Her</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/no-god/1891187414</v>
+        <v>https://music.apple.com/us/song/i-never-see-her/6764149225</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-17</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Alone Together</v>
+        <v>I Never See Her - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:45</v>
+        <v>3:04</v>
       </c>
       <c r="H164" t="str">
-        <v>Show Me the Body</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
+        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/no-god/1891187411</v>
+        <v>https://music.apple.com/us/album/i-never-see-her/1895660748</v>
       </c>
       <c r="L164" t="str">
-        <v>No God - Show Me the Body</v>
+        <v>I Never See Her - Spacey Jane</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>burden</v>
+        <v>No God</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/burden/6767688180</v>
+        <v>https://music.apple.com/us/song/no-god/1891187414</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-17</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>burden - Single</v>
+        <v>Alone Together</v>
       </c>
       <c r="G165" t="str">
-        <v>3:24</v>
+        <v>2:45</v>
       </c>
       <c r="H165" t="str">
-        <v>Abe Parker</v>
+        <v>Show Me the Body</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/abe-parker/490444584</v>
+        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/burden/6767688179</v>
+        <v>https://music.apple.com/us/album/no-god/1891187411</v>
       </c>
       <c r="L165" t="str">
-        <v>burden - Abe Parker</v>
+        <v>No God - Show Me the Body</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Chico Raro</v>
+        <v>burden</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/chico-raro/6767713536</v>
+        <v>https://music.apple.com/us/song/burden/6767688180</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-17</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Chico Raro - Single</v>
+        <v>burden - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:17</v>
+        <v>3:24</v>
       </c>
       <c r="H166" t="str">
-        <v>Arón Piper</v>
+        <v>Abe Parker</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/ar%C3%B3n-piper/691972942</v>
+        <v>https://music.apple.com/us/artist/abe-parker/490444584</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/chico-raro/6767713527</v>
+        <v>https://music.apple.com/us/album/burden/6767688179</v>
       </c>
       <c r="L166" t="str">
-        <v>Chico Raro - Arón Piper</v>
+        <v>burden - Abe Parker</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>What's Done Is Done</v>
+        <v>Chico Raro</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/whats-done-is-done/6763088629</v>
+        <v>https://music.apple.com/us/song/chico-raro/6767713536</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-17</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>What's Done Is Done - Single</v>
+        <v>Chico Raro - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:53</v>
+        <v>3:17</v>
       </c>
       <c r="H167" t="str">
-        <v>Jorja Smith</v>
+        <v>Arón Piper</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
+        <v>https://music.apple.com/us/artist/ar%C3%B3n-piper/691972942</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/whats-done-is-done/1895156626</v>
+        <v>https://music.apple.com/us/album/chico-raro/6767713527</v>
       </c>
       <c r="L167" t="str">
-        <v>What's Done Is Done - Jorja Smith</v>
+        <v>Chico Raro - Arón Piper</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>round and round</v>
+        <v>What's Done Is Done</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/round-and-round/1885665987</v>
+        <v>https://music.apple.com/us/song/whats-done-is-done/6763088629</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-17</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>round and round - Single</v>
+        <v>What's Done Is Done - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>2:47</v>
+        <v>2:53</v>
       </c>
       <c r="H168" t="str">
-        <v>bbno$</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/bbno%24/1161580951</v>
+        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/round-and-round/1885665982</v>
+        <v>https://music.apple.com/us/album/whats-done-is-done/1895156626</v>
       </c>
       <c r="L168" t="str">
-        <v>round and round - bbno$</v>
+        <v>What's Done Is Done - Jorja Smith</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Ain’t That Deep</v>
+        <v>round and round</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/aint-that-deep/1882831449</v>
+        <v>https://music.apple.com/us/song/round-and-round/1885665987</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-17</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>The Last Balloon</v>
+        <v>round and round - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>2:39</v>
+        <v>2:47</v>
       </c>
       <c r="H169" t="str">
-        <v>Tank and the Bangas</v>
+        <v>bbno$</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
+        <v>https://music.apple.com/us/artist/bbno%24/1161580951</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/aint-that-deep/1882831446</v>
+        <v>https://music.apple.com/us/album/round-and-round/1885665982</v>
       </c>
       <c r="L169" t="str">
-        <v>Ain’t That Deep - Tank and the Bangas</v>
+        <v>round and round - bbno$</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Emily</v>
+        <v>Ain’t That Deep</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/emily/1893405442</v>
+        <v>https://music.apple.com/us/song/aint-that-deep/1882831449</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-17</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>So Much To Say - EP</v>
+        <v>The Last Balloon</v>
       </c>
       <c r="G170" t="str">
-        <v>2:35</v>
+        <v>2:39</v>
       </c>
       <c r="H170" t="str">
-        <v>Daisy Grenade</v>
+        <v>Tank and the Bangas</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/daisy-grenade/1611437131</v>
+        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/emily/1893405440</v>
+        <v>https://music.apple.com/us/album/aint-that-deep/1882831446</v>
       </c>
       <c r="L170" t="str">
-        <v>Emily - Daisy Grenade</v>
+        <v>Ain’t That Deep - Tank and the Bangas</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Hold</v>
+        <v>Emily</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/hold/6767296480</v>
+        <v>https://music.apple.com/us/song/emily/1893405442</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-17</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Hold - Single</v>
+        <v>So Much To Say - EP</v>
       </c>
       <c r="G171" t="str">
-        <v>4:07</v>
+        <v>2:35</v>
       </c>
       <c r="H171" t="str">
-        <v>Sabrina Sterling</v>
+        <v>Daisy Grenade</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/sabrina-sterling/1577892147</v>
+        <v>https://music.apple.com/us/artist/daisy-grenade/1611437131</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/hold/1896462063</v>
+        <v>https://music.apple.com/us/album/emily/1893405440</v>
       </c>
       <c r="L171" t="str">
-        <v>Hold - Sabrina Sterling</v>
+        <v>Emily - Daisy Grenade</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Flying Monkey</v>
+        <v>Hold</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/flying-monkey/1894351228</v>
+        <v>https://music.apple.com/us/song/hold/6767296480</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-17</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Flying Monkey - Single</v>
+        <v>Hold - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>4:09</v>
+        <v>4:07</v>
       </c>
       <c r="H172" t="str">
-        <v>Blue Medusa</v>
+        <v>Sabrina Sterling</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
+        <v>https://music.apple.com/us/artist/sabrina-sterling/1577892147</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/flying-monkey/1894351227</v>
+        <v>https://music.apple.com/us/album/hold/1896462063</v>
       </c>
       <c r="L172" t="str">
-        <v>Flying Monkey - Blue Medusa</v>
+        <v>Hold - Sabrina Sterling</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Anything Goes</v>
+        <v>Flying Monkey</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/anything-goes/1891118972</v>
+        <v>https://music.apple.com/us/song/flying-monkey/1894351228</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-17</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Anything Goes</v>
+        <v>Flying Monkey - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:00</v>
+        <v>4:09</v>
       </c>
       <c r="H173" t="str">
-        <v>Kaleena Zanders</v>
+        <v>Blue Medusa</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/anything-goes/1891118971</v>
+        <v>https://music.apple.com/us/album/flying-monkey/1894351227</v>
       </c>
       <c r="L173" t="str">
-        <v>Anything Goes - Kaleena Zanders</v>
+        <v>Flying Monkey - Blue Medusa</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>We Are</v>
+        <v>Anything Goes</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/we-are/1894252873</v>
+        <v>https://music.apple.com/us/song/anything-goes/1891118972</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-17</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>We Are - Single</v>
+        <v>Anything Goes</v>
       </c>
       <c r="G174" t="str">
-        <v>3:33</v>
+        <v>3:00</v>
       </c>
       <c r="H174" t="str">
-        <v>Adam Ten</v>
+        <v>Kaleena Zanders</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/adam-ten/1472226854</v>
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/we-are/1894252870</v>
+        <v>https://music.apple.com/us/album/anything-goes/1891118971</v>
       </c>
       <c r="L174" t="str">
-        <v>We Are - Adam Ten</v>
+        <v>Anything Goes - Kaleena Zanders</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>It's For the Kids</v>
+        <v>We Are</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/its-for-the-kids/1867327679</v>
+        <v>https://music.apple.com/us/song/we-are/1894252873</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-17</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Cursum Perficio</v>
+        <v>We Are - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>4:20</v>
+        <v>3:33</v>
       </c>
       <c r="H175" t="str">
-        <v>Anthrax</v>
+        <v>Adam Ten</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/anthrax/80417</v>
+        <v>https://music.apple.com/us/artist/adam-ten/1472226854</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/its-for-the-kids/1867327673</v>
+        <v>https://music.apple.com/us/album/we-are/1894252870</v>
       </c>
       <c r="L175" t="str">
-        <v>It's For the Kids - Anthrax</v>
+        <v>We Are - Adam Ten</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Pure Ecstasy</v>
+        <v>It's For the Kids</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/pure-ecstasy/6762228978</v>
+        <v>https://music.apple.com/us/song/its-for-the-kids/1867327679</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-17</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Pure Ecstasy</v>
+        <v>Cursum Perficio</v>
       </c>
       <c r="G176" t="str">
-        <v>3:05</v>
+        <v>4:20</v>
       </c>
       <c r="H176" t="str">
-        <v>Beartooth</v>
+        <v>Anthrax</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
+        <v>https://music.apple.com/us/artist/anthrax/80417</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/pure-ecstasy/1893453878</v>
+        <v>https://music.apple.com/us/album/its-for-the-kids/1867327673</v>
       </c>
       <c r="L176" t="str">
-        <v>Pure Ecstasy - Beartooth</v>
+        <v>It's For the Kids - Anthrax</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Something Wicked</v>
+        <v>Pure Ecstasy</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/something-wicked/6766252959</v>
+        <v>https://music.apple.com/us/song/pure-ecstasy/6762228978</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-17</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Something Wicked - Single</v>
+        <v>Pure Ecstasy</v>
       </c>
       <c r="G177" t="str">
-        <v>3:28</v>
+        <v>3:05</v>
       </c>
       <c r="H177" t="str">
-        <v>Breaking Benjamin</v>
+        <v>Beartooth</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/breaking-benjamin/3299379</v>
+        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/something-wicked/1896253678</v>
+        <v>https://music.apple.com/us/album/pure-ecstasy/1893453878</v>
       </c>
       <c r="L177" t="str">
-        <v>Something Wicked - Breaking Benjamin</v>
+        <v>Pure Ecstasy - Beartooth</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Feel The Funk</v>
+        <v>Something Wicked</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/feel-the-funk/6763294007</v>
+        <v>https://music.apple.com/us/song/something-wicked/6766252959</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-17</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>The Funk EP - Single</v>
+        <v>Something Wicked - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:26</v>
+        <v>3:28</v>
       </c>
       <c r="H178" t="str">
-        <v>Riordan</v>
+        <v>Breaking Benjamin</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/riordan/1517575029</v>
+        <v>https://music.apple.com/us/artist/breaking-benjamin/3299379</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/feel-the-funk/1895251685</v>
+        <v>https://music.apple.com/us/album/something-wicked/1896253678</v>
       </c>
       <c r="L178" t="str">
-        <v>Feel The Funk - Riordan</v>
+        <v>Something Wicked - Breaking Benjamin</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Everglades (Remix)</v>
+        <v>Feel The Funk</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/everglades-remix/6767719584</v>
+        <v>https://music.apple.com/us/song/feel-the-funk/6763294007</v>
       </c>
       <c r="D179" t="str">
         <v>2026-05-17</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Everglades (Remix) - Single</v>
+        <v>The Funk EP - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:42</v>
+        <v>3:26</v>
       </c>
       <c r="H179" t="str">
-        <v>Aziedoesntexist</v>
+        <v>Riordan</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/aziedoesntexist/1831152556</v>
+        <v>https://music.apple.com/us/artist/riordan/1517575029</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/everglades-remix/6767719577</v>
+        <v>https://music.apple.com/us/album/feel-the-funk/1895251685</v>
       </c>
       <c r="L179" t="str">
-        <v>Everglades (Remix) - Aziedoesntexist</v>
+        <v>Feel The Funk - Riordan</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Walk</v>
+        <v>Everglades (Remix)</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/walk/1892180098</v>
+        <v>https://music.apple.com/us/song/everglades-remix/6767719584</v>
       </c>
       <c r="D180" t="str">
         <v>2026-05-17</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Walk - Single</v>
+        <v>Everglades (Remix) - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:25</v>
+        <v>2:42</v>
       </c>
       <c r="H180" t="str">
-        <v>Melodicb</v>
+        <v>Aziedoesntexist</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/melodicb/1440206517</v>
+        <v>https://music.apple.com/us/artist/aziedoesntexist/1831152556</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/walk/1892180097</v>
+        <v>https://music.apple.com/us/album/everglades-remix/6767719577</v>
       </c>
       <c r="L180" t="str">
-        <v>Walk - Melodicb</v>
+        <v>Everglades (Remix) - Aziedoesntexist</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Volver a Ti</v>
+        <v>Walk</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/volver-a-ti/6766258204</v>
+        <v>https://music.apple.com/us/song/walk/1892180098</v>
       </c>
       <c r="D181" t="str">
         <v>2026-05-17</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Norteña</v>
+        <v>Walk - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:47</v>
+        <v>2:25</v>
       </c>
       <c r="H181" t="str">
-        <v>Julieta Venegas</v>
+        <v>Melodicb</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/julieta-venegas/302960</v>
+        <v>https://music.apple.com/us/artist/melodicb/1440206517</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/volver-a-ti/1896255736</v>
+        <v>https://music.apple.com/us/album/walk/1892180097</v>
       </c>
       <c r="L181" t="str">
-        <v>Volver a Ti - Julieta Venegas</v>
+        <v>Walk - Melodicb</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Bahamas</v>
+        <v>Volver a Ti</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/bahamas/6764695848</v>
+        <v>https://music.apple.com/us/song/volver-a-ti/6766258204</v>
       </c>
       <c r="D182" t="str">
         <v>2026-05-17</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Bahamas - Single</v>
+        <v>Norteña</v>
       </c>
       <c r="G182" t="str">
-        <v>2:06</v>
+        <v>3:47</v>
       </c>
       <c r="H182" t="str">
-        <v>LENCHO</v>
+        <v>Julieta Venegas</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/lencho/1854923384</v>
+        <v>https://music.apple.com/us/artist/julieta-venegas/302960</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/bahamas/6764695847</v>
+        <v>https://music.apple.com/us/album/volver-a-ti/1896255736</v>
       </c>
       <c r="L182" t="str">
-        <v>Bahamas - LENCHO</v>
+        <v>Volver a Ti - Julieta Venegas</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Same Old Song</v>
+        <v>Bahamas</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/same-old-song/6762860685</v>
+        <v>https://music.apple.com/us/song/bahamas/6764695848</v>
       </c>
       <c r="D183" t="str">
         <v>2026-05-17</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Same Old Song - Single</v>
+        <v>Bahamas - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>4:12</v>
+        <v>2:06</v>
       </c>
       <c r="H183" t="str">
-        <v>Lila Drew</v>
+        <v>LENCHO</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/lila-drew/1439482732</v>
+        <v>https://music.apple.com/us/artist/lencho/1854923384</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/same-old-song/1895047985</v>
+        <v>https://music.apple.com/us/album/bahamas/6764695847</v>
       </c>
       <c r="L183" t="str">
-        <v>Same Old Song - Lila Drew</v>
+        <v>Bahamas - LENCHO</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>gentle</v>
+        <v>Same Old Song</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/gentle/6762828356</v>
+        <v>https://music.apple.com/us/song/same-old-song/6762860685</v>
       </c>
       <c r="D184" t="str">
         <v>2026-05-17</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>gentle - Single</v>
+        <v>Same Old Song - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:48</v>
+        <v>4:12</v>
       </c>
       <c r="H184" t="str">
-        <v>Venus Anon</v>
+        <v>Lila Drew</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/venus-anon/1635970130</v>
+        <v>https://music.apple.com/us/artist/lila-drew/1439482732</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/gentle/1895031896</v>
+        <v>https://music.apple.com/us/album/same-old-song/1895047985</v>
       </c>
       <c r="L184" t="str">
-        <v>gentle - Venus Anon</v>
+        <v>Same Old Song - Lila Drew</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Letters of Your Name</v>
+        <v>gentle</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/letters-of-your-name/1892919741</v>
+        <v>https://music.apple.com/us/song/gentle/6762828356</v>
       </c>
       <c r="D185" t="str">
         <v>2026-05-17</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Congratulations</v>
+        <v>gentle - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:21</v>
+        <v>2:48</v>
       </c>
       <c r="H185" t="str">
-        <v>Jacob Ungerleider</v>
+        <v>Venus Anon</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/jacob-ungerleider/1460845591</v>
+        <v>https://music.apple.com/us/artist/venus-anon/1635970130</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/letters-of-your-name/1892919737</v>
+        <v>https://music.apple.com/us/album/gentle/1895031896</v>
       </c>
       <c r="L185" t="str">
-        <v>Letters of Your Name - Jacob Ungerleider</v>
+        <v>gentle - Venus Anon</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Seratonin</v>
+        <v>Letters of Your Name</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/seratonin/6763447428</v>
+        <v>https://music.apple.com/us/song/letters-of-your-name/1892919741</v>
       </c>
       <c r="D186" t="str">
         <v>2026-05-17</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Seratonin - Single</v>
+        <v>Congratulations</v>
       </c>
       <c r="G186" t="str">
-        <v>1:55</v>
+        <v>3:21</v>
       </c>
       <c r="H186" t="str">
-        <v>James Hype</v>
+        <v>Jacob Ungerleider</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/james-hype/925734064</v>
+        <v>https://music.apple.com/us/artist/jacob-ungerleider/1460845591</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/seratonin/1895320367</v>
+        <v>https://music.apple.com/us/album/letters-of-your-name/1892919737</v>
       </c>
       <c r="L186" t="str">
-        <v>Seratonin - James Hype</v>
+        <v>Letters of Your Name - Jacob Ungerleider</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>A Digital Touch</v>
+        <v>Seratonin</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/a-digital-touch/6765592539</v>
+        <v>https://music.apple.com/us/song/seratonin/6763447428</v>
       </c>
       <c r="D187" t="str">
         <v>2026-05-17</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>A Digital Touch - Single</v>
+        <v>Seratonin - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:53</v>
+        <v>1:55</v>
       </c>
       <c r="H187" t="str">
-        <v>Evening Elephants</v>
+        <v>James Hype</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
+        <v>https://music.apple.com/us/artist/james-hype/925734064</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/a-digital-touch/1896003252</v>
+        <v>https://music.apple.com/us/album/seratonin/1895320367</v>
       </c>
       <c r="L187" t="str">
-        <v>A Digital Touch - Evening Elephants</v>
+        <v>Seratonin - James Hype</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Dead Man's Dog</v>
+        <v>A Digital Touch</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/dead-mans-dog/6763447424</v>
+        <v>https://music.apple.com/us/song/a-digital-touch/6765592539</v>
       </c>
       <c r="D188" t="str">
         <v>2026-05-17</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Aiming Torches At The Sun - EP</v>
+        <v>A Digital Touch - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>4:33</v>
+        <v>2:53</v>
       </c>
       <c r="H188" t="str">
-        <v>Dermot Henry</v>
+        <v>Evening Elephants</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/dermot-henry/1704074611</v>
+        <v>https://music.apple.com/us/artist/evening-elephants/1655904238</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/dead-mans-dog/1895320369</v>
+        <v>https://music.apple.com/us/album/a-digital-touch/1896003252</v>
       </c>
       <c r="L188" t="str">
-        <v>Dead Man's Dog - Dermot Henry</v>
+        <v>A Digital Touch - Evening Elephants</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Fault of God</v>
+        <v>Dead Man's Dog</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/fault-of-god/1887702403</v>
+        <v>https://music.apple.com/us/song/dead-mans-dog/6763447424</v>
       </c>
       <c r="D189" t="str">
         <v>2026-05-17</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Active Child</v>
+        <v>Aiming Torches At The Sun - EP</v>
       </c>
       <c r="G189" t="str">
-        <v>4:13</v>
+        <v>4:33</v>
       </c>
       <c r="H189" t="str">
-        <v>Active Child</v>
+        <v>Dermot Henry</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/active-child/355288617</v>
+        <v>https://music.apple.com/us/artist/dermot-henry/1704074611</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/fault-of-god/1887701924</v>
+        <v>https://music.apple.com/us/album/dead-mans-dog/1895320369</v>
       </c>
       <c r="L189" t="str">
-        <v>Fault of God - Active Child</v>
+        <v>Dead Man's Dog - Dermot Henry</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Zone (feat. Poppy Baskcomb)</v>
+        <v>Fault of God</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/zone-feat-poppy-baskcomb/6763982867</v>
+        <v>https://music.apple.com/us/song/fault-of-god/1887702403</v>
       </c>
       <c r="D190" t="str">
         <v>2026-05-17</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Zone (feat. Poppy Baskcomb) - Single</v>
+        <v>Active Child</v>
       </c>
       <c r="G190" t="str">
-        <v>2:56</v>
+        <v>4:13</v>
       </c>
       <c r="H190" t="str">
-        <v>MK</v>
+        <v>Active Child</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/mk/63097617</v>
+        <v>https://music.apple.com/us/artist/active-child/355288617</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/zone-feat-poppy-baskcomb/1895585800</v>
+        <v>https://music.apple.com/us/album/fault-of-god/1887701924</v>
       </c>
       <c r="L190" t="str">
-        <v>Zone (feat. Poppy Baskcomb) - MK</v>
+        <v>Fault of God - Active Child</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Word Vomit</v>
+        <v>Zone (feat. Poppy Baskcomb)</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/word-vomit/1887315297</v>
+        <v>https://music.apple.com/us/song/zone-feat-poppy-baskcomb/6763982867</v>
       </c>
       <c r="D191" t="str">
         <v>2026-05-17</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Word Vomit - Single</v>
+        <v>Zone (feat. Poppy Baskcomb) - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>2:46</v>
+        <v>2:56</v>
       </c>
       <c r="H191" t="str">
-        <v>Baby Queen</v>
+        <v>MK</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
+        <v>https://music.apple.com/us/artist/mk/63097617</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/word-vomit/1887315294</v>
+        <v>https://music.apple.com/us/album/zone-feat-poppy-baskcomb/1895585800</v>
       </c>
       <c r="L191" t="str">
-        <v>Word Vomit - Baby Queen</v>
+        <v>Zone (feat. Poppy Baskcomb) - MK</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Evil in this House</v>
+        <v>Word Vomit</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/evil-in-this-house/1892398371</v>
+        <v>https://music.apple.com/us/song/word-vomit/1887315297</v>
       </c>
       <c r="D192" t="str">
         <v>2026-05-17</v>
@@ -7671,68 +7671,106 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Necropolitan</v>
+        <v>Word Vomit - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>4:21</v>
+        <v>2:46</v>
       </c>
       <c r="H192" t="str">
-        <v>Green Lung</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/green-lung/1244071662</v>
+        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/evil-in-this-house/1892398281</v>
+        <v>https://music.apple.com/us/album/word-vomit/1887315294</v>
       </c>
       <c r="L192" t="str">
-        <v>Evil in this House - Green Lung</v>
+        <v>Word Vomit - Baby Queen</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
+        <v>Evil in this House</v>
+      </c>
+      <c r="B193" t="str">
+        <v/>
+      </c>
+      <c r="C193" t="str">
+        <v>https://music.apple.com/us/song/evil-in-this-house/1892398371</v>
+      </c>
+      <c r="D193" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E193" t="str">
+        <v/>
+      </c>
+      <c r="F193" t="str">
+        <v>Necropolitan</v>
+      </c>
+      <c r="G193" t="str">
+        <v>4:21</v>
+      </c>
+      <c r="H193" t="str">
+        <v>Green Lung</v>
+      </c>
+      <c r="I193" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J193" t="str">
+        <v>https://music.apple.com/us/artist/green-lung/1244071662</v>
+      </c>
+      <c r="K193" t="str">
+        <v>https://music.apple.com/us/album/evil-in-this-house/1892398281</v>
+      </c>
+      <c r="L193" t="str">
+        <v>Evil in this House - Green Lung</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
         <v>Heaven on High</v>
       </c>
-      <c r="B193" t="str">
-        <v/>
-      </c>
-      <c r="C193" t="str">
+      <c r="B194" t="str">
+        <v/>
+      </c>
+      <c r="C194" t="str">
         <v>https://music.apple.com/us/song/heaven-on-high/1881724153</v>
       </c>
-      <c r="D193" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E193" t="str">
-        <v/>
-      </c>
-      <c r="F193" t="str">
+      <c r="D194" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E194" t="str">
+        <v/>
+      </c>
+      <c r="F194" t="str">
         <v>A Pale White Dot</v>
       </c>
-      <c r="G193" t="str">
+      <c r="G194" t="str">
         <v>4:19</v>
       </c>
-      <c r="H193" t="str">
+      <c r="H194" t="str">
         <v>Periphery</v>
       </c>
-      <c r="I193" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J193" t="str">
+      <c r="I194" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J194" t="str">
         <v>https://music.apple.com/us/artist/periphery/187683869</v>
       </c>
-      <c r="K193" t="str">
+      <c r="K194" t="str">
         <v>https://music.apple.com/us/album/heaven-on-high/1881724003</v>
       </c>
-      <c r="L193" t="str">
+      <c r="L194" t="str">
         <v>Heaven on High - Periphery</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L193"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L194"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-05-week03/titles.xlsx
+++ b/data/global/2026-05-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L194"/>
+  <dimension ref="A1:L193"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>בן ארצי – ישראל</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-17</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%9f-%d7%90%d7%a8%d7%a6%d7%99-%d7%99%d7%a9%d7%a8%d7%90%d7%9c/</v>
+        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-17</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "ישראל” של בן ארצי בנוי כעל פרדוקס רגשי: אהבה עמוקה למדינה לצד תחושת אכזבה קשה ממנה. זה לא שיר מחאה זועם או מהפכני, אלא שיר של אדם שמרגיש שייך – ולכן גם פגוע. דווקא בגלל הטון הפשוט והישיר שלו,</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>בן ארצי – ישראל</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Eurovision 2026</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B3" t="str">
-        <v>11h ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
+        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-17</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>11h ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B4" t="str">
-        <v>9h ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
+        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-17</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>9h ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B5" t="str">
-        <v>12h ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
+        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-17</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>12h ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B6" t="str">
-        <v>10h ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
+        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-17</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>10h ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B7" t="str">
-        <v>10h ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
+        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-17</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>10h ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>10h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
+        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-17</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>10h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Evanescence</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>1d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
+        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-17</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Evanescence</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B10" t="str">
-        <v>4d ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
+        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-17</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>4d ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B11" t="str">
-        <v>17h ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
+        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-17</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>17h ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Armin van Buuren</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
+        <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>17h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
+        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-17</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>17h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Madison Cunningham</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
+        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video)</v>
+        <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
+        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-17</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Johnny Orlando</v>
+        <v>Carver Jones</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
+        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video)</v>
+        <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
+        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-17</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Carver Jones</v>
+        <v>Jazmin bean</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
+        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video)</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B15" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
+        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-17</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Jazmin bean</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
+        <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B16" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
+        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-17</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Baby Queen</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
+        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Switchfoot - Absolution (Official Audio)</v>
+        <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B17" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
+        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-17</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Switchfoot</v>
+        <v>Grace Potter</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
+        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio)</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B18" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
+        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-17</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Grace Potter</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
+        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-17</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
+        <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B20" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
+        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-17</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>The All-American Rejects</v>
+        <v>Henry Moodie</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
+        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser)</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
+        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-17</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Henry Moodie</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
+        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-17</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Spacey Jane</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
+        <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B23" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
+        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-17</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Megan Moroney</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
+        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser)</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
+        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-17</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
+        <v>Keith Urban - Steal Away (Visualizer)</v>
       </c>
       <c r="B25" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
+        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-17</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Matt Hansen</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
+        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Keith Urban - Steal Away (Visualizer)</v>
+        <v>VALÉ - Mugshot (Official Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
+        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-17</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Keith Urban</v>
+        <v>VALÉ</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
+        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>VALÉ - Mugshot (Official Video)</v>
+        <v>Mackenzie Carpenter - High Pony (Audio)</v>
       </c>
       <c r="B27" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
+        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-17</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>VALÉ</v>
+        <v>Mackenzie Carpenter</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
+        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio)</v>
+        <v>Towa Bird - Afterglow (Lyric Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
+        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-17</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Mackenzie Carpenter</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
+        <v>Towa Bird - Afterglow (Lyric Video) - Towa Bird</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Towa Bird - Afterglow (Lyric Video)</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
       </c>
       <c r="B29" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
+        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-17</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Towa Bird</v>
+        <v>Sabrina Sterling</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Towa Bird - Afterglow (Lyric Video) - Towa Bird</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
+        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-17</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Sabrina Sterling</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
+        <v>Becky G - EPA (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
+        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-17</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Little Big Town</v>
+        <v>Becky G</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
+        <v>Becky G - EPA (Official Video) - Becky G</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Becky G - EPA (Official Video)</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
+        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-17</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Becky G</v>
+        <v>Daisy the Great</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Becky G - EPA (Official Video) - Becky G</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
+        <v>Towa Bird - Dog (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
+        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-17</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Daisy the Great</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
+        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Towa Bird - Dog (Official Music Video)</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
       </c>
       <c r="B34" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
+        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-17</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Towa Bird</v>
+        <v>Madonna</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
+        <v>Ally Salort - Housekeeping (Lyric Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
+        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-17</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Madonna</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
+        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video)</v>
+        <v>Bella White - Better - Official Music Video</v>
       </c>
       <c r="B36" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
+        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-17</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Ally Salort</v>
+        <v>Bella White</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
+        <v>Bella White - Better - Official Music Video - Bella White</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Bella White - Better - Official Music Video</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
+        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-17</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Bella White</v>
+        <v>Charles Wesley Godwin</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Bella White - Better - Official Music Video - Bella White</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
+        <v>Towa Bird - All Gone (Lyric Video) ft. Kathleen Hanna</v>
       </c>
       <c r="B38" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
+        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-17</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Charles Wesley Godwin</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
+        <v>Towa Bird - All Gone (Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Towa Bird - All Gone (Lyric Video) ft. Kathleen Hanna</v>
+        <v>Miranda Lambert - Crisco (Visualizer)</v>
       </c>
       <c r="B39" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
+        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-17</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Towa Bird</v>
+        <v>Miranda Lambert</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Towa Bird - All Gone (Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
+        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer)</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
       </c>
       <c r="B40" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
+        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-17</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Miranda Lambert</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
+        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-17</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Lady Gaga</v>
+        <v>Gracie Abrams</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
+        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-17</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Gracie Abrams</v>
+        <v>The Last Dinner Party</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
       </c>
       <c r="B43" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
+        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-17</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>The Last Dinner Party</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
+        <v>Jorja Smith - What's Done Is Done</v>
       </c>
       <c r="B44" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
+        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-17</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Martin Garrix</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
+        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Jorja Smith - What's Done Is Done</v>
+        <v>LP - Shelly (Official Music Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
+        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-17</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Jorja Smith</v>
+        <v>LP</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
+        <v>LP - Shelly (Official Music Video) - LP</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>LP - Shelly (Official Music Video)</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
       </c>
       <c r="B46" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
+        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-17</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>LP</v>
+        <v>The Rolling Stones</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>LP - Shelly (Official Music Video) - LP</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
       </c>
       <c r="B47" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
+        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-17</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>The Rolling Stones</v>
+        <v>Oasis</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
       </c>
       <c r="B48" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
+        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-17</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Oasis</v>
+        <v>Breaking Benjamin</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
+        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
       </c>
       <c r="B49" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
+        <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-17</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Breaking Benjamin</v>
+        <v>VictorBiliac</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
+        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit ) - VictorBiliac</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
+        <v>From The Inside (Live in Mumbai) - Linkin Park</v>
       </c>
       <c r="B50" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
+        <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-17</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>VictorBiliac</v>
+        <v>Linkin Park</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit ) - VictorBiliac</v>
+        <v>From The Inside (Live in Mumbai) - Linkin Park - Linkin Park</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>From The Inside (Live in Mumbai) - Linkin Park</v>
+        <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>4d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
+        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-17</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>4d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Linkin Park</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>From The Inside (Live in Mumbai) - Linkin Park - Linkin Park</v>
+        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Harry Styles - Dance No More (Official Video)</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
+        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-17</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Harry Styles</v>
+        <v>Eagles</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B53" t="str">
-        <v>9d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
+        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-17</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>9d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Eagles</v>
+        <v>Nora Fatehi</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B54" t="str">
-        <v>7d ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
+        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-17</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>7d ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Nora Fatehi</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B55" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
+        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-17</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Eurovision Song Contest and Alis</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
       </c>
       <c r="B56" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
+        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-17</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Eurovision Song Contest and Alis</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
+        <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>2mo ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
+        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-17</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2mo ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>The Head And The Heart</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
+        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video)</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B58" t="str">
-        <v>8d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
+        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-17</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>8d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>The Head And The Heart</v>
+        <v>Simply Red</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
+        <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>10d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
+        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-17</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>10d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Simply Red</v>
+        <v>Talking Heads</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
+        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video)</v>
+        <v>Ellise - Liplock (Official Music Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>6d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
+        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-17</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>6d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Talking Heads</v>
+        <v>Ellise</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
+        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Ellise - Liplock (Official Music Video)</v>
+        <v>Tori Kelly - Dive (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
+        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-17</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Ellise</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
+        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Tori Kelly - Dive (Official Music Video)</v>
+        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
       </c>
       <c r="B62" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
+        <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-17</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Tori Kelly</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
+        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024) - David Gilmour</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
+        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
       </c>
       <c r="B63" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
+        <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-17</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>David Gilmour</v>
+        <v>Scorpions</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024) - David Gilmour</v>
+        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
+        <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
+        <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-17</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Scorpions</v>
+        <v>Claire Leslie</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022) - Scorpions</v>
+        <v>Claire Leslie - Passenger Seat (Official Music Video) - Claire Leslie</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
+        <v>Michael Schulte - Lovesick (Official Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
+        <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-17</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Claire Leslie</v>
+        <v>Michael Schulte</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Claire Leslie - Passenger Seat (Official Music Video) - Claire Leslie</v>
+        <v>Michael Schulte - Lovesick (Official Video) - Michael Schulte</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Michael Schulte - Lovesick (Official Video)</v>
+        <v>Caity Baser - Holiday Song (Official Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
+        <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-17</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Michael Schulte</v>
+        <v>Caity Baser</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Michael Schulte - Lovesick (Official Video) - Michael Schulte</v>
+        <v>Caity Baser - Holiday Song (Official Video) - Caity Baser</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Caity Baser - Holiday Song (Official Video)</v>
+        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
       </c>
       <c r="B67" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
+        <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-17</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Caity Baser</v>
+        <v>Sam Fischer</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Caity Baser - Holiday Song (Official Video) - Caity Baser</v>
+        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser) - Sam Fischer</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
+        <v>Porches- HABIT (Official Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
+        <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-17</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Sam Fischer</v>
+        <v>Porches</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser) - Sam Fischer</v>
+        <v>Porches- HABIT (Official Video) - Porches</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Porches- HABIT (Official Video)</v>
+        <v>Charli xcx - Rock Music (Official Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
+        <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-17</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Porches</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Porches- HABIT (Official Video) - Porches</v>
+        <v>Charli xcx - Rock Music (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Charli xcx - Rock Music (Official Video)</v>
+        <v>Jon Batiste - Alla Blues (Audio)</v>
       </c>
       <c r="B70" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
+        <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-17</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Charli xcx</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Charli xcx - Rock Music (Official Video) - Charli xcx</v>
+        <v>Jon Batiste - Alla Blues (Audio) - Jon Batiste</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Jon Batiste - Alla Blues (Audio)</v>
+        <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
+        <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-17</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Jon Batiste</v>
+        <v>Tigirlily Gold</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Jon Batiste - Alla Blues (Audio) - Jon Batiste</v>
+        <v>Tigirlily Gold - I Do or Die (Official Music Video) - Tigirlily Gold</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
+        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
+        <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-17</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Tigirlily Gold</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Tigirlily Gold - I Do or Die (Official Music Video) - Tigirlily Gold</v>
+        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
+        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
       </c>
       <c r="B73" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
+        <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-17</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video) - PAUL McCARTNEY</v>
+        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
+        <v>Tori Kelly - Control (Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
+        <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-17</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Bruno Mars</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video] - Bruno Mars</v>
+        <v>Tori Kelly - Control (Official Visualizer) - Tori Kelly</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Tori Kelly - Control (Official Visualizer)</v>
+        <v>Bea Miller - depressed on the internet (Lyric Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
+        <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-17</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Tori Kelly</v>
+        <v>bea miller</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Tori Kelly - Control (Official Visualizer) - Tori Kelly</v>
+        <v>Bea Miller - depressed on the internet (Lyric Video) - bea miller</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Bea Miller - depressed on the internet (Lyric Video)</v>
+        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
       </c>
       <c r="B76" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
+        <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-17</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>bea miller</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Bea Miller - depressed on the internet (Lyric Video) - bea miller</v>
+        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
+        <v>Madison Beer - free (Official Audio)</v>
       </c>
       <c r="B77" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
+        <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-17</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>The Chainsmokers</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer) - The Chainsmokers</v>
+        <v>Madison Beer - free (Official Audio) - Madison Beer</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Madison Beer - free (Official Audio)</v>
+        <v>Tori Kelly - Dive (Official Audio)</v>
       </c>
       <c r="B78" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
+        <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-17</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Madison Beer</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Madison Beer - free (Official Audio) - Madison Beer</v>
+        <v>Tori Kelly - Dive (Official Audio) - Tori Kelly</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Tori Kelly - Dive (Official Audio)</v>
+        <v>Jeremy Camp - Reflector (Official Audio)</v>
       </c>
       <c r="B79" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
+        <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-17</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Tori Kelly</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Tori Kelly - Dive (Official Audio) - Tori Kelly</v>
+        <v>Jeremy Camp - Reflector (Official Audio) - JeremyCampMusic</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Jeremy Camp - Reflector (Official Audio)</v>
+        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
       </c>
       <c r="B80" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
+        <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-17</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>JeremyCampMusic</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Jeremy Camp - Reflector (Official Audio) - JeremyCampMusic</v>
+        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
+        <v>Ashley Cooke - high school sweetheart</v>
       </c>
       <c r="B81" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
+        <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-17</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>The Chainsmokers</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer) - The Chainsmokers</v>
+        <v>Ashley Cooke - high school sweetheart - Ashley Cooke</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Ashley Cooke - high school sweetheart</v>
+        <v>Ari Abdul - Ego (Visualizer)</v>
       </c>
       <c r="B82" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
+        <v>https://www.youtube.com/watch?v=L0FjVr6LpVU</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-17</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Ashley Cooke</v>
+        <v>Ari Abdul</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Ashley Cooke - high school sweetheart - Ashley Cooke</v>
+        <v>Ari Abdul - Ego (Visualizer) - Ari Abdul</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Ari Abdul - Ego (Visualizer)</v>
+        <v>Quinn XCII - HOOPLA (Official Music Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=L0FjVr6LpVU</v>
+        <v>https://www.youtube.com/watch?v=eNbGA1pgmFk</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-17</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Ari Abdul</v>
+        <v>Quinn XCII</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Ari Abdul - Ego (Visualizer) - Ari Abdul</v>
+        <v>Quinn XCII - HOOPLA (Official Music Video) - Quinn XCII</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Quinn XCII - HOOPLA (Official Music Video)</v>
+        <v>Madison Beer - lovergirl (Official Music Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=eNbGA1pgmFk</v>
+        <v>https://www.youtube.com/watch?v=q4lU1N3oqYQ</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-17</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Quinn XCII</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Quinn XCII - HOOPLA (Official Music Video) - Quinn XCII</v>
+        <v>Madison Beer - lovergirl (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Madison Beer - lovergirl (Official Music Video)</v>
+        <v>David J - WHAT IF I'M IN LOVE (Official Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=q4lU1N3oqYQ</v>
+        <v>https://www.youtube.com/watch?v=-SF7Hm_ikaY</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-17</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Madison Beer</v>
+        <v>David J</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Madison Beer - lovergirl (Official Music Video) - Madison Beer</v>
+        <v>David J - WHAT IF I'M IN LOVE (Official Video) - David J</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>David J - WHAT IF I'M IN LOVE (Official Video)</v>
+        <v>The Last Dinner Party - Big Dog (On The Road)</v>
       </c>
       <c r="B86" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=-SF7Hm_ikaY</v>
+        <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-17</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>David J</v>
+        <v>The Last Dinner Party</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>David J - WHAT IF I'M IN LOVE (Official Video) - David J</v>
+        <v>The Last Dinner Party - Big Dog (On The Road) - The Last Dinner Party</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>The Last Dinner Party - Big Dog (On The Road)</v>
+        <v>OCEAN ALLEY - HOLD ON (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
+        <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-17</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>The Last Dinner Party</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>The Last Dinner Party - Big Dog (On The Road) - The Last Dinner Party</v>
+        <v>OCEAN ALLEY - HOLD ON (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>OCEAN ALLEY - HOLD ON (Official Video)</v>
+        <v>Dagny - Closet Disco Queen (Lyric Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
+        <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-17</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Ocean Alley</v>
+        <v>Dagny</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>OCEAN ALLEY - HOLD ON (Official Video) - Ocean Alley</v>
+        <v>Dagny - Closet Disco Queen (Lyric Video) - Dagny</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Dagny - Closet Disco Queen (Lyric Video)</v>
+        <v>Purple Disco Machine - Disco Cherry (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
+        <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-17</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Dagny</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Dagny - Closet Disco Queen (Lyric Video) - Dagny</v>
+        <v>Purple Disco Machine - Disco Cherry (Official Video) - Purple Disco Machine</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Purple Disco Machine - Disco Cherry (Official Video)</v>
+        <v>Paris Paloma - Stem the Flow [Official Music Video]</v>
       </c>
       <c r="B90" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
+        <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-17</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Purple Disco Machine - Disco Cherry (Official Video) - Purple Disco Machine</v>
+        <v>Paris Paloma - Stem the Flow [Official Music Video] - Paris Paloma</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Paris Paloma - Stem the Flow [Official Music Video]</v>
+        <v>Lucy Blue - Who you love (Visualiser)</v>
       </c>
       <c r="B91" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
+        <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-17</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Paris Paloma</v>
+        <v>Lucy Blue</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Paris Paloma - Stem the Flow [Official Music Video] - Paris Paloma</v>
+        <v>Lucy Blue - Who you love (Visualiser) - Lucy Blue</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Lucy Blue - Who you love (Visualiser)</v>
+        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026)</v>
       </c>
       <c r="B92" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
+        <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-17</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Lucy Blue</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Lucy Blue - Who you love (Visualiser) - Lucy Blue</v>
+        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026) - Olivia Dean</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026)</v>
+        <v>Aaron Frazer - It's A Shame (Official Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
+        <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-17</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Olivia Dean</v>
+        <v>Aaron Frazer</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026) - Olivia Dean</v>
+        <v>Aaron Frazer - It's A Shame (Official Video) - Aaron Frazer</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Aaron Frazer - It's A Shame (Official Video)</v>
+        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify</v>
       </c>
       <c r="B94" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
+        <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-17</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Aaron Frazer</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Aaron Frazer - It's A Shame (Official Video) - Aaron Frazer</v>
+        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify</v>
+        <v>DANNA - OUT OF MY BODY</v>
       </c>
       <c r="B95" t="str">
-        <v>10d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
+        <v>https://www.youtube.com/watch?v=uW_Ye0kQ9Ac</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-17</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>10d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Holly Humberstone</v>
+        <v>Danna</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>DANNA - OUT OF MY BODY - Danna</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>DANNA - OUT OF MY BODY</v>
+        <v>The Rolling Stones - In The Stars (Official Lyric Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=uW_Ye0kQ9Ac</v>
+        <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-17</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Danna</v>
+        <v>The Rolling Stones</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>DANNA - OUT OF MY BODY - Danna</v>
+        <v>The Rolling Stones - In The Stars (Official Lyric Video) - The Rolling Stones</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>The Rolling Stones - In The Stars (Official Lyric Video)</v>
+        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser)</v>
       </c>
       <c r="B97" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
+        <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-17</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>The Rolling Stones</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>The Rolling Stones - In The Stars (Official Lyric Video) - The Rolling Stones</v>
+        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser)</v>
+        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
       </c>
       <c r="B98" t="str">
-        <v>11d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
+        <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-17</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>11d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Dermot Kennedy</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser) - Dermot Kennedy</v>
+        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
+        <v>Rick Astley - Raindrops (Official Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
+        <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-17</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2) - SIENNA SPIRO</v>
+        <v>Rick Astley - Raindrops (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Rick Astley - Raindrops (Official Video)</v>
+        <v>Jessie J - THREW IT AWAY (Official Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
+        <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-17</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Rick Astley</v>
+        <v>Jessie J</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Rick Astley - Raindrops (Official Video) - Rick Astley</v>
+        <v>Jessie J - THREW IT AWAY (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Jessie J - THREW IT AWAY (Official Video)</v>
+        <v>The Takes - Ain't Love (Lyric Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
+        <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-17</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Jessie J</v>
+        <v>The Takes</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Jessie J - THREW IT AWAY (Official Video) - Jessie J</v>
+        <v>The Takes - Ain't Love (Lyric Video) - The Takes</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>The Takes - Ain't Love (Lyric Video)</v>
+        <v>Hit the Wall</v>
       </c>
       <c r="B102" t="str">
-        <v>2w ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
+        <v>https://music.apple.com/us/song/hit-the-wall/6766750846</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-17</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>2w ago</v>
+        <v>Daughter from Hell</v>
       </c>
       <c r="G102" t="str">
-        <v/>
+        <v>3:14</v>
       </c>
       <c r="H102" t="str">
-        <v>The Takes</v>
+        <v>Gracie Abrams</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/gracie-abrams/1450554836</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/hit-the-wall/6766750836</v>
       </c>
       <c r="L102" t="str">
-        <v>The Takes - Ain't Love (Lyric Video) - The Takes</v>
+        <v>Hit the Wall - Gracie Abrams</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Hit the Wall</v>
+        <v>Ran To Atlanta</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/hit-the-wall/6766750846</v>
+        <v>https://music.apple.com/us/song/ran-to-atlanta/6769568597</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-17</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Daughter from Hell</v>
+        <v>ICEMAN</v>
       </c>
       <c r="G103" t="str">
-        <v>3:14</v>
+        <v>4:07</v>
       </c>
       <c r="H103" t="str">
-        <v>Gracie Abrams</v>
+        <v>Drake</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/gracie-abrams/1450554836</v>
+        <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/hit-the-wall/6766750836</v>
+        <v>https://music.apple.com/us/album/ran-to-atlanta/6769568449</v>
       </c>
       <c r="L103" t="str">
-        <v>Hit the Wall - Gracie Abrams</v>
+        <v>Ran To Atlanta - Drake</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Ran To Atlanta</v>
+        <v>Hoe Phase</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/ran-to-atlanta/6769568597</v>
+        <v>https://music.apple.com/us/song/hoe-phase/6769556949</v>
       </c>
       <c r="D104" t="str">
         <v>2026-05-17</v>
@@ -4327,10 +4327,10 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>ICEMAN</v>
+        <v>MAID OF HONOUR</v>
       </c>
       <c r="G104" t="str">
-        <v>4:07</v>
+        <v>3:23</v>
       </c>
       <c r="H104" t="str">
         <v>Drake</v>
@@ -4342,21 +4342,21 @@
         <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/ran-to-atlanta/6769568449</v>
+        <v>https://music.apple.com/us/album/hoe-phase/6769556940</v>
       </c>
       <c r="L104" t="str">
-        <v>Ran To Atlanta - Drake</v>
+        <v>Hoe Phase - Drake</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Hoe Phase</v>
+        <v>I’m Spent</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/hoe-phase/6769556949</v>
+        <v>https://music.apple.com/us/song/im-spent/6769551476</v>
       </c>
       <c r="D105" t="str">
         <v>2026-05-17</v>
@@ -4365,10 +4365,10 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>MAID OF HONOUR</v>
+        <v>HABIBTI</v>
       </c>
       <c r="G105" t="str">
-        <v>3:23</v>
+        <v>2:24</v>
       </c>
       <c r="H105" t="str">
         <v>Drake</v>
@@ -4380,21 +4380,21 @@
         <v>https://music.apple.com/us/artist/drake/271256</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/hoe-phase/6769556940</v>
+        <v>https://music.apple.com/us/album/im-spent/6769551464</v>
       </c>
       <c r="L105" t="str">
-        <v>Hoe Phase - Drake</v>
+        <v>I’m Spent - Drake</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>I’m Spent</v>
+        <v>Abracadabra (Apple Music Live)</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/im-spent/6769551476</v>
+        <v>https://music.apple.com/us/song/abracadabra-apple-music-live/6768201780</v>
       </c>
       <c r="D106" t="str">
         <v>2026-05-17</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>HABIBTI</v>
+        <v>Apple Music Live: MAYHEM Requiem</v>
       </c>
       <c r="G106" t="str">
-        <v>2:24</v>
+        <v>4:04</v>
       </c>
       <c r="H106" t="str">
-        <v>Drake</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/drake/271256</v>
+        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/im-spent/6769551464</v>
+        <v>https://music.apple.com/us/album/abracadabra-apple-music-live/6768201775</v>
       </c>
       <c r="L106" t="str">
-        <v>I’m Spent - Drake</v>
+        <v>Abracadabra (Apple Music Live) - Lady Gaga</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Abracadabra (Apple Music Live)</v>
+        <v>Falling out of Love</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/abracadabra-apple-music-live/6768201780</v>
+        <v>https://music.apple.com/us/song/falling-out-of-love/1891161448</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-17</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Apple Music Live: MAYHEM Requiem</v>
+        <v>Reality Awaits</v>
       </c>
       <c r="G107" t="str">
-        <v>4:04</v>
+        <v>6:21</v>
       </c>
       <c r="H107" t="str">
-        <v>Lady Gaga</v>
+        <v>The Strokes</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
+        <v>https://music.apple.com/us/artist/the-strokes/560289</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/abracadabra-apple-music-live/6768201775</v>
+        <v>https://music.apple.com/us/album/falling-out-of-love/1891161441</v>
       </c>
       <c r="L107" t="str">
-        <v>Abracadabra (Apple Music Live) - Lady Gaga</v>
+        <v>Falling out of Love - The Strokes</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Falling out of Love</v>
+        <v>Dai Dai</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/falling-out-of-love/1891161448</v>
+        <v>https://music.apple.com/us/song/dai-dai/6768469976</v>
       </c>
       <c r="D108" t="str">
         <v>2026-05-17</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Reality Awaits</v>
+        <v>Dai Dai - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>6:21</v>
+        <v>3:43</v>
       </c>
       <c r="H108" t="str">
-        <v>The Strokes</v>
+        <v>Shakira</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/the-strokes/560289</v>
+        <v>https://music.apple.com/us/artist/shakira/889327</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/falling-out-of-love/1891161441</v>
+        <v>https://music.apple.com/us/album/dai-dai/6768469975</v>
       </c>
       <c r="L108" t="str">
-        <v>Falling out of Love - The Strokes</v>
+        <v>Dai Dai - Shakira</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Dai Dai</v>
+        <v>Tu recuerdo</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/dai-dai/6768469976</v>
+        <v>https://music.apple.com/us/song/tu-recuerdo/6763660843</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-17</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Dai Dai - Single</v>
+        <v>Loco X Volver</v>
       </c>
       <c r="G109" t="str">
-        <v>3:43</v>
+        <v>3:55</v>
       </c>
       <c r="H109" t="str">
-        <v>Shakira</v>
+        <v>Maluma</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/shakira/889327</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/dai-dai/6768469975</v>
+        <v>https://music.apple.com/us/album/tu-recuerdo/1895423065</v>
       </c>
       <c r="L109" t="str">
-        <v>Dai Dai - Shakira</v>
+        <v>Tu recuerdo - Maluma</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Tu recuerdo</v>
+        <v>Traitor (Roles Reversed)</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/tu-recuerdo/6763660843</v>
+        <v>https://music.apple.com/us/song/traitor-roles-reversed/6767665959</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-17</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Loco X Volver</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G110" t="str">
-        <v>3:55</v>
+        <v>3:27</v>
       </c>
       <c r="H110" t="str">
-        <v>Maluma</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/tu-recuerdo/1895423065</v>
+        <v>https://music.apple.com/us/album/traitor-roles-reversed/6767665713</v>
       </c>
       <c r="L110" t="str">
-        <v>Tu recuerdo - Maluma</v>
+        <v>Traitor (Roles Reversed) - Megan Moroney</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Traitor (Roles Reversed)</v>
+        <v>Dirty Rosie</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/traitor-roles-reversed/6767665959</v>
+        <v>https://music.apple.com/us/song/dirty-rosie/6767044374</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-17</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Cloud 9</v>
+        <v>Little Miss Twain</v>
       </c>
       <c r="G111" t="str">
-        <v>3:27</v>
+        <v>2:46</v>
       </c>
       <c r="H111" t="str">
-        <v>Megan Moroney</v>
+        <v>Shania Twain</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v>https://music.apple.com/us/artist/shania-twain/129974</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/traitor-roles-reversed/6767665713</v>
+        <v>https://music.apple.com/us/album/dirty-rosie/1896356105</v>
       </c>
       <c r="L111" t="str">
-        <v>Traitor (Roles Reversed) - Megan Moroney</v>
+        <v>Dirty Rosie - Shania Twain</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Dirty Rosie</v>
+        <v>Like you mean it</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/dirty-rosie/6767044374</v>
+        <v>https://music.apple.com/us/song/like-you-mean-it/6767024693</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-17</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Little Miss Twain</v>
+        <v>When the lights turn on</v>
       </c>
       <c r="G112" t="str">
-        <v>2:46</v>
+        <v>2:27</v>
       </c>
       <c r="H112" t="str">
-        <v>Shania Twain</v>
+        <v>MICO</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/shania-twain/129974</v>
+        <v>https://music.apple.com/us/artist/mico/1457367370</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/dirty-rosie/1896356105</v>
+        <v>https://music.apple.com/us/album/like-you-mean-it/6767024688</v>
       </c>
       <c r="L112" t="str">
-        <v>Dirty Rosie - Shania Twain</v>
+        <v>Like you mean it - MICO</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Like you mean it</v>
+        <v>Hardy (feat. Clairo)</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/like-you-mean-it/6767024693</v>
+        <v>https://music.apple.com/us/song/hardy-feat-clairo/1876953073</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-17</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>When the lights turn on</v>
+        <v>American Stories</v>
       </c>
       <c r="G113" t="str">
-        <v>2:27</v>
+        <v>3:53</v>
       </c>
       <c r="H113" t="str">
-        <v>MICO</v>
+        <v>Rostam</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/mico/1457367370</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/like-you-mean-it/6767024688</v>
+        <v>https://music.apple.com/us/album/hardy-feat-c